--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE08ACC-D1A1-4C15-AC9E-2A930EBD804F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221870DE-CC19-4AE0-8E53-6D107EA083CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1294,7 +1294,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 10-02-2026, 09:34</t>
+    <t>Ostatnia aktualizacja: 24-02-2026, 08:37</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="U6" s="4">
-        <v>42.7</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="2" t="s">
@@ -2579,7 +2579,7 @@
         <v>0.06</v>
       </c>
       <c r="R13" s="5">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="S13" s="5">
         <v>0.05</v>
@@ -2587,7 +2587,9 @@
       <c r="T13" s="5">
         <v>0.05</v>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="5">
+        <v>0.05</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="2" t="s">
         <v>30</v>
@@ -8256,7 +8258,9 @@
       <c r="T114" s="4">
         <v>7.9</v>
       </c>
-      <c r="U114" s="3"/>
+      <c r="U114" s="4">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="V114" s="3"/>
       <c r="W114" s="2" t="s">
         <v>30</v>
@@ -8900,7 +8904,7 @@
         <v>36</v>
       </c>
       <c r="U125" s="4">
-        <v>42.7</v>
+        <v>41.8</v>
       </c>
       <c r="V125" s="3"/>
       <c r="W125" s="2" t="s">
@@ -9784,7 +9788,9 @@
       <c r="T138" s="5">
         <v>16.559999999999999</v>
       </c>
-      <c r="U138" s="3"/>
+      <c r="U138" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V138" s="3"/>
       <c r="W138" s="2" t="s">
         <v>182</v>
@@ -9981,7 +9987,9 @@
       <c r="T141" s="4">
         <v>9.5</v>
       </c>
-      <c r="U141" s="3"/>
+      <c r="U141" s="4">
+        <v>10.6</v>
+      </c>
       <c r="V141" s="3"/>
       <c r="W141" s="2" t="s">
         <v>30</v>
@@ -13381,7 +13389,9 @@
       <c r="T191" s="4">
         <v>13.2</v>
       </c>
-      <c r="U191" s="3"/>
+      <c r="U191" s="4">
+        <v>12.5</v>
+      </c>
       <c r="V191" s="3"/>
       <c r="W191" s="2" t="s">
         <v>30</v>
@@ -13434,21 +13444,23 @@
         <v>71.7</v>
       </c>
       <c r="P192" s="4">
-        <v>77.099999999999994</v>
+        <v>71.5</v>
       </c>
       <c r="Q192" s="4">
-        <v>78.3</v>
+        <v>72.3</v>
       </c>
       <c r="R192" s="4">
-        <v>80.400000000000006</v>
+        <v>74.5</v>
       </c>
       <c r="S192" s="4">
-        <v>81.2</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="T192" s="4">
-        <v>83.3</v>
-      </c>
-      <c r="U192" s="3"/>
+        <v>76.400000000000006</v>
+      </c>
+      <c r="U192" s="4">
+        <v>77.5</v>
+      </c>
       <c r="V192" s="3"/>
       <c r="W192" s="2" t="s">
         <v>30</v>
@@ -14346,7 +14358,9 @@
       <c r="T208" s="4">
         <v>21.6</v>
       </c>
-      <c r="U208" s="3"/>
+      <c r="U208" s="4">
+        <v>24.2</v>
+      </c>
       <c r="V208" s="3"/>
       <c r="W208" s="2" t="s">
         <v>30</v>
@@ -15728,7 +15742,9 @@
       <c r="T230" s="6">
         <v>26</v>
       </c>
-      <c r="U230" s="3"/>
+      <c r="U230" s="6">
+        <v>21</v>
+      </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
         <v>101</v>
@@ -15931,9 +15947,11 @@
         <v>6.7</v>
       </c>
       <c r="T233" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="U233" s="3"/>
+        <v>7.8</v>
+      </c>
+      <c r="U233" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
         <v>182</v>
@@ -16197,7 +16215,9 @@
       <c r="T237" s="5">
         <v>16.559999999999999</v>
       </c>
-      <c r="U237" s="3"/>
+      <c r="U237" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
         <v>182</v>
@@ -18258,16 +18278,16 @@
         <v>282</v>
       </c>
       <c r="G269" s="5">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="H269" s="5">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="I269" s="5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="J269" s="5">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="K269" s="5">
         <v>1.86</v>
@@ -19502,7 +19522,9 @@
       <c r="T288" s="4">
         <v>5.0999999999999996</v>
       </c>
-      <c r="U288" s="3"/>
+      <c r="U288" s="4">
+        <v>4.8</v>
+      </c>
       <c r="V288" s="3"/>
       <c r="W288" s="2" t="s">
         <v>30</v>
@@ -20084,7 +20106,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221870DE-CC19-4AE0-8E53-6D107EA083CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEA01A5-C05E-4B79-92F0-B298B1D0CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2083" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="423">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -856,6 +856,9 @@
     <t>Wsparcie miast w radzeniu sobie z nagłymi zmianami, kryzysami, zarówno społeczno-gospodarczymi, jak i natury środowiskowej oraz zagwarantowanie mieszkańcom bezpieczeństwa i wysokiej jakości życia</t>
   </si>
   <si>
+    <t>11.2.a Deficyt mieszkań dla gospodarstw domowych o niskich dochodach na 1 tys. ludności na obszarach miejskich</t>
+  </si>
+  <si>
     <t>11.2.b Odsetek mieszkańców korzystających z instalacji ściekowych na obszarach miejskich</t>
   </si>
   <si>
@@ -1294,7 +1297,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 24-02-2026, 08:37</t>
+    <t>Ostatnia aktualizacja: 10-03-2026, 12:37</t>
   </si>
 </sst>
 </file>
@@ -2038,18 +2041,20 @@
         <v>115.4</v>
       </c>
       <c r="Q5" s="4">
-        <v>115.1</v>
+        <v>115.8</v>
       </c>
       <c r="R5" s="4">
-        <v>121.5</v>
+        <v>122.2</v>
       </c>
       <c r="S5" s="4">
-        <v>132.5</v>
+        <v>127.2</v>
       </c>
       <c r="T5" s="4">
         <v>130.4</v>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4">
+        <v>135.69999999999999</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="2" t="s">
         <v>30</v>
@@ -2520,7 +2525,9 @@
       <c r="T12" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="5">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="2" t="s">
         <v>46</v>
@@ -3230,7 +3237,9 @@
       <c r="T24" s="4">
         <v>61.3</v>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4">
+        <v>61.6</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="2" t="s">
         <v>30</v>
@@ -3297,7 +3306,9 @@
       <c r="T25" s="4">
         <v>64.599999999999994</v>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4">
+        <v>65.3</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="2" t="s">
         <v>30</v>
@@ -3364,7 +3375,9 @@
       <c r="T26" s="4">
         <v>400.4</v>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="4">
+        <v>400.1</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="2" t="s">
         <v>30</v>
@@ -3431,7 +3444,9 @@
       <c r="T27" s="4">
         <v>381.8</v>
       </c>
-      <c r="U27" s="3"/>
+      <c r="U27" s="4">
+        <v>377.8</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="2" t="s">
         <v>30</v>
@@ -3498,7 +3513,9 @@
       <c r="T28" s="4">
         <v>417.8</v>
       </c>
-      <c r="U28" s="3"/>
+      <c r="U28" s="4">
+        <v>421.1</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="2" t="s">
         <v>30</v>
@@ -3565,7 +3582,9 @@
       <c r="T29" s="4">
         <v>407.7</v>
       </c>
-      <c r="U29" s="3"/>
+      <c r="U29" s="4">
+        <v>409.1</v>
+      </c>
       <c r="V29" s="3"/>
       <c r="W29" s="2" t="s">
         <v>30</v>
@@ -3632,7 +3651,9 @@
       <c r="T30" s="4">
         <v>389.8</v>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4">
+        <v>387.1</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="2" t="s">
         <v>30</v>
@@ -3699,7 +3720,9 @@
       <c r="T31" s="4">
         <v>264.39999999999998</v>
       </c>
-      <c r="U31" s="3"/>
+      <c r="U31" s="4">
+        <v>265.39999999999998</v>
+      </c>
       <c r="V31" s="3"/>
       <c r="W31" s="2" t="s">
         <v>30</v>
@@ -3766,7 +3789,9 @@
       <c r="T32" s="4">
         <v>292.8</v>
       </c>
-      <c r="U32" s="3"/>
+      <c r="U32" s="4">
+        <v>294.5</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="2" t="s">
         <v>30</v>
@@ -3833,7 +3858,9 @@
       <c r="T33" s="4">
         <v>237.9</v>
       </c>
-      <c r="U33" s="3"/>
+      <c r="U33" s="4">
+        <v>238.3</v>
+      </c>
       <c r="V33" s="3"/>
       <c r="W33" s="2" t="s">
         <v>30</v>
@@ -3900,7 +3927,9 @@
       <c r="T34" s="4">
         <v>287.7</v>
       </c>
-      <c r="U34" s="3"/>
+      <c r="U34" s="4">
+        <v>289.8</v>
+      </c>
       <c r="V34" s="3"/>
       <c r="W34" s="2" t="s">
         <v>30</v>
@@ -3967,7 +3996,9 @@
       <c r="T35" s="4">
         <v>230.2</v>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4">
+        <v>229.6</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="2" t="s">
         <v>30</v>
@@ -4034,7 +4065,9 @@
       <c r="T36" s="4">
         <v>25.7</v>
       </c>
-      <c r="U36" s="3"/>
+      <c r="U36" s="4">
+        <v>24.3</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="2" t="s">
         <v>30</v>
@@ -4101,7 +4134,9 @@
       <c r="T37" s="4">
         <v>24</v>
       </c>
-      <c r="U37" s="3"/>
+      <c r="U37" s="4">
+        <v>23.2</v>
+      </c>
       <c r="V37" s="3"/>
       <c r="W37" s="2" t="s">
         <v>30</v>
@@ -4168,7 +4203,9 @@
       <c r="T38" s="4">
         <v>27.3</v>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4">
+        <v>25.4</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="2" t="s">
         <v>30</v>
@@ -4235,7 +4272,9 @@
       <c r="T39" s="4">
         <v>26.2</v>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4">
+        <v>24.7</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="2" t="s">
         <v>30</v>
@@ -4302,7 +4341,9 @@
       <c r="T40" s="4">
         <v>24.4</v>
       </c>
-      <c r="U40" s="3"/>
+      <c r="U40" s="4">
+        <v>23.9</v>
+      </c>
       <c r="V40" s="3"/>
       <c r="W40" s="2" t="s">
         <v>30</v>
@@ -4361,15 +4402,17 @@
         <v>22.9</v>
       </c>
       <c r="R41" s="4">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="S41" s="4">
         <v>26.6</v>
       </c>
       <c r="T41" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="U41" s="3"/>
+        <v>25.8</v>
+      </c>
+      <c r="U41" s="4">
+        <v>25.3</v>
+      </c>
       <c r="V41" s="3"/>
       <c r="W41" s="2" t="s">
         <v>30</v>
@@ -4425,7 +4468,7 @@
         <v>27.5</v>
       </c>
       <c r="Q42" s="4">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="R42" s="4">
         <v>30</v>
@@ -4436,7 +4479,9 @@
       <c r="T42" s="4">
         <v>29.8</v>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4">
+        <v>29.3</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="2" t="s">
         <v>30</v>
@@ -4495,15 +4540,17 @@
         <v>17.7</v>
       </c>
       <c r="R43" s="4">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="S43" s="4">
         <v>22.2</v>
       </c>
       <c r="T43" s="4">
-        <v>21.9</v>
-      </c>
-      <c r="U43" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="U43" s="4">
+        <v>21.7</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="2" t="s">
         <v>30</v>
@@ -4565,12 +4612,14 @@
         <v>25.5</v>
       </c>
       <c r="S44" s="4">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="T44" s="4">
         <v>26.9</v>
       </c>
-      <c r="U44" s="3"/>
+      <c r="U44" s="4">
+        <v>26.6</v>
+      </c>
       <c r="V44" s="3"/>
       <c r="W44" s="2" t="s">
         <v>30</v>
@@ -4632,12 +4681,14 @@
         <v>25.3</v>
       </c>
       <c r="S45" s="4">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="T45" s="4">
         <v>24.1</v>
       </c>
-      <c r="U45" s="3"/>
+      <c r="U45" s="4">
+        <v>23.5</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="2" t="s">
         <v>30</v>
@@ -4684,9 +4735,11 @@
         <v>34.799999999999997</v>
       </c>
       <c r="T46" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="U46" s="3"/>
+        <v>36.5</v>
+      </c>
+      <c r="U46" s="4">
+        <v>37.700000000000003</v>
+      </c>
       <c r="V46" s="3"/>
       <c r="W46" s="2" t="s">
         <v>30</v>
@@ -4735,7 +4788,9 @@
       <c r="T47" s="4">
         <v>65</v>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4">
+        <v>66.2</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="2" t="s">
         <v>30</v>
@@ -5439,9 +5494,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="S62" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="T62" s="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="T62" s="4">
+        <v>5.5</v>
+      </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
       <c r="W62" s="2" t="s">
@@ -5500,7 +5557,9 @@
       <c r="S63" s="4">
         <v>4.5</v>
       </c>
-      <c r="T63" s="3"/>
+      <c r="T63" s="4">
+        <v>5.2</v>
+      </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
       <c r="W63" s="2" t="s">
@@ -5557,9 +5616,11 @@
         <v>0.3</v>
       </c>
       <c r="S64" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="T64" s="3"/>
+        <v>0.3</v>
+      </c>
+      <c r="T64" s="4">
+        <v>0.3</v>
+      </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
       <c r="W64" s="2" t="s">
@@ -7417,17 +7478,19 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="6">
+      <c r="R96" s="4">
         <v>21</v>
       </c>
       <c r="S96" s="3"/>
-      <c r="T96" s="6">
+      <c r="T96" s="4">
         <v>20</v>
       </c>
-      <c r="U96" s="6">
+      <c r="U96" s="4">
         <v>22</v>
       </c>
-      <c r="V96" s="3"/>
+      <c r="V96" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W96" s="2" t="s">
         <v>30</v>
       </c>
@@ -7462,17 +7525,19 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
-      <c r="R97" s="6">
+      <c r="R97" s="4">
         <v>20</v>
       </c>
       <c r="S97" s="3"/>
-      <c r="T97" s="6">
+      <c r="T97" s="4">
         <v>19</v>
       </c>
-      <c r="U97" s="6">
+      <c r="U97" s="4">
         <v>20</v>
       </c>
-      <c r="V97" s="3"/>
+      <c r="V97" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W97" s="2" t="s">
         <v>30</v>
       </c>
@@ -7507,17 +7572,19 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="6">
+      <c r="R98" s="4">
         <v>22</v>
       </c>
       <c r="S98" s="3"/>
-      <c r="T98" s="6">
+      <c r="T98" s="4">
         <v>21</v>
       </c>
-      <c r="U98" s="6">
+      <c r="U98" s="4">
         <v>25</v>
       </c>
-      <c r="V98" s="3"/>
+      <c r="V98" s="4">
+        <v>23.6</v>
+      </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
       </c>
@@ -7642,17 +7709,19 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
-      <c r="R101" s="6">
+      <c r="R101" s="4">
         <v>36</v>
       </c>
       <c r="S101" s="3"/>
-      <c r="T101" s="6">
+      <c r="T101" s="4">
         <v>31</v>
       </c>
-      <c r="U101" s="6">
+      <c r="U101" s="4">
         <v>36</v>
       </c>
-      <c r="V101" s="3"/>
+      <c r="V101" s="4">
+        <v>38.6</v>
+      </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
       </c>
@@ -7697,7 +7766,9 @@
       <c r="U102" s="6">
         <v>37</v>
       </c>
-      <c r="V102" s="3"/>
+      <c r="V102" s="6">
+        <v>41</v>
+      </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
       </c>
@@ -7732,17 +7803,19 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
-      <c r="R103" s="6">
+      <c r="R103" s="4">
         <v>28</v>
       </c>
       <c r="S103" s="3"/>
-      <c r="T103" s="6">
+      <c r="T103" s="4">
         <v>27</v>
       </c>
-      <c r="U103" s="6">
+      <c r="U103" s="4">
         <v>31</v>
       </c>
-      <c r="V103" s="3"/>
+      <c r="V103" s="4">
+        <v>32.200000000000003</v>
+      </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
       </c>
@@ -7777,17 +7850,19 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
-      <c r="R104" s="6">
+      <c r="R104" s="4">
         <v>17</v>
       </c>
       <c r="S104" s="3"/>
-      <c r="T104" s="6">
+      <c r="T104" s="4">
         <v>18</v>
       </c>
-      <c r="U104" s="6">
+      <c r="U104" s="4">
         <v>19</v>
       </c>
-      <c r="V104" s="3"/>
+      <c r="V104" s="4">
+        <v>20.9</v>
+      </c>
       <c r="W104" s="2" t="s">
         <v>30</v>
       </c>
@@ -7822,17 +7897,19 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
-      <c r="R105" s="6">
+      <c r="R105" s="4">
         <v>8</v>
       </c>
       <c r="S105" s="3"/>
-      <c r="T105" s="6">
+      <c r="T105" s="4">
         <v>9</v>
       </c>
-      <c r="U105" s="6">
+      <c r="U105" s="4">
         <v>12</v>
       </c>
-      <c r="V105" s="3"/>
+      <c r="V105" s="4">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="W105" s="2" t="s">
         <v>30</v>
       </c>
@@ -7867,17 +7944,19 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
-      <c r="R106" s="6">
+      <c r="R106" s="4">
         <v>3</v>
       </c>
       <c r="S106" s="3"/>
-      <c r="T106" s="6">
+      <c r="T106" s="4">
         <v>3</v>
       </c>
-      <c r="U106" s="6">
+      <c r="U106" s="4">
         <v>3</v>
       </c>
-      <c r="V106" s="3"/>
+      <c r="V106" s="4">
+        <v>2.7</v>
+      </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
       </c>
@@ -8256,7 +8335,7 @@
         <v>7.9</v>
       </c>
       <c r="T114" s="4">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="U114" s="4">
         <v>4.0999999999999996</v>
@@ -14728,56 +14807,28 @@
         <v>28</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G214" s="4">
-        <v>88</v>
-      </c>
-      <c r="H214" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I214" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J214" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K214" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M214" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N214" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P214" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q214" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R214" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S214" s="4">
-        <v>95</v>
-      </c>
-      <c r="T214" s="4">
-        <v>94.8</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+      <c r="P214" s="3"/>
+      <c r="Q214" s="3"/>
+      <c r="R214" s="3"/>
+      <c r="S214" s="3"/>
+      <c r="T214" s="3"/>
       <c r="U214" s="4">
-        <v>94.6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="V214" s="3"/>
       <c r="W214" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="215" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -14800,49 +14851,49 @@
         <v>36</v>
       </c>
       <c r="G215" s="4">
-        <v>95.3</v>
+        <v>88</v>
       </c>
       <c r="H215" s="4">
-        <v>95.4</v>
+        <v>88.4</v>
       </c>
       <c r="I215" s="4">
-        <v>95.4</v>
+        <v>91.7</v>
       </c>
       <c r="J215" s="4">
-        <v>95.5</v>
+        <v>93.3</v>
       </c>
       <c r="K215" s="4">
-        <v>96.4</v>
+        <v>93.9</v>
       </c>
       <c r="L215" s="4">
-        <v>96.5</v>
+        <v>94.6</v>
       </c>
       <c r="M215" s="4">
-        <v>96.5</v>
+        <v>94.8</v>
       </c>
       <c r="N215" s="4">
-        <v>96.6</v>
+        <v>94.5</v>
       </c>
       <c r="O215" s="4">
-        <v>96.6</v>
+        <v>94.6</v>
       </c>
       <c r="P215" s="4">
-        <v>96.6</v>
+        <v>94.8</v>
       </c>
       <c r="Q215" s="4">
-        <v>96.7</v>
+        <v>94.7</v>
       </c>
       <c r="R215" s="4">
-        <v>96.7</v>
+        <v>94.6</v>
       </c>
       <c r="S215" s="4">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="T215" s="4">
-        <v>96.8</v>
+        <v>94.8</v>
       </c>
       <c r="U215" s="4">
-        <v>96.8</v>
+        <v>94.6</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="2" t="s">
@@ -14868,29 +14919,51 @@
       <c r="F216" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G216" s="3"/>
-      <c r="H216" s="3"/>
-      <c r="I216" s="3"/>
-      <c r="J216" s="3"/>
-      <c r="K216" s="3"/>
-      <c r="L216" s="3"/>
-      <c r="M216" s="3"/>
-      <c r="N216" s="3"/>
-      <c r="O216" s="3"/>
-      <c r="P216" s="3"/>
+      <c r="G216" s="4">
+        <v>95.3</v>
+      </c>
+      <c r="H216" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="I216" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="J216" s="4">
+        <v>95.5</v>
+      </c>
+      <c r="K216" s="4">
+        <v>96.4</v>
+      </c>
+      <c r="L216" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="M216" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="N216" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="O216" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="P216" s="4">
+        <v>96.6</v>
+      </c>
       <c r="Q216" s="4">
-        <v>15.7</v>
+        <v>96.7</v>
       </c>
       <c r="R216" s="4">
-        <v>14.8</v>
+        <v>96.7</v>
       </c>
       <c r="S216" s="4">
-        <v>14.8</v>
+        <v>96.7</v>
       </c>
       <c r="T216" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="U216" s="3"/>
+        <v>96.8</v>
+      </c>
+      <c r="U216" s="4">
+        <v>96.8</v>
+      </c>
       <c r="V216" s="3"/>
       <c r="W216" s="2" t="s">
         <v>30</v>
@@ -14926,16 +14999,16 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
       <c r="Q217" s="4">
-        <v>13.3</v>
+        <v>15.7</v>
       </c>
       <c r="R217" s="4">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="S217" s="4">
-        <v>13.1</v>
+        <v>14.8</v>
       </c>
       <c r="T217" s="4">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="U217" s="3"/>
       <c r="V217" s="3"/>
@@ -14943,15 +15016,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="218" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -14962,47 +15035,27 @@
       <c r="F218" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G218" s="4">
-        <v>41.6</v>
-      </c>
-      <c r="H218" s="4">
-        <v>44.7</v>
-      </c>
-      <c r="I218" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="J218" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="K218" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="L218" s="4">
-        <v>49.8</v>
-      </c>
-      <c r="M218" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="N218" s="4">
-        <v>51.2</v>
-      </c>
-      <c r="O218" s="4">
-        <v>52.4</v>
-      </c>
-      <c r="P218" s="4">
-        <v>53.4</v>
-      </c>
+      <c r="G218" s="3"/>
+      <c r="H218" s="3"/>
+      <c r="I218" s="3"/>
+      <c r="J218" s="3"/>
+      <c r="K218" s="3"/>
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+      <c r="P218" s="3"/>
       <c r="Q218" s="4">
-        <v>53.9</v>
+        <v>13.3</v>
       </c>
       <c r="R218" s="4">
-        <v>54.8</v>
+        <v>13.5</v>
       </c>
       <c r="S218" s="4">
-        <v>55.8</v>
+        <v>13.1</v>
       </c>
       <c r="T218" s="4">
-        <v>53.6</v>
+        <v>13.3</v>
       </c>
       <c r="U218" s="3"/>
       <c r="V218" s="3"/>
@@ -15015,7 +15068,7 @@
         <v>260</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>281</v>
@@ -15027,48 +15080,52 @@
         <v>28</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G219" s="3"/>
-      <c r="H219" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G219" s="4">
+        <v>41.6</v>
+      </c>
+      <c r="H219" s="4">
+        <v>44.7</v>
+      </c>
       <c r="I219" s="4">
-        <v>29.8</v>
+        <v>46.5</v>
       </c>
       <c r="J219" s="4">
-        <v>31.1</v>
+        <v>48.2</v>
       </c>
       <c r="K219" s="4">
-        <v>30.3</v>
+        <v>49.6</v>
       </c>
       <c r="L219" s="4">
-        <v>32.299999999999997</v>
+        <v>49.8</v>
       </c>
       <c r="M219" s="4">
-        <v>34.700000000000003</v>
+        <v>50.6</v>
       </c>
       <c r="N219" s="4">
-        <v>35.6</v>
+        <v>51.2</v>
       </c>
       <c r="O219" s="4">
-        <v>37.5</v>
+        <v>52.4</v>
       </c>
       <c r="P219" s="4">
-        <v>35.9</v>
+        <v>53.4</v>
       </c>
       <c r="Q219" s="4">
-        <v>36.6</v>
+        <v>53.9</v>
       </c>
       <c r="R219" s="4">
-        <v>36.1</v>
+        <v>54.8</v>
       </c>
       <c r="S219" s="4">
-        <v>35.4</v>
+        <v>55.8</v>
       </c>
       <c r="T219" s="4">
-        <v>35.6</v>
+        <v>53.6</v>
       </c>
       <c r="U219" s="4">
-        <v>35.4</v>
+        <v>54.5</v>
       </c>
       <c r="V219" s="3"/>
       <c r="W219" s="2" t="s">
@@ -15080,10 +15137,10 @@
         <v>260</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>27</v>
@@ -15092,39 +15149,63 @@
         <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G220" s="3"/>
       <c r="H220" s="3"/>
-      <c r="I220" s="3"/>
-      <c r="J220" s="3"/>
-      <c r="K220" s="3"/>
-      <c r="L220" s="3"/>
-      <c r="M220" s="3"/>
-      <c r="N220" s="3"/>
-      <c r="O220" s="3"/>
-      <c r="P220" s="3"/>
-      <c r="Q220" s="5">
-        <v>83.49</v>
-      </c>
-      <c r="R220" s="3"/>
-      <c r="S220" s="3"/>
-      <c r="T220" s="3"/>
-      <c r="U220" s="3"/>
+      <c r="I220" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="J220" s="4">
+        <v>31.1</v>
+      </c>
+      <c r="K220" s="4">
+        <v>30.3</v>
+      </c>
+      <c r="L220" s="4">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="M220" s="4">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="N220" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="O220" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="P220" s="4">
+        <v>35.9</v>
+      </c>
+      <c r="Q220" s="4">
+        <v>36.6</v>
+      </c>
+      <c r="R220" s="4">
+        <v>36.1</v>
+      </c>
+      <c r="S220" s="4">
+        <v>35.4</v>
+      </c>
+      <c r="T220" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="U220" s="4">
+        <v>35.4</v>
+      </c>
       <c r="V220" s="3"/>
       <c r="W220" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="221" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="221" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>27</v>
@@ -15133,52 +15214,28 @@
         <v>28</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G221" s="3"/>
       <c r="H221" s="3"/>
-      <c r="I221" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="J221" s="5">
-        <v>1.41</v>
-      </c>
-      <c r="K221" s="5">
-        <v>1.43</v>
-      </c>
-      <c r="L221" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="M221" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="N221" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="O221" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="P221" s="5">
-        <v>1.57</v>
-      </c>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
       <c r="Q221" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="R221" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="S221" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="T221" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="U221" s="5">
-        <v>1.62</v>
-      </c>
+        <v>83.49</v>
+      </c>
+      <c r="R221" s="3"/>
+      <c r="S221" s="3"/>
+      <c r="T221" s="3"/>
+      <c r="U221" s="3"/>
       <c r="V221" s="3"/>
       <c r="W221" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
     </row>
     <row r="222" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15186,10 +15243,10 @@
         <v>260</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>27</v>
@@ -15198,44 +15255,52 @@
         <v>28</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="3"/>
-      <c r="I222" s="3"/>
-      <c r="J222" s="3"/>
-      <c r="K222" s="3"/>
-      <c r="L222" s="4">
-        <v>12.1</v>
-      </c>
-      <c r="M222" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="N222" s="4">
-        <v>11.6</v>
-      </c>
-      <c r="O222" s="4">
-        <v>11.4</v>
-      </c>
-      <c r="P222" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="Q222" s="4">
-        <v>9</v>
-      </c>
-      <c r="R222" s="4">
-        <v>7.7</v>
-      </c>
-      <c r="S222" s="4">
-        <v>7.6</v>
-      </c>
-      <c r="T222" s="4">
-        <v>7.6</v>
-      </c>
-      <c r="U222" s="3"/>
+      <c r="I222" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="J222" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="K222" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="L222" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="M222" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="N222" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="O222" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="P222" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="Q222" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="R222" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="S222" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="T222" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="U222" s="5">
+        <v>1.62</v>
+      </c>
       <c r="V222" s="3"/>
       <c r="W222" s="2" t="s">
-        <v>290</v>
+        <v>30</v>
       </c>
     </row>
     <row r="223" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15243,10 +15308,10 @@
         <v>260</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>27</v>
@@ -15257,52 +15322,42 @@
       <c r="F223" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G223" s="4">
-        <v>166.5</v>
-      </c>
-      <c r="H223" s="4">
-        <v>166.2</v>
-      </c>
-      <c r="I223" s="4">
-        <v>165.6</v>
-      </c>
-      <c r="J223" s="4">
-        <v>155.5</v>
-      </c>
-      <c r="K223" s="4">
-        <v>159.69999999999999</v>
-      </c>
+      <c r="G223" s="3"/>
+      <c r="H223" s="3"/>
+      <c r="I223" s="3"/>
+      <c r="J223" s="3"/>
+      <c r="K223" s="3"/>
       <c r="L223" s="4">
-        <v>158.30000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="M223" s="4">
-        <v>162.69999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="N223" s="4">
-        <v>161.69999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="O223" s="4">
-        <v>163.4</v>
+        <v>11.4</v>
       </c>
       <c r="P223" s="4">
-        <v>167.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q223" s="4">
-        <v>99.3</v>
+        <v>9</v>
       </c>
       <c r="R223" s="4">
-        <v>110.1</v>
+        <v>7.7</v>
       </c>
       <c r="S223" s="4">
-        <v>135.6</v>
+        <v>7.6</v>
       </c>
       <c r="T223" s="4">
-        <v>144.6</v>
+        <v>7.6</v>
       </c>
       <c r="U223" s="3"/>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
-        <v>171</v>
+        <v>291</v>
       </c>
     </row>
     <row r="224" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15310,10 +15365,10 @@
         <v>260</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -15322,56 +15377,56 @@
         <v>28</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G224" s="4">
-        <v>3.7</v>
+        <v>166.5</v>
       </c>
       <c r="H224" s="4">
-        <v>3.4</v>
+        <v>166.2</v>
       </c>
       <c r="I224" s="4">
-        <v>4.0999999999999996</v>
+        <v>165.6</v>
       </c>
       <c r="J224" s="4">
-        <v>3.8</v>
+        <v>155.5</v>
       </c>
       <c r="K224" s="4">
-        <v>3.9</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="L224" s="4">
-        <v>3.9</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="M224" s="4">
-        <v>4.5999999999999996</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="N224" s="4">
-        <v>5.0999999999999996</v>
+        <v>161.69999999999999</v>
       </c>
       <c r="O224" s="4">
-        <v>5.4</v>
+        <v>163.4</v>
       </c>
       <c r="P224" s="4">
-        <v>6.1</v>
+        <v>167.6</v>
       </c>
       <c r="Q224" s="4">
-        <v>6.5</v>
+        <v>99.3</v>
       </c>
       <c r="R224" s="4">
-        <v>6.6</v>
+        <v>110.1</v>
       </c>
       <c r="S224" s="4">
-        <v>6.6</v>
+        <v>135.6</v>
       </c>
       <c r="T224" s="4">
-        <v>6.3</v>
+        <v>144.6</v>
       </c>
       <c r="U224" s="4">
-        <v>5.8</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15379,7 +15434,7 @@
         <v>260</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>294</v>
@@ -15393,50 +15448,50 @@
       <c r="F225" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G225" s="5">
-        <v>0.26</v>
-      </c>
-      <c r="H225" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="I225" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J225" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="K225" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="L225" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="M225" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="N225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="P225" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="Q225" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="R225" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="S225" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="T225" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="U225" s="5">
-        <v>0.18</v>
+      <c r="G225" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="H225" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="I225" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J225" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K225" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="L225" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="M225" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N225" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O225" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="P225" s="4">
+        <v>6.1</v>
+      </c>
+      <c r="Q225" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="R225" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="S225" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T225" s="4">
+        <v>6.3</v>
+      </c>
+      <c r="U225" s="4">
+        <v>5.8</v>
       </c>
       <c r="V225" s="3"/>
       <c r="W225" s="2" t="s">
@@ -15448,7 +15503,7 @@
         <v>260</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>295</v>
@@ -15462,31 +15517,51 @@
       <c r="F226" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="3"/>
-      <c r="J226" s="3"/>
-      <c r="K226" s="3"/>
-      <c r="L226" s="3"/>
-      <c r="M226" s="3"/>
-      <c r="N226" s="3"/>
-      <c r="O226" s="3"/>
-      <c r="P226" s="6">
-        <v>74110</v>
-      </c>
-      <c r="Q226" s="6">
-        <v>68436</v>
-      </c>
-      <c r="R226" s="6">
-        <v>65117</v>
-      </c>
-      <c r="S226" s="6">
-        <v>64070</v>
-      </c>
-      <c r="T226" s="6">
-        <v>61349</v>
-      </c>
-      <c r="U226" s="3"/>
+      <c r="G226" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="H226" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="I226" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J226" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K226" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="L226" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="M226" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="N226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="P226" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="Q226" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="R226" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="S226" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="T226" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="U226" s="5">
+        <v>0.18</v>
+      </c>
       <c r="V226" s="3"/>
       <c r="W226" s="2" t="s">
         <v>30</v>
@@ -15497,7 +15572,7 @@
         <v>260</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>296</v>
@@ -15514,44 +15589,44 @@
       <c r="G227" s="3"/>
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
-      <c r="J227" s="6">
-        <v>546870</v>
-      </c>
+      <c r="J227" s="3"/>
       <c r="K227" s="3"/>
-      <c r="L227" s="6">
-        <v>512116</v>
-      </c>
-      <c r="M227" s="6">
-        <v>501544</v>
-      </c>
+      <c r="L227" s="3"/>
+      <c r="M227" s="3"/>
       <c r="N227" s="3"/>
-      <c r="O227" s="6">
-        <v>487452</v>
-      </c>
-      <c r="P227" s="3"/>
+      <c r="O227" s="3"/>
+      <c r="P227" s="6">
+        <v>74110</v>
+      </c>
       <c r="Q227" s="6">
-        <v>469607</v>
-      </c>
-      <c r="R227" s="3"/>
+        <v>68436</v>
+      </c>
+      <c r="R227" s="6">
+        <v>65117</v>
+      </c>
       <c r="S227" s="6">
-        <v>457891</v>
-      </c>
-      <c r="T227" s="3"/>
-      <c r="U227" s="3"/>
+        <v>64070</v>
+      </c>
+      <c r="T227" s="6">
+        <v>61349</v>
+      </c>
+      <c r="U227" s="6">
+        <v>59560</v>
+      </c>
       <c r="V227" s="3"/>
       <c r="W227" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>27</v>
@@ -15560,52 +15635,36 @@
         <v>28</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G228" s="6">
-        <v>22795</v>
-      </c>
-      <c r="H228" s="6">
-        <v>21359</v>
-      </c>
-      <c r="I228" s="6">
-        <v>20022</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G228" s="3"/>
+      <c r="H228" s="3"/>
+      <c r="I228" s="3"/>
       <c r="J228" s="6">
-        <v>19636</v>
-      </c>
-      <c r="K228" s="6">
-        <v>18137</v>
-      </c>
+        <v>546870</v>
+      </c>
+      <c r="K228" s="3"/>
       <c r="L228" s="6">
-        <v>16793</v>
+        <v>512116</v>
       </c>
       <c r="M228" s="6">
-        <v>15086</v>
-      </c>
-      <c r="N228" s="6">
-        <v>14505</v>
-      </c>
+        <v>501544</v>
+      </c>
+      <c r="N228" s="3"/>
       <c r="O228" s="6">
-        <v>14165</v>
-      </c>
-      <c r="P228" s="6">
-        <v>11466</v>
-      </c>
+        <v>487452</v>
+      </c>
+      <c r="P228" s="3"/>
       <c r="Q228" s="6">
-        <v>8767</v>
-      </c>
-      <c r="R228" s="6">
-        <v>8374</v>
-      </c>
+        <v>469607</v>
+      </c>
+      <c r="R228" s="3"/>
       <c r="S228" s="6">
-        <v>7344</v>
-      </c>
-      <c r="T228" s="6">
-        <v>5553</v>
-      </c>
+        <v>457891</v>
+      </c>
+      <c r="T228" s="3"/>
       <c r="U228" s="6">
-        <v>5297</v>
+        <v>446959</v>
       </c>
       <c r="V228" s="3"/>
       <c r="W228" s="2" t="s">
@@ -15617,10 +15676,10 @@
         <v>260</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>27</v>
@@ -15629,64 +15688,64 @@
         <v>28</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G229" s="6">
-        <v>961</v>
+        <v>22795</v>
       </c>
       <c r="H229" s="6">
-        <v>136730</v>
+        <v>21359</v>
       </c>
       <c r="I229" s="6">
-        <v>11553</v>
+        <v>20022</v>
       </c>
       <c r="J229" s="6">
-        <v>15701</v>
+        <v>19636</v>
       </c>
       <c r="K229" s="6">
-        <v>2758</v>
+        <v>18137</v>
       </c>
       <c r="L229" s="6">
-        <v>69422</v>
+        <v>16793</v>
       </c>
       <c r="M229" s="6">
-        <v>44764</v>
+        <v>15086</v>
       </c>
       <c r="N229" s="6">
-        <v>78118</v>
+        <v>14505</v>
       </c>
       <c r="O229" s="6">
-        <v>14958</v>
+        <v>14165</v>
       </c>
       <c r="P229" s="6">
-        <v>68943</v>
+        <v>11466</v>
       </c>
       <c r="Q229" s="6">
-        <v>57788</v>
+        <v>8767</v>
       </c>
       <c r="R229" s="6">
-        <v>27276</v>
+        <v>8374</v>
       </c>
       <c r="S229" s="6">
-        <v>256675</v>
+        <v>7344</v>
       </c>
       <c r="T229" s="6">
-        <v>211015</v>
+        <v>5553</v>
       </c>
       <c r="U229" s="6">
-        <v>1435</v>
+        <v>5297</v>
       </c>
       <c r="V229" s="3"/>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>301</v>
@@ -15698,67 +15757,67 @@
         <v>28</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>29</v>
+        <v>300</v>
       </c>
       <c r="G230" s="6">
-        <v>6</v>
+        <v>961</v>
       </c>
       <c r="H230" s="6">
-        <v>8</v>
+        <v>136730</v>
       </c>
       <c r="I230" s="6">
-        <v>8</v>
+        <v>11553</v>
       </c>
       <c r="J230" s="6">
-        <v>10</v>
+        <v>15701</v>
       </c>
       <c r="K230" s="6">
-        <v>9</v>
+        <v>2758</v>
       </c>
       <c r="L230" s="6">
-        <v>10</v>
+        <v>69422</v>
       </c>
       <c r="M230" s="6">
-        <v>11</v>
+        <v>44764</v>
       </c>
       <c r="N230" s="6">
-        <v>13</v>
+        <v>78118</v>
       </c>
       <c r="O230" s="6">
-        <v>12</v>
+        <v>14958</v>
       </c>
       <c r="P230" s="6">
-        <v>16</v>
+        <v>68943</v>
       </c>
       <c r="Q230" s="6">
-        <v>21</v>
+        <v>57788</v>
       </c>
       <c r="R230" s="6">
-        <v>24</v>
+        <v>27276</v>
       </c>
       <c r="S230" s="6">
-        <v>25</v>
+        <v>256675</v>
       </c>
       <c r="T230" s="6">
-        <v>26</v>
+        <v>211015</v>
       </c>
       <c r="U230" s="6">
-        <v>21</v>
+        <v>1435</v>
       </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="231" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>27</v>
@@ -15767,67 +15826,67 @@
         <v>28</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G231" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H231" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="I231" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J231" s="5">
-        <v>0.61</v>
-      </c>
-      <c r="K231" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="L231" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="M231" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="N231" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="O231" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="P231" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="Q231" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="R231" s="5">
-        <v>0.86</v>
-      </c>
-      <c r="S231" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="T231" s="5">
-        <v>1.18</v>
-      </c>
-      <c r="U231" s="5">
-        <v>1.38</v>
+        <v>29</v>
+      </c>
+      <c r="G231" s="6">
+        <v>6</v>
+      </c>
+      <c r="H231" s="6">
+        <v>8</v>
+      </c>
+      <c r="I231" s="6">
+        <v>8</v>
+      </c>
+      <c r="J231" s="6">
+        <v>10</v>
+      </c>
+      <c r="K231" s="6">
+        <v>9</v>
+      </c>
+      <c r="L231" s="6">
+        <v>10</v>
+      </c>
+      <c r="M231" s="6">
+        <v>11</v>
+      </c>
+      <c r="N231" s="6">
+        <v>13</v>
+      </c>
+      <c r="O231" s="6">
+        <v>12</v>
+      </c>
+      <c r="P231" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>21</v>
+      </c>
+      <c r="R231" s="6">
+        <v>24</v>
+      </c>
+      <c r="S231" s="6">
+        <v>25</v>
+      </c>
+      <c r="T231" s="6">
+        <v>26</v>
+      </c>
+      <c r="U231" s="6">
+        <v>21</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="2" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
     </row>
     <row r="232" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>27</v>
@@ -15836,52 +15895,52 @@
         <v>28</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="G232" s="5">
-        <v>16.5</v>
+        <v>0.59</v>
       </c>
       <c r="H232" s="5">
-        <v>20.43</v>
+        <v>0.5</v>
       </c>
       <c r="I232" s="5">
-        <v>17.52</v>
+        <v>0.59</v>
       </c>
       <c r="J232" s="5">
-        <v>16.72</v>
+        <v>0.63</v>
       </c>
       <c r="K232" s="5">
-        <v>16.579999999999998</v>
+        <v>0.66</v>
       </c>
       <c r="L232" s="5">
-        <v>16.47</v>
+        <v>0.69</v>
       </c>
       <c r="M232" s="5">
-        <v>16.920000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="N232" s="5">
-        <v>18.010000000000002</v>
+        <v>0.69</v>
       </c>
       <c r="O232" s="5">
-        <v>18.47</v>
+        <v>0.71</v>
       </c>
       <c r="P232" s="5">
-        <v>17.59</v>
+        <v>0.78</v>
       </c>
       <c r="Q232" s="5">
-        <v>17.579999999999998</v>
+        <v>0.77</v>
       </c>
       <c r="R232" s="5">
-        <v>18.25</v>
+        <v>0.81</v>
       </c>
       <c r="S232" s="5">
-        <v>18.309999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="T232" s="5">
-        <v>17.34</v>
+        <v>0.9</v>
       </c>
       <c r="U232" s="5">
-        <v>16.68</v>
+        <v>0.97</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
@@ -15890,10 +15949,10 @@
     </row>
     <row r="233" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>307</v>
@@ -15905,67 +15964,67 @@
         <v>28</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G233" s="4">
-        <v>11.1</v>
-      </c>
-      <c r="H233" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="I233" s="4">
-        <v>11</v>
-      </c>
-      <c r="J233" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="K233" s="4">
-        <v>13</v>
-      </c>
-      <c r="L233" s="4">
-        <v>11.9</v>
-      </c>
-      <c r="M233" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="N233" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="O233" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P233" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Q233" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="R233" s="4">
-        <v>7</v>
-      </c>
-      <c r="S233" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="T233" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="U233" s="4">
-        <v>7.7</v>
+        <v>300</v>
+      </c>
+      <c r="G233" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="H233" s="5">
+        <v>20.43</v>
+      </c>
+      <c r="I233" s="5">
+        <v>17.52</v>
+      </c>
+      <c r="J233" s="5">
+        <v>16.72</v>
+      </c>
+      <c r="K233" s="5">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="L233" s="5">
+        <v>16.47</v>
+      </c>
+      <c r="M233" s="5">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="N233" s="5">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="O233" s="5">
+        <v>18.47</v>
+      </c>
+      <c r="P233" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="Q233" s="5">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="R233" s="5">
+        <v>18.25</v>
+      </c>
+      <c r="S233" s="5">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="T233" s="5">
+        <v>17.34</v>
+      </c>
+      <c r="U233" s="5">
+        <v>16.68</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>27</v>
@@ -15976,59 +16035,65 @@
       <c r="F234" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G234" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H234" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="I234" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="J234" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="K234" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="L234" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="M234" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="N234" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="O234" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="P234" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="Q234" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R234" s="3"/>
-      <c r="S234" s="3"/>
-      <c r="T234" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="U234" s="3"/>
+      <c r="G234" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="H234" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="I234" s="4">
+        <v>11</v>
+      </c>
+      <c r="J234" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="K234" s="4">
+        <v>13</v>
+      </c>
+      <c r="L234" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="M234" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="N234" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="O234" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="P234" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q234" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="R234" s="4">
+        <v>7</v>
+      </c>
+      <c r="S234" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="T234" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U234" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V234" s="3"/>
       <c r="W234" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="235" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>27</v>
@@ -16037,65 +16102,61 @@
         <v>28</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="G235" s="4">
-        <v>100</v>
-      </c>
-      <c r="H235" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I235" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J235" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K235" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L235" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M235" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N235" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O235" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P235" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q235" s="4">
-        <v>90.5</v>
-      </c>
-      <c r="R235" s="4">
-        <v>99</v>
-      </c>
-      <c r="S235" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T235" s="4">
-        <v>84.8</v>
+        <v>36</v>
+      </c>
+      <c r="G235" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H235" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I235" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J235" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K235" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L235" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M235" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N235" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O235" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P235" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q235" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R235" s="3"/>
+      <c r="S235" s="3"/>
+      <c r="T235" s="5">
+        <v>3.1</v>
       </c>
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
       <c r="W235" s="2" t="s">
-        <v>314</v>
+        <v>51</v>
       </c>
     </row>
     <row r="236" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>27</v>
@@ -16104,65 +16165,65 @@
         <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G236" s="4">
         <v>100</v>
       </c>
       <c r="H236" s="4">
-        <v>99.6</v>
+        <v>99.8</v>
       </c>
       <c r="I236" s="4">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="J236" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K236" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L236" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M236" s="4">
         <v>96.8</v>
       </c>
-      <c r="K236" s="4">
-        <v>93.7</v>
-      </c>
-      <c r="L236" s="4">
-        <v>94.4</v>
-      </c>
-      <c r="M236" s="4">
-        <v>97</v>
-      </c>
       <c r="N236" s="4">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="O236" s="4">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="P236" s="4">
-        <v>95.1</v>
+        <v>95</v>
       </c>
       <c r="Q236" s="4">
-        <v>91.5</v>
+        <v>90.5</v>
       </c>
       <c r="R236" s="4">
-        <v>98.4</v>
+        <v>99</v>
       </c>
       <c r="S236" s="4">
-        <v>93.8</v>
+        <v>94.2</v>
       </c>
       <c r="T236" s="4">
-        <v>85.8</v>
+        <v>84.8</v>
       </c>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="237" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>27</v>
@@ -16171,64 +16232,62 @@
         <v>28</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G237" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H237" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I237" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J237" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K237" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L237" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M237" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N237" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O237" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P237" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q237" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R237" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S237" s="5">
-        <v>16.63</v>
-      </c>
-      <c r="T237" s="5">
-        <v>16.559999999999999</v>
-      </c>
-      <c r="U237" s="5">
-        <v>17.77</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="G237" s="4">
+        <v>100</v>
+      </c>
+      <c r="H237" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="I237" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J237" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="K237" s="4">
+        <v>93.7</v>
+      </c>
+      <c r="L237" s="4">
+        <v>94.4</v>
+      </c>
+      <c r="M237" s="4">
+        <v>97</v>
+      </c>
+      <c r="N237" s="4">
+        <v>100.6</v>
+      </c>
+      <c r="O237" s="4">
+        <v>100.6</v>
+      </c>
+      <c r="P237" s="4">
+        <v>95.1</v>
+      </c>
+      <c r="Q237" s="4">
+        <v>91.5</v>
+      </c>
+      <c r="R237" s="4">
+        <v>98.4</v>
+      </c>
+      <c r="S237" s="4">
+        <v>93.8</v>
+      </c>
+      <c r="T237" s="4">
+        <v>85.8</v>
+      </c>
+      <c r="U237" s="3"/>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
-        <v>182</v>
+        <v>315</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>318</v>
@@ -16240,65 +16299,67 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G238" s="6">
-        <v>563</v>
-      </c>
-      <c r="H238" s="6">
-        <v>531</v>
-      </c>
-      <c r="I238" s="6">
-        <v>661</v>
-      </c>
-      <c r="J238" s="6">
-        <v>778</v>
-      </c>
-      <c r="K238" s="6">
-        <v>847</v>
-      </c>
-      <c r="L238" s="6">
-        <v>909</v>
-      </c>
-      <c r="M238" s="6">
-        <v>930</v>
-      </c>
-      <c r="N238" s="6">
-        <v>946</v>
-      </c>
-      <c r="O238" s="6">
-        <v>991</v>
-      </c>
-      <c r="P238" s="6">
-        <v>1050</v>
-      </c>
-      <c r="Q238" s="6">
-        <v>1073</v>
-      </c>
-      <c r="R238" s="6">
-        <v>1189</v>
-      </c>
-      <c r="S238" s="6">
-        <v>1318</v>
-      </c>
-      <c r="T238" s="6">
-        <v>1372</v>
-      </c>
-      <c r="U238" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G238" s="5">
+        <v>9.2799999999999994</v>
+      </c>
+      <c r="H238" s="5">
+        <v>10.34</v>
+      </c>
+      <c r="I238" s="5">
+        <v>10.96</v>
+      </c>
+      <c r="J238" s="5">
+        <v>11.45</v>
+      </c>
+      <c r="K238" s="5">
+        <v>11.61</v>
+      </c>
+      <c r="L238" s="5">
+        <v>11.88</v>
+      </c>
+      <c r="M238" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="N238" s="5">
+        <v>11.06</v>
+      </c>
+      <c r="O238" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="P238" s="5">
+        <v>15.38</v>
+      </c>
+      <c r="Q238" s="5">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="R238" s="5">
+        <v>15.6</v>
+      </c>
+      <c r="S238" s="5">
+        <v>16.63</v>
+      </c>
+      <c r="T238" s="5">
+        <v>16.559999999999999</v>
+      </c>
+      <c r="U238" s="5">
+        <v>17.77</v>
+      </c>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16307,67 +16368,67 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G239" s="6">
-        <v>2218</v>
+        <v>563</v>
       </c>
       <c r="H239" s="6">
-        <v>3117</v>
+        <v>531</v>
       </c>
       <c r="I239" s="6">
-        <v>4139</v>
+        <v>661</v>
       </c>
       <c r="J239" s="6">
-        <v>5205</v>
+        <v>778</v>
       </c>
       <c r="K239" s="6">
-        <v>5793</v>
+        <v>847</v>
       </c>
       <c r="L239" s="6">
-        <v>7105</v>
+        <v>909</v>
       </c>
       <c r="M239" s="6">
-        <v>8017</v>
+        <v>930</v>
       </c>
       <c r="N239" s="6">
-        <v>8195</v>
+        <v>946</v>
       </c>
       <c r="O239" s="6">
-        <v>8486</v>
+        <v>991</v>
       </c>
       <c r="P239" s="6">
-        <v>9547</v>
+        <v>1050</v>
       </c>
       <c r="Q239" s="6">
-        <v>12490</v>
+        <v>1073</v>
       </c>
       <c r="R239" s="6">
-        <v>16935</v>
+        <v>1189</v>
       </c>
       <c r="S239" s="6">
-        <v>22670</v>
+        <v>1318</v>
       </c>
       <c r="T239" s="6">
-        <v>28779</v>
+        <v>1372</v>
       </c>
       <c r="U239" s="6">
-        <v>33623</v>
+        <v>1556</v>
       </c>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>322</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16376,62 +16437,64 @@
         <v>28</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G240" s="4">
-        <v>91.3</v>
-      </c>
-      <c r="H240" s="4">
-        <v>91.3</v>
-      </c>
-      <c r="I240" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="J240" s="4">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="K240" s="4">
-        <v>93.5</v>
-      </c>
-      <c r="L240" s="4">
-        <v>87</v>
-      </c>
-      <c r="M240" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="N240" s="4">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="O240" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="P240" s="4">
-        <v>47.8</v>
-      </c>
-      <c r="Q240" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="R240" s="4">
-        <v>54.4</v>
-      </c>
-      <c r="S240" s="4">
-        <v>30.4</v>
-      </c>
-      <c r="T240" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="U240" s="3"/>
+        <v>322</v>
+      </c>
+      <c r="G240" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H240" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I240" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J240" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K240" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L240" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M240" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N240" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O240" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P240" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q240" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R240" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S240" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T240" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U240" s="6">
+        <v>33623</v>
+      </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
-        <v>101</v>
+        <v>323</v>
       </c>
     </row>
     <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>325</v>
@@ -16443,53 +16506,51 @@
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G241" s="6">
-        <v>28</v>
-      </c>
-      <c r="H241" s="6">
-        <v>27</v>
-      </c>
-      <c r="I241" s="6">
-        <v>26</v>
-      </c>
-      <c r="J241" s="6">
-        <v>25</v>
-      </c>
-      <c r="K241" s="6">
-        <v>24</v>
-      </c>
-      <c r="L241" s="6">
-        <v>23</v>
-      </c>
-      <c r="M241" s="6">
-        <v>22</v>
-      </c>
-      <c r="N241" s="6">
-        <v>22</v>
-      </c>
-      <c r="O241" s="6">
-        <v>22</v>
-      </c>
-      <c r="P241" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q241" s="6">
-        <v>19</v>
-      </c>
-      <c r="R241" s="6">
-        <v>17</v>
-      </c>
-      <c r="S241" s="6">
-        <v>16</v>
-      </c>
-      <c r="T241" s="6">
-        <v>16</v>
-      </c>
-      <c r="U241" s="6">
-        <v>15</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G241" s="4">
+        <v>91.3</v>
+      </c>
+      <c r="H241" s="4">
+        <v>91.3</v>
+      </c>
+      <c r="I241" s="4">
+        <v>84.8</v>
+      </c>
+      <c r="J241" s="4">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="K241" s="4">
+        <v>93.5</v>
+      </c>
+      <c r="L241" s="4">
+        <v>87</v>
+      </c>
+      <c r="M241" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="N241" s="4">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="O241" s="4">
+        <v>84.8</v>
+      </c>
+      <c r="P241" s="4">
+        <v>47.8</v>
+      </c>
+      <c r="Q241" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="R241" s="4">
+        <v>54.4</v>
+      </c>
+      <c r="S241" s="4">
+        <v>30.4</v>
+      </c>
+      <c r="T241" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="U241" s="3"/>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
         <v>101</v>
@@ -16497,10 +16558,10 @@
     </row>
     <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>326</v>
@@ -16512,63 +16573,67 @@
         <v>28</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>327</v>
+        <v>100</v>
       </c>
       <c r="G242" s="6">
-        <v>2186</v>
+        <v>28</v>
       </c>
       <c r="H242" s="6">
-        <v>1721</v>
+        <v>27</v>
       </c>
       <c r="I242" s="6">
-        <v>2035</v>
+        <v>26</v>
       </c>
       <c r="J242" s="6">
-        <v>2174</v>
+        <v>25</v>
       </c>
       <c r="K242" s="6">
-        <v>1981</v>
+        <v>24</v>
       </c>
       <c r="L242" s="6">
-        <v>1725</v>
+        <v>23</v>
       </c>
       <c r="M242" s="6">
-        <v>1826</v>
+        <v>22</v>
       </c>
       <c r="N242" s="6">
-        <v>1792</v>
+        <v>22</v>
       </c>
       <c r="O242" s="6">
-        <v>1744</v>
+        <v>22</v>
       </c>
       <c r="P242" s="6">
-        <v>1494</v>
+        <v>21</v>
       </c>
       <c r="Q242" s="6">
-        <v>1820</v>
+        <v>19</v>
       </c>
       <c r="R242" s="6">
-        <v>2205</v>
+        <v>17</v>
       </c>
       <c r="S242" s="6">
-        <v>1959</v>
-      </c>
-      <c r="T242" s="3"/>
-      <c r="U242" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="T242" s="6">
+        <v>16</v>
+      </c>
+      <c r="U242" s="6">
+        <v>15</v>
+      </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
-        <v>328</v>
+        <v>101</v>
       </c>
     </row>
     <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>27</v>
@@ -16577,63 +16642,65 @@
         <v>28</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G243" s="6">
-        <v>48641</v>
+        <v>2186</v>
       </c>
       <c r="H243" s="6">
-        <v>48212</v>
+        <v>1721</v>
       </c>
       <c r="I243" s="6">
-        <v>46053</v>
+        <v>2035</v>
       </c>
       <c r="J243" s="6">
-        <v>43064</v>
+        <v>2174</v>
       </c>
       <c r="K243" s="6">
-        <v>43315</v>
+        <v>1981</v>
       </c>
       <c r="L243" s="6">
-        <v>46834</v>
+        <v>1725</v>
       </c>
       <c r="M243" s="6">
-        <v>52332</v>
+        <v>1826</v>
       </c>
       <c r="N243" s="6">
-        <v>62146</v>
+        <v>1792</v>
       </c>
       <c r="O243" s="6">
-        <v>63975</v>
+        <v>1744</v>
       </c>
       <c r="P243" s="6">
-        <v>64742</v>
+        <v>1494</v>
       </c>
       <c r="Q243" s="6">
-        <v>61823</v>
+        <v>1820</v>
       </c>
       <c r="R243" s="6">
-        <v>66958</v>
+        <v>2205</v>
       </c>
       <c r="S243" s="6">
-        <v>68339</v>
-      </c>
-      <c r="T243" s="3"/>
+        <v>1959</v>
+      </c>
+      <c r="T243" s="6">
+        <v>1801</v>
+      </c>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="244" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>27</v>
@@ -16642,64 +16709,62 @@
         <v>28</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J244" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K244" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L244" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M244" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N244" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R244" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S244" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T244" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U244" s="5">
-        <v>0.59</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="G244" s="6">
+        <v>48641</v>
+      </c>
+      <c r="H244" s="6">
+        <v>48212</v>
+      </c>
+      <c r="I244" s="6">
+        <v>46053</v>
+      </c>
+      <c r="J244" s="6">
+        <v>43064</v>
+      </c>
+      <c r="K244" s="6">
+        <v>43315</v>
+      </c>
+      <c r="L244" s="6">
+        <v>47177</v>
+      </c>
+      <c r="M244" s="6">
+        <v>52332</v>
+      </c>
+      <c r="N244" s="6">
+        <v>62146</v>
+      </c>
+      <c r="O244" s="6">
+        <v>63975</v>
+      </c>
+      <c r="P244" s="6">
+        <v>64742</v>
+      </c>
+      <c r="Q244" s="6">
+        <v>62093</v>
+      </c>
+      <c r="R244" s="6">
+        <v>66958</v>
+      </c>
+      <c r="S244" s="6">
+        <v>68530</v>
+      </c>
+      <c r="T244" s="6">
+        <v>67711</v>
+      </c>
+      <c r="U244" s="3"/>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
-        <v>30</v>
+        <v>329</v>
       </c>
     </row>
     <row r="245" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>333</v>
@@ -16711,65 +16776,67 @@
         <v>28</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G245" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H245" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I245" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J245" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K245" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L245" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M245" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N245" s="3"/>
-      <c r="O245" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P245" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q245" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R245" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S245" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T245" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U245" s="4">
-        <v>881284.3</v>
+        <v>283</v>
+      </c>
+      <c r="G245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J245" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K245" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L245" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M245" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N245" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R245" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S245" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T245" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U245" s="5">
+        <v>0.59</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>27</v>
@@ -16778,53 +16845,65 @@
         <v>28</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G246" s="3"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
-      <c r="J246" s="3"/>
-      <c r="K246" s="3"/>
-      <c r="L246" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M246" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N246" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O246" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P246" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q246" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R246" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S246" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T246" s="3"/>
-      <c r="U246" s="3"/>
+        <v>335</v>
+      </c>
+      <c r="G246" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H246" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I246" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J246" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K246" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L246" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M246" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N246" s="3"/>
+      <c r="O246" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P246" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q246" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R246" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S246" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T246" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U246" s="4">
+        <v>881284.3</v>
+      </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>336</v>
+        <v>171</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>27</v>
@@ -16833,51 +16912,53 @@
         <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="3"/>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="3"/>
-      <c r="N247" s="3"/>
-      <c r="O247" s="6">
-        <v>1</v>
-      </c>
-      <c r="P247" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q247" s="6">
-        <v>63</v>
-      </c>
-      <c r="R247" s="6">
-        <v>66</v>
-      </c>
-      <c r="S247" s="6">
-        <v>70</v>
-      </c>
-      <c r="T247" s="6">
-        <v>75</v>
-      </c>
-      <c r="U247" s="6">
-        <v>80</v>
-      </c>
+      <c r="L247" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M247" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N247" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O247" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P247" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q247" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R247" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S247" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T247" s="3"/>
+      <c r="U247" s="3"/>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="248" spans="1:23" ht="108" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="248" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>27</v>
@@ -16886,7 +16967,7 @@
         <v>28</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="3"/>
@@ -16896,35 +16977,41 @@
       <c r="L248" s="3"/>
       <c r="M248" s="3"/>
       <c r="N248" s="3"/>
-      <c r="O248" s="3"/>
-      <c r="P248" s="3"/>
-      <c r="Q248" s="3"/>
-      <c r="R248" s="3"/>
+      <c r="O248" s="6">
+        <v>1</v>
+      </c>
+      <c r="P248" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>63</v>
+      </c>
+      <c r="R248" s="6">
+        <v>66</v>
+      </c>
       <c r="S248" s="6">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="T248" s="6">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="U248" s="6">
-        <v>6</v>
-      </c>
-      <c r="V248" s="6">
-        <v>4</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="249" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="249" spans="1:23" ht="108" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>27</v>
@@ -16933,7 +17020,7 @@
         <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
@@ -16946,107 +17033,85 @@
       <c r="O249" s="3"/>
       <c r="P249" s="3"/>
       <c r="Q249" s="3"/>
-      <c r="R249" s="6">
+      <c r="R249" s="3"/>
+      <c r="S249" s="6">
+        <v>16</v>
+      </c>
+      <c r="T249" s="6">
+        <v>7</v>
+      </c>
+      <c r="U249" s="6">
+        <v>6</v>
+      </c>
+      <c r="V249" s="6">
+        <v>4</v>
+      </c>
+      <c r="W249" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G250" s="3"/>
+      <c r="H250" s="3"/>
+      <c r="I250" s="3"/>
+      <c r="J250" s="3"/>
+      <c r="K250" s="3"/>
+      <c r="L250" s="3"/>
+      <c r="M250" s="3"/>
+      <c r="N250" s="3"/>
+      <c r="O250" s="3"/>
+      <c r="P250" s="3"/>
+      <c r="Q250" s="3"/>
+      <c r="R250" s="6">
         <v>133</v>
       </c>
-      <c r="S249" s="6">
+      <c r="S250" s="6">
         <v>80</v>
       </c>
-      <c r="T249" s="6">
+      <c r="T250" s="6">
         <v>97</v>
       </c>
-      <c r="U249" s="6">
+      <c r="U250" s="6">
         <v>44</v>
-      </c>
-      <c r="V249" s="3"/>
-      <c r="W249" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="250" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G250" s="6">
-        <v>40</v>
-      </c>
-      <c r="H250" s="6">
-        <v>60</v>
-      </c>
-      <c r="I250" s="6">
-        <v>40</v>
-      </c>
-      <c r="J250" s="6">
-        <v>40</v>
-      </c>
-      <c r="K250" s="6">
-        <v>40</v>
-      </c>
-      <c r="L250" s="6">
-        <v>40</v>
-      </c>
-      <c r="M250" s="6">
-        <v>60</v>
-      </c>
-      <c r="N250" s="6">
-        <v>40</v>
-      </c>
-      <c r="O250" s="6">
-        <v>40</v>
-      </c>
-      <c r="P250" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q250" s="6">
-        <v>60</v>
-      </c>
-      <c r="R250" s="6">
-        <v>67</v>
-      </c>
-      <c r="S250" s="6">
-        <v>50</v>
-      </c>
-      <c r="T250" s="6">
-        <v>67</v>
-      </c>
-      <c r="U250" s="6">
-        <v>67</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>36</v>
@@ -17058,13 +17123,13 @@
         <v>60</v>
       </c>
       <c r="I251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K251" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L251" s="6">
         <v>40</v>
@@ -17076,43 +17141,43 @@
         <v>40</v>
       </c>
       <c r="O251" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P251" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q251" s="6">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R251" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S251" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T251" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U251" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>353</v>
@@ -17121,10 +17186,10 @@
         <v>36</v>
       </c>
       <c r="G252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H252" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I252" s="6">
         <v>20</v>
@@ -17136,52 +17201,52 @@
         <v>20</v>
       </c>
       <c r="L252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M252" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N252" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O252" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P252" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q252" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R252" s="6">
         <v>17</v>
       </c>
       <c r="S252" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T252" s="6">
         <v>17</v>
       </c>
       <c r="U252" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>354</v>
@@ -17190,133 +17255,133 @@
         <v>36</v>
       </c>
       <c r="G253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H253" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K253" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M253" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N253" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O253" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P253" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q253" s="6">
         <v>40</v>
       </c>
       <c r="R253" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S253" s="6">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="T253" s="6">
         <v>17</v>
       </c>
       <c r="U253" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E254" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F254" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G254" s="4">
-        <v>100</v>
-      </c>
-      <c r="H254" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I254" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J254" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K254" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L254" s="4">
-        <v>106</v>
-      </c>
-      <c r="M254" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N254" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O254" s="4">
-        <v>130</v>
-      </c>
-      <c r="P254" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q254" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R254" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S254" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T254" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U254" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G254" s="6">
+        <v>60</v>
+      </c>
+      <c r="H254" s="6">
+        <v>40</v>
+      </c>
+      <c r="I254" s="6">
+        <v>60</v>
+      </c>
+      <c r="J254" s="6">
+        <v>60</v>
+      </c>
+      <c r="K254" s="6">
+        <v>60</v>
+      </c>
+      <c r="L254" s="6">
+        <v>60</v>
+      </c>
+      <c r="M254" s="6">
+        <v>40</v>
+      </c>
+      <c r="N254" s="6">
+        <v>60</v>
+      </c>
+      <c r="O254" s="6">
+        <v>75</v>
+      </c>
+      <c r="P254" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q254" s="6">
+        <v>40</v>
+      </c>
+      <c r="R254" s="6">
+        <v>33</v>
+      </c>
+      <c r="S254" s="6">
+        <v>50</v>
+      </c>
+      <c r="T254" s="6">
+        <v>17</v>
+      </c>
+      <c r="U254" s="6">
+        <v>25</v>
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17325,67 +17390,67 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G255" s="4">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="H255" s="4">
-        <v>57.7</v>
+        <v>100.8</v>
       </c>
       <c r="I255" s="4">
-        <v>58.8</v>
+        <v>99.9</v>
       </c>
       <c r="J255" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K255" s="4">
-        <v>68.7</v>
+        <v>104.9</v>
       </c>
       <c r="L255" s="4">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="M255" s="4">
-        <v>72.900000000000006</v>
+        <v>119.9</v>
       </c>
       <c r="N255" s="4">
-        <v>78.099999999999994</v>
+        <v>119.4</v>
       </c>
       <c r="O255" s="4">
-        <v>91.8</v>
+        <v>130</v>
       </c>
       <c r="P255" s="4">
-        <v>93.9</v>
+        <v>189.5</v>
       </c>
       <c r="Q255" s="4">
-        <v>88.5</v>
+        <v>186.6</v>
       </c>
       <c r="R255" s="4">
-        <v>96.7</v>
+        <v>190.1</v>
       </c>
       <c r="S255" s="4">
-        <v>119</v>
+        <v>200.8</v>
       </c>
       <c r="T255" s="4">
-        <v>136.4</v>
+        <v>205.6</v>
       </c>
       <c r="U255" s="4">
-        <v>124.2</v>
+        <v>208.5</v>
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17394,67 +17459,67 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G256" s="4">
-        <v>90.8</v>
+        <v>59.5</v>
       </c>
       <c r="H256" s="4">
-        <v>88.8</v>
+        <v>57.7</v>
       </c>
       <c r="I256" s="4">
-        <v>86.5</v>
+        <v>58.8</v>
       </c>
       <c r="J256" s="4">
-        <v>87</v>
+        <v>64.3</v>
       </c>
       <c r="K256" s="4">
-        <v>85</v>
+        <v>68.7</v>
       </c>
       <c r="L256" s="4">
-        <v>87.4</v>
+        <v>69.5</v>
       </c>
       <c r="M256" s="4">
-        <v>88.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N256" s="4">
-        <v>84.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O256" s="4">
-        <v>77.3</v>
+        <v>91.8</v>
       </c>
       <c r="P256" s="4">
-        <v>79.7</v>
+        <v>93.9</v>
       </c>
       <c r="Q256" s="4">
-        <v>81.900000000000006</v>
+        <v>88.5</v>
       </c>
       <c r="R256" s="4">
-        <v>74.8</v>
+        <v>96.7</v>
       </c>
       <c r="S256" s="4">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="T256" s="4">
-        <v>77.2</v>
+        <v>136.4</v>
       </c>
       <c r="U256" s="4">
-        <v>76.3</v>
+        <v>124.2</v>
       </c>
       <c r="V256" s="3"/>
       <c r="W256" s="2" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17463,67 +17528,67 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G257" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H257" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I257" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K257" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L257" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M257" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P257" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q257" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R257" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S257" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T257" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U257" s="7">
-        <v>0.192</v>
+        <v>365</v>
+      </c>
+      <c r="G257" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H257" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I257" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J257" s="4">
+        <v>87</v>
+      </c>
+      <c r="K257" s="4">
+        <v>85</v>
+      </c>
+      <c r="L257" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M257" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N257" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O257" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P257" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q257" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R257" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S257" s="4">
+        <v>77</v>
+      </c>
+      <c r="T257" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U257" s="4">
+        <v>76.3</v>
       </c>
       <c r="V257" s="3"/>
       <c r="W257" s="2" t="s">
-        <v>366</v>
+        <v>101</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>27</v>
@@ -17534,65 +17599,65 @@
       <c r="F258" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G258" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H258" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I258" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J258" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K258" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L258" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M258" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R258" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S258" s="4">
-        <v>31</v>
-      </c>
-      <c r="T258" s="4">
-        <v>31</v>
-      </c>
-      <c r="U258" s="4">
-        <v>31</v>
+      <c r="G258" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H258" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I258" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K258" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L258" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M258" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P258" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q258" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R258" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S258" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T258" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U258" s="7">
+        <v>0.192</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>30</v>
+        <v>367</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>27</v>
@@ -17601,190 +17666,190 @@
         <v>28</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G259" s="6">
-        <v>28</v>
-      </c>
-      <c r="H259" s="6">
-        <v>27</v>
-      </c>
-      <c r="I259" s="6">
-        <v>26</v>
-      </c>
-      <c r="J259" s="6">
-        <v>25</v>
-      </c>
-      <c r="K259" s="6">
-        <v>24</v>
-      </c>
-      <c r="L259" s="6">
-        <v>23</v>
-      </c>
-      <c r="M259" s="6">
-        <v>22</v>
-      </c>
-      <c r="N259" s="6">
-        <v>22</v>
-      </c>
-      <c r="O259" s="6">
-        <v>22</v>
-      </c>
-      <c r="P259" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q259" s="6">
-        <v>19</v>
-      </c>
-      <c r="R259" s="6">
-        <v>17</v>
-      </c>
-      <c r="S259" s="6">
-        <v>16</v>
-      </c>
-      <c r="T259" s="6">
-        <v>16</v>
-      </c>
-      <c r="U259" s="6">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="G259" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H259" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I259" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J259" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K259" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L259" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M259" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R259" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S259" s="4">
+        <v>31</v>
+      </c>
+      <c r="T259" s="4">
+        <v>31</v>
+      </c>
+      <c r="U259" s="4">
+        <v>31</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="260" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>370</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G260" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H260" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I260" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J260" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K260" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L260" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M260" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N260" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O260" s="4">
-        <v>74</v>
-      </c>
-      <c r="P260" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q260" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R260" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S260" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T260" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U260" s="4">
-        <v>76.2</v>
+        <v>100</v>
+      </c>
+      <c r="G260" s="6">
+        <v>28</v>
+      </c>
+      <c r="H260" s="6">
+        <v>27</v>
+      </c>
+      <c r="I260" s="6">
+        <v>26</v>
+      </c>
+      <c r="J260" s="6">
+        <v>25</v>
+      </c>
+      <c r="K260" s="6">
+        <v>24</v>
+      </c>
+      <c r="L260" s="6">
+        <v>23</v>
+      </c>
+      <c r="M260" s="6">
+        <v>22</v>
+      </c>
+      <c r="N260" s="6">
+        <v>22</v>
+      </c>
+      <c r="O260" s="6">
+        <v>22</v>
+      </c>
+      <c r="P260" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>19</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>16</v>
+      </c>
+      <c r="T260" s="6">
+        <v>16</v>
+      </c>
+      <c r="U260" s="6">
+        <v>15</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G261" s="4">
-        <v>88</v>
+        <v>64.7</v>
       </c>
       <c r="H261" s="4">
-        <v>88.4</v>
+        <v>65.7</v>
       </c>
       <c r="I261" s="4">
-        <v>91.7</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J261" s="4">
-        <v>93.3</v>
+        <v>70.3</v>
       </c>
       <c r="K261" s="4">
-        <v>93.9</v>
+        <v>71.5</v>
       </c>
       <c r="L261" s="4">
-        <v>94.6</v>
+        <v>72.7</v>
       </c>
       <c r="M261" s="4">
-        <v>94.8</v>
+        <v>73.5</v>
       </c>
       <c r="N261" s="4">
-        <v>94.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O261" s="4">
-        <v>94.6</v>
+        <v>74</v>
       </c>
       <c r="P261" s="4">
-        <v>94.8</v>
+        <v>74.5</v>
       </c>
       <c r="Q261" s="4">
-        <v>94.7</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R261" s="4">
-        <v>94.6</v>
+        <v>75.2</v>
       </c>
       <c r="S261" s="4">
-        <v>95</v>
+        <v>75.7</v>
       </c>
       <c r="T261" s="4">
-        <v>94.8</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U261" s="4">
-        <v>94.6</v>
+        <v>76.2</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
@@ -17793,67 +17858,67 @@
     </row>
     <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G262" s="4">
-        <v>28.5</v>
+        <v>88</v>
       </c>
       <c r="H262" s="4">
-        <v>30.6</v>
+        <v>88.4</v>
       </c>
       <c r="I262" s="4">
-        <v>33.1</v>
+        <v>91.7</v>
       </c>
       <c r="J262" s="4">
-        <v>35.299999999999997</v>
+        <v>93.3</v>
       </c>
       <c r="K262" s="4">
-        <v>37.4</v>
+        <v>93.9</v>
       </c>
       <c r="L262" s="4">
-        <v>39.6</v>
+        <v>94.6</v>
       </c>
       <c r="M262" s="4">
-        <v>41.2</v>
+        <v>94.8</v>
       </c>
       <c r="N262" s="4">
-        <v>42</v>
+        <v>94.5</v>
       </c>
       <c r="O262" s="4">
-        <v>42.9</v>
+        <v>94.6</v>
       </c>
       <c r="P262" s="4">
-        <v>44</v>
+        <v>94.8</v>
       </c>
       <c r="Q262" s="4">
-        <v>45.4</v>
+        <v>94.7</v>
       </c>
       <c r="R262" s="4">
-        <v>46.5</v>
+        <v>94.6</v>
       </c>
       <c r="S262" s="4">
-        <v>47.2</v>
+        <v>95</v>
       </c>
       <c r="T262" s="4">
-        <v>48.2</v>
+        <v>94.8</v>
       </c>
       <c r="U262" s="4">
-        <v>49.3</v>
+        <v>94.6</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
@@ -17862,82 +17927,82 @@
     </row>
     <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>371</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G263" s="4">
-        <v>65.7</v>
+        <v>28.5</v>
       </c>
       <c r="H263" s="4">
-        <v>64.8</v>
+        <v>30.6</v>
       </c>
       <c r="I263" s="4">
-        <v>67.400000000000006</v>
+        <v>33.1</v>
       </c>
       <c r="J263" s="4">
-        <v>69.8</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K263" s="4">
-        <v>70.5</v>
+        <v>37.4</v>
       </c>
       <c r="L263" s="4">
-        <v>70.900000000000006</v>
+        <v>39.6</v>
       </c>
       <c r="M263" s="4">
-        <v>71.400000000000006</v>
+        <v>41.2</v>
       </c>
       <c r="N263" s="4">
-        <v>72.5</v>
+        <v>42</v>
       </c>
       <c r="O263" s="4">
-        <v>73.2</v>
+        <v>42.9</v>
       </c>
       <c r="P263" s="4">
-        <v>73.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="Q263" s="4">
-        <v>73.3</v>
+        <v>45.4</v>
       </c>
       <c r="R263" s="4">
-        <v>72.8</v>
+        <v>46.5</v>
       </c>
       <c r="S263" s="4">
-        <v>76.3</v>
+        <v>47.2</v>
       </c>
       <c r="T263" s="4">
-        <v>78.099999999999994</v>
+        <v>48.2</v>
       </c>
       <c r="U263" s="4">
-        <v>78.599999999999994</v>
+        <v>49.3</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -17946,52 +18011,52 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G264" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H264" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I264" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J264" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K264" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L264" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M264" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N264" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O264" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P264" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R264" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S264" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T264" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U264" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G264" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H264" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J264" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K264" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L264" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M264" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N264" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O264" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P264" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R264" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T264" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U264" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
@@ -18000,13 +18065,13 @@
     </row>
     <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18015,52 +18080,52 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G265" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H265" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I265" s="4">
-        <v>6</v>
-      </c>
-      <c r="J265" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K265" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L265" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M265" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N265" s="4">
-        <v>3</v>
-      </c>
-      <c r="O265" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P265" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q265" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R265" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S265" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T265" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="U265" s="4">
-        <v>4.5</v>
+        <v>375</v>
+      </c>
+      <c r="G265" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H265" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I265" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J265" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K265" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L265" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M265" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N265" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O265" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P265" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q265" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R265" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S265" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T265" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U265" s="6">
+        <v>104040</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
@@ -18069,13 +18134,13 @@
     </row>
     <row r="266" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18086,65 +18151,65 @@
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G266" s="6">
-        <v>70</v>
-      </c>
-      <c r="H266" s="6">
-        <v>75</v>
-      </c>
-      <c r="I266" s="6">
-        <v>66</v>
-      </c>
-      <c r="J266" s="6">
-        <v>64</v>
-      </c>
-      <c r="K266" s="6">
-        <v>70</v>
-      </c>
-      <c r="L266" s="6">
-        <v>66</v>
-      </c>
-      <c r="M266" s="6">
-        <v>80</v>
-      </c>
-      <c r="N266" s="6">
-        <v>89</v>
-      </c>
-      <c r="O266" s="6">
-        <v>86</v>
-      </c>
-      <c r="P266" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q266" s="6">
-        <v>85</v>
-      </c>
-      <c r="R266" s="6">
-        <v>82</v>
-      </c>
-      <c r="S266" s="6">
-        <v>83</v>
-      </c>
-      <c r="T266" s="6">
-        <v>88</v>
-      </c>
-      <c r="U266" s="6">
-        <v>88</v>
+      <c r="G266" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H266" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I266" s="4">
+        <v>6</v>
+      </c>
+      <c r="J266" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K266" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L266" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M266" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N266" s="4">
+        <v>3</v>
+      </c>
+      <c r="O266" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P266" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q266" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R266" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S266" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T266" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U266" s="4">
+        <v>4.5</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>379</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18156,50 +18221,66 @@
         <v>36</v>
       </c>
       <c r="G267" s="6">
-        <v>55</v>
-      </c>
-      <c r="H267" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H267" s="6">
+        <v>75</v>
+      </c>
       <c r="I267" s="6">
-        <v>58</v>
-      </c>
-      <c r="J267" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="J267" s="6">
+        <v>64</v>
+      </c>
       <c r="K267" s="6">
-        <v>60</v>
-      </c>
-      <c r="L267" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="L267" s="6">
+        <v>66</v>
+      </c>
       <c r="M267" s="6">
-        <v>64</v>
-      </c>
-      <c r="N267" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="N267" s="6">
+        <v>89</v>
+      </c>
       <c r="O267" s="6">
-        <v>65</v>
-      </c>
-      <c r="P267" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="P267" s="6">
+        <v>89</v>
+      </c>
       <c r="Q267" s="6">
-        <v>74</v>
-      </c>
-      <c r="R267" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="R267" s="6">
+        <v>82</v>
+      </c>
       <c r="S267" s="6">
-        <v>63</v>
-      </c>
-      <c r="T267" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="T267" s="6">
+        <v>88</v>
+      </c>
       <c r="U267" s="6">
-        <v>71</v>
-      </c>
-      <c r="V267" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="V267" s="6">
+        <v>86</v>
+      </c>
       <c r="W267" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B268" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18208,65 +18289,53 @@
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="G268" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H268" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I268" s="5">
-        <v>1</v>
-      </c>
-      <c r="J268" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K268" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L268" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M268" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N268" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O268" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P268" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q268" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R268" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S268" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T268" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U268" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G268" s="6">
+        <v>55</v>
+      </c>
+      <c r="H268" s="3"/>
+      <c r="I268" s="6">
+        <v>58</v>
+      </c>
+      <c r="J268" s="3"/>
+      <c r="K268" s="6">
+        <v>60</v>
+      </c>
+      <c r="L268" s="3"/>
+      <c r="M268" s="6">
+        <v>64</v>
+      </c>
+      <c r="N268" s="3"/>
+      <c r="O268" s="6">
+        <v>65</v>
+      </c>
+      <c r="P268" s="3"/>
+      <c r="Q268" s="6">
+        <v>74</v>
+      </c>
+      <c r="R268" s="3"/>
+      <c r="S268" s="6">
+        <v>63</v>
+      </c>
+      <c r="T268" s="3"/>
+      <c r="U268" s="6">
+        <v>71</v>
+      </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>198</v>
+        <v>380</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>27</v>
@@ -18275,136 +18344,142 @@
         <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>282</v>
+        <v>384</v>
       </c>
       <c r="G269" s="5">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="H269" s="5">
-        <v>1.79</v>
+        <v>0.96</v>
       </c>
       <c r="I269" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J269" s="5">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="K269" s="5">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="L269" s="5">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="M269" s="5">
-        <v>1.99</v>
+        <v>0.91</v>
       </c>
       <c r="N269" s="5">
-        <v>1.88</v>
+        <v>0.81</v>
       </c>
       <c r="O269" s="5">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="P269" s="5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q269" s="5">
-        <v>2.21</v>
+        <v>0.85</v>
       </c>
       <c r="R269" s="5">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="S269" s="5">
-        <v>2.21</v>
+        <v>0.72</v>
       </c>
       <c r="T269" s="5">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="U269" s="5">
-        <v>4.07</v>
+        <v>0.69</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
-        <v>386</v>
+        <v>198</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G270" s="6">
-        <v>10</v>
-      </c>
-      <c r="H270" s="6">
-        <v>9</v>
-      </c>
-      <c r="I270" s="6">
-        <v>11</v>
-      </c>
-      <c r="J270" s="6">
-        <v>11</v>
-      </c>
-      <c r="K270" s="6">
-        <v>15</v>
-      </c>
-      <c r="L270" s="6">
-        <v>16</v>
-      </c>
-      <c r="M270" s="6">
-        <v>19</v>
-      </c>
-      <c r="N270" s="6">
-        <v>21</v>
-      </c>
-      <c r="O270" s="6">
-        <v>25</v>
-      </c>
-      <c r="P270" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q270" s="6">
-        <v>34</v>
-      </c>
-      <c r="R270" s="6">
-        <v>40</v>
-      </c>
-      <c r="S270" s="3"/>
-      <c r="T270" s="3"/>
-      <c r="U270" s="3"/>
+        <v>283</v>
+      </c>
+      <c r="G270" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H270" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I270" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J270" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K270" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M270" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N270" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O270" s="5">
+        <v>2</v>
+      </c>
+      <c r="P270" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R270" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S270" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T270" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U270" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>30</v>
+        <v>387</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>36</v>
@@ -18419,13 +18494,13 @@
         <v>11</v>
       </c>
       <c r="J271" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K271" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L271" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M271" s="6">
         <v>19</v>
@@ -18434,16 +18509,16 @@
         <v>21</v>
       </c>
       <c r="O271" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P271" s="6">
         <v>31</v>
       </c>
       <c r="Q271" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R271" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S271" s="3"/>
       <c r="T271" s="3"/>
@@ -18455,19 +18530,19 @@
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>36</v>
@@ -18479,16 +18554,16 @@
         <v>9</v>
       </c>
       <c r="I272" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J272" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K272" s="6">
+        <v>14</v>
+      </c>
+      <c r="L272" s="6">
         <v>15</v>
-      </c>
-      <c r="L272" s="6">
-        <v>16</v>
       </c>
       <c r="M272" s="6">
         <v>19</v>
@@ -18497,16 +18572,16 @@
         <v>21</v>
       </c>
       <c r="O272" s="6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P272" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q272" s="6">
         <v>32</v>
       </c>
-      <c r="Q272" s="6">
-        <v>35</v>
-      </c>
       <c r="R272" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S272" s="3"/>
       <c r="T272" s="3"/>
@@ -18518,58 +18593,58 @@
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G273" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H273" s="6">
+        <v>9</v>
+      </c>
+      <c r="I273" s="6">
+        <v>10</v>
+      </c>
+      <c r="J273" s="6">
         <v>11</v>
       </c>
-      <c r="I273" s="6">
-        <v>13</v>
-      </c>
-      <c r="J273" s="6">
+      <c r="K273" s="6">
         <v>15</v>
       </c>
-      <c r="K273" s="6">
-        <v>18</v>
-      </c>
       <c r="L273" s="6">
+        <v>16</v>
+      </c>
+      <c r="M273" s="6">
         <v>19</v>
       </c>
-      <c r="M273" s="6">
-        <v>23</v>
-      </c>
       <c r="N273" s="6">
+        <v>21</v>
+      </c>
+      <c r="O273" s="6">
         <v>26</v>
       </c>
-      <c r="O273" s="6">
-        <v>30</v>
-      </c>
       <c r="P273" s="6">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q273" s="6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R273" s="6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S273" s="3"/>
       <c r="T273" s="3"/>
@@ -18581,58 +18656,58 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G274" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H274" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I274" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J274" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K274" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L274" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M274" s="6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N274" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O274" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P274" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q274" s="6">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R274" s="6">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S274" s="3"/>
       <c r="T274" s="3"/>
@@ -18644,58 +18719,58 @@
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>389</v>
+        <v>39</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H275" s="6">
+        <v>5</v>
+      </c>
+      <c r="I275" s="6">
         <v>6</v>
       </c>
-      <c r="I275" s="6">
-        <v>8</v>
-      </c>
       <c r="J275" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K275" s="6">
         <v>9</v>
       </c>
       <c r="L275" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M275" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N275" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O275" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P275" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q275" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R275" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S275" s="3"/>
       <c r="T275" s="3"/>
@@ -18707,13 +18782,13 @@
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>81</v>
@@ -18725,40 +18800,40 @@
         <v>36</v>
       </c>
       <c r="G276" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H276" s="6">
+        <v>6</v>
+      </c>
+      <c r="I276" s="6">
+        <v>8</v>
+      </c>
+      <c r="J276" s="6">
+        <v>9</v>
+      </c>
+      <c r="K276" s="6">
+        <v>9</v>
+      </c>
+      <c r="L276" s="6">
+        <v>8</v>
+      </c>
+      <c r="M276" s="6">
+        <v>9</v>
+      </c>
+      <c r="N276" s="6">
+        <v>11</v>
+      </c>
+      <c r="O276" s="6">
         <v>16</v>
       </c>
-      <c r="I276" s="6">
-        <v>19</v>
-      </c>
-      <c r="J276" s="6">
-        <v>20</v>
-      </c>
-      <c r="K276" s="6">
-        <v>28</v>
-      </c>
-      <c r="L276" s="6">
-        <v>28</v>
-      </c>
-      <c r="M276" s="6">
-        <v>32</v>
-      </c>
-      <c r="N276" s="6">
-        <v>35</v>
-      </c>
-      <c r="O276" s="6">
-        <v>39</v>
-      </c>
       <c r="P276" s="6">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="Q276" s="6">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="R276" s="6">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="S276" s="3"/>
       <c r="T276" s="3"/>
@@ -18770,13 +18845,13 @@
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>81</v>
@@ -18788,40 +18863,40 @@
         <v>36</v>
       </c>
       <c r="G277" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H277" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I277" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J277" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K277" s="6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L277" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M277" s="6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N277" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O277" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P277" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q277" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="R277" s="6">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S277" s="3"/>
       <c r="T277" s="3"/>
@@ -18833,13 +18908,13 @@
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>81</v>
@@ -18851,40 +18926,40 @@
         <v>36</v>
       </c>
       <c r="G278" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H278" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I278" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J278" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K278" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L278" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M278" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N278" s="6">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O278" s="6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="P278" s="6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q278" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R278" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
@@ -18896,13 +18971,13 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>81</v>
@@ -18914,40 +18989,40 @@
         <v>36</v>
       </c>
       <c r="G279" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H279" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I279" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J279" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K279" s="6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L279" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M279" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N279" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O279" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P279" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q279" s="6">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R279" s="6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -18959,13 +19034,13 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>81</v>
@@ -18977,40 +19052,40 @@
         <v>36</v>
       </c>
       <c r="G280" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H280" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I280" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J280" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K280" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L280" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M280" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N280" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O280" s="6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P280" s="6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Q280" s="6">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R280" s="6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -19022,58 +19097,58 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>132</v>
+        <v>395</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H281" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I281" s="6">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J281" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K281" s="6">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L281" s="6">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="M281" s="6">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N281" s="6">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="O281" s="6">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="P281" s="6">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Q281" s="6">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="R281" s="6">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -19085,58 +19160,58 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H282" s="6">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I282" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J282" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K282" s="6">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L282" s="6">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M282" s="6">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="N282" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="O282" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="P282" s="6">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="Q282" s="6">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="R282" s="6">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19148,58 +19223,58 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>141</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H283" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I283" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J283" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K283" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L283" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M283" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N283" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O283" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P283" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Q283" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R283" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19211,58 +19286,58 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H284" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I284" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J284" s="6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K284" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L284" s="6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M284" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N284" s="6">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O284" s="6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="P284" s="6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q284" s="6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R284" s="6">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19274,58 +19349,58 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
+        <v>14</v>
+      </c>
+      <c r="H285" s="6">
+        <v>13</v>
+      </c>
+      <c r="I285" s="6">
         <v>15</v>
       </c>
-      <c r="H285" s="6">
-        <v>14</v>
-      </c>
-      <c r="I285" s="6">
-        <v>16</v>
-      </c>
       <c r="J285" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K285" s="6">
+        <v>21</v>
+      </c>
+      <c r="L285" s="6">
         <v>23</v>
       </c>
-      <c r="L285" s="6">
+      <c r="M285" s="6">
         <v>25</v>
       </c>
-      <c r="M285" s="6">
-        <v>27</v>
-      </c>
       <c r="N285" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O285" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P285" s="6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q285" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R285" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19337,58 +19412,58 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H286" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I286" s="6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J286" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K286" s="6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L286" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="M286" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N286" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O286" s="6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="P286" s="6">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="Q286" s="6">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="R286" s="6">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19400,58 +19475,58 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H287" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I287" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J287" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K287" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L287" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M287" s="6">
         <v>7</v>
       </c>
       <c r="N287" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O287" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P287" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q287" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R287" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
@@ -19463,82 +19538,76 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G288" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H288" s="4">
-        <v>6</v>
-      </c>
-      <c r="I288" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J288" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K288" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L288" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M288" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N288" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O288" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P288" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R288" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S288" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T288" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U288" s="4">
-        <v>4.8</v>
-      </c>
+      <c r="G288" s="6">
+        <v>4</v>
+      </c>
+      <c r="H288" s="6">
+        <v>3</v>
+      </c>
+      <c r="I288" s="6">
+        <v>5</v>
+      </c>
+      <c r="J288" s="6">
+        <v>4</v>
+      </c>
+      <c r="K288" s="6">
+        <v>5</v>
+      </c>
+      <c r="L288" s="6">
+        <v>5</v>
+      </c>
+      <c r="M288" s="6">
+        <v>7</v>
+      </c>
+      <c r="N288" s="6">
+        <v>8</v>
+      </c>
+      <c r="O288" s="6">
+        <v>9</v>
+      </c>
+      <c r="P288" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q288" s="6">
+        <v>14</v>
+      </c>
+      <c r="R288" s="6">
+        <v>17</v>
+      </c>
+      <c r="S288" s="3"/>
+      <c r="T288" s="3"/>
+      <c r="U288" s="3"/>
       <c r="V288" s="3"/>
       <c r="W288" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -19547,67 +19616,67 @@
         <v>28</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G289" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H289" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I289" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J289" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K289" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L289" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M289" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N289" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O289" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P289" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q289" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R289" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S289" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T289" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U289" s="5">
-        <v>1840.15</v>
+        <v>36</v>
+      </c>
+      <c r="G289" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H289" s="4">
+        <v>6</v>
+      </c>
+      <c r="I289" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K289" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L289" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M289" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O289" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R289" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T289" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U289" s="4">
+        <v>4.8</v>
       </c>
       <c r="V289" s="3"/>
       <c r="W289" s="2" t="s">
-        <v>401</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>27</v>
@@ -19616,67 +19685,67 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G290" s="5">
-        <v>96.04</v>
+        <v>377.75</v>
       </c>
       <c r="H290" s="5">
-        <v>90.68</v>
+        <v>417.47</v>
       </c>
       <c r="I290" s="5">
-        <v>111.55</v>
+        <v>421.06</v>
       </c>
       <c r="J290" s="5">
-        <v>127.11</v>
+        <v>487.12</v>
       </c>
       <c r="K290" s="5">
-        <v>82.28</v>
+        <v>451.84</v>
       </c>
       <c r="L290" s="5">
-        <v>100.19</v>
+        <v>440.89</v>
       </c>
       <c r="M290" s="5">
-        <v>148.99</v>
+        <v>662.95</v>
       </c>
       <c r="N290" s="5">
-        <v>222.11</v>
+        <v>679.46</v>
       </c>
       <c r="O290" s="5">
-        <v>244.93</v>
+        <v>766.04</v>
       </c>
       <c r="P290" s="5">
-        <v>223.31</v>
+        <v>776.56</v>
       </c>
       <c r="Q290" s="5">
-        <v>225.08</v>
+        <v>829.27</v>
       </c>
       <c r="R290" s="5">
-        <v>296.20999999999998</v>
+        <v>983.51</v>
       </c>
       <c r="S290" s="5">
-        <v>2661.32</v>
+        <v>3494.39</v>
       </c>
       <c r="T290" s="5">
-        <v>1701.94</v>
+        <v>2580.38</v>
       </c>
       <c r="U290" s="5">
-        <v>705.25</v>
+        <v>1840.15</v>
       </c>
       <c r="V290" s="3"/>
       <c r="W290" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -19685,67 +19754,67 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>36</v>
+        <v>401</v>
       </c>
       <c r="G291" s="5">
-        <v>0.08</v>
+        <v>96.04</v>
       </c>
       <c r="H291" s="5">
-        <v>0.08</v>
+        <v>90.68</v>
       </c>
       <c r="I291" s="5">
-        <v>0.09</v>
+        <v>111.55</v>
       </c>
       <c r="J291" s="5">
-        <v>0.1</v>
+        <v>127.11</v>
       </c>
       <c r="K291" s="5">
-        <v>0.09</v>
+        <v>82.28</v>
       </c>
       <c r="L291" s="5">
-        <v>0.1</v>
+        <v>100.19</v>
       </c>
       <c r="M291" s="5">
-        <v>0.15</v>
+        <v>148.99</v>
       </c>
       <c r="N291" s="5">
-        <v>0.13</v>
+        <v>222.11</v>
       </c>
       <c r="O291" s="5">
-        <v>0.14000000000000001</v>
+        <v>244.93</v>
       </c>
       <c r="P291" s="5">
-        <v>0.14000000000000001</v>
+        <v>223.31</v>
       </c>
       <c r="Q291" s="5">
-        <v>0.14000000000000001</v>
+        <v>225.08</v>
       </c>
       <c r="R291" s="5">
-        <v>0.15</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S291" s="5">
-        <v>0.53</v>
+        <v>2661.32</v>
       </c>
       <c r="T291" s="5">
-        <v>0.33</v>
+        <v>1701.94</v>
       </c>
       <c r="U291" s="5">
-        <v>0.21</v>
+        <v>705.25</v>
       </c>
       <c r="V291" s="3"/>
       <c r="W291" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -19754,61 +19823,67 @@
         <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="G292" s="3"/>
-      <c r="H292" s="3"/>
-      <c r="I292" s="3"/>
-      <c r="J292" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K292" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L292" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M292" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N292" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O292" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P292" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q292" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R292" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S292" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T292" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U292" s="7">
-        <v>20.382000000000001</v>
+        <v>36</v>
+      </c>
+      <c r="G292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N292" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S292" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T292" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U292" s="5">
+        <v>0.21</v>
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -19817,61 +19892,61 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
       <c r="I293" s="3"/>
-      <c r="J293" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K293" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L293" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M293" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N293" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O293" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P293" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q293" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R293" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S293" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T293" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U293" s="5">
-        <v>8.32</v>
+      <c r="J293" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K293" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L293" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M293" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N293" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O293" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P293" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q293" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R293" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S293" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T293" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U293" s="7">
+        <v>20.382000000000001</v>
       </c>
       <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -19880,53 +19955,61 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>29</v>
+        <v>401</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
       <c r="I294" s="3"/>
-      <c r="J294" s="3"/>
-      <c r="K294" s="6">
-        <v>1</v>
-      </c>
-      <c r="L294" s="6">
-        <v>1</v>
-      </c>
-      <c r="M294" s="6">
-        <v>8</v>
-      </c>
-      <c r="N294" s="6">
-        <v>2</v>
-      </c>
-      <c r="O294" s="3"/>
-      <c r="P294" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q294" s="6">
-        <v>2</v>
-      </c>
-      <c r="R294" s="3"/>
-      <c r="S294" s="3"/>
-      <c r="T294" s="6">
-        <v>8</v>
-      </c>
-      <c r="U294" s="6">
-        <v>7</v>
+      <c r="J294" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K294" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L294" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M294" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N294" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O294" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P294" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q294" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R294" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S294" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T294" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U294" s="5">
+        <v>8.32</v>
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -19939,12 +20022,8 @@
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
-      <c r="I295" s="6">
-        <v>2</v>
-      </c>
-      <c r="J295" s="6">
-        <v>2</v>
-      </c>
+      <c r="I295" s="3"/>
+      <c r="J295" s="3"/>
       <c r="K295" s="6">
         <v>1</v>
       </c>
@@ -19952,46 +20031,40 @@
         <v>1</v>
       </c>
       <c r="M295" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N295" s="6">
-        <v>1</v>
-      </c>
-      <c r="O295" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O295" s="3"/>
       <c r="P295" s="6">
         <v>1</v>
       </c>
       <c r="Q295" s="6">
-        <v>4</v>
-      </c>
-      <c r="R295" s="6">
-        <v>1</v>
-      </c>
-      <c r="S295" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R295" s="3"/>
+      <c r="S295" s="3"/>
       <c r="T295" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U295" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V295" s="3"/>
       <c r="W295" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20000,59 +20073,63 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
-      <c r="I296" s="3"/>
-      <c r="J296" s="3"/>
+      <c r="I296" s="6">
+        <v>2</v>
+      </c>
+      <c r="J296" s="6">
+        <v>2</v>
+      </c>
       <c r="K296" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L296" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M296" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N296" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O296" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P296" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q296" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R296" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S296" s="6">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="T296" s="6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U296" s="6">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20067,31 +20144,91 @@
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
-      <c r="K297" s="3"/>
-      <c r="L297" s="3"/>
-      <c r="M297" s="3"/>
-      <c r="N297" s="3"/>
-      <c r="O297" s="3"/>
-      <c r="P297" s="3"/>
-      <c r="Q297" s="3"/>
-      <c r="R297" s="3"/>
-      <c r="S297" s="3"/>
+      <c r="K297" s="6">
+        <v>5</v>
+      </c>
+      <c r="L297" s="6">
+        <v>13</v>
+      </c>
+      <c r="M297" s="6">
+        <v>19</v>
+      </c>
+      <c r="N297" s="6">
+        <v>18</v>
+      </c>
+      <c r="O297" s="6">
+        <v>15</v>
+      </c>
+      <c r="P297" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q297" s="6">
+        <v>8</v>
+      </c>
+      <c r="R297" s="6">
+        <v>28</v>
+      </c>
+      <c r="S297" s="6">
+        <v>53</v>
+      </c>
       <c r="T297" s="6">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="U297" s="6">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="V297" s="3"/>
       <c r="W297" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="298" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="D298" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+      <c r="S298" s="3"/>
+      <c r="T298" s="6">
+        <v>114</v>
+      </c>
+      <c r="U298" s="6">
+        <v>61</v>
+      </c>
+      <c r="V298" s="3"/>
+      <c r="W298" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20106,7 +20243,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEA01A5-C05E-4B79-92F0-B298B1D0CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43344410-4006-421E-AB63-8016C86A556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,7 +949,7 @@
     <t>12.1.a Produktywność zasobów</t>
   </si>
   <si>
-    <t>euro/kg</t>
+    <t>euro (w cenach stałych z 2015 r.)/kg</t>
   </si>
   <si>
     <t>12.1.b Krajowa Konsumpcja Materialna (DMC) na 1 mieszkańca</t>
@@ -1297,7 +1297,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 10-03-2026, 12:37</t>
+    <t>Ostatnia aktualizacja: 17-03-2026, 07:50</t>
   </si>
 </sst>
 </file>
@@ -3376,7 +3376,7 @@
         <v>400.4</v>
       </c>
       <c r="U26" s="4">
-        <v>400.1</v>
+        <v>400.2</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="2" t="s">
@@ -4789,7 +4789,7 @@
         <v>65</v>
       </c>
       <c r="U47" s="4">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="2" t="s">
@@ -9862,10 +9862,10 @@
         <v>15.6</v>
       </c>
       <c r="S138" s="5">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="T138" s="5">
-        <v>16.559999999999999</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U138" s="5">
         <v>17.77</v>
@@ -13275,7 +13275,9 @@
       <c r="T188" s="4">
         <v>15.8</v>
       </c>
-      <c r="U188" s="3"/>
+      <c r="U188" s="4">
+        <v>15.2</v>
+      </c>
       <c r="V188" s="3"/>
       <c r="W188" s="2" t="s">
         <v>30</v>
@@ -14999,18 +15001,20 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
       <c r="Q217" s="4">
-        <v>15.7</v>
+        <v>5.4</v>
       </c>
       <c r="R217" s="4">
-        <v>14.8</v>
+        <v>5.3</v>
       </c>
       <c r="S217" s="4">
-        <v>14.8</v>
+        <v>5.2</v>
       </c>
       <c r="T217" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="U217" s="3"/>
+        <v>6.6</v>
+      </c>
+      <c r="U217" s="4">
+        <v>10.7</v>
+      </c>
       <c r="V217" s="3"/>
       <c r="W217" s="2" t="s">
         <v>30</v>
@@ -15046,18 +15050,20 @@
       <c r="O218" s="3"/>
       <c r="P218" s="3"/>
       <c r="Q218" s="4">
-        <v>13.3</v>
+        <v>3.9</v>
       </c>
       <c r="R218" s="4">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="S218" s="4">
-        <v>13.1</v>
+        <v>5</v>
       </c>
       <c r="T218" s="4">
-        <v>13.3</v>
-      </c>
-      <c r="U218" s="3"/>
+        <v>7.3</v>
+      </c>
+      <c r="U218" s="4">
+        <v>14.5</v>
+      </c>
       <c r="V218" s="3"/>
       <c r="W218" s="2" t="s">
         <v>30</v>
@@ -16338,10 +16344,10 @@
         <v>15.6</v>
       </c>
       <c r="S238" s="5">
-        <v>16.63</v>
+        <v>16.64</v>
       </c>
       <c r="T238" s="5">
-        <v>16.559999999999999</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U238" s="5">
         <v>17.77</v>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43344410-4006-421E-AB63-8016C86A556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FA667-D7B8-47E1-B3AE-95D076BB0C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -1036,9 +1036,6 @@
     <t>13.4.b Pojemność obiektów małej retencji wodnej</t>
   </si>
   <si>
-    <t>dam&lt;sub&gt;3&lt;/sub&gt;</t>
-  </si>
-  <si>
     <t>13.4.c Długość linii brzegowej zabezpieczonej w ciągu roku przed zjawiskiem erozji i powodzi od strony morza</t>
   </si>
   <si>
@@ -1060,7 +1057,7 @@
     <t>szt.</t>
   </si>
   <si>
-    <t>&lt;p&gt;Ministerstwo Klimatu i Środowiska&lt;/p&gt; &lt;p&gt;Generalna Dyrekcja Ochrony  Środowiska&lt;/p&gt; &lt;p&gt;Regionalne dyrekcje ochrony środowiska&lt;/p&gt; &lt;p&gt;Ministerstwo  Spraw Wewnętrznych i Administracji&lt;/p&gt; &lt;p&gt;Ministerstwo Rolnictwa i Rozwoju Wsi  (instytucja współdziałająca)&lt;/p&gt;</t>
+    <t>Ministerstwo Klimatu i Środowiska / Generalna Dyrekcja Ochrony Środowiska / Regionalne dyrekcje ochrony środowiska / Ministerstwo Spraw Wewnętrznych i Administracji / Ministerstwo Rolnictwa i Rozwoju Wsi (instytucja współdziałająca)</t>
   </si>
   <si>
     <t>13.6.b Zasięg realizowanych przedsięwzięć edukacyjno-informacyjnych</t>
@@ -1297,7 +1294,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 17-03-2026, 07:50</t>
+    <t>Ostatnia aktualizacja: 24-03-2026, 11:45</t>
   </si>
 </sst>
 </file>
@@ -2122,7 +2119,9 @@
       <c r="U6" s="4">
         <v>41.8</v>
       </c>
-      <c r="V6" s="3"/>
+      <c r="V6" s="4">
+        <v>44.2</v>
+      </c>
       <c r="W6" s="2" t="s">
         <v>37</v>
       </c>
@@ -2187,7 +2186,9 @@
       <c r="U7" s="4">
         <v>60.4</v>
       </c>
-      <c r="V7" s="3"/>
+      <c r="V7" s="4">
+        <v>60.5</v>
+      </c>
       <c r="W7" s="2" t="s">
         <v>37</v>
       </c>
@@ -2252,7 +2253,9 @@
       <c r="U8" s="4">
         <v>21</v>
       </c>
-      <c r="V8" s="3"/>
+      <c r="V8" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W8" s="2" t="s">
         <v>37</v>
       </c>
@@ -2780,11 +2783,21 @@
       <c r="Q16" s="4">
         <v>16.5</v>
       </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="R16" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="S16" s="4">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="T16" s="4">
+        <v>22.2</v>
+      </c>
+      <c r="U16" s="4">
+        <v>16.7</v>
+      </c>
+      <c r="V16" s="4">
+        <v>15.7</v>
+      </c>
       <c r="W16" s="2" t="s">
         <v>53</v>
       </c>
@@ -5675,7 +5688,9 @@
       <c r="U65" s="4">
         <v>84.3</v>
       </c>
-      <c r="V65" s="3"/>
+      <c r="V65" s="4">
+        <v>87.5</v>
+      </c>
       <c r="W65" s="2" t="s">
         <v>97</v>
       </c>
@@ -8985,7 +9000,9 @@
       <c r="U125" s="4">
         <v>41.8</v>
       </c>
-      <c r="V125" s="3"/>
+      <c r="V125" s="4">
+        <v>44.2</v>
+      </c>
       <c r="W125" s="2" t="s">
         <v>164</v>
       </c>
@@ -9050,7 +9067,9 @@
       <c r="U126" s="4">
         <v>60.4</v>
       </c>
-      <c r="V126" s="3"/>
+      <c r="V126" s="4">
+        <v>60.5</v>
+      </c>
       <c r="W126" s="2" t="s">
         <v>164</v>
       </c>
@@ -9115,7 +9134,9 @@
       <c r="U127" s="4">
         <v>21</v>
       </c>
-      <c r="V127" s="3"/>
+      <c r="V127" s="4">
+        <v>23.5</v>
+      </c>
       <c r="W127" s="2" t="s">
         <v>164</v>
       </c>
@@ -11749,10 +11770,10 @@
         <v>56</v>
       </c>
       <c r="P166" s="4">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="Q166" s="4">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="R166" s="4">
         <v>58.2</v>
@@ -15352,7 +15373,7 @@
         <v>9</v>
       </c>
       <c r="R223" s="4">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="S223" s="4">
         <v>7.6</v>
@@ -15360,7 +15381,9 @@
       <c r="T223" s="4">
         <v>7.6</v>
       </c>
-      <c r="U223" s="3"/>
+      <c r="U223" s="4">
+        <v>7.7</v>
+      </c>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
         <v>291</v>
@@ -15432,7 +15455,7 @@
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -16851,7 +16874,7 @@
         <v>28</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>335</v>
+        <v>170</v>
       </c>
       <c r="G246" s="4">
         <v>732401.6</v>
@@ -16909,7 +16932,7 @@
         <v>332</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>27</v>
@@ -16953,7 +16976,7 @@
       <c r="U247" s="3"/>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="248" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -16961,10 +16984,10 @@
         <v>311</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>27</v>
@@ -17009,15 +17032,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="108" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>311</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>27</v>
@@ -17026,7 +17049,7 @@
         <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="3"/>
@@ -17053,7 +17076,7 @@
         <v>4</v>
       </c>
       <c r="W249" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -17061,10 +17084,10 @@
         <v>311</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>27</v>
@@ -17073,7 +17096,7 @@
         <v>28</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G250" s="3"/>
       <c r="H250" s="3"/>
@@ -17100,24 +17123,24 @@
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="C251" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="D251" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="E251" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>36</v>
@@ -17169,24 +17192,24 @@
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="C252" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="D252" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E252" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>36</v>
@@ -17238,24 +17261,24 @@
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="C253" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="D253" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E253" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>36</v>
@@ -17307,24 +17330,24 @@
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="D254" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="E254" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>36</v>
@@ -17376,18 +17399,18 @@
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17396,7 +17419,7 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G255" s="4">
         <v>100</v>
@@ -17450,13 +17473,13 @@
     </row>
     <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17465,7 +17488,7 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G256" s="4">
         <v>59.5</v>
@@ -17519,13 +17542,13 @@
     </row>
     <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="C257" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17534,7 +17557,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G257" s="4">
         <v>90.8</v>
@@ -17588,13 +17611,13 @@
     </row>
     <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="C258" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D258" s="2" t="s">
         <v>27</v>
@@ -17652,18 +17675,18 @@
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="C259" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>27</v>
@@ -17726,13 +17749,13 @@
     </row>
     <row r="260" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>27</v>
@@ -17795,13 +17818,13 @@
     </row>
     <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>35</v>
@@ -17864,13 +17887,13 @@
     </row>
     <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>35</v>
@@ -17933,13 +17956,13 @@
     </row>
     <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>35</v>
@@ -18002,13 +18025,13 @@
     </row>
     <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18071,13 +18094,13 @@
     </row>
     <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18086,7 +18109,7 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G265" s="6">
         <v>70108</v>
@@ -18140,13 +18163,13 @@
     </row>
     <row r="266" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18209,13 +18232,13 @@
     </row>
     <row r="267" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="C267" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18275,18 +18298,18 @@
         <v>86</v>
       </c>
       <c r="W267" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>378</v>
-      </c>
       <c r="C268" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18330,18 +18353,18 @@
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>27</v>
@@ -18350,7 +18373,7 @@
         <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G269" s="5">
         <v>1.02</v>
@@ -18404,13 +18427,13 @@
     </row>
     <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>27</v>
@@ -18468,18 +18491,18 @@
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>62</v>
@@ -18536,13 +18559,13 @@
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C272" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>62</v>
@@ -18599,13 +18622,13 @@
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>62</v>
@@ -18662,13 +18685,13 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>35</v>
@@ -18725,13 +18748,13 @@
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B275" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>35</v>
@@ -18788,19 +18811,19 @@
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B276" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>36</v>
@@ -18851,19 +18874,19 @@
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B277" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>36</v>
@@ -18914,19 +18937,19 @@
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B278" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C278" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>36</v>
@@ -18977,19 +19000,19 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B279" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>36</v>
@@ -19040,19 +19063,19 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B280" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
@@ -19103,19 +19126,19 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
@@ -19166,13 +19189,13 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B282" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C282" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>141</v>
@@ -19229,13 +19252,13 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>141</v>
@@ -19292,13 +19315,13 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B284" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>141</v>
@@ -19355,13 +19378,13 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B285" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>144</v>
@@ -19418,13 +19441,13 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B286" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>144</v>
@@ -19481,13 +19504,13 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B287" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>144</v>
@@ -19544,13 +19567,13 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B288" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>144</v>
@@ -19607,13 +19630,13 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -19676,13 +19699,13 @@
     </row>
     <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B290" s="2" t="s">
+      <c r="C290" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>27</v>
@@ -19691,7 +19714,7 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G290" s="5">
         <v>377.75</v>
@@ -19740,18 +19763,18 @@
       </c>
       <c r="V290" s="3"/>
       <c r="W290" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B291" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -19760,7 +19783,7 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G291" s="5">
         <v>96.04</v>
@@ -19809,18 +19832,18 @@
       </c>
       <c r="V291" s="3"/>
       <c r="W291" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="292" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -19878,18 +19901,18 @@
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -19898,7 +19921,7 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="3"/>
@@ -19941,18 +19964,18 @@
       </c>
       <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B294" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -19961,7 +19984,7 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="3"/>
@@ -20004,18 +20027,18 @@
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -20057,20 +20080,22 @@
       <c r="U295" s="6">
         <v>7</v>
       </c>
-      <c r="V295" s="3"/>
+      <c r="V295" s="6">
+        <v>2</v>
+      </c>
       <c r="W295" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B296" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20122,20 +20147,22 @@
       <c r="U296" s="6">
         <v>4</v>
       </c>
-      <c r="V296" s="3"/>
+      <c r="V296" s="6">
+        <v>2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20183,20 +20210,22 @@
       <c r="U297" s="6">
         <v>70</v>
       </c>
-      <c r="V297" s="3"/>
+      <c r="V297" s="6">
+        <v>69</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B298" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20226,15 +20255,17 @@
       <c r="U298" s="6">
         <v>61</v>
       </c>
-      <c r="V298" s="3"/>
+      <c r="V298" s="6">
+        <v>97</v>
+      </c>
       <c r="W298" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20249,7 +20280,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FA667-D7B8-47E1-B3AE-95D076BB0C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E241D798-F0DD-428B-96E5-FA921B139621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="423">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -1270,6 +1270,9 @@
     <t>17.4.a Udział KAS w projektach twinningowych, działaniach finansowanych z Taiex oraz ze środków krajowych</t>
   </si>
   <si>
+    <t>liczba przedsięwzięć</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ministerstwo Finansów </t>
   </si>
   <si>
@@ -1294,7 +1297,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 24-03-2026, 11:45</t>
+    <t>Ostatnia aktualizacja: 21-04-2026, 11:39</t>
   </si>
 </sst>
 </file>
@@ -2117,7 +2120,7 @@
         <v>36</v>
       </c>
       <c r="U6" s="4">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="V6" s="4">
         <v>44.2</v>
@@ -2184,7 +2187,7 @@
         <v>51.4</v>
       </c>
       <c r="U7" s="4">
-        <v>60.4</v>
+        <v>58.2</v>
       </c>
       <c r="V7" s="4">
         <v>60.5</v>
@@ -2251,7 +2254,7 @@
         <v>15.1</v>
       </c>
       <c r="U8" s="4">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="V8" s="4">
         <v>23.5</v>
@@ -6246,7 +6249,9 @@
       <c r="U75" s="4">
         <v>95.4</v>
       </c>
-      <c r="V75" s="3"/>
+      <c r="V75" s="4">
+        <v>95.1</v>
+      </c>
       <c r="W75" s="2" t="s">
         <v>117</v>
       </c>
@@ -8998,7 +9003,7 @@
         <v>36</v>
       </c>
       <c r="U125" s="4">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="V125" s="4">
         <v>44.2</v>
@@ -9065,7 +9070,7 @@
         <v>51.4</v>
       </c>
       <c r="U126" s="4">
-        <v>60.4</v>
+        <v>58.2</v>
       </c>
       <c r="V126" s="4">
         <v>60.5</v>
@@ -9132,7 +9137,7 @@
         <v>15.1</v>
       </c>
       <c r="U127" s="4">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="V127" s="4">
         <v>23.5</v>
@@ -13299,7 +13304,9 @@
       <c r="U188" s="4">
         <v>15.2</v>
       </c>
-      <c r="V188" s="3"/>
+      <c r="V188" s="4">
+        <v>15.9</v>
+      </c>
       <c r="W188" s="2" t="s">
         <v>30</v>
       </c>
@@ -14201,7 +14208,9 @@
       <c r="U204" s="6">
         <v>294</v>
       </c>
-      <c r="V204" s="3"/>
+      <c r="V204" s="6">
+        <v>372</v>
+      </c>
       <c r="W204" s="2" t="s">
         <v>259</v>
       </c>
@@ -16227,7 +16236,7 @@
         <v>95</v>
       </c>
       <c r="Q236" s="4">
-        <v>90.5</v>
+        <v>90.4</v>
       </c>
       <c r="R236" s="4">
         <v>99</v>
@@ -16236,9 +16245,11 @@
         <v>94.2</v>
       </c>
       <c r="T236" s="4">
-        <v>84.8</v>
-      </c>
-      <c r="U236" s="3"/>
+        <v>84.9</v>
+      </c>
+      <c r="U236" s="4">
+        <v>83.4</v>
+      </c>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
         <v>315</v>
@@ -16267,45 +16278,47 @@
         <v>100</v>
       </c>
       <c r="H237" s="4">
-        <v>99.6</v>
+        <v>99.7</v>
       </c>
       <c r="I237" s="4">
         <v>97.8</v>
       </c>
       <c r="J237" s="4">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="K237" s="4">
-        <v>93.7</v>
+        <v>93.6</v>
       </c>
       <c r="L237" s="4">
-        <v>94.4</v>
+        <v>94.3</v>
       </c>
       <c r="M237" s="4">
-        <v>97</v>
+        <v>96.9</v>
       </c>
       <c r="N237" s="4">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="O237" s="4">
-        <v>100.6</v>
+        <v>100.4</v>
       </c>
       <c r="P237" s="4">
-        <v>95.1</v>
+        <v>94.9</v>
       </c>
       <c r="Q237" s="4">
-        <v>91.5</v>
+        <v>91.2</v>
       </c>
       <c r="R237" s="4">
-        <v>98.4</v>
+        <v>98.2</v>
       </c>
       <c r="S237" s="4">
-        <v>93.8</v>
+        <v>93.6</v>
       </c>
       <c r="T237" s="4">
-        <v>85.8</v>
-      </c>
-      <c r="U237" s="3"/>
+        <v>85.7</v>
+      </c>
+      <c r="U237" s="4">
+        <v>84.2</v>
+      </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
         <v>315</v>
@@ -16513,7 +16526,9 @@
       <c r="U240" s="6">
         <v>33623</v>
       </c>
-      <c r="V240" s="3"/>
+      <c r="V240" s="6">
+        <v>37777</v>
+      </c>
       <c r="W240" s="2" t="s">
         <v>323</v>
       </c>
@@ -17027,7 +17042,9 @@
       <c r="U248" s="6">
         <v>80</v>
       </c>
-      <c r="V248" s="3"/>
+      <c r="V248" s="6">
+        <v>86</v>
+      </c>
       <c r="W248" s="2" t="s">
         <v>188</v>
       </c>
@@ -17121,7 +17138,9 @@
       <c r="U250" s="6">
         <v>44</v>
       </c>
-      <c r="V250" s="3"/>
+      <c r="V250" s="6">
+        <v>89</v>
+      </c>
       <c r="W250" s="2" t="s">
         <v>345</v>
       </c>
@@ -20047,7 +20066,7 @@
         <v>28</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
@@ -20084,7 +20103,7 @@
         <v>2</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -20092,10 +20111,10 @@
         <v>397</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20104,7 +20123,7 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>29</v>
+        <v>413</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
@@ -20151,7 +20170,7 @@
         <v>2</v>
       </c>
       <c r="W296" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -20159,10 +20178,10 @@
         <v>397</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20214,7 +20233,7 @@
         <v>69</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -20222,10 +20241,10 @@
         <v>397</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20259,13 +20278,13 @@
         <v>97</v>
       </c>
       <c r="W298" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B300" s="8"/>
     </row>
@@ -20280,7 +20299,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E241D798-F0DD-428B-96E5-FA921B139621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EAFBC5-2490-4EBB-8EC3-5F2F8E6682F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1297,7 +1297,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 21-04-2026, 11:39</t>
+    <t>Ostatnia aktualizacja: 28-04-2026, 10:52</t>
   </si>
 </sst>
 </file>
@@ -5831,7 +5831,9 @@
       <c r="U67" s="4">
         <v>34.9</v>
       </c>
-      <c r="V67" s="3"/>
+      <c r="V67" s="4">
+        <v>32.799999999999997</v>
+      </c>
       <c r="W67" s="2" t="s">
         <v>30</v>
       </c>
@@ -6458,7 +6460,9 @@
       <c r="U78" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="V78" s="3"/>
+      <c r="V78" s="4">
+        <v>4</v>
+      </c>
       <c r="W78" s="2" t="s">
         <v>30</v>
       </c>
@@ -6665,7 +6669,9 @@
       <c r="U81" s="4">
         <v>10</v>
       </c>
-      <c r="V81" s="3"/>
+      <c r="V81" s="4">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="W81" s="2" t="s">
         <v>30</v>
       </c>
@@ -8429,7 +8435,9 @@
       <c r="U115" s="4">
         <v>8.5</v>
       </c>
-      <c r="V115" s="3"/>
+      <c r="V115" s="4">
+        <v>8</v>
+      </c>
       <c r="W115" s="2" t="s">
         <v>30</v>
       </c>
@@ -16987,9 +16995,15 @@
       <c r="S247" s="5">
         <v>4.7300000000000004</v>
       </c>
-      <c r="T247" s="3"/>
-      <c r="U247" s="3"/>
-      <c r="V247" s="3"/>
+      <c r="T247" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U247" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V247" s="5">
+        <v>5.95</v>
+      </c>
       <c r="W247" s="2" t="s">
         <v>336</v>
       </c>
@@ -19981,7 +19995,9 @@
       <c r="U293" s="7">
         <v>20.382000000000001</v>
       </c>
-      <c r="V293" s="3"/>
+      <c r="V293" s="7">
+        <v>5.3920000000000003</v>
+      </c>
       <c r="W293" s="2" t="s">
         <v>401</v>
       </c>
@@ -20299,7 +20315,7 @@
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE121B8-8CD1-4E63-97EA-B3291DD232DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A002F2D3-8696-4E7D-9220-3E2740092518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="427">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -1021,6 +1021,24 @@
     <t xml:space="preserve">Agencja Rynku Energii S.A. </t>
   </si>
   <si>
+    <t>Wzmocnienie roli adaptacji do zmian klimatu jako równoważnego z mitygacją środka walki ze zmianą klimatu</t>
+  </si>
+  <si>
+    <t>13.3.a Inwestycje w działania na rzecz łagodzenia zmian klimatu w relacji do PKB</t>
+  </si>
+  <si>
+    <t>13.3.b Straty ekonomiczne związane z klimatem</t>
+  </si>
+  <si>
+    <t>na osobę (w cenach stałych)</t>
+  </si>
+  <si>
+    <t>euro</t>
+  </si>
+  <si>
+    <t>w mln (w cenach stałych)</t>
+  </si>
+  <si>
     <t>Zwiększenie odporności kraju na skutki zmian klimatycznych</t>
   </si>
   <si>
@@ -1291,7 +1309,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 12-05-2026, 12:02</t>
+    <t>Ostatnia aktualizacja: 20-05-2026, 10:30</t>
   </si>
 </sst>
 </file>
@@ -1837,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W304"/>
+  <dimension ref="A1:W307"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -9922,21 +9940,51 @@
       <c r="F139" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
-      <c r="J139" s="3"/>
-      <c r="K139" s="3"/>
-      <c r="L139" s="3"/>
-      <c r="M139" s="3"/>
-      <c r="N139" s="3"/>
-      <c r="O139" s="3"/>
-      <c r="P139" s="3"/>
-      <c r="Q139" s="3"/>
-      <c r="R139" s="3"/>
-      <c r="S139" s="3"/>
-      <c r="T139" s="3"/>
-      <c r="U139" s="3"/>
+      <c r="G139" s="7">
+        <v>6.64</v>
+      </c>
+      <c r="H139" s="7">
+        <v>6.9180000000000001</v>
+      </c>
+      <c r="I139" s="7">
+        <v>6.5330000000000004</v>
+      </c>
+      <c r="J139" s="7">
+        <v>6.6660000000000004</v>
+      </c>
+      <c r="K139" s="7">
+        <v>6.319</v>
+      </c>
+      <c r="L139" s="7">
+        <v>5.6859999999999999</v>
+      </c>
+      <c r="M139" s="7">
+        <v>3.9740000000000002</v>
+      </c>
+      <c r="N139" s="7">
+        <v>4.2320000000000002</v>
+      </c>
+      <c r="O139" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="P139" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="Q139" s="7">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="R139" s="7">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="S139" s="7">
+        <v>5.7910000000000004</v>
+      </c>
+      <c r="T139" s="7">
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="U139" s="7">
+        <v>6.0330000000000004</v>
+      </c>
       <c r="V139" s="3"/>
       <c r="W139" s="2" t="s">
         <v>183</v>
@@ -9961,21 +10009,51 @@
       <c r="F140" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="3"/>
-      <c r="J140" s="3"/>
-      <c r="K140" s="3"/>
-      <c r="L140" s="3"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
-      <c r="O140" s="3"/>
-      <c r="P140" s="3"/>
-      <c r="Q140" s="3"/>
-      <c r="R140" s="3"/>
-      <c r="S140" s="3"/>
-      <c r="T140" s="3"/>
-      <c r="U140" s="3"/>
+      <c r="G140" s="7">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="H140" s="7">
+        <v>8.0779999999999994</v>
+      </c>
+      <c r="I140" s="7">
+        <v>10.61</v>
+      </c>
+      <c r="J140" s="7">
+        <v>10.676</v>
+      </c>
+      <c r="K140" s="7">
+        <v>12.36</v>
+      </c>
+      <c r="L140" s="7">
+        <v>13.401</v>
+      </c>
+      <c r="M140" s="7">
+        <v>13.342000000000001</v>
+      </c>
+      <c r="N140" s="7">
+        <v>13.082000000000001</v>
+      </c>
+      <c r="O140" s="7">
+        <v>13.026999999999999</v>
+      </c>
+      <c r="P140" s="7">
+        <v>14.356</v>
+      </c>
+      <c r="Q140" s="7">
+        <v>16.236999999999998</v>
+      </c>
+      <c r="R140" s="7">
+        <v>17.167000000000002</v>
+      </c>
+      <c r="S140" s="7">
+        <v>21.009</v>
+      </c>
+      <c r="T140" s="7">
+        <v>25.792999999999999</v>
+      </c>
+      <c r="U140" s="7">
+        <v>30.37</v>
+      </c>
       <c r="V140" s="3"/>
       <c r="W140" s="2" t="s">
         <v>183</v>
@@ -10000,21 +10078,51 @@
       <c r="F141" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G141" s="3"/>
-      <c r="H141" s="3"/>
-      <c r="I141" s="3"/>
-      <c r="J141" s="3"/>
-      <c r="K141" s="3"/>
-      <c r="L141" s="3"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-      <c r="O141" s="3"/>
-      <c r="P141" s="3"/>
-      <c r="Q141" s="3"/>
-      <c r="R141" s="3"/>
-      <c r="S141" s="3"/>
-      <c r="T141" s="3"/>
-      <c r="U141" s="3"/>
+      <c r="G141" s="7">
+        <v>11.811999999999999</v>
+      </c>
+      <c r="H141" s="7">
+        <v>13.24</v>
+      </c>
+      <c r="I141" s="7">
+        <v>13.497</v>
+      </c>
+      <c r="J141" s="7">
+        <v>14.265000000000001</v>
+      </c>
+      <c r="K141" s="7">
+        <v>14.237</v>
+      </c>
+      <c r="L141" s="7">
+        <v>14.795</v>
+      </c>
+      <c r="M141" s="7">
+        <v>14.919</v>
+      </c>
+      <c r="N141" s="7">
+        <v>14.779</v>
+      </c>
+      <c r="O141" s="7">
+        <v>21.472999999999999</v>
+      </c>
+      <c r="P141" s="7">
+        <v>22.004999999999999</v>
+      </c>
+      <c r="Q141" s="7">
+        <v>22.143000000000001</v>
+      </c>
+      <c r="R141" s="7">
+        <v>20.978000000000002</v>
+      </c>
+      <c r="S141" s="7">
+        <v>22.094999999999999</v>
+      </c>
+      <c r="T141" s="7">
+        <v>20.61</v>
+      </c>
+      <c r="U141" s="7">
+        <v>21.286999999999999</v>
+      </c>
       <c r="V141" s="3"/>
       <c r="W141" s="2" t="s">
         <v>183</v>
@@ -16531,21 +16639,51 @@
       <c r="F242" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G242" s="3"/>
-      <c r="H242" s="3"/>
-      <c r="I242" s="3"/>
-      <c r="J242" s="3"/>
-      <c r="K242" s="3"/>
-      <c r="L242" s="3"/>
-      <c r="M242" s="3"/>
-      <c r="N242" s="3"/>
-      <c r="O242" s="3"/>
-      <c r="P242" s="3"/>
-      <c r="Q242" s="3"/>
-      <c r="R242" s="3"/>
-      <c r="S242" s="3"/>
-      <c r="T242" s="3"/>
-      <c r="U242" s="3"/>
+      <c r="G242" s="7">
+        <v>6.64</v>
+      </c>
+      <c r="H242" s="7">
+        <v>6.9180000000000001</v>
+      </c>
+      <c r="I242" s="7">
+        <v>6.5330000000000004</v>
+      </c>
+      <c r="J242" s="7">
+        <v>6.6660000000000004</v>
+      </c>
+      <c r="K242" s="7">
+        <v>6.319</v>
+      </c>
+      <c r="L242" s="7">
+        <v>5.6859999999999999</v>
+      </c>
+      <c r="M242" s="7">
+        <v>3.9740000000000002</v>
+      </c>
+      <c r="N242" s="7">
+        <v>4.2320000000000002</v>
+      </c>
+      <c r="O242" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="P242" s="7">
+        <v>6.2</v>
+      </c>
+      <c r="Q242" s="7">
+        <v>6.5750000000000002</v>
+      </c>
+      <c r="R242" s="7">
+        <v>5.6740000000000004</v>
+      </c>
+      <c r="S242" s="7">
+        <v>5.7910000000000004</v>
+      </c>
+      <c r="T242" s="7">
+        <v>6.3390000000000004</v>
+      </c>
+      <c r="U242" s="7">
+        <v>6.0330000000000004</v>
+      </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
         <v>183</v>
@@ -16570,21 +16708,51 @@
       <c r="F243" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G243" s="3"/>
-      <c r="H243" s="3"/>
-      <c r="I243" s="3"/>
-      <c r="J243" s="3"/>
-      <c r="K243" s="3"/>
-      <c r="L243" s="3"/>
-      <c r="M243" s="3"/>
-      <c r="N243" s="3"/>
-      <c r="O243" s="3"/>
-      <c r="P243" s="3"/>
-      <c r="Q243" s="3"/>
-      <c r="R243" s="3"/>
-      <c r="S243" s="3"/>
-      <c r="T243" s="3"/>
-      <c r="U243" s="3"/>
+      <c r="G243" s="7">
+        <v>6.5490000000000004</v>
+      </c>
+      <c r="H243" s="7">
+        <v>8.0779999999999994</v>
+      </c>
+      <c r="I243" s="7">
+        <v>10.61</v>
+      </c>
+      <c r="J243" s="7">
+        <v>10.676</v>
+      </c>
+      <c r="K243" s="7">
+        <v>12.36</v>
+      </c>
+      <c r="L243" s="7">
+        <v>13.401</v>
+      </c>
+      <c r="M243" s="7">
+        <v>13.342000000000001</v>
+      </c>
+      <c r="N243" s="7">
+        <v>13.082000000000001</v>
+      </c>
+      <c r="O243" s="7">
+        <v>13.026999999999999</v>
+      </c>
+      <c r="P243" s="7">
+        <v>14.356</v>
+      </c>
+      <c r="Q243" s="7">
+        <v>16.236999999999998</v>
+      </c>
+      <c r="R243" s="7">
+        <v>17.167000000000002</v>
+      </c>
+      <c r="S243" s="7">
+        <v>21.009</v>
+      </c>
+      <c r="T243" s="7">
+        <v>25.792999999999999</v>
+      </c>
+      <c r="U243" s="7">
+        <v>30.37</v>
+      </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
         <v>183</v>
@@ -16609,21 +16777,51 @@
       <c r="F244" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G244" s="3"/>
-      <c r="H244" s="3"/>
-      <c r="I244" s="3"/>
-      <c r="J244" s="3"/>
-      <c r="K244" s="3"/>
-      <c r="L244" s="3"/>
-      <c r="M244" s="3"/>
-      <c r="N244" s="3"/>
-      <c r="O244" s="3"/>
-      <c r="P244" s="3"/>
-      <c r="Q244" s="3"/>
-      <c r="R244" s="3"/>
-      <c r="S244" s="3"/>
-      <c r="T244" s="3"/>
-      <c r="U244" s="3"/>
+      <c r="G244" s="7">
+        <v>11.811999999999999</v>
+      </c>
+      <c r="H244" s="7">
+        <v>13.24</v>
+      </c>
+      <c r="I244" s="7">
+        <v>13.497</v>
+      </c>
+      <c r="J244" s="7">
+        <v>14.265000000000001</v>
+      </c>
+      <c r="K244" s="7">
+        <v>14.237</v>
+      </c>
+      <c r="L244" s="7">
+        <v>14.795</v>
+      </c>
+      <c r="M244" s="7">
+        <v>14.919</v>
+      </c>
+      <c r="N244" s="7">
+        <v>14.779</v>
+      </c>
+      <c r="O244" s="7">
+        <v>21.472999999999999</v>
+      </c>
+      <c r="P244" s="7">
+        <v>22.004999999999999</v>
+      </c>
+      <c r="Q244" s="7">
+        <v>22.143000000000001</v>
+      </c>
+      <c r="R244" s="7">
+        <v>20.978000000000002</v>
+      </c>
+      <c r="S244" s="7">
+        <v>22.094999999999999</v>
+      </c>
+      <c r="T244" s="7">
+        <v>20.61</v>
+      </c>
+      <c r="U244" s="7">
+        <v>21.286999999999999</v>
+      </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
         <v>183</v>
@@ -16717,21 +16915,51 @@
       <c r="F246" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="G246" s="3"/>
-      <c r="H246" s="3"/>
-      <c r="I246" s="3"/>
-      <c r="J246" s="3"/>
-      <c r="K246" s="3"/>
-      <c r="L246" s="3"/>
-      <c r="M246" s="3"/>
-      <c r="N246" s="3"/>
-      <c r="O246" s="3"/>
-      <c r="P246" s="3"/>
-      <c r="Q246" s="3"/>
-      <c r="R246" s="3"/>
-      <c r="S246" s="3"/>
-      <c r="T246" s="3"/>
-      <c r="U246" s="3"/>
+      <c r="G246" s="6">
+        <v>440</v>
+      </c>
+      <c r="H246" s="6">
+        <v>101</v>
+      </c>
+      <c r="I246" s="6">
+        <v>151</v>
+      </c>
+      <c r="J246" s="6">
+        <v>217</v>
+      </c>
+      <c r="K246" s="6">
+        <v>239</v>
+      </c>
+      <c r="L246" s="6">
+        <v>674</v>
+      </c>
+      <c r="M246" s="6">
+        <v>705</v>
+      </c>
+      <c r="N246" s="6">
+        <v>712</v>
+      </c>
+      <c r="O246" s="6">
+        <v>743</v>
+      </c>
+      <c r="P246" s="6">
+        <v>788</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>805</v>
+      </c>
+      <c r="R246" s="6">
+        <v>892</v>
+      </c>
+      <c r="S246" s="6">
+        <v>988</v>
+      </c>
+      <c r="T246" s="6">
+        <v>1029</v>
+      </c>
+      <c r="U246" s="6">
+        <v>1167</v>
+      </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
         <v>30</v>
@@ -16756,21 +16984,51 @@
       <c r="F247" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="G247" s="3"/>
-      <c r="H247" s="3"/>
-      <c r="I247" s="3"/>
-      <c r="J247" s="3"/>
-      <c r="K247" s="3"/>
-      <c r="L247" s="3"/>
-      <c r="M247" s="3"/>
-      <c r="N247" s="3"/>
-      <c r="O247" s="3"/>
-      <c r="P247" s="3"/>
-      <c r="Q247" s="3"/>
-      <c r="R247" s="3"/>
-      <c r="S247" s="3"/>
-      <c r="T247" s="3"/>
-      <c r="U247" s="3"/>
+      <c r="G247" s="6">
+        <v>123</v>
+      </c>
+      <c r="H247" s="6">
+        <v>101</v>
+      </c>
+      <c r="I247" s="6">
+        <v>151</v>
+      </c>
+      <c r="J247" s="6">
+        <v>217</v>
+      </c>
+      <c r="K247" s="6">
+        <v>239</v>
+      </c>
+      <c r="L247" s="6">
+        <v>235</v>
+      </c>
+      <c r="M247" s="6">
+        <v>225</v>
+      </c>
+      <c r="N247" s="6">
+        <v>234</v>
+      </c>
+      <c r="O247" s="6">
+        <v>248</v>
+      </c>
+      <c r="P247" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>268</v>
+      </c>
+      <c r="R247" s="6">
+        <v>297</v>
+      </c>
+      <c r="S247" s="6">
+        <v>329</v>
+      </c>
+      <c r="T247" s="6">
+        <v>343</v>
+      </c>
+      <c r="U247" s="6">
+        <v>389</v>
+      </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
         <v>30</v>
@@ -16847,7 +17105,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="249" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>315</v>
       </c>
@@ -16864,59 +17122,57 @@
         <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J249" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K249" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L249" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M249" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N249" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R249" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S249" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T249" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U249" s="5">
-        <v>0.59</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G249" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L249" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U249" s="3"/>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="250" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>315</v>
       </c>
@@ -16930,60 +17186,62 @@
         <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>28</v>
+        <v>333</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G250" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H250" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I250" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J250" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K250" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L250" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M250" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N250" s="3"/>
-      <c r="O250" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P250" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q250" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R250" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S250" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T250" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U250" s="4">
-        <v>881284.3</v>
+        <v>334</v>
+      </c>
+      <c r="G250" s="5">
+        <v>137.94999999999999</v>
+      </c>
+      <c r="H250" s="5">
+        <v>0</v>
+      </c>
+      <c r="I250" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="J250" s="5">
+        <v>0</v>
+      </c>
+      <c r="K250" s="5">
+        <v>0</v>
+      </c>
+      <c r="L250" s="5">
+        <v>0</v>
+      </c>
+      <c r="M250" s="5">
+        <v>0</v>
+      </c>
+      <c r="N250" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="O250" s="5">
+        <v>25.44</v>
+      </c>
+      <c r="P250" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="5">
+        <v>12.02</v>
+      </c>
+      <c r="R250" s="5">
+        <v>0.89</v>
+      </c>
+      <c r="S250" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="T250" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="U250" s="5">
+        <v>80.36</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="251" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>315</v>
       </c>
@@ -16991,57 +17249,65 @@
         <v>330</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G251" s="3"/>
-      <c r="H251" s="3"/>
-      <c r="I251" s="3"/>
-      <c r="J251" s="3"/>
-      <c r="K251" s="3"/>
-      <c r="L251" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M251" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N251" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O251" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P251" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q251" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R251" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S251" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T251" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U251" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V251" s="5">
-        <v>5.95</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="G251" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H251" s="6">
+        <v>0</v>
+      </c>
+      <c r="I251" s="6">
+        <v>7</v>
+      </c>
+      <c r="J251" s="6">
+        <v>0</v>
+      </c>
+      <c r="K251" s="6">
+        <v>0</v>
+      </c>
+      <c r="L251" s="6">
+        <v>0</v>
+      </c>
+      <c r="M251" s="6">
+        <v>0</v>
+      </c>
+      <c r="N251" s="6">
+        <v>87</v>
+      </c>
+      <c r="O251" s="6">
+        <v>966</v>
+      </c>
+      <c r="P251" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q251" s="6">
+        <v>451</v>
+      </c>
+      <c r="R251" s="6">
+        <v>33</v>
+      </c>
+      <c r="S251" s="6">
+        <v>1</v>
+      </c>
+      <c r="T251" s="6">
+        <v>1</v>
+      </c>
+      <c r="U251" s="6">
+        <v>2938</v>
+      </c>
+      <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>334</v>
+        <v>27</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17049,10 +17315,10 @@
         <v>315</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>27</v>
@@ -17063,48 +17329,62 @@
       <c r="F252" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="G252" s="3"/>
-      <c r="H252" s="3"/>
-      <c r="I252" s="3"/>
-      <c r="J252" s="3"/>
-      <c r="K252" s="3"/>
-      <c r="L252" s="3"/>
-      <c r="M252" s="3"/>
-      <c r="N252" s="3"/>
-      <c r="O252" s="6">
-        <v>1</v>
-      </c>
-      <c r="P252" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q252" s="6">
-        <v>63</v>
-      </c>
-      <c r="R252" s="6">
-        <v>66</v>
-      </c>
-      <c r="S252" s="6">
-        <v>70</v>
-      </c>
-      <c r="T252" s="6">
-        <v>75</v>
-      </c>
-      <c r="U252" s="6">
-        <v>80</v>
-      </c>
-      <c r="V252" s="6">
-        <v>86</v>
-      </c>
+      <c r="G252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="253" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>338</v>
@@ -17116,45 +17396,65 @@
         <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="G253" s="3"/>
-      <c r="H253" s="3"/>
-      <c r="I253" s="3"/>
-      <c r="J253" s="3"/>
-      <c r="K253" s="3"/>
-      <c r="L253" s="3"/>
-      <c r="M253" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="G253" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H253" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I253" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J253" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K253" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L253" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M253" s="4">
+        <v>826034.2</v>
+      </c>
       <c r="N253" s="3"/>
-      <c r="O253" s="3"/>
-      <c r="P253" s="3"/>
-      <c r="Q253" s="3"/>
-      <c r="R253" s="3"/>
-      <c r="S253" s="6">
-        <v>16</v>
-      </c>
-      <c r="T253" s="6">
-        <v>7</v>
-      </c>
-      <c r="U253" s="6">
-        <v>6</v>
-      </c>
-      <c r="V253" s="6">
-        <v>4</v>
-      </c>
+      <c r="O253" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P253" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q253" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R253" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S253" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T253" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U253" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17163,530 +17463,486 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="3"/>
       <c r="I254" s="3"/>
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
-      <c r="L254" s="3"/>
-      <c r="M254" s="3"/>
-      <c r="N254" s="3"/>
-      <c r="O254" s="3"/>
-      <c r="P254" s="3"/>
-      <c r="Q254" s="3"/>
-      <c r="R254" s="6">
+      <c r="L254" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N254" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O254" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P254" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S254" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T254" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U254" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="W254" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G255" s="3"/>
+      <c r="H255" s="3"/>
+      <c r="I255" s="3"/>
+      <c r="J255" s="3"/>
+      <c r="K255" s="3"/>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
+      <c r="N255" s="3"/>
+      <c r="O255" s="6">
+        <v>1</v>
+      </c>
+      <c r="P255" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>63</v>
+      </c>
+      <c r="R255" s="6">
+        <v>66</v>
+      </c>
+      <c r="S255" s="6">
+        <v>70</v>
+      </c>
+      <c r="T255" s="6">
+        <v>75</v>
+      </c>
+      <c r="U255" s="6">
+        <v>80</v>
+      </c>
+      <c r="V255" s="6">
+        <v>86</v>
+      </c>
+      <c r="W255" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G256" s="3"/>
+      <c r="H256" s="3"/>
+      <c r="I256" s="3"/>
+      <c r="J256" s="3"/>
+      <c r="K256" s="3"/>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
+      <c r="N256" s="3"/>
+      <c r="O256" s="3"/>
+      <c r="P256" s="3"/>
+      <c r="Q256" s="3"/>
+      <c r="R256" s="3"/>
+      <c r="S256" s="6">
+        <v>16</v>
+      </c>
+      <c r="T256" s="6">
+        <v>7</v>
+      </c>
+      <c r="U256" s="6">
+        <v>6</v>
+      </c>
+      <c r="V256" s="6">
+        <v>4</v>
+      </c>
+      <c r="W256" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G257" s="3"/>
+      <c r="H257" s="3"/>
+      <c r="I257" s="3"/>
+      <c r="J257" s="3"/>
+      <c r="K257" s="3"/>
+      <c r="L257" s="3"/>
+      <c r="M257" s="3"/>
+      <c r="N257" s="3"/>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="3"/>
+      <c r="R257" s="6">
         <v>133</v>
       </c>
-      <c r="S254" s="6">
+      <c r="S257" s="6">
         <v>80</v>
       </c>
-      <c r="T254" s="6">
+      <c r="T257" s="6">
         <v>97</v>
       </c>
-      <c r="U254" s="6">
+      <c r="U257" s="6">
         <v>44</v>
       </c>
-      <c r="V254" s="6">
+      <c r="V257" s="6">
         <v>89</v>
       </c>
-      <c r="W254" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G255" s="6">
-        <v>40</v>
-      </c>
-      <c r="H255" s="6">
-        <v>60</v>
-      </c>
-      <c r="I255" s="6">
-        <v>40</v>
-      </c>
-      <c r="J255" s="6">
-        <v>40</v>
-      </c>
-      <c r="K255" s="6">
-        <v>40</v>
-      </c>
-      <c r="L255" s="6">
-        <v>40</v>
-      </c>
-      <c r="M255" s="6">
-        <v>60</v>
-      </c>
-      <c r="N255" s="6">
-        <v>40</v>
-      </c>
-      <c r="O255" s="6">
-        <v>40</v>
-      </c>
-      <c r="P255" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>60</v>
-      </c>
-      <c r="R255" s="6">
-        <v>67</v>
-      </c>
-      <c r="S255" s="6">
-        <v>50</v>
-      </c>
-      <c r="T255" s="6">
-        <v>67</v>
-      </c>
-      <c r="U255" s="6">
-        <v>67</v>
-      </c>
-      <c r="V255" s="3"/>
-      <c r="W255" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E256" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G256" s="6">
-        <v>40</v>
-      </c>
-      <c r="H256" s="6">
-        <v>60</v>
-      </c>
-      <c r="I256" s="6">
-        <v>20</v>
-      </c>
-      <c r="J256" s="6">
-        <v>20</v>
-      </c>
-      <c r="K256" s="6">
-        <v>20</v>
-      </c>
-      <c r="L256" s="6">
-        <v>40</v>
-      </c>
-      <c r="M256" s="6">
-        <v>60</v>
-      </c>
-      <c r="N256" s="6">
-        <v>40</v>
-      </c>
-      <c r="O256" s="6">
-        <v>25</v>
-      </c>
-      <c r="P256" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q256" s="6">
-        <v>20</v>
-      </c>
-      <c r="R256" s="6">
-        <v>17</v>
-      </c>
-      <c r="S256" s="6">
-        <v>0</v>
-      </c>
-      <c r="T256" s="6">
-        <v>17</v>
-      </c>
-      <c r="U256" s="6">
-        <v>0</v>
-      </c>
-      <c r="V256" s="3"/>
-      <c r="W256" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E257" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G257" s="6">
-        <v>0</v>
-      </c>
-      <c r="H257" s="6">
-        <v>0</v>
-      </c>
-      <c r="I257" s="6">
-        <v>20</v>
-      </c>
-      <c r="J257" s="6">
-        <v>20</v>
-      </c>
-      <c r="K257" s="6">
-        <v>20</v>
-      </c>
-      <c r="L257" s="6">
-        <v>0</v>
-      </c>
-      <c r="M257" s="6">
-        <v>0</v>
-      </c>
-      <c r="N257" s="6">
-        <v>0</v>
-      </c>
-      <c r="O257" s="6">
-        <v>0</v>
-      </c>
-      <c r="P257" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="6">
-        <v>40</v>
-      </c>
-      <c r="R257" s="6">
-        <v>17</v>
-      </c>
-      <c r="S257" s="6">
-        <v>17</v>
-      </c>
-      <c r="T257" s="6">
-        <v>17</v>
-      </c>
-      <c r="U257" s="6">
-        <v>50</v>
-      </c>
-      <c r="V257" s="3"/>
       <c r="W257" s="2" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="258" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G258" s="6">
+        <v>40</v>
+      </c>
+      <c r="H258" s="6">
         <v>60</v>
       </c>
-      <c r="H258" s="6">
+      <c r="I258" s="6">
         <v>40</v>
       </c>
-      <c r="I258" s="6">
+      <c r="J258" s="6">
+        <v>40</v>
+      </c>
+      <c r="K258" s="6">
+        <v>40</v>
+      </c>
+      <c r="L258" s="6">
+        <v>40</v>
+      </c>
+      <c r="M258" s="6">
         <v>60</v>
       </c>
-      <c r="J258" s="6">
+      <c r="N258" s="6">
+        <v>40</v>
+      </c>
+      <c r="O258" s="6">
+        <v>40</v>
+      </c>
+      <c r="P258" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q258" s="6">
         <v>60</v>
       </c>
-      <c r="K258" s="6">
-        <v>60</v>
-      </c>
-      <c r="L258" s="6">
-        <v>60</v>
-      </c>
-      <c r="M258" s="6">
-        <v>40</v>
-      </c>
-      <c r="N258" s="6">
-        <v>60</v>
-      </c>
-      <c r="O258" s="6">
-        <v>75</v>
-      </c>
-      <c r="P258" s="6">
-        <v>75</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>40</v>
-      </c>
       <c r="R258" s="6">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="S258" s="6">
         <v>50</v>
       </c>
       <c r="T258" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U258" s="6">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B259" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E259" s="3" t="s">
-        <v>28</v>
+        <v>356</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G259" s="4">
-        <v>100</v>
-      </c>
-      <c r="H259" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I259" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J259" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K259" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L259" s="4">
-        <v>106</v>
-      </c>
-      <c r="M259" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N259" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O259" s="4">
-        <v>130</v>
-      </c>
-      <c r="P259" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q259" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R259" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S259" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T259" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U259" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G259" s="6">
+        <v>40</v>
+      </c>
+      <c r="H259" s="6">
+        <v>60</v>
+      </c>
+      <c r="I259" s="6">
+        <v>20</v>
+      </c>
+      <c r="J259" s="6">
+        <v>20</v>
+      </c>
+      <c r="K259" s="6">
+        <v>20</v>
+      </c>
+      <c r="L259" s="6">
+        <v>40</v>
+      </c>
+      <c r="M259" s="6">
+        <v>60</v>
+      </c>
+      <c r="N259" s="6">
+        <v>40</v>
+      </c>
+      <c r="O259" s="6">
+        <v>25</v>
+      </c>
+      <c r="P259" s="6">
+        <v>25</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>20</v>
+      </c>
+      <c r="R259" s="6">
+        <v>17</v>
+      </c>
+      <c r="S259" s="6">
+        <v>0</v>
+      </c>
+      <c r="T259" s="6">
+        <v>17</v>
+      </c>
+      <c r="U259" s="6">
+        <v>0</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="260" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E260" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F260" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G260" s="4">
-        <v>59.5</v>
-      </c>
-      <c r="H260" s="4">
-        <v>57.7</v>
-      </c>
-      <c r="I260" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="J260" s="4">
-        <v>64.3</v>
-      </c>
-      <c r="K260" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="L260" s="4">
-        <v>69.5</v>
-      </c>
-      <c r="M260" s="4">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="N260" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="O260" s="4">
-        <v>91.8</v>
-      </c>
-      <c r="P260" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="Q260" s="4">
-        <v>88.5</v>
-      </c>
-      <c r="R260" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="S260" s="4">
-        <v>119</v>
-      </c>
-      <c r="T260" s="4">
-        <v>136.4</v>
-      </c>
-      <c r="U260" s="4">
-        <v>124.2</v>
+        <v>36</v>
+      </c>
+      <c r="G260" s="6">
+        <v>0</v>
+      </c>
+      <c r="H260" s="6">
+        <v>0</v>
+      </c>
+      <c r="I260" s="6">
+        <v>20</v>
+      </c>
+      <c r="J260" s="6">
+        <v>20</v>
+      </c>
+      <c r="K260" s="6">
+        <v>20</v>
+      </c>
+      <c r="L260" s="6">
+        <v>0</v>
+      </c>
+      <c r="M260" s="6">
+        <v>0</v>
+      </c>
+      <c r="N260" s="6">
+        <v>0</v>
+      </c>
+      <c r="O260" s="6">
+        <v>0</v>
+      </c>
+      <c r="P260" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>40</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>17</v>
+      </c>
+      <c r="T260" s="6">
+        <v>17</v>
+      </c>
+      <c r="U260" s="6">
+        <v>50</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="261" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>28</v>
+        <v>358</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G261" s="4">
-        <v>90.8</v>
-      </c>
-      <c r="H261" s="4">
-        <v>88.8</v>
-      </c>
-      <c r="I261" s="4">
-        <v>86.5</v>
-      </c>
-      <c r="J261" s="4">
-        <v>87</v>
-      </c>
-      <c r="K261" s="4">
-        <v>85</v>
-      </c>
-      <c r="L261" s="4">
-        <v>87.4</v>
-      </c>
-      <c r="M261" s="4">
-        <v>88.7</v>
-      </c>
-      <c r="N261" s="4">
-        <v>84.6</v>
-      </c>
-      <c r="O261" s="4">
-        <v>77.3</v>
-      </c>
-      <c r="P261" s="4">
-        <v>79.7</v>
-      </c>
-      <c r="Q261" s="4">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="R261" s="4">
-        <v>74.8</v>
-      </c>
-      <c r="S261" s="4">
-        <v>77</v>
-      </c>
-      <c r="T261" s="4">
-        <v>77.2</v>
-      </c>
-      <c r="U261" s="4">
-        <v>76.3</v>
+        <v>36</v>
+      </c>
+      <c r="G261" s="6">
+        <v>60</v>
+      </c>
+      <c r="H261" s="6">
+        <v>40</v>
+      </c>
+      <c r="I261" s="6">
+        <v>60</v>
+      </c>
+      <c r="J261" s="6">
+        <v>60</v>
+      </c>
+      <c r="K261" s="6">
+        <v>60</v>
+      </c>
+      <c r="L261" s="6">
+        <v>60</v>
+      </c>
+      <c r="M261" s="6">
+        <v>40</v>
+      </c>
+      <c r="N261" s="6">
+        <v>60</v>
+      </c>
+      <c r="O261" s="6">
+        <v>75</v>
+      </c>
+      <c r="P261" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q261" s="6">
+        <v>40</v>
+      </c>
+      <c r="R261" s="6">
+        <v>33</v>
+      </c>
+      <c r="S261" s="6">
+        <v>50</v>
+      </c>
+      <c r="T261" s="6">
+        <v>17</v>
+      </c>
+      <c r="U261" s="6">
+        <v>25</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="262" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="C262" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>27</v>
@@ -17695,67 +17951,67 @@
         <v>28</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G262" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H262" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I262" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K262" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L262" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M262" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P262" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q262" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R262" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S262" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T262" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U262" s="7">
-        <v>0.192</v>
+        <v>361</v>
+      </c>
+      <c r="G262" s="4">
+        <v>100</v>
+      </c>
+      <c r="H262" s="4">
+        <v>100.8</v>
+      </c>
+      <c r="I262" s="4">
+        <v>99.9</v>
+      </c>
+      <c r="J262" s="4">
+        <v>101.8</v>
+      </c>
+      <c r="K262" s="4">
+        <v>104.9</v>
+      </c>
+      <c r="L262" s="4">
+        <v>106</v>
+      </c>
+      <c r="M262" s="4">
+        <v>119.9</v>
+      </c>
+      <c r="N262" s="4">
+        <v>119.4</v>
+      </c>
+      <c r="O262" s="4">
+        <v>130</v>
+      </c>
+      <c r="P262" s="4">
+        <v>189.5</v>
+      </c>
+      <c r="Q262" s="4">
+        <v>186.6</v>
+      </c>
+      <c r="R262" s="4">
+        <v>190.1</v>
+      </c>
+      <c r="S262" s="4">
+        <v>200.8</v>
+      </c>
+      <c r="T262" s="4">
+        <v>205.6</v>
+      </c>
+      <c r="U262" s="4">
+        <v>208.5</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -17764,52 +18020,52 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>36</v>
+        <v>364</v>
       </c>
       <c r="G263" s="4">
-        <v>30.5</v>
+        <v>59.5</v>
       </c>
       <c r="H263" s="4">
-        <v>30.5</v>
+        <v>57.7</v>
       </c>
       <c r="I263" s="4">
-        <v>30.6</v>
+        <v>58.8</v>
       </c>
       <c r="J263" s="4">
-        <v>30.6</v>
+        <v>64.3</v>
       </c>
       <c r="K263" s="4">
-        <v>30.7</v>
+        <v>68.7</v>
       </c>
       <c r="L263" s="4">
-        <v>30.8</v>
+        <v>69.5</v>
       </c>
       <c r="M263" s="4">
-        <v>30.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N263" s="4">
-        <v>30.9</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O263" s="4">
-        <v>30.9</v>
+        <v>91.8</v>
       </c>
       <c r="P263" s="4">
-        <v>30.9</v>
+        <v>93.9</v>
       </c>
       <c r="Q263" s="4">
-        <v>30.9</v>
+        <v>88.5</v>
       </c>
       <c r="R263" s="4">
-        <v>30.9</v>
+        <v>96.7</v>
       </c>
       <c r="S263" s="4">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="T263" s="4">
-        <v>31</v>
+        <v>136.4</v>
       </c>
       <c r="U263" s="4">
-        <v>31</v>
+        <v>124.2</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
@@ -17818,7 +18074,7 @@
     </row>
     <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>366</v>
@@ -17833,52 +18089,52 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G264" s="6">
-        <v>28</v>
-      </c>
-      <c r="H264" s="6">
-        <v>27</v>
-      </c>
-      <c r="I264" s="6">
-        <v>26</v>
-      </c>
-      <c r="J264" s="6">
-        <v>25</v>
-      </c>
-      <c r="K264" s="6">
-        <v>24</v>
-      </c>
-      <c r="L264" s="6">
-        <v>23</v>
-      </c>
-      <c r="M264" s="6">
-        <v>22</v>
-      </c>
-      <c r="N264" s="6">
-        <v>22</v>
-      </c>
-      <c r="O264" s="6">
-        <v>22</v>
-      </c>
-      <c r="P264" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>19</v>
-      </c>
-      <c r="R264" s="6">
-        <v>17</v>
-      </c>
-      <c r="S264" s="6">
-        <v>16</v>
-      </c>
-      <c r="T264" s="6">
-        <v>16</v>
-      </c>
-      <c r="U264" s="6">
-        <v>15</v>
+        <v>368</v>
+      </c>
+      <c r="G264" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H264" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J264" s="4">
+        <v>87</v>
+      </c>
+      <c r="K264" s="4">
+        <v>85</v>
+      </c>
+      <c r="L264" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M264" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N264" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O264" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P264" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R264" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>77</v>
+      </c>
+      <c r="T264" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U264" s="4">
+        <v>76.3</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
@@ -17887,16 +18143,16 @@
     </row>
     <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>366</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>28</v>
@@ -17904,119 +18160,119 @@
       <c r="F265" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G265" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H265" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I265" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J265" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K265" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L265" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M265" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N265" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O265" s="4">
-        <v>74</v>
-      </c>
-      <c r="P265" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q265" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R265" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S265" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T265" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U265" s="4">
-        <v>76.2</v>
+      <c r="G265" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H265" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I265" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K265" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L265" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M265" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q265" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T265" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U265" s="7">
+        <v>0.192</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>30</v>
+        <v>370</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>366</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G266" s="4">
-        <v>88</v>
+        <v>30.5</v>
       </c>
       <c r="H266" s="4">
-        <v>88.4</v>
+        <v>30.5</v>
       </c>
       <c r="I266" s="4">
-        <v>91.7</v>
+        <v>30.6</v>
       </c>
       <c r="J266" s="4">
-        <v>93.3</v>
+        <v>30.6</v>
       </c>
       <c r="K266" s="4">
-        <v>93.9</v>
+        <v>30.7</v>
       </c>
       <c r="L266" s="4">
-        <v>94.6</v>
+        <v>30.8</v>
       </c>
       <c r="M266" s="4">
-        <v>94.8</v>
+        <v>30.8</v>
       </c>
       <c r="N266" s="4">
-        <v>94.5</v>
+        <v>30.9</v>
       </c>
       <c r="O266" s="4">
-        <v>94.6</v>
+        <v>30.9</v>
       </c>
       <c r="P266" s="4">
-        <v>94.8</v>
+        <v>30.9</v>
       </c>
       <c r="Q266" s="4">
-        <v>94.7</v>
+        <v>30.9</v>
       </c>
       <c r="R266" s="4">
-        <v>94.6</v>
+        <v>30.9</v>
       </c>
       <c r="S266" s="4">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="T266" s="4">
-        <v>94.8</v>
+        <v>31</v>
       </c>
       <c r="U266" s="4">
-        <v>94.6</v>
+        <v>31</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
@@ -18025,85 +18281,85 @@
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G267" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H267" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I267" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J267" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K267" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L267" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M267" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N267" s="4">
-        <v>42</v>
-      </c>
-      <c r="O267" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P267" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q267" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R267" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S267" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T267" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U267" s="4">
-        <v>49.3</v>
+        <v>100</v>
+      </c>
+      <c r="G267" s="6">
+        <v>28</v>
+      </c>
+      <c r="H267" s="6">
+        <v>27</v>
+      </c>
+      <c r="I267" s="6">
+        <v>26</v>
+      </c>
+      <c r="J267" s="6">
+        <v>25</v>
+      </c>
+      <c r="K267" s="6">
+        <v>24</v>
+      </c>
+      <c r="L267" s="6">
+        <v>23</v>
+      </c>
+      <c r="M267" s="6">
+        <v>22</v>
+      </c>
+      <c r="N267" s="6">
+        <v>22</v>
+      </c>
+      <c r="O267" s="6">
+        <v>22</v>
+      </c>
+      <c r="P267" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q267" s="6">
+        <v>19</v>
+      </c>
+      <c r="R267" s="6">
+        <v>17</v>
+      </c>
+      <c r="S267" s="6">
+        <v>16</v>
+      </c>
+      <c r="T267" s="6">
+        <v>16</v>
+      </c>
+      <c r="U267" s="6">
+        <v>15</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
@@ -18112,202 +18368,202 @@
         <v>36</v>
       </c>
       <c r="G268" s="4">
+        <v>64.7</v>
+      </c>
+      <c r="H268" s="4">
         <v>65.7</v>
       </c>
-      <c r="H268" s="4">
-        <v>64.8</v>
-      </c>
       <c r="I268" s="4">
-        <v>67.400000000000006</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J268" s="4">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K268" s="4">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="L268" s="4">
-        <v>70.900000000000006</v>
+        <v>72.7</v>
       </c>
       <c r="M268" s="4">
-        <v>71.400000000000006</v>
+        <v>73.5</v>
       </c>
       <c r="N268" s="4">
-        <v>72.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="P268" s="4">
-        <v>73.900000000000006</v>
+        <v>74.5</v>
       </c>
       <c r="Q268" s="4">
-        <v>73.3</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R268" s="4">
-        <v>72.8</v>
+        <v>75.2</v>
       </c>
       <c r="S268" s="4">
-        <v>76.3</v>
+        <v>75.7</v>
       </c>
       <c r="T268" s="4">
-        <v>78.099999999999994</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U268" s="4">
-        <v>78.599999999999994</v>
+        <v>76.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G269" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H269" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I269" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J269" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K269" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L269" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M269" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N269" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O269" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P269" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q269" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R269" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S269" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T269" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U269" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G269" s="4">
+        <v>88</v>
+      </c>
+      <c r="H269" s="4">
+        <v>88.4</v>
+      </c>
+      <c r="I269" s="4">
+        <v>91.7</v>
+      </c>
+      <c r="J269" s="4">
+        <v>93.3</v>
+      </c>
+      <c r="K269" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="L269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="M269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="N269" s="4">
+        <v>94.5</v>
+      </c>
+      <c r="O269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="P269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="Q269" s="4">
+        <v>94.7</v>
+      </c>
+      <c r="R269" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="S269" s="4">
+        <v>95</v>
+      </c>
+      <c r="T269" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="U269" s="4">
+        <v>94.6</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G270" s="4">
-        <v>2.9</v>
+        <v>28.5</v>
       </c>
       <c r="H270" s="4">
-        <v>3.8</v>
+        <v>30.6</v>
       </c>
       <c r="I270" s="4">
-        <v>6</v>
+        <v>33.1</v>
       </c>
       <c r="J270" s="4">
-        <v>4.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K270" s="4">
-        <v>4.5999999999999996</v>
+        <v>37.4</v>
       </c>
       <c r="L270" s="4">
-        <v>4.2</v>
+        <v>39.6</v>
       </c>
       <c r="M270" s="4">
-        <v>3.1</v>
+        <v>41.2</v>
       </c>
       <c r="N270" s="4">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="O270" s="4">
-        <v>3.2</v>
+        <v>42.9</v>
       </c>
       <c r="P270" s="4">
-        <v>3.4</v>
+        <v>44</v>
       </c>
       <c r="Q270" s="4">
-        <v>3.2</v>
+        <v>45.4</v>
       </c>
       <c r="R270" s="4">
-        <v>4.5</v>
+        <v>46.5</v>
       </c>
       <c r="S270" s="4">
-        <v>6.6</v>
+        <v>47.2</v>
       </c>
       <c r="T270" s="4">
-        <v>5.8</v>
+        <v>48.2</v>
       </c>
       <c r="U270" s="4">
-        <v>4.5</v>
+        <v>49.3</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B271" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>27</v>
@@ -18318,67 +18574,65 @@
       <c r="F271" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G271" s="6">
-        <v>70</v>
-      </c>
-      <c r="H271" s="6">
-        <v>75</v>
-      </c>
-      <c r="I271" s="6">
-        <v>66</v>
-      </c>
-      <c r="J271" s="6">
-        <v>64</v>
-      </c>
-      <c r="K271" s="6">
-        <v>70</v>
-      </c>
-      <c r="L271" s="6">
-        <v>66</v>
-      </c>
-      <c r="M271" s="6">
-        <v>80</v>
-      </c>
-      <c r="N271" s="6">
-        <v>89</v>
-      </c>
-      <c r="O271" s="6">
-        <v>86</v>
-      </c>
-      <c r="P271" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q271" s="6">
-        <v>85</v>
-      </c>
-      <c r="R271" s="6">
-        <v>82</v>
-      </c>
-      <c r="S271" s="6">
-        <v>83</v>
-      </c>
-      <c r="T271" s="6">
-        <v>88</v>
-      </c>
-      <c r="U271" s="6">
-        <v>88</v>
-      </c>
-      <c r="V271" s="6">
-        <v>86</v>
-      </c>
+      <c r="G271" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H271" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I271" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J271" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K271" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L271" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M271" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N271" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O271" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P271" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q271" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R271" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S271" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T271" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U271" s="4">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18387,53 +18641,67 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>36</v>
+        <v>378</v>
       </c>
       <c r="G272" s="6">
-        <v>55</v>
-      </c>
-      <c r="H272" s="3"/>
+        <v>70108</v>
+      </c>
+      <c r="H272" s="6">
+        <v>248240</v>
+      </c>
       <c r="I272" s="6">
-        <v>58</v>
-      </c>
-      <c r="J272" s="3"/>
+        <v>168221</v>
+      </c>
+      <c r="J272" s="6">
+        <v>72837</v>
+      </c>
       <c r="K272" s="6">
-        <v>60</v>
-      </c>
-      <c r="L272" s="3"/>
+        <v>64283</v>
+      </c>
+      <c r="L272" s="6">
+        <v>68694</v>
+      </c>
       <c r="M272" s="6">
-        <v>64</v>
-      </c>
-      <c r="N272" s="3"/>
+        <v>60135</v>
+      </c>
+      <c r="N272" s="6">
+        <v>46337</v>
+      </c>
       <c r="O272" s="6">
-        <v>65</v>
-      </c>
-      <c r="P272" s="3"/>
+        <v>50289</v>
+      </c>
+      <c r="P272" s="6">
+        <v>104107</v>
+      </c>
       <c r="Q272" s="6">
-        <v>74</v>
-      </c>
-      <c r="R272" s="3"/>
+        <v>201963</v>
+      </c>
+      <c r="R272" s="6">
+        <v>84506</v>
+      </c>
       <c r="S272" s="6">
-        <v>63</v>
-      </c>
-      <c r="T272" s="3"/>
+        <v>295948</v>
+      </c>
+      <c r="T272" s="6">
+        <v>123796</v>
+      </c>
       <c r="U272" s="6">
-        <v>71</v>
+        <v>104040</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18442,67 +18710,67 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G273" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H273" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I273" s="5">
-        <v>1</v>
-      </c>
-      <c r="J273" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K273" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L273" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M273" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N273" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O273" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P273" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q273" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R273" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S273" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T273" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U273" s="5">
-        <v>0.69</v>
+        <v>36</v>
+      </c>
+      <c r="G273" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H273" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I273" s="4">
+        <v>6</v>
+      </c>
+      <c r="J273" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K273" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L273" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M273" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N273" s="4">
+        <v>3</v>
+      </c>
+      <c r="O273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P273" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R273" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S273" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T273" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U273" s="4">
+        <v>4.5</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>202</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -18511,70 +18779,72 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G274" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H274" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I274" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J274" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K274" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M274" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N274" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O274" s="5">
-        <v>2</v>
-      </c>
-      <c r="P274" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R274" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S274" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T274" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U274" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="V274" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G274" s="6">
+        <v>70</v>
+      </c>
+      <c r="H274" s="6">
+        <v>75</v>
+      </c>
+      <c r="I274" s="6">
+        <v>66</v>
+      </c>
+      <c r="J274" s="6">
+        <v>64</v>
+      </c>
+      <c r="K274" s="6">
+        <v>70</v>
+      </c>
+      <c r="L274" s="6">
+        <v>66</v>
+      </c>
+      <c r="M274" s="6">
+        <v>80</v>
+      </c>
+      <c r="N274" s="6">
+        <v>89</v>
+      </c>
+      <c r="O274" s="6">
+        <v>86</v>
+      </c>
+      <c r="P274" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>85</v>
+      </c>
+      <c r="R274" s="6">
+        <v>82</v>
+      </c>
+      <c r="S274" s="6">
+        <v>83</v>
+      </c>
+      <c r="T274" s="6">
+        <v>88</v>
+      </c>
+      <c r="U274" s="6">
+        <v>88</v>
+      </c>
+      <c r="V274" s="6">
+        <v>86</v>
+      </c>
       <c r="W274" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>28</v>
@@ -18583,52 +18853,44 @@
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>10</v>
-      </c>
-      <c r="H275" s="6">
-        <v>9</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H275" s="3"/>
       <c r="I275" s="6">
-        <v>11</v>
-      </c>
-      <c r="J275" s="6">
-        <v>11</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="J275" s="3"/>
       <c r="K275" s="6">
-        <v>15</v>
-      </c>
-      <c r="L275" s="6">
-        <v>16</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="L275" s="3"/>
       <c r="M275" s="6">
-        <v>19</v>
-      </c>
-      <c r="N275" s="6">
-        <v>21</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="N275" s="3"/>
       <c r="O275" s="6">
-        <v>25</v>
-      </c>
-      <c r="P275" s="6">
-        <v>31</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="P275" s="3"/>
       <c r="Q275" s="6">
-        <v>34</v>
-      </c>
-      <c r="R275" s="6">
-        <v>40</v>
-      </c>
-      <c r="S275" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="R275" s="3"/>
+      <c r="S275" s="6">
+        <v>63</v>
+      </c>
       <c r="T275" s="3"/>
-      <c r="U275" s="3"/>
+      <c r="U275" s="6">
+        <v>71</v>
+      </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>30</v>
+        <v>383</v>
       </c>
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>385</v>
@@ -18637,175 +18899,187 @@
         <v>386</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G276" s="6">
-        <v>10</v>
-      </c>
-      <c r="H276" s="6">
-        <v>9</v>
-      </c>
-      <c r="I276" s="6">
-        <v>11</v>
-      </c>
-      <c r="J276" s="6">
-        <v>12</v>
-      </c>
-      <c r="K276" s="6">
-        <v>14</v>
-      </c>
-      <c r="L276" s="6">
-        <v>15</v>
-      </c>
-      <c r="M276" s="6">
-        <v>19</v>
-      </c>
-      <c r="N276" s="6">
-        <v>21</v>
-      </c>
-      <c r="O276" s="6">
-        <v>24</v>
-      </c>
-      <c r="P276" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q276" s="6">
-        <v>32</v>
-      </c>
-      <c r="R276" s="6">
-        <v>39</v>
-      </c>
-      <c r="S276" s="3"/>
-      <c r="T276" s="3"/>
-      <c r="U276" s="3"/>
+        <v>387</v>
+      </c>
+      <c r="G276" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H276" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I276" s="5">
+        <v>1</v>
+      </c>
+      <c r="J276" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K276" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L276" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M276" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N276" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O276" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P276" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q276" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R276" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S276" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T276" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U276" s="5">
+        <v>0.69</v>
+      </c>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>30</v>
+        <v>202</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G277" s="6">
-        <v>10</v>
-      </c>
-      <c r="H277" s="6">
-        <v>9</v>
-      </c>
-      <c r="I277" s="6">
-        <v>10</v>
-      </c>
-      <c r="J277" s="6">
-        <v>11</v>
-      </c>
-      <c r="K277" s="6">
-        <v>15</v>
-      </c>
-      <c r="L277" s="6">
-        <v>16</v>
-      </c>
-      <c r="M277" s="6">
-        <v>19</v>
-      </c>
-      <c r="N277" s="6">
-        <v>21</v>
-      </c>
-      <c r="O277" s="6">
-        <v>26</v>
-      </c>
-      <c r="P277" s="6">
-        <v>32</v>
-      </c>
-      <c r="Q277" s="6">
-        <v>35</v>
-      </c>
-      <c r="R277" s="6">
-        <v>41</v>
-      </c>
-      <c r="S277" s="3"/>
-      <c r="T277" s="3"/>
-      <c r="U277" s="3"/>
+        <v>287</v>
+      </c>
+      <c r="G277" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H277" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I277" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J277" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K277" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M277" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N277" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O277" s="5">
+        <v>2</v>
+      </c>
+      <c r="P277" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R277" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S277" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T277" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U277" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>30</v>
+        <v>390</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G278" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H278" s="6">
+        <v>9</v>
+      </c>
+      <c r="I278" s="6">
         <v>11</v>
       </c>
-      <c r="I278" s="6">
-        <v>13</v>
-      </c>
       <c r="J278" s="6">
+        <v>11</v>
+      </c>
+      <c r="K278" s="6">
         <v>15</v>
       </c>
-      <c r="K278" s="6">
-        <v>18</v>
-      </c>
       <c r="L278" s="6">
+        <v>16</v>
+      </c>
+      <c r="M278" s="6">
         <v>19</v>
       </c>
-      <c r="M278" s="6">
-        <v>23</v>
-      </c>
       <c r="N278" s="6">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O278" s="6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P278" s="6">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q278" s="6">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R278" s="6">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="S278" s="3"/>
       <c r="T278" s="3"/>
@@ -18817,58 +19091,58 @@
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G279" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H279" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I279" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J279" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K279" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L279" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M279" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N279" s="6">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O279" s="6">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P279" s="6">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="Q279" s="6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R279" s="6">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -18880,19 +19154,19 @@
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>387</v>
+        <v>64</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
@@ -18901,37 +19175,37 @@
         <v>10</v>
       </c>
       <c r="H280" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I280" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J280" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K280" s="6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L280" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M280" s="6">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N280" s="6">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="O280" s="6">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="P280" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q280" s="6">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="R280" s="6">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -18943,58 +19217,58 @@
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>388</v>
+        <v>38</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
+        <v>12</v>
+      </c>
+      <c r="H281" s="6">
+        <v>11</v>
+      </c>
+      <c r="I281" s="6">
+        <v>13</v>
+      </c>
+      <c r="J281" s="6">
+        <v>15</v>
+      </c>
+      <c r="K281" s="6">
         <v>18</v>
       </c>
-      <c r="H281" s="6">
-        <v>16</v>
-      </c>
-      <c r="I281" s="6">
+      <c r="L281" s="6">
         <v>19</v>
       </c>
-      <c r="J281" s="6">
-        <v>20</v>
-      </c>
-      <c r="K281" s="6">
-        <v>28</v>
-      </c>
-      <c r="L281" s="6">
-        <v>28</v>
-      </c>
       <c r="M281" s="6">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N281" s="6">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="O281" s="6">
+        <v>30</v>
+      </c>
+      <c r="P281" s="6">
+        <v>37</v>
+      </c>
+      <c r="Q281" s="6">
         <v>39</v>
       </c>
-      <c r="P281" s="6">
-        <v>47</v>
-      </c>
-      <c r="Q281" s="6">
-        <v>53</v>
-      </c>
       <c r="R281" s="6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -19006,58 +19280,58 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>389</v>
+        <v>39</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
+        <v>6</v>
+      </c>
+      <c r="H282" s="6">
+        <v>5</v>
+      </c>
+      <c r="I282" s="6">
+        <v>6</v>
+      </c>
+      <c r="J282" s="6">
+        <v>6</v>
+      </c>
+      <c r="K282" s="6">
+        <v>9</v>
+      </c>
+      <c r="L282" s="6">
+        <v>10</v>
+      </c>
+      <c r="M282" s="6">
+        <v>12</v>
+      </c>
+      <c r="N282" s="6">
         <v>13</v>
       </c>
-      <c r="H282" s="6">
-        <v>13</v>
-      </c>
-      <c r="I282" s="6">
-        <v>16</v>
-      </c>
-      <c r="J282" s="6">
-        <v>19</v>
-      </c>
-      <c r="K282" s="6">
-        <v>24</v>
-      </c>
-      <c r="L282" s="6">
+      <c r="O282" s="6">
+        <v>17</v>
+      </c>
+      <c r="P282" s="6">
+        <v>23</v>
+      </c>
+      <c r="Q282" s="6">
         <v>25</v>
       </c>
-      <c r="M282" s="6">
-        <v>27</v>
-      </c>
-      <c r="N282" s="6">
-        <v>33</v>
-      </c>
-      <c r="O282" s="6">
-        <v>36</v>
-      </c>
-      <c r="P282" s="6">
-        <v>46</v>
-      </c>
-      <c r="Q282" s="6">
-        <v>48</v>
-      </c>
       <c r="R282" s="6">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19069,58 +19343,58 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
+        <v>10</v>
+      </c>
+      <c r="H283" s="6">
+        <v>6</v>
+      </c>
+      <c r="I283" s="6">
+        <v>8</v>
+      </c>
+      <c r="J283" s="6">
         <v>9</v>
       </c>
-      <c r="H283" s="6">
+      <c r="K283" s="6">
         <v>9</v>
       </c>
-      <c r="I283" s="6">
+      <c r="L283" s="6">
+        <v>8</v>
+      </c>
+      <c r="M283" s="6">
+        <v>9</v>
+      </c>
+      <c r="N283" s="6">
         <v>11</v>
       </c>
-      <c r="J283" s="6">
-        <v>12</v>
-      </c>
-      <c r="K283" s="6">
-        <v>15</v>
-      </c>
-      <c r="L283" s="6">
-        <v>15</v>
-      </c>
-      <c r="M283" s="6">
-        <v>18</v>
-      </c>
-      <c r="N283" s="6">
-        <v>19</v>
-      </c>
       <c r="O283" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="P283" s="6">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q283" s="6">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R283" s="6">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19132,58 +19406,58 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H284" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I284" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J284" s="6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K284" s="6">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="L284" s="6">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M284" s="6">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="N284" s="6">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O284" s="6">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="P284" s="6">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="Q284" s="6">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="R284" s="6">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19195,58 +19469,58 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H285" s="6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I285" s="6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J285" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K285" s="6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L285" s="6">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="M285" s="6">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N285" s="6">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="O285" s="6">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="P285" s="6">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="Q285" s="6">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="R285" s="6">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19258,58 +19532,58 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>132</v>
+        <v>396</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H286" s="6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I286" s="6">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J286" s="6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K286" s="6">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="L286" s="6">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="M286" s="6">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="N286" s="6">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="O286" s="6">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="P286" s="6">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="Q286" s="6">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="R286" s="6">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19321,37 +19595,37 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>143</v>
+        <v>397</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
+        <v>4</v>
+      </c>
+      <c r="H287" s="6">
+        <v>5</v>
+      </c>
+      <c r="I287" s="6">
+        <v>6</v>
+      </c>
+      <c r="J287" s="6">
+        <v>6</v>
+      </c>
+      <c r="K287" s="6">
         <v>7</v>
-      </c>
-      <c r="H287" s="6">
-        <v>6</v>
-      </c>
-      <c r="I287" s="6">
-        <v>8</v>
-      </c>
-      <c r="J287" s="6">
-        <v>8</v>
-      </c>
-      <c r="K287" s="6">
-        <v>10</v>
       </c>
       <c r="L287" s="6">
         <v>10</v>
@@ -19360,16 +19634,16 @@
         <v>12</v>
       </c>
       <c r="N287" s="6">
+        <v>12</v>
+      </c>
+      <c r="O287" s="6">
         <v>14</v>
       </c>
-      <c r="O287" s="6">
-        <v>17</v>
-      </c>
       <c r="P287" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q287" s="6">
         <v>23</v>
-      </c>
-      <c r="Q287" s="6">
-        <v>25</v>
       </c>
       <c r="R287" s="6">
         <v>29</v>
@@ -19384,19 +19658,19 @@
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>142</v>
+        <v>398</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
@@ -19405,37 +19679,37 @@
         <v>2</v>
       </c>
       <c r="H288" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I288" s="6">
         <v>2</v>
       </c>
       <c r="J288" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K288" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L288" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M288" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N288" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O288" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P288" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q288" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R288" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
@@ -19447,58 +19721,58 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G289" s="6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H289" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I289" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J289" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K289" s="6">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L289" s="6">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M289" s="6">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="N289" s="6">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="O289" s="6">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="P289" s="6">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="Q289" s="6">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="R289" s="6">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
@@ -19510,58 +19784,58 @@
     </row>
     <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G290" s="6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H290" s="6">
+        <v>6</v>
+      </c>
+      <c r="I290" s="6">
+        <v>8</v>
+      </c>
+      <c r="J290" s="6">
+        <v>8</v>
+      </c>
+      <c r="K290" s="6">
+        <v>10</v>
+      </c>
+      <c r="L290" s="6">
+        <v>10</v>
+      </c>
+      <c r="M290" s="6">
+        <v>12</v>
+      </c>
+      <c r="N290" s="6">
         <v>14</v>
       </c>
-      <c r="I290" s="6">
-        <v>16</v>
-      </c>
-      <c r="J290" s="6">
-        <v>18</v>
-      </c>
-      <c r="K290" s="6">
+      <c r="O290" s="6">
+        <v>17</v>
+      </c>
+      <c r="P290" s="6">
         <v>23</v>
       </c>
-      <c r="L290" s="6">
+      <c r="Q290" s="6">
         <v>25</v>
       </c>
-      <c r="M290" s="6">
-        <v>27</v>
-      </c>
-      <c r="N290" s="6">
-        <v>30</v>
-      </c>
-      <c r="O290" s="6">
-        <v>35</v>
-      </c>
-      <c r="P290" s="6">
-        <v>44</v>
-      </c>
-      <c r="Q290" s="6">
-        <v>46</v>
-      </c>
       <c r="R290" s="6">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
@@ -19573,58 +19847,58 @@
     </row>
     <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G291" s="6">
+        <v>2</v>
+      </c>
+      <c r="H291" s="6">
+        <v>1</v>
+      </c>
+      <c r="I291" s="6">
+        <v>2</v>
+      </c>
+      <c r="J291" s="6">
+        <v>1</v>
+      </c>
+      <c r="K291" s="6">
+        <v>1</v>
+      </c>
+      <c r="L291" s="6">
+        <v>2</v>
+      </c>
+      <c r="M291" s="6">
+        <v>2</v>
+      </c>
+      <c r="N291" s="6">
+        <v>2</v>
+      </c>
+      <c r="O291" s="6">
+        <v>4</v>
+      </c>
+      <c r="P291" s="6">
+        <v>5</v>
+      </c>
+      <c r="Q291" s="6">
+        <v>5</v>
+      </c>
+      <c r="R291" s="6">
         <v>8</v>
-      </c>
-      <c r="H291" s="6">
-        <v>5</v>
-      </c>
-      <c r="I291" s="6">
-        <v>6</v>
-      </c>
-      <c r="J291" s="6">
-        <v>7</v>
-      </c>
-      <c r="K291" s="6">
-        <v>7</v>
-      </c>
-      <c r="L291" s="6">
-        <v>7</v>
-      </c>
-      <c r="M291" s="6">
-        <v>7</v>
-      </c>
-      <c r="N291" s="6">
-        <v>11</v>
-      </c>
-      <c r="O291" s="6">
-        <v>10</v>
-      </c>
-      <c r="P291" s="6">
-        <v>17</v>
-      </c>
-      <c r="Q291" s="6">
-        <v>25</v>
-      </c>
-      <c r="R291" s="6">
-        <v>22</v>
       </c>
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
@@ -19636,58 +19910,58 @@
     </row>
     <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>144</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G292" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H292" s="6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I292" s="6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J292" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K292" s="6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L292" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="M292" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="N292" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O292" s="6">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="P292" s="6">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="Q292" s="6">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="R292" s="6">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
@@ -19699,222 +19973,202 @@
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G293" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H293" s="4">
+      <c r="G293" s="6">
+        <v>15</v>
+      </c>
+      <c r="H293" s="6">
+        <v>14</v>
+      </c>
+      <c r="I293" s="6">
+        <v>16</v>
+      </c>
+      <c r="J293" s="6">
+        <v>18</v>
+      </c>
+      <c r="K293" s="6">
+        <v>23</v>
+      </c>
+      <c r="L293" s="6">
+        <v>25</v>
+      </c>
+      <c r="M293" s="6">
+        <v>27</v>
+      </c>
+      <c r="N293" s="6">
+        <v>30</v>
+      </c>
+      <c r="O293" s="6">
+        <v>35</v>
+      </c>
+      <c r="P293" s="6">
+        <v>44</v>
+      </c>
+      <c r="Q293" s="6">
+        <v>46</v>
+      </c>
+      <c r="R293" s="6">
+        <v>54</v>
+      </c>
+      <c r="S293" s="3"/>
+      <c r="T293" s="3"/>
+      <c r="U293" s="3"/>
+      <c r="V293" s="3"/>
+      <c r="W293" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G294" s="6">
+        <v>8</v>
+      </c>
+      <c r="H294" s="6">
+        <v>5</v>
+      </c>
+      <c r="I294" s="6">
         <v>6</v>
       </c>
-      <c r="I293" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K293" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L293" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M293" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O293" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q293" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R293" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T293" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U293" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V293" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="W293" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="G294" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H294" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I294" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J294" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K294" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L294" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M294" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N294" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O294" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P294" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q294" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R294" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S294" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T294" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U294" s="5">
-        <v>1840.15</v>
-      </c>
+      <c r="J294" s="6">
+        <v>7</v>
+      </c>
+      <c r="K294" s="6">
+        <v>7</v>
+      </c>
+      <c r="L294" s="6">
+        <v>7</v>
+      </c>
+      <c r="M294" s="6">
+        <v>7</v>
+      </c>
+      <c r="N294" s="6">
+        <v>11</v>
+      </c>
+      <c r="O294" s="6">
+        <v>10</v>
+      </c>
+      <c r="P294" s="6">
+        <v>17</v>
+      </c>
+      <c r="Q294" s="6">
+        <v>25</v>
+      </c>
+      <c r="R294" s="6">
+        <v>22</v>
+      </c>
+      <c r="S294" s="3"/>
+      <c r="T294" s="3"/>
+      <c r="U294" s="3"/>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="G295" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H295" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I295" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J295" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K295" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L295" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M295" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N295" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O295" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P295" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q295" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R295" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S295" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T295" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U295" s="5">
-        <v>705.25</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G295" s="6">
+        <v>4</v>
+      </c>
+      <c r="H295" s="6">
+        <v>3</v>
+      </c>
+      <c r="I295" s="6">
+        <v>5</v>
+      </c>
+      <c r="J295" s="6">
+        <v>4</v>
+      </c>
+      <c r="K295" s="6">
+        <v>5</v>
+      </c>
+      <c r="L295" s="6">
+        <v>5</v>
+      </c>
+      <c r="M295" s="6">
+        <v>7</v>
+      </c>
+      <c r="N295" s="6">
+        <v>8</v>
+      </c>
+      <c r="O295" s="6">
+        <v>9</v>
+      </c>
+      <c r="P295" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q295" s="6">
+        <v>14</v>
+      </c>
+      <c r="R295" s="6">
+        <v>17</v>
+      </c>
+      <c r="S295" s="3"/>
+      <c r="T295" s="3"/>
+      <c r="U295" s="3"/>
       <c r="V295" s="3"/>
       <c r="W295" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="296" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="C296" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -19925,65 +20179,67 @@
       <c r="F296" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G296" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H296" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I296" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J296" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K296" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L296" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M296" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N296" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R296" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S296" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T296" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U296" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V296" s="3"/>
+      <c r="G296" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H296" s="4">
+        <v>6</v>
+      </c>
+      <c r="I296" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K296" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L296" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M296" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O296" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R296" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T296" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U296" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V296" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -19992,63 +20248,67 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G297" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H297" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I297" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J297" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K297" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L297" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M297" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N297" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O297" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P297" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q297" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R297" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S297" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T297" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U297" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V297" s="3"/>
+      <c r="W297" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K297" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L297" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M297" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N297" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O297" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P297" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q297" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R297" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S297" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T297" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U297" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V297" s="7">
-        <v>5.3920000000000003</v>
-      </c>
-      <c r="W297" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A298" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B298" s="2" t="s">
+      <c r="C298" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20057,61 +20317,67 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="G298" s="3"/>
-      <c r="H298" s="3"/>
-      <c r="I298" s="3"/>
+        <v>404</v>
+      </c>
+      <c r="G298" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H298" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I298" s="5">
+        <v>111.55</v>
+      </c>
       <c r="J298" s="5">
-        <v>8.07</v>
+        <v>127.11</v>
       </c>
       <c r="K298" s="5">
-        <v>3.54</v>
+        <v>82.28</v>
       </c>
       <c r="L298" s="5">
-        <v>2.98</v>
+        <v>100.19</v>
       </c>
       <c r="M298" s="5">
-        <v>2.44</v>
+        <v>148.99</v>
       </c>
       <c r="N298" s="5">
-        <v>2.25</v>
+        <v>222.11</v>
       </c>
       <c r="O298" s="5">
-        <v>63.36</v>
+        <v>244.93</v>
       </c>
       <c r="P298" s="5">
-        <v>7.61</v>
+        <v>223.31</v>
       </c>
       <c r="Q298" s="5">
-        <v>6.64</v>
+        <v>225.08</v>
       </c>
       <c r="R298" s="5">
-        <v>3.65</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S298" s="5">
-        <v>9.59</v>
+        <v>2661.32</v>
       </c>
       <c r="T298" s="5">
-        <v>4.2699999999999996</v>
+        <v>1701.94</v>
       </c>
       <c r="U298" s="5">
-        <v>8.32</v>
+        <v>705.25</v>
       </c>
       <c r="V298" s="3"/>
       <c r="W298" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>27</v>
@@ -20120,55 +20386,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G299" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H299" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I299" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J299" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K299" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L299" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M299" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N299" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q299" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R299" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S299" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T299" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U299" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V299" s="3"/>
+      <c r="W299" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C300" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="3"/>
-      <c r="K299" s="6">
-        <v>1</v>
-      </c>
-      <c r="L299" s="6">
-        <v>1</v>
-      </c>
-      <c r="M299" s="6">
-        <v>8</v>
-      </c>
-      <c r="N299" s="6">
-        <v>2</v>
-      </c>
-      <c r="O299" s="3"/>
-      <c r="P299" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q299" s="6">
-        <v>2</v>
-      </c>
-      <c r="R299" s="3"/>
-      <c r="S299" s="3"/>
-      <c r="T299" s="6">
-        <v>8</v>
-      </c>
-      <c r="U299" s="6">
-        <v>7</v>
-      </c>
-      <c r="V299" s="6">
-        <v>2</v>
-      </c>
-      <c r="W299" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20177,65 +20455,63 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="3"/>
-      <c r="I300" s="6">
-        <v>2</v>
-      </c>
-      <c r="J300" s="6">
-        <v>2</v>
-      </c>
-      <c r="K300" s="6">
-        <v>1</v>
-      </c>
-      <c r="L300" s="6">
-        <v>1</v>
-      </c>
-      <c r="M300" s="6">
-        <v>1</v>
-      </c>
-      <c r="N300" s="6">
-        <v>1</v>
-      </c>
-      <c r="O300" s="6">
-        <v>1</v>
-      </c>
-      <c r="P300" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q300" s="6">
-        <v>4</v>
-      </c>
-      <c r="R300" s="6">
-        <v>1</v>
-      </c>
-      <c r="S300" s="6">
-        <v>1</v>
-      </c>
-      <c r="T300" s="6">
-        <v>0</v>
-      </c>
-      <c r="U300" s="6">
-        <v>4</v>
-      </c>
-      <c r="V300" s="6">
-        <v>2</v>
+      <c r="I300" s="3"/>
+      <c r="J300" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K300" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L300" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M300" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N300" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O300" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P300" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q300" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R300" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S300" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T300" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U300" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V300" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W300" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>27</v>
@@ -20244,61 +20520,61 @@
         <v>28</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>32</v>
+        <v>404</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="6">
-        <v>5</v>
-      </c>
-      <c r="L301" s="6">
-        <v>13</v>
-      </c>
-      <c r="M301" s="6">
-        <v>19</v>
-      </c>
-      <c r="N301" s="6">
-        <v>18</v>
-      </c>
-      <c r="O301" s="6">
-        <v>15</v>
-      </c>
-      <c r="P301" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q301" s="6">
-        <v>8</v>
-      </c>
-      <c r="R301" s="6">
-        <v>28</v>
-      </c>
-      <c r="S301" s="6">
-        <v>53</v>
-      </c>
-      <c r="T301" s="6">
-        <v>65</v>
-      </c>
-      <c r="U301" s="6">
-        <v>70</v>
-      </c>
-      <c r="V301" s="6">
-        <v>69</v>
-      </c>
+      <c r="J301" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K301" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L301" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M301" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N301" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O301" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P301" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q301" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R301" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S301" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T301" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U301" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V301" s="3"/>
       <c r="W301" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>27</v>
@@ -20307,47 +20583,234 @@
         <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
       <c r="J302" s="3"/>
-      <c r="K302" s="3"/>
-      <c r="L302" s="3"/>
-      <c r="M302" s="3"/>
-      <c r="N302" s="3"/>
+      <c r="K302" s="6">
+        <v>1</v>
+      </c>
+      <c r="L302" s="6">
+        <v>1</v>
+      </c>
+      <c r="M302" s="6">
+        <v>8</v>
+      </c>
+      <c r="N302" s="6">
+        <v>2</v>
+      </c>
       <c r="O302" s="3"/>
-      <c r="P302" s="3"/>
-      <c r="Q302" s="3"/>
+      <c r="P302" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q302" s="6">
+        <v>2</v>
+      </c>
       <c r="R302" s="3"/>
       <c r="S302" s="3"/>
       <c r="T302" s="6">
+        <v>8</v>
+      </c>
+      <c r="U302" s="6">
+        <v>7</v>
+      </c>
+      <c r="V302" s="6">
+        <v>2</v>
+      </c>
+      <c r="W302" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G303" s="3"/>
+      <c r="H303" s="3"/>
+      <c r="I303" s="6">
+        <v>2</v>
+      </c>
+      <c r="J303" s="6">
+        <v>2</v>
+      </c>
+      <c r="K303" s="6">
+        <v>1</v>
+      </c>
+      <c r="L303" s="6">
+        <v>1</v>
+      </c>
+      <c r="M303" s="6">
+        <v>1</v>
+      </c>
+      <c r="N303" s="6">
+        <v>1</v>
+      </c>
+      <c r="O303" s="6">
+        <v>1</v>
+      </c>
+      <c r="P303" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q303" s="6">
+        <v>4</v>
+      </c>
+      <c r="R303" s="6">
+        <v>1</v>
+      </c>
+      <c r="S303" s="6">
+        <v>1</v>
+      </c>
+      <c r="T303" s="6">
+        <v>0</v>
+      </c>
+      <c r="U303" s="6">
+        <v>4</v>
+      </c>
+      <c r="V303" s="6">
+        <v>2</v>
+      </c>
+      <c r="W303" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="6">
+        <v>5</v>
+      </c>
+      <c r="L304" s="6">
+        <v>13</v>
+      </c>
+      <c r="M304" s="6">
+        <v>19</v>
+      </c>
+      <c r="N304" s="6">
+        <v>18</v>
+      </c>
+      <c r="O304" s="6">
+        <v>15</v>
+      </c>
+      <c r="P304" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q304" s="6">
+        <v>8</v>
+      </c>
+      <c r="R304" s="6">
+        <v>28</v>
+      </c>
+      <c r="S304" s="6">
+        <v>53</v>
+      </c>
+      <c r="T304" s="6">
+        <v>65</v>
+      </c>
+      <c r="U304" s="6">
+        <v>70</v>
+      </c>
+      <c r="V304" s="6">
+        <v>69</v>
+      </c>
+      <c r="W304" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="3"/>
+      <c r="J305" s="3"/>
+      <c r="K305" s="3"/>
+      <c r="L305" s="3"/>
+      <c r="M305" s="3"/>
+      <c r="N305" s="3"/>
+      <c r="O305" s="3"/>
+      <c r="P305" s="3"/>
+      <c r="Q305" s="3"/>
+      <c r="R305" s="3"/>
+      <c r="S305" s="3"/>
+      <c r="T305" s="6">
         <v>114</v>
       </c>
-      <c r="U302" s="6">
+      <c r="U305" s="6">
         <v>61</v>
       </c>
-      <c r="V302" s="6">
+      <c r="V305" s="6">
         <v>97</v>
       </c>
-      <c r="W302" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="303" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="B304" s="8"/>
+      <c r="W305" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B307" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A304:B304"/>
+    <mergeCell ref="A307:B307"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niewiadomskaew\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A002F2D3-8696-4E7D-9220-3E2740092518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2661B06E-F93F-419C-A8E5-6DBB2E707273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="427">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -1309,7 +1309,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 20-05-2026, 10:30</t>
+    <t>Ostatnia aktualizacja: 26-05-2026, 10:02</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W307"/>
+  <dimension ref="A1:W310"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -7516,18 +7516,18 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
-      <c r="R96" s="4">
+      <c r="R96" s="6">
         <v>21</v>
       </c>
       <c r="S96" s="3"/>
-      <c r="T96" s="4">
+      <c r="T96" s="6">
         <v>20</v>
       </c>
-      <c r="U96" s="4">
+      <c r="U96" s="6">
         <v>22</v>
       </c>
-      <c r="V96" s="4">
-        <v>23.5</v>
+      <c r="V96" s="6">
+        <v>24</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>30</v>
@@ -7563,18 +7563,18 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
-      <c r="R97" s="4">
+      <c r="R97" s="6">
         <v>20</v>
       </c>
       <c r="S97" s="3"/>
-      <c r="T97" s="4">
+      <c r="T97" s="6">
         <v>19</v>
       </c>
-      <c r="U97" s="4">
+      <c r="U97" s="6">
         <v>20</v>
       </c>
-      <c r="V97" s="4">
-        <v>23.5</v>
+      <c r="V97" s="6">
+        <v>24</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>30</v>
@@ -7610,18 +7610,18 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
-      <c r="R98" s="4">
+      <c r="R98" s="6">
         <v>22</v>
       </c>
       <c r="S98" s="3"/>
-      <c r="T98" s="4">
+      <c r="T98" s="6">
         <v>21</v>
       </c>
-      <c r="U98" s="4">
+      <c r="U98" s="6">
         <v>25</v>
       </c>
-      <c r="V98" s="4">
-        <v>23.6</v>
+      <c r="V98" s="6">
+        <v>24</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>30</v>
@@ -7747,18 +7747,18 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
-      <c r="R101" s="4">
+      <c r="R101" s="6">
         <v>36</v>
       </c>
       <c r="S101" s="3"/>
-      <c r="T101" s="4">
+      <c r="T101" s="6">
         <v>31</v>
       </c>
-      <c r="U101" s="4">
+      <c r="U101" s="6">
         <v>36</v>
       </c>
-      <c r="V101" s="4">
-        <v>38.6</v>
+      <c r="V101" s="6">
+        <v>39</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
@@ -7841,18 +7841,18 @@
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
-      <c r="R103" s="4">
+      <c r="R103" s="6">
         <v>28</v>
       </c>
       <c r="S103" s="3"/>
-      <c r="T103" s="4">
+      <c r="T103" s="6">
         <v>27</v>
       </c>
-      <c r="U103" s="4">
+      <c r="U103" s="6">
         <v>31</v>
       </c>
-      <c r="V103" s="4">
-        <v>32.200000000000003</v>
+      <c r="V103" s="6">
+        <v>32</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>30</v>
@@ -7888,18 +7888,18 @@
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
-      <c r="R104" s="4">
+      <c r="R104" s="6">
         <v>17</v>
       </c>
       <c r="S104" s="3"/>
-      <c r="T104" s="4">
+      <c r="T104" s="6">
         <v>18</v>
       </c>
-      <c r="U104" s="4">
+      <c r="U104" s="6">
         <v>19</v>
       </c>
-      <c r="V104" s="4">
-        <v>20.9</v>
+      <c r="V104" s="6">
+        <v>21</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>30</v>
@@ -7935,18 +7935,18 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
-      <c r="R105" s="4">
+      <c r="R105" s="6">
         <v>8</v>
       </c>
       <c r="S105" s="3"/>
-      <c r="T105" s="4">
+      <c r="T105" s="6">
         <v>9</v>
       </c>
-      <c r="U105" s="4">
+      <c r="U105" s="6">
         <v>12</v>
       </c>
-      <c r="V105" s="4">
-        <v>8.8000000000000007</v>
+      <c r="V105" s="6">
+        <v>9</v>
       </c>
       <c r="W105" s="2" t="s">
         <v>30</v>
@@ -7982,18 +7982,18 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
-      <c r="R106" s="4">
+      <c r="R106" s="6">
         <v>3</v>
       </c>
       <c r="S106" s="3"/>
-      <c r="T106" s="4">
+      <c r="T106" s="6">
         <v>3</v>
       </c>
-      <c r="U106" s="4">
+      <c r="U106" s="6">
         <v>3</v>
       </c>
-      <c r="V106" s="4">
-        <v>2.7</v>
+      <c r="V106" s="6">
+        <v>3</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>30</v>
@@ -12968,10 +12968,10 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="P183" s="4">
-        <v>8.1999999999999993</v>
+        <v>7.9</v>
       </c>
       <c r="Q183" s="4">
-        <v>8.8000000000000007</v>
+        <v>8.6</v>
       </c>
       <c r="R183" s="4">
         <v>11.2</v>
@@ -12985,7 +12985,9 @@
       <c r="U183" s="4">
         <v>7</v>
       </c>
-      <c r="V183" s="3"/>
+      <c r="V183" s="4">
+        <v>7.1</v>
+      </c>
       <c r="W183" s="2" t="s">
         <v>30</v>
       </c>
@@ -13037,10 +13039,10 @@
         <v>10.1</v>
       </c>
       <c r="P184" s="4">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q184" s="4">
-        <v>9.6</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="R184" s="4">
         <v>11.8</v>
@@ -13054,7 +13056,9 @@
       <c r="U184" s="4">
         <v>6.9</v>
       </c>
-      <c r="V184" s="3"/>
+      <c r="V184" s="4">
+        <v>7.6</v>
+      </c>
       <c r="W184" s="2" t="s">
         <v>30</v>
       </c>
@@ -13106,10 +13110,10 @@
         <v>7.4</v>
       </c>
       <c r="P185" s="4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Q185" s="4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="R185" s="4">
         <v>10.6</v>
@@ -13123,7 +13127,9 @@
       <c r="U185" s="4">
         <v>7</v>
       </c>
-      <c r="V185" s="3"/>
+      <c r="V185" s="4">
+        <v>6.7</v>
+      </c>
       <c r="W185" s="2" t="s">
         <v>30</v>
       </c>
@@ -15758,7 +15764,9 @@
       <c r="U228" s="4">
         <v>5.8</v>
       </c>
-      <c r="V228" s="3"/>
+      <c r="V228" s="4">
+        <v>6</v>
+      </c>
       <c r="W228" s="2" t="s">
         <v>30</v>
       </c>
@@ -15827,7 +15835,9 @@
       <c r="U229" s="5">
         <v>0.18</v>
       </c>
-      <c r="V229" s="3"/>
+      <c r="V229" s="5">
+        <v>0.25</v>
+      </c>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
@@ -17255,128 +17265,128 @@
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>335</v>
+        <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>334</v>
       </c>
       <c r="G251" s="6">
-        <v>5248</v>
+        <v>28</v>
       </c>
       <c r="H251" s="6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I251" s="6">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J251" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K251" s="6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L251" s="6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M251" s="6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N251" s="6">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="O251" s="6">
-        <v>966</v>
+        <v>22</v>
       </c>
       <c r="P251" s="6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q251" s="6">
-        <v>451</v>
+        <v>19</v>
       </c>
       <c r="R251" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S251" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="T251" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U251" s="6">
-        <v>2938</v>
+        <v>15</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J252" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K252" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L252" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M252" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N252" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R252" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S252" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T252" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U252" s="5">
-        <v>0.59</v>
+        <v>334</v>
+      </c>
+      <c r="G252" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H252" s="6">
+        <v>0</v>
+      </c>
+      <c r="I252" s="6">
+        <v>7</v>
+      </c>
+      <c r="J252" s="6">
+        <v>0</v>
+      </c>
+      <c r="K252" s="6">
+        <v>0</v>
+      </c>
+      <c r="L252" s="6">
+        <v>0</v>
+      </c>
+      <c r="M252" s="6">
+        <v>0</v>
+      </c>
+      <c r="N252" s="6">
+        <v>87</v>
+      </c>
+      <c r="O252" s="6">
+        <v>966</v>
+      </c>
+      <c r="P252" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q252" s="6">
+        <v>451</v>
+      </c>
+      <c r="R252" s="6">
+        <v>33</v>
+      </c>
+      <c r="S252" s="6">
+        <v>1</v>
+      </c>
+      <c r="T252" s="6">
+        <v>1</v>
+      </c>
+      <c r="U252" s="6">
+        <v>2938</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17387,7 +17397,7 @@
         <v>336</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>27</v>
@@ -17396,54 +17406,56 @@
         <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G253" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H253" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I253" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J253" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K253" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L253" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M253" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N253" s="3"/>
-      <c r="O253" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P253" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q253" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R253" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S253" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T253" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U253" s="4">
-        <v>881284.3</v>
+        <v>287</v>
+      </c>
+      <c r="G253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J253" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K253" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L253" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M253" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N253" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R253" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S253" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T253" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U253" s="5">
+        <v>0.59</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17454,7 +17466,7 @@
         <v>336</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17463,48 +17475,54 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
-      <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
-      <c r="L254" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M254" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N254" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O254" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P254" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q254" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R254" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S254" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T254" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U254" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V254" s="5">
-        <v>5.95</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G254" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H254" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I254" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J254" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K254" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L254" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M254" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N254" s="3"/>
+      <c r="O254" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P254" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q254" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R254" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S254" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T254" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U254" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>340</v>
+        <v>171</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
@@ -17512,10 +17530,10 @@
         <v>315</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17524,53 +17542,59 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="3"/>
       <c r="I255" s="3"/>
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
-      <c r="L255" s="3"/>
-      <c r="M255" s="3"/>
-      <c r="N255" s="3"/>
-      <c r="O255" s="6">
-        <v>1</v>
-      </c>
-      <c r="P255" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>63</v>
-      </c>
-      <c r="R255" s="6">
-        <v>66</v>
-      </c>
-      <c r="S255" s="6">
-        <v>70</v>
-      </c>
-      <c r="T255" s="6">
-        <v>75</v>
-      </c>
-      <c r="U255" s="6">
-        <v>80</v>
-      </c>
-      <c r="V255" s="6">
-        <v>86</v>
+      <c r="L255" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M255" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N255" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O255" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P255" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q255" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R255" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S255" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T255" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U255" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V255" s="5">
+        <v>5.95</v>
       </c>
       <c r="W255" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17579,7 +17603,7 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>345</v>
+        <v>287</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
@@ -17589,27 +17613,35 @@
       <c r="L256" s="3"/>
       <c r="M256" s="3"/>
       <c r="N256" s="3"/>
-      <c r="O256" s="3"/>
-      <c r="P256" s="3"/>
-      <c r="Q256" s="3"/>
-      <c r="R256" s="3"/>
+      <c r="O256" s="6">
+        <v>1</v>
+      </c>
+      <c r="P256" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q256" s="6">
+        <v>63</v>
+      </c>
+      <c r="R256" s="6">
+        <v>66</v>
+      </c>
       <c r="S256" s="6">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="T256" s="6">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="U256" s="6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="V256" s="6">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="W256" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>315</v>
       </c>
@@ -17617,7 +17649,7 @@
         <v>343</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17626,7 +17658,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -17639,92 +17671,70 @@
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
       <c r="Q257" s="3"/>
-      <c r="R257" s="6">
+      <c r="R257" s="3"/>
+      <c r="S257" s="6">
+        <v>16</v>
+      </c>
+      <c r="T257" s="6">
+        <v>7</v>
+      </c>
+      <c r="U257" s="6">
+        <v>6</v>
+      </c>
+      <c r="V257" s="6">
+        <v>4</v>
+      </c>
+      <c r="W257" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G258" s="3"/>
+      <c r="H258" s="3"/>
+      <c r="I258" s="3"/>
+      <c r="J258" s="3"/>
+      <c r="K258" s="3"/>
+      <c r="L258" s="3"/>
+      <c r="M258" s="3"/>
+      <c r="N258" s="3"/>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="3"/>
+      <c r="R258" s="6">
         <v>133</v>
       </c>
-      <c r="S257" s="6">
+      <c r="S258" s="6">
         <v>80</v>
       </c>
-      <c r="T257" s="6">
+      <c r="T258" s="6">
         <v>97</v>
       </c>
-      <c r="U257" s="6">
+      <c r="U258" s="6">
         <v>44</v>
       </c>
-      <c r="V257" s="6">
+      <c r="V258" s="6">
         <v>89</v>
       </c>
-      <c r="W257" s="2" t="s">
+      <c r="W258" s="2" t="s">
         <v>349</v>
-      </c>
-    </row>
-    <row r="258" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G258" s="6">
-        <v>40</v>
-      </c>
-      <c r="H258" s="6">
-        <v>60</v>
-      </c>
-      <c r="I258" s="6">
-        <v>40</v>
-      </c>
-      <c r="J258" s="6">
-        <v>40</v>
-      </c>
-      <c r="K258" s="6">
-        <v>40</v>
-      </c>
-      <c r="L258" s="6">
-        <v>40</v>
-      </c>
-      <c r="M258" s="6">
-        <v>60</v>
-      </c>
-      <c r="N258" s="6">
-        <v>40</v>
-      </c>
-      <c r="O258" s="6">
-        <v>40</v>
-      </c>
-      <c r="P258" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>60</v>
-      </c>
-      <c r="R258" s="6">
-        <v>67</v>
-      </c>
-      <c r="S258" s="6">
-        <v>50</v>
-      </c>
-      <c r="T258" s="6">
-        <v>67</v>
-      </c>
-      <c r="U258" s="6">
-        <v>67</v>
-      </c>
-      <c r="V258" s="3"/>
-      <c r="W258" s="2" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="259" spans="1:23" ht="81" x14ac:dyDescent="0.25">
@@ -17741,7 +17751,7 @@
         <v>353</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>36</v>
@@ -17753,13 +17763,13 @@
         <v>60</v>
       </c>
       <c r="I259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K259" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L259" s="6">
         <v>40</v>
@@ -17771,25 +17781,25 @@
         <v>40</v>
       </c>
       <c r="O259" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P259" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q259" s="6">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="R259" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S259" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T259" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U259" s="6">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
@@ -17810,16 +17820,16 @@
         <v>353</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I260" s="6">
         <v>20</v>
@@ -17831,34 +17841,34 @@
         <v>20</v>
       </c>
       <c r="L260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O260" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P260" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q260" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R260" s="6">
         <v>17</v>
       </c>
       <c r="S260" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T260" s="6">
         <v>17</v>
       </c>
       <c r="U260" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
@@ -17879,139 +17889,139 @@
         <v>353</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H261" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K261" s="6">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M261" s="6">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N261" s="6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O261" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P261" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q261" s="6">
         <v>40</v>
       </c>
       <c r="R261" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S261" s="6">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="T261" s="6">
         <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>28</v>
+        <v>358</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G262" s="4">
-        <v>100</v>
-      </c>
-      <c r="H262" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I262" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J262" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K262" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L262" s="4">
-        <v>106</v>
-      </c>
-      <c r="M262" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N262" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O262" s="4">
-        <v>130</v>
-      </c>
-      <c r="P262" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q262" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R262" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S262" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T262" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U262" s="4">
-        <v>208.5</v>
+        <v>36</v>
+      </c>
+      <c r="G262" s="6">
+        <v>60</v>
+      </c>
+      <c r="H262" s="6">
+        <v>40</v>
+      </c>
+      <c r="I262" s="6">
+        <v>60</v>
+      </c>
+      <c r="J262" s="6">
+        <v>60</v>
+      </c>
+      <c r="K262" s="6">
+        <v>60</v>
+      </c>
+      <c r="L262" s="6">
+        <v>60</v>
+      </c>
+      <c r="M262" s="6">
+        <v>40</v>
+      </c>
+      <c r="N262" s="6">
+        <v>60</v>
+      </c>
+      <c r="O262" s="6">
+        <v>75</v>
+      </c>
+      <c r="P262" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>40</v>
+      </c>
+      <c r="R262" s="6">
+        <v>33</v>
+      </c>
+      <c r="S262" s="6">
+        <v>50</v>
+      </c>
+      <c r="T262" s="6">
+        <v>17</v>
+      </c>
+      <c r="U262" s="6">
+        <v>25</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -18020,67 +18030,67 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G263" s="4">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="H263" s="4">
-        <v>57.7</v>
+        <v>100.8</v>
       </c>
       <c r="I263" s="4">
-        <v>58.8</v>
+        <v>99.9</v>
       </c>
       <c r="J263" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K263" s="4">
-        <v>68.7</v>
+        <v>104.9</v>
       </c>
       <c r="L263" s="4">
-        <v>69.5</v>
+        <v>106</v>
       </c>
       <c r="M263" s="4">
-        <v>72.900000000000006</v>
+        <v>119.9</v>
       </c>
       <c r="N263" s="4">
-        <v>78.099999999999994</v>
+        <v>119.4</v>
       </c>
       <c r="O263" s="4">
-        <v>91.8</v>
+        <v>130</v>
       </c>
       <c r="P263" s="4">
-        <v>93.9</v>
+        <v>189.5</v>
       </c>
       <c r="Q263" s="4">
-        <v>88.5</v>
+        <v>186.6</v>
       </c>
       <c r="R263" s="4">
-        <v>96.7</v>
+        <v>190.1</v>
       </c>
       <c r="S263" s="4">
-        <v>119</v>
+        <v>200.8</v>
       </c>
       <c r="T263" s="4">
-        <v>136.4</v>
+        <v>205.6</v>
       </c>
       <c r="U263" s="4">
-        <v>124.2</v>
+        <v>208.5</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18089,56 +18099,56 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G264" s="4">
-        <v>90.8</v>
+        <v>59.5</v>
       </c>
       <c r="H264" s="4">
-        <v>88.8</v>
+        <v>57.7</v>
       </c>
       <c r="I264" s="4">
-        <v>86.5</v>
+        <v>58.8</v>
       </c>
       <c r="J264" s="4">
-        <v>87</v>
+        <v>64.3</v>
       </c>
       <c r="K264" s="4">
-        <v>85</v>
+        <v>68.7</v>
       </c>
       <c r="L264" s="4">
-        <v>87.4</v>
+        <v>69.5</v>
       </c>
       <c r="M264" s="4">
-        <v>88.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N264" s="4">
-        <v>84.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O264" s="4">
-        <v>77.3</v>
+        <v>91.8</v>
       </c>
       <c r="P264" s="4">
-        <v>79.7</v>
+        <v>93.9</v>
       </c>
       <c r="Q264" s="4">
-        <v>81.900000000000006</v>
+        <v>88.5</v>
       </c>
       <c r="R264" s="4">
-        <v>74.8</v>
+        <v>96.7</v>
       </c>
       <c r="S264" s="4">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="T264" s="4">
-        <v>77.2</v>
+        <v>136.4</v>
       </c>
       <c r="U264" s="4">
-        <v>76.3</v>
+        <v>124.2</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18149,7 +18159,7 @@
         <v>366</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18158,56 +18168,56 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G265" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H265" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I265" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K265" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L265" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M265" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q265" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T265" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U265" s="7">
-        <v>0.192</v>
+        <v>368</v>
+      </c>
+      <c r="G265" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H265" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I265" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J265" s="4">
+        <v>87</v>
+      </c>
+      <c r="K265" s="4">
+        <v>85</v>
+      </c>
+      <c r="L265" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M265" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N265" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O265" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P265" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q265" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R265" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S265" s="4">
+        <v>77</v>
+      </c>
+      <c r="T265" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U265" s="4">
+        <v>76.3</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>370</v>
+        <v>101</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18218,7 +18228,7 @@
         <v>366</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18229,54 +18239,54 @@
       <c r="F266" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G266" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H266" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I266" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J266" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K266" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L266" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M266" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R266" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S266" s="4">
-        <v>31</v>
-      </c>
-      <c r="T266" s="4">
-        <v>31</v>
-      </c>
-      <c r="U266" s="4">
-        <v>31</v>
+      <c r="G266" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H266" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I266" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K266" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L266" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M266" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P266" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q266" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R266" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S266" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T266" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U266" s="7">
+        <v>0.192</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>30</v>
+        <v>370</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18284,10 +18294,10 @@
         <v>365</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18296,56 +18306,56 @@
         <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G267" s="6">
-        <v>28</v>
-      </c>
-      <c r="H267" s="6">
-        <v>27</v>
-      </c>
-      <c r="I267" s="6">
-        <v>26</v>
-      </c>
-      <c r="J267" s="6">
-        <v>25</v>
-      </c>
-      <c r="K267" s="6">
-        <v>24</v>
-      </c>
-      <c r="L267" s="6">
-        <v>23</v>
-      </c>
-      <c r="M267" s="6">
-        <v>22</v>
-      </c>
-      <c r="N267" s="6">
-        <v>22</v>
-      </c>
-      <c r="O267" s="6">
-        <v>22</v>
-      </c>
-      <c r="P267" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q267" s="6">
-        <v>19</v>
-      </c>
-      <c r="R267" s="6">
-        <v>17</v>
-      </c>
-      <c r="S267" s="6">
-        <v>16</v>
-      </c>
-      <c r="T267" s="6">
-        <v>16</v>
-      </c>
-      <c r="U267" s="6">
-        <v>15</v>
+        <v>36</v>
+      </c>
+      <c r="G267" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H267" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I267" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J267" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K267" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L267" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M267" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R267" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S267" s="4">
+        <v>31</v>
+      </c>
+      <c r="T267" s="4">
+        <v>31</v>
+      </c>
+      <c r="U267" s="4">
+        <v>31</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18356,65 +18366,65 @@
         <v>372</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G268" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H268" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I268" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J268" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K268" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L268" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M268" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N268" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O268" s="4">
-        <v>74</v>
-      </c>
-      <c r="P268" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q268" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R268" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S268" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T268" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U268" s="4">
-        <v>76.2</v>
+        <v>100</v>
+      </c>
+      <c r="G268" s="6">
+        <v>28</v>
+      </c>
+      <c r="H268" s="6">
+        <v>27</v>
+      </c>
+      <c r="I268" s="6">
+        <v>26</v>
+      </c>
+      <c r="J268" s="6">
+        <v>25</v>
+      </c>
+      <c r="K268" s="6">
+        <v>24</v>
+      </c>
+      <c r="L268" s="6">
+        <v>23</v>
+      </c>
+      <c r="M268" s="6">
+        <v>22</v>
+      </c>
+      <c r="N268" s="6">
+        <v>22</v>
+      </c>
+      <c r="O268" s="6">
+        <v>22</v>
+      </c>
+      <c r="P268" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q268" s="6">
+        <v>19</v>
+      </c>
+      <c r="R268" s="6">
+        <v>17</v>
+      </c>
+      <c r="S268" s="6">
+        <v>16</v>
+      </c>
+      <c r="T268" s="6">
+        <v>16</v>
+      </c>
+      <c r="U268" s="6">
+        <v>15</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -18431,55 +18441,55 @@
         <v>35</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G269" s="4">
-        <v>88</v>
+        <v>64.7</v>
       </c>
       <c r="H269" s="4">
-        <v>88.4</v>
+        <v>65.7</v>
       </c>
       <c r="I269" s="4">
-        <v>91.7</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J269" s="4">
-        <v>93.3</v>
+        <v>70.3</v>
       </c>
       <c r="K269" s="4">
-        <v>93.9</v>
+        <v>71.5</v>
       </c>
       <c r="L269" s="4">
-        <v>94.6</v>
+        <v>72.7</v>
       </c>
       <c r="M269" s="4">
-        <v>94.8</v>
+        <v>73.5</v>
       </c>
       <c r="N269" s="4">
-        <v>94.5</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O269" s="4">
-        <v>94.6</v>
+        <v>74</v>
       </c>
       <c r="P269" s="4">
-        <v>94.8</v>
+        <v>74.5</v>
       </c>
       <c r="Q269" s="4">
-        <v>94.7</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R269" s="4">
-        <v>94.6</v>
+        <v>75.2</v>
       </c>
       <c r="S269" s="4">
-        <v>95</v>
+        <v>75.7</v>
       </c>
       <c r="T269" s="4">
-        <v>94.8</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U269" s="4">
-        <v>94.6</v>
+        <v>76.2</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
@@ -18500,55 +18510,55 @@
         <v>35</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G270" s="4">
-        <v>28.5</v>
+        <v>88</v>
       </c>
       <c r="H270" s="4">
-        <v>30.6</v>
+        <v>88.4</v>
       </c>
       <c r="I270" s="4">
-        <v>33.1</v>
+        <v>91.7</v>
       </c>
       <c r="J270" s="4">
-        <v>35.299999999999997</v>
+        <v>93.3</v>
       </c>
       <c r="K270" s="4">
-        <v>37.4</v>
+        <v>93.9</v>
       </c>
       <c r="L270" s="4">
-        <v>39.6</v>
+        <v>94.6</v>
       </c>
       <c r="M270" s="4">
-        <v>41.2</v>
+        <v>94.8</v>
       </c>
       <c r="N270" s="4">
-        <v>42</v>
+        <v>94.5</v>
       </c>
       <c r="O270" s="4">
-        <v>42.9</v>
+        <v>94.6</v>
       </c>
       <c r="P270" s="4">
-        <v>44</v>
+        <v>94.8</v>
       </c>
       <c r="Q270" s="4">
-        <v>45.4</v>
+        <v>94.7</v>
       </c>
       <c r="R270" s="4">
-        <v>46.5</v>
+        <v>94.6</v>
       </c>
       <c r="S270" s="4">
-        <v>47.2</v>
+        <v>95</v>
       </c>
       <c r="T270" s="4">
-        <v>48.2</v>
+        <v>94.8</v>
       </c>
       <c r="U270" s="4">
-        <v>49.3</v>
+        <v>94.6</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
@@ -18563,76 +18573,76 @@
         <v>372</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G271" s="4">
-        <v>65.7</v>
+        <v>28.5</v>
       </c>
       <c r="H271" s="4">
-        <v>64.8</v>
+        <v>30.6</v>
       </c>
       <c r="I271" s="4">
-        <v>67.400000000000006</v>
+        <v>33.1</v>
       </c>
       <c r="J271" s="4">
-        <v>69.8</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K271" s="4">
-        <v>70.5</v>
+        <v>37.4</v>
       </c>
       <c r="L271" s="4">
-        <v>70.900000000000006</v>
+        <v>39.6</v>
       </c>
       <c r="M271" s="4">
-        <v>71.400000000000006</v>
+        <v>41.2</v>
       </c>
       <c r="N271" s="4">
-        <v>72.5</v>
+        <v>42</v>
       </c>
       <c r="O271" s="4">
-        <v>73.2</v>
+        <v>42.9</v>
       </c>
       <c r="P271" s="4">
-        <v>73.900000000000006</v>
+        <v>44</v>
       </c>
       <c r="Q271" s="4">
-        <v>73.3</v>
+        <v>45.4</v>
       </c>
       <c r="R271" s="4">
-        <v>72.8</v>
+        <v>46.5</v>
       </c>
       <c r="S271" s="4">
-        <v>76.3</v>
+        <v>47.2</v>
       </c>
       <c r="T271" s="4">
-        <v>78.099999999999994</v>
+        <v>48.2</v>
       </c>
       <c r="U271" s="4">
-        <v>78.599999999999994</v>
+        <v>49.3</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>365</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18641,52 +18651,52 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="G272" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H272" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I272" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J272" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K272" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L272" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M272" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N272" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O272" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P272" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q272" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R272" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S272" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T272" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U272" s="6">
-        <v>104040</v>
+        <v>36</v>
+      </c>
+      <c r="G272" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H272" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I272" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J272" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K272" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L272" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M272" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N272" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O272" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P272" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q272" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R272" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S272" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T272" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U272" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
@@ -18701,7 +18711,7 @@
         <v>376</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18710,52 +18720,52 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G273" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H273" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I273" s="4">
-        <v>6</v>
-      </c>
-      <c r="J273" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K273" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L273" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M273" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N273" s="4">
-        <v>3</v>
-      </c>
-      <c r="O273" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P273" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q273" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R273" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S273" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T273" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="U273" s="4">
-        <v>4.5</v>
+        <v>378</v>
+      </c>
+      <c r="G273" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H273" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I273" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J273" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K273" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L273" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M273" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N273" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O273" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P273" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q273" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R273" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S273" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T273" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U273" s="6">
+        <v>104040</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
@@ -18764,13 +18774,13 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -18781,56 +18791,54 @@
       <c r="F274" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G274" s="6">
-        <v>70</v>
-      </c>
-      <c r="H274" s="6">
-        <v>75</v>
-      </c>
-      <c r="I274" s="6">
-        <v>66</v>
-      </c>
-      <c r="J274" s="6">
-        <v>64</v>
-      </c>
-      <c r="K274" s="6">
-        <v>70</v>
-      </c>
-      <c r="L274" s="6">
-        <v>66</v>
-      </c>
-      <c r="M274" s="6">
-        <v>80</v>
-      </c>
-      <c r="N274" s="6">
-        <v>89</v>
-      </c>
-      <c r="O274" s="6">
-        <v>86</v>
-      </c>
-      <c r="P274" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q274" s="6">
-        <v>85</v>
-      </c>
-      <c r="R274" s="6">
-        <v>82</v>
-      </c>
-      <c r="S274" s="6">
-        <v>83</v>
-      </c>
-      <c r="T274" s="6">
-        <v>88</v>
-      </c>
-      <c r="U274" s="6">
-        <v>88</v>
-      </c>
-      <c r="V274" s="6">
-        <v>86</v>
-      </c>
+      <c r="G274" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H274" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I274" s="4">
+        <v>6</v>
+      </c>
+      <c r="J274" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K274" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L274" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M274" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N274" s="4">
+        <v>3</v>
+      </c>
+      <c r="O274" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P274" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q274" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R274" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S274" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T274" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U274" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -18841,7 +18849,7 @@
         <v>381</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>27</v>
@@ -18853,37 +18861,53 @@
         <v>36</v>
       </c>
       <c r="G275" s="6">
-        <v>55</v>
-      </c>
-      <c r="H275" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="H275" s="6">
+        <v>75</v>
+      </c>
       <c r="I275" s="6">
-        <v>58</v>
-      </c>
-      <c r="J275" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="J275" s="6">
+        <v>64</v>
+      </c>
       <c r="K275" s="6">
-        <v>60</v>
-      </c>
-      <c r="L275" s="3"/>
+        <v>70</v>
+      </c>
+      <c r="L275" s="6">
+        <v>66</v>
+      </c>
       <c r="M275" s="6">
-        <v>64</v>
-      </c>
-      <c r="N275" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="N275" s="6">
+        <v>89</v>
+      </c>
       <c r="O275" s="6">
-        <v>65</v>
-      </c>
-      <c r="P275" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="P275" s="6">
+        <v>89</v>
+      </c>
       <c r="Q275" s="6">
-        <v>74</v>
-      </c>
-      <c r="R275" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="R275" s="6">
+        <v>82</v>
+      </c>
       <c r="S275" s="6">
-        <v>63</v>
-      </c>
-      <c r="T275" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="T275" s="6">
+        <v>88</v>
+      </c>
       <c r="U275" s="6">
-        <v>71</v>
-      </c>
-      <c r="V275" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="V275" s="6">
+        <v>86</v>
+      </c>
       <c r="W275" s="2" t="s">
         <v>383</v>
       </c>
@@ -18893,10 +18917,10 @@
         <v>380</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -18905,56 +18929,42 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="G276" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H276" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I276" s="5">
-        <v>1</v>
-      </c>
-      <c r="J276" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K276" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L276" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M276" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N276" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O276" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P276" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q276" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R276" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S276" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T276" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U276" s="5">
-        <v>0.69</v>
+        <v>36</v>
+      </c>
+      <c r="G276" s="6">
+        <v>55</v>
+      </c>
+      <c r="H276" s="3"/>
+      <c r="I276" s="6">
+        <v>58</v>
+      </c>
+      <c r="J276" s="3"/>
+      <c r="K276" s="6">
+        <v>60</v>
+      </c>
+      <c r="L276" s="3"/>
+      <c r="M276" s="6">
+        <v>64</v>
+      </c>
+      <c r="N276" s="3"/>
+      <c r="O276" s="6">
+        <v>65</v>
+      </c>
+      <c r="P276" s="3"/>
+      <c r="Q276" s="6">
+        <v>74</v>
+      </c>
+      <c r="R276" s="3"/>
+      <c r="S276" s="6">
+        <v>63</v>
+      </c>
+      <c r="T276" s="3"/>
+      <c r="U276" s="6">
+        <v>71</v>
       </c>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>202</v>
+        <v>383</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -18962,10 +18972,10 @@
         <v>380</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -18974,56 +18984,56 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>287</v>
+        <v>387</v>
       </c>
       <c r="G277" s="5">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="H277" s="5">
-        <v>1.79</v>
+        <v>0.96</v>
       </c>
       <c r="I277" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J277" s="5">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="K277" s="5">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="L277" s="5">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="M277" s="5">
-        <v>1.99</v>
+        <v>0.91</v>
       </c>
       <c r="N277" s="5">
-        <v>1.88</v>
+        <v>0.81</v>
       </c>
       <c r="O277" s="5">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="P277" s="5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q277" s="5">
-        <v>2.21</v>
+        <v>0.85</v>
       </c>
       <c r="R277" s="5">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="S277" s="5">
-        <v>2.21</v>
+        <v>0.72</v>
       </c>
       <c r="T277" s="5">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="U277" s="5">
-        <v>4.07</v>
+        <v>0.69</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>390</v>
+        <v>202</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -19031,62 +19041,68 @@
         <v>380</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G278" s="6">
-        <v>10</v>
-      </c>
-      <c r="H278" s="6">
-        <v>9</v>
-      </c>
-      <c r="I278" s="6">
-        <v>11</v>
-      </c>
-      <c r="J278" s="6">
-        <v>11</v>
-      </c>
-      <c r="K278" s="6">
-        <v>15</v>
-      </c>
-      <c r="L278" s="6">
-        <v>16</v>
-      </c>
-      <c r="M278" s="6">
-        <v>19</v>
-      </c>
-      <c r="N278" s="6">
-        <v>21</v>
-      </c>
-      <c r="O278" s="6">
-        <v>25</v>
-      </c>
-      <c r="P278" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q278" s="6">
-        <v>34</v>
-      </c>
-      <c r="R278" s="6">
-        <v>40</v>
-      </c>
-      <c r="S278" s="3"/>
-      <c r="T278" s="3"/>
-      <c r="U278" s="3"/>
+        <v>287</v>
+      </c>
+      <c r="G278" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I278" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K278" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M278" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N278" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O278" s="5">
+        <v>2</v>
+      </c>
+      <c r="P278" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R278" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T278" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U278" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>30</v>
+        <v>390</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -19103,7 +19119,7 @@
         <v>62</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>36</v>
@@ -19118,13 +19134,13 @@
         <v>11</v>
       </c>
       <c r="J279" s="6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K279" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L279" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M279" s="6">
         <v>19</v>
@@ -19133,16 +19149,16 @@
         <v>21</v>
       </c>
       <c r="O279" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P279" s="6">
         <v>31</v>
       </c>
       <c r="Q279" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R279" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S279" s="3"/>
       <c r="T279" s="3"/>
@@ -19166,7 +19182,7 @@
         <v>62</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>36</v>
@@ -19178,16 +19194,16 @@
         <v>9</v>
       </c>
       <c r="I280" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J280" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K280" s="6">
+        <v>14</v>
+      </c>
+      <c r="L280" s="6">
         <v>15</v>
-      </c>
-      <c r="L280" s="6">
-        <v>16</v>
       </c>
       <c r="M280" s="6">
         <v>19</v>
@@ -19196,16 +19212,16 @@
         <v>21</v>
       </c>
       <c r="O280" s="6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P280" s="6">
+        <v>31</v>
+      </c>
+      <c r="Q280" s="6">
         <v>32</v>
       </c>
-      <c r="Q280" s="6">
-        <v>35</v>
-      </c>
       <c r="R280" s="6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="S280" s="3"/>
       <c r="T280" s="3"/>
@@ -19226,49 +19242,49 @@
         <v>392</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G281" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H281" s="6">
+        <v>9</v>
+      </c>
+      <c r="I281" s="6">
+        <v>10</v>
+      </c>
+      <c r="J281" s="6">
         <v>11</v>
       </c>
-      <c r="I281" s="6">
-        <v>13</v>
-      </c>
-      <c r="J281" s="6">
+      <c r="K281" s="6">
         <v>15</v>
       </c>
-      <c r="K281" s="6">
-        <v>18</v>
-      </c>
       <c r="L281" s="6">
+        <v>16</v>
+      </c>
+      <c r="M281" s="6">
         <v>19</v>
       </c>
-      <c r="M281" s="6">
-        <v>23</v>
-      </c>
       <c r="N281" s="6">
+        <v>21</v>
+      </c>
+      <c r="O281" s="6">
         <v>26</v>
       </c>
-      <c r="O281" s="6">
-        <v>30</v>
-      </c>
       <c r="P281" s="6">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q281" s="6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R281" s="6">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="S281" s="3"/>
       <c r="T281" s="3"/>
@@ -19292,46 +19308,46 @@
         <v>35</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G282" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H282" s="6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I282" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J282" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K282" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L282" s="6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M282" s="6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="N282" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="O282" s="6">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="P282" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q282" s="6">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R282" s="6">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="S282" s="3"/>
       <c r="T282" s="3"/>
@@ -19352,49 +19368,49 @@
         <v>392</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>393</v>
+        <v>39</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G283" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H283" s="6">
+        <v>5</v>
+      </c>
+      <c r="I283" s="6">
         <v>6</v>
       </c>
-      <c r="I283" s="6">
-        <v>8</v>
-      </c>
       <c r="J283" s="6">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K283" s="6">
         <v>9</v>
       </c>
       <c r="L283" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M283" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N283" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O283" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P283" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q283" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R283" s="6">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S283" s="3"/>
       <c r="T283" s="3"/>
@@ -19418,46 +19434,46 @@
         <v>81</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G284" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H284" s="6">
+        <v>6</v>
+      </c>
+      <c r="I284" s="6">
+        <v>8</v>
+      </c>
+      <c r="J284" s="6">
+        <v>9</v>
+      </c>
+      <c r="K284" s="6">
+        <v>9</v>
+      </c>
+      <c r="L284" s="6">
+        <v>8</v>
+      </c>
+      <c r="M284" s="6">
+        <v>9</v>
+      </c>
+      <c r="N284" s="6">
+        <v>11</v>
+      </c>
+      <c r="O284" s="6">
         <v>16</v>
       </c>
-      <c r="I284" s="6">
-        <v>19</v>
-      </c>
-      <c r="J284" s="6">
-        <v>20</v>
-      </c>
-      <c r="K284" s="6">
-        <v>28</v>
-      </c>
-      <c r="L284" s="6">
-        <v>28</v>
-      </c>
-      <c r="M284" s="6">
-        <v>32</v>
-      </c>
-      <c r="N284" s="6">
-        <v>35</v>
-      </c>
-      <c r="O284" s="6">
-        <v>39</v>
-      </c>
       <c r="P284" s="6">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="Q284" s="6">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="R284" s="6">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="S284" s="3"/>
       <c r="T284" s="3"/>
@@ -19481,46 +19497,46 @@
         <v>81</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G285" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H285" s="6">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I285" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J285" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K285" s="6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L285" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M285" s="6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N285" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O285" s="6">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P285" s="6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q285" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="R285" s="6">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S285" s="3"/>
       <c r="T285" s="3"/>
@@ -19544,46 +19560,46 @@
         <v>81</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G286" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H286" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I286" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J286" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K286" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L286" s="6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M286" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N286" s="6">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="O286" s="6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="P286" s="6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="Q286" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="R286" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="S286" s="3"/>
       <c r="T286" s="3"/>
@@ -19607,46 +19623,46 @@
         <v>81</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G287" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H287" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I287" s="6">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J287" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K287" s="6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L287" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M287" s="6">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N287" s="6">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O287" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P287" s="6">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q287" s="6">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R287" s="6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S287" s="3"/>
       <c r="T287" s="3"/>
@@ -19670,46 +19686,46 @@
         <v>81</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G288" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H288" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I288" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J288" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K288" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L288" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M288" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N288" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O288" s="6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P288" s="6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="Q288" s="6">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R288" s="6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="S288" s="3"/>
       <c r="T288" s="3"/>
@@ -19730,49 +19746,49 @@
         <v>392</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>132</v>
+        <v>398</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G289" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H289" s="6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I289" s="6">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J289" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K289" s="6">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L289" s="6">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="M289" s="6">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N289" s="6">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="O289" s="6">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="P289" s="6">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Q289" s="6">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="R289" s="6">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="S289" s="3"/>
       <c r="T289" s="3"/>
@@ -19796,46 +19812,46 @@
         <v>141</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G290" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H290" s="6">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I290" s="6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J290" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K290" s="6">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L290" s="6">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M290" s="6">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="N290" s="6">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="O290" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="P290" s="6">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="Q290" s="6">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="R290" s="6">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
@@ -19859,46 +19875,46 @@
         <v>141</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G291" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H291" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I291" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J291" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K291" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L291" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M291" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N291" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O291" s="6">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="P291" s="6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="Q291" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R291" s="6">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="S291" s="3"/>
       <c r="T291" s="3"/>
@@ -19919,49 +19935,49 @@
         <v>392</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G292" s="6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H292" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I292" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J292" s="6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K292" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="L292" s="6">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M292" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N292" s="6">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="O292" s="6">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="P292" s="6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="Q292" s="6">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R292" s="6">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="S292" s="3"/>
       <c r="T292" s="3"/>
@@ -19985,46 +20001,46 @@
         <v>144</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G293" s="6">
+        <v>14</v>
+      </c>
+      <c r="H293" s="6">
+        <v>13</v>
+      </c>
+      <c r="I293" s="6">
         <v>15</v>
       </c>
-      <c r="H293" s="6">
-        <v>14</v>
-      </c>
-      <c r="I293" s="6">
-        <v>16</v>
-      </c>
       <c r="J293" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K293" s="6">
+        <v>21</v>
+      </c>
+      <c r="L293" s="6">
         <v>23</v>
       </c>
-      <c r="L293" s="6">
+      <c r="M293" s="6">
         <v>25</v>
       </c>
-      <c r="M293" s="6">
-        <v>27</v>
-      </c>
       <c r="N293" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O293" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P293" s="6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q293" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R293" s="6">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S293" s="3"/>
       <c r="T293" s="3"/>
@@ -20048,46 +20064,46 @@
         <v>144</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G294" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H294" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I294" s="6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J294" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K294" s="6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L294" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="M294" s="6">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N294" s="6">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O294" s="6">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="P294" s="6">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="Q294" s="6">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="R294" s="6">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="S294" s="3"/>
       <c r="T294" s="3"/>
@@ -20111,46 +20127,46 @@
         <v>144</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>36</v>
       </c>
       <c r="G295" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H295" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I295" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J295" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K295" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L295" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M295" s="6">
         <v>7</v>
       </c>
       <c r="N295" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O295" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P295" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q295" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="R295" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S295" s="3"/>
       <c r="T295" s="3"/>
@@ -20165,81 +20181,73 @@
         <v>380</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G296" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H296" s="4">
-        <v>6</v>
-      </c>
-      <c r="I296" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J296" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K296" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L296" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M296" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N296" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O296" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P296" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q296" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R296" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S296" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T296" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U296" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V296" s="4">
-        <v>5.2</v>
-      </c>
+      <c r="G296" s="6">
+        <v>4</v>
+      </c>
+      <c r="H296" s="6">
+        <v>3</v>
+      </c>
+      <c r="I296" s="6">
+        <v>5</v>
+      </c>
+      <c r="J296" s="6">
+        <v>4</v>
+      </c>
+      <c r="K296" s="6">
+        <v>5</v>
+      </c>
+      <c r="L296" s="6">
+        <v>5</v>
+      </c>
+      <c r="M296" s="6">
+        <v>7</v>
+      </c>
+      <c r="N296" s="6">
+        <v>8</v>
+      </c>
+      <c r="O296" s="6">
+        <v>9</v>
+      </c>
+      <c r="P296" s="6">
+        <v>12</v>
+      </c>
+      <c r="Q296" s="6">
+        <v>14</v>
+      </c>
+      <c r="R296" s="6">
+        <v>17</v>
+      </c>
+      <c r="S296" s="3"/>
+      <c r="T296" s="3"/>
+      <c r="U296" s="3"/>
+      <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20248,56 +20256,58 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G297" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H297" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I297" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J297" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K297" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L297" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M297" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N297" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O297" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P297" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q297" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R297" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S297" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T297" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U297" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V297" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="G297" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H297" s="4">
+        <v>6</v>
+      </c>
+      <c r="I297" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J297" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K297" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L297" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M297" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N297" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O297" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P297" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q297" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R297" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S297" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T297" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U297" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V297" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>405</v>
+        <v>30</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -20305,10 +20315,10 @@
         <v>401</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20320,64 +20330,64 @@
         <v>404</v>
       </c>
       <c r="G298" s="5">
-        <v>96.04</v>
+        <v>377.75</v>
       </c>
       <c r="H298" s="5">
-        <v>90.68</v>
+        <v>417.47</v>
       </c>
       <c r="I298" s="5">
-        <v>111.55</v>
+        <v>421.06</v>
       </c>
       <c r="J298" s="5">
-        <v>127.11</v>
+        <v>487.12</v>
       </c>
       <c r="K298" s="5">
-        <v>82.28</v>
+        <v>451.84</v>
       </c>
       <c r="L298" s="5">
-        <v>100.19</v>
+        <v>440.89</v>
       </c>
       <c r="M298" s="5">
-        <v>148.99</v>
+        <v>662.95</v>
       </c>
       <c r="N298" s="5">
-        <v>222.11</v>
+        <v>679.46</v>
       </c>
       <c r="O298" s="5">
-        <v>244.93</v>
+        <v>766.04</v>
       </c>
       <c r="P298" s="5">
-        <v>223.31</v>
+        <v>776.56</v>
       </c>
       <c r="Q298" s="5">
-        <v>225.08</v>
+        <v>829.27</v>
       </c>
       <c r="R298" s="5">
-        <v>296.20999999999998</v>
+        <v>983.51</v>
       </c>
       <c r="S298" s="5">
-        <v>2661.32</v>
+        <v>3494.39</v>
       </c>
       <c r="T298" s="5">
-        <v>1701.94</v>
+        <v>2580.38</v>
       </c>
       <c r="U298" s="5">
-        <v>705.25</v>
+        <v>1840.15</v>
       </c>
       <c r="V298" s="3"/>
       <c r="W298" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>401</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>27</v>
@@ -20386,67 +20396,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>36</v>
+        <v>404</v>
       </c>
       <c r="G299" s="5">
-        <v>0.08</v>
+        <v>96.04</v>
       </c>
       <c r="H299" s="5">
-        <v>0.08</v>
+        <v>90.68</v>
       </c>
       <c r="I299" s="5">
-        <v>0.09</v>
+        <v>111.55</v>
       </c>
       <c r="J299" s="5">
-        <v>0.1</v>
+        <v>127.11</v>
       </c>
       <c r="K299" s="5">
-        <v>0.09</v>
+        <v>82.28</v>
       </c>
       <c r="L299" s="5">
-        <v>0.1</v>
+        <v>100.19</v>
       </c>
       <c r="M299" s="5">
-        <v>0.15</v>
+        <v>148.99</v>
       </c>
       <c r="N299" s="5">
-        <v>0.13</v>
+        <v>222.11</v>
       </c>
       <c r="O299" s="5">
-        <v>0.14000000000000001</v>
+        <v>244.93</v>
       </c>
       <c r="P299" s="5">
-        <v>0.14000000000000001</v>
+        <v>223.31</v>
       </c>
       <c r="Q299" s="5">
-        <v>0.14000000000000001</v>
+        <v>225.08</v>
       </c>
       <c r="R299" s="5">
-        <v>0.15</v>
+        <v>296.20999999999998</v>
       </c>
       <c r="S299" s="5">
-        <v>0.53</v>
+        <v>2661.32</v>
       </c>
       <c r="T299" s="5">
-        <v>0.33</v>
+        <v>1701.94</v>
       </c>
       <c r="U299" s="5">
-        <v>0.21</v>
+        <v>705.25</v>
       </c>
       <c r="V299" s="3"/>
       <c r="W299" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>401</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20455,50 +20465,54 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K300" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L300" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M300" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N300" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O300" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P300" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q300" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R300" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S300" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T300" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U300" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V300" s="7">
-        <v>5.3920000000000003</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G300" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H300" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I300" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J300" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K300" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L300" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M300" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N300" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q300" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R300" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S300" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T300" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U300" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V300" s="3"/>
       <c r="W300" s="2" t="s">
         <v>405</v>
       </c>
@@ -20508,10 +20522,10 @@
         <v>401</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>27</v>
@@ -20520,61 +20534,63 @@
         <v>28</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
-      <c r="J301" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K301" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L301" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M301" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N301" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O301" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P301" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q301" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R301" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S301" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T301" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U301" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V301" s="3"/>
+      <c r="J301" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K301" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L301" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M301" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N301" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O301" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P301" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q301" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R301" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S301" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T301" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U301" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V301" s="7">
+        <v>5.3920000000000003</v>
+      </c>
       <c r="W301" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="302" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>401</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>27</v>
@@ -20583,44 +20599,50 @@
         <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
-      <c r="J302" s="3"/>
-      <c r="K302" s="6">
-        <v>1</v>
-      </c>
-      <c r="L302" s="6">
-        <v>1</v>
-      </c>
-      <c r="M302" s="6">
-        <v>8</v>
-      </c>
-      <c r="N302" s="6">
-        <v>2</v>
-      </c>
-      <c r="O302" s="3"/>
-      <c r="P302" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="6">
-        <v>2</v>
-      </c>
-      <c r="R302" s="3"/>
-      <c r="S302" s="3"/>
-      <c r="T302" s="6">
-        <v>8</v>
-      </c>
-      <c r="U302" s="6">
-        <v>7</v>
-      </c>
-      <c r="V302" s="6">
-        <v>2</v>
-      </c>
+      <c r="J302" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K302" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L302" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M302" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N302" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O302" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P302" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q302" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R302" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S302" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T302" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U302" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V302" s="3"/>
       <c r="W302" s="2" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
     </row>
     <row r="303" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -20628,10 +20650,10 @@
         <v>401</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>27</v>
@@ -20644,12 +20666,8 @@
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="3"/>
-      <c r="I303" s="6">
-        <v>2</v>
-      </c>
-      <c r="J303" s="6">
-        <v>2</v>
-      </c>
+      <c r="I303" s="3"/>
+      <c r="J303" s="3"/>
       <c r="K303" s="6">
         <v>1</v>
       </c>
@@ -20657,31 +20675,25 @@
         <v>1</v>
       </c>
       <c r="M303" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N303" s="6">
-        <v>1</v>
-      </c>
-      <c r="O303" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O303" s="3"/>
       <c r="P303" s="6">
         <v>1</v>
       </c>
       <c r="Q303" s="6">
-        <v>4</v>
-      </c>
-      <c r="R303" s="6">
-        <v>1</v>
-      </c>
-      <c r="S303" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R303" s="3"/>
+      <c r="S303" s="3"/>
       <c r="T303" s="6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U303" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V303" s="6">
         <v>2</v>
@@ -20695,10 +20707,10 @@
         <v>401</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>27</v>
@@ -20707,61 +20719,65 @@
         <v>28</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="3"/>
-      <c r="I304" s="3"/>
-      <c r="J304" s="3"/>
+      <c r="I304" s="6">
+        <v>2</v>
+      </c>
+      <c r="J304" s="6">
+        <v>2</v>
+      </c>
       <c r="K304" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L304" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M304" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N304" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O304" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P304" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q304" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R304" s="6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S304" s="6">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="T304" s="6">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="U304" s="6">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="V304" s="6">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="W304" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="305" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>401</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D305" s="2" t="s">
         <v>27</v>
@@ -20776,47 +20792,112 @@
       <c r="H305" s="3"/>
       <c r="I305" s="3"/>
       <c r="J305" s="3"/>
-      <c r="K305" s="3"/>
-      <c r="L305" s="3"/>
-      <c r="M305" s="3"/>
-      <c r="N305" s="3"/>
-      <c r="O305" s="3"/>
-      <c r="P305" s="3"/>
-      <c r="Q305" s="3"/>
-      <c r="R305" s="3"/>
-      <c r="S305" s="3"/>
+      <c r="K305" s="6">
+        <v>5</v>
+      </c>
+      <c r="L305" s="6">
+        <v>13</v>
+      </c>
+      <c r="M305" s="6">
+        <v>19</v>
+      </c>
+      <c r="N305" s="6">
+        <v>18</v>
+      </c>
+      <c r="O305" s="6">
+        <v>15</v>
+      </c>
+      <c r="P305" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q305" s="6">
+        <v>8</v>
+      </c>
+      <c r="R305" s="6">
+        <v>28</v>
+      </c>
+      <c r="S305" s="6">
+        <v>53</v>
+      </c>
       <c r="T305" s="6">
+        <v>65</v>
+      </c>
+      <c r="U305" s="6">
+        <v>70</v>
+      </c>
+      <c r="V305" s="6">
+        <v>69</v>
+      </c>
+      <c r="W305" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+      <c r="L306" s="3"/>
+      <c r="M306" s="3"/>
+      <c r="N306" s="3"/>
+      <c r="O306" s="3"/>
+      <c r="P306" s="3"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+      <c r="S306" s="3"/>
+      <c r="T306" s="6">
         <v>114</v>
       </c>
-      <c r="U305" s="6">
+      <c r="U306" s="6">
         <v>61</v>
       </c>
-      <c r="V305" s="6">
+      <c r="V306" s="6">
         <v>97</v>
       </c>
-      <c r="W305" s="2" t="s">
+      <c r="W306" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="306" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
+    <row r="307" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="B307" s="8"/>
-    </row>
+      <c r="B309" s="8"/>
+    </row>
+    <row r="310" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A307:B307"/>
+    <mergeCell ref="A309:B309"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="57" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8E1604-ECCA-4107-A69E-E939BBB4EDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C28685-D9C7-4CF7-8327-704E60F96E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -1327,7 +1327,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 21-07-2026, 11:58</t>
+    <t>Ostatnia aktualizacja: 23-07-2026, 12:34</t>
   </si>
 </sst>
 </file>
@@ -7925,58 +7925,58 @@
         <v>66</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G101" s="4">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="H101" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="I101" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="J101" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="K101" s="4">
+        <v>12</v>
+      </c>
+      <c r="L101" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="M101" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="N101" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="O101" s="4">
+        <v>10.1</v>
+      </c>
+      <c r="P101" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="R101" s="4">
         <v>11.8</v>
       </c>
-      <c r="I101" s="4">
-        <v>12</v>
-      </c>
-      <c r="J101" s="4">
-        <v>12.6</v>
-      </c>
-      <c r="K101" s="4">
-        <v>12.4</v>
-      </c>
-      <c r="L101" s="4">
-        <v>11.5</v>
-      </c>
-      <c r="M101" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="N101" s="4">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O101" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="P101" s="4">
-        <v>6.8</v>
-      </c>
-      <c r="Q101" s="4">
-        <v>7.9</v>
-      </c>
-      <c r="R101" s="4">
-        <v>10.6</v>
-      </c>
       <c r="S101" s="4">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="T101" s="4">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="U101" s="4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="V101" s="4">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>30</v>
@@ -7996,58 +7996,58 @@
         <v>66</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G102" s="4">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="H102" s="4">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="I102" s="4">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="K102" s="4">
         <v>12.4</v>
       </c>
-      <c r="K102" s="4">
-        <v>12</v>
-      </c>
       <c r="L102" s="4">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="M102" s="4">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="N102" s="4">
-        <v>10.7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="O102" s="4">
-        <v>10.1</v>
+        <v>7.4</v>
       </c>
       <c r="P102" s="4">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="Q102" s="4">
-        <v>9.3000000000000007</v>
+        <v>7.9</v>
       </c>
       <c r="R102" s="4">
-        <v>11.8</v>
+        <v>10.6</v>
       </c>
       <c r="S102" s="4">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="T102" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="U102" s="4">
+        <v>7</v>
+      </c>
+      <c r="V102" s="4">
         <v>6.7</v>
-      </c>
-      <c r="U102" s="4">
-        <v>6.9</v>
-      </c>
-      <c r="V102" s="4">
-        <v>7.6</v>
       </c>
       <c r="W102" s="2" t="s">
         <v>30</v>
@@ -10628,50 +10628,50 @@
       <c r="F147" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G147" s="5">
         <v>6.64</v>
       </c>
-      <c r="H147" s="7">
-        <v>6.9180000000000001</v>
-      </c>
-      <c r="I147" s="7">
-        <v>6.5330000000000004</v>
-      </c>
-      <c r="J147" s="7">
-        <v>6.6660000000000004</v>
-      </c>
-      <c r="K147" s="7">
-        <v>6.319</v>
-      </c>
-      <c r="L147" s="7">
-        <v>5.6859999999999999</v>
-      </c>
-      <c r="M147" s="7">
-        <v>3.9740000000000002</v>
-      </c>
-      <c r="N147" s="7">
-        <v>4.2320000000000002</v>
-      </c>
-      <c r="O147" s="7">
+      <c r="H147" s="5">
+        <v>6.92</v>
+      </c>
+      <c r="I147" s="5">
+        <v>6.53</v>
+      </c>
+      <c r="J147" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="K147" s="5">
+        <v>6.32</v>
+      </c>
+      <c r="L147" s="5">
+        <v>5.69</v>
+      </c>
+      <c r="M147" s="5">
+        <v>3.97</v>
+      </c>
+      <c r="N147" s="5">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="O147" s="5">
         <v>5.72</v>
       </c>
-      <c r="P147" s="7">
+      <c r="P147" s="5">
         <v>6.2</v>
       </c>
-      <c r="Q147" s="7">
-        <v>6.5750000000000002</v>
-      </c>
-      <c r="R147" s="7">
-        <v>5.6740000000000004</v>
-      </c>
-      <c r="S147" s="7">
-        <v>5.7910000000000004</v>
-      </c>
-      <c r="T147" s="7">
-        <v>6.3390000000000004</v>
-      </c>
-      <c r="U147" s="7">
-        <v>6.0330000000000004</v>
+      <c r="Q147" s="5">
+        <v>6.58</v>
+      </c>
+      <c r="R147" s="5">
+        <v>5.67</v>
+      </c>
+      <c r="S147" s="5">
+        <v>5.79</v>
+      </c>
+      <c r="T147" s="5">
+        <v>6.34</v>
+      </c>
+      <c r="U147" s="5">
+        <v>6.03</v>
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="2" t="s">
@@ -10697,49 +10697,49 @@
       <c r="F148" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G148" s="7">
-        <v>6.5490000000000004</v>
-      </c>
-      <c r="H148" s="7">
-        <v>8.0779999999999994</v>
-      </c>
-      <c r="I148" s="7">
+      <c r="G148" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H148" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I148" s="5">
         <v>10.61</v>
       </c>
-      <c r="J148" s="7">
-        <v>10.676</v>
-      </c>
-      <c r="K148" s="7">
+      <c r="J148" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K148" s="5">
         <v>12.36</v>
       </c>
-      <c r="L148" s="7">
-        <v>13.401</v>
-      </c>
-      <c r="M148" s="7">
-        <v>13.342000000000001</v>
-      </c>
-      <c r="N148" s="7">
-        <v>13.082000000000001</v>
-      </c>
-      <c r="O148" s="7">
-        <v>13.026999999999999</v>
-      </c>
-      <c r="P148" s="7">
-        <v>14.356</v>
-      </c>
-      <c r="Q148" s="7">
-        <v>16.236999999999998</v>
-      </c>
-      <c r="R148" s="7">
-        <v>17.167000000000002</v>
-      </c>
-      <c r="S148" s="7">
-        <v>21.009</v>
-      </c>
-      <c r="T148" s="7">
-        <v>25.792999999999999</v>
-      </c>
-      <c r="U148" s="7">
+      <c r="L148" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M148" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N148" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O148" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P148" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q148" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R148" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S148" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T148" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U148" s="5">
         <v>30.37</v>
       </c>
       <c r="V148" s="3"/>
@@ -10766,50 +10766,50 @@
       <c r="F149" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G149" s="7">
-        <v>11.811999999999999</v>
-      </c>
-      <c r="H149" s="7">
+      <c r="G149" s="5">
+        <v>11.81</v>
+      </c>
+      <c r="H149" s="5">
         <v>13.24</v>
       </c>
-      <c r="I149" s="7">
-        <v>13.497</v>
-      </c>
-      <c r="J149" s="7">
-        <v>14.265000000000001</v>
-      </c>
-      <c r="K149" s="7">
-        <v>14.237</v>
-      </c>
-      <c r="L149" s="7">
-        <v>14.795</v>
-      </c>
-      <c r="M149" s="7">
-        <v>14.919</v>
-      </c>
-      <c r="N149" s="7">
-        <v>14.779</v>
-      </c>
-      <c r="O149" s="7">
-        <v>21.472999999999999</v>
-      </c>
-      <c r="P149" s="7">
-        <v>22.004999999999999</v>
-      </c>
-      <c r="Q149" s="7">
-        <v>22.143000000000001</v>
-      </c>
-      <c r="R149" s="7">
-        <v>20.978000000000002</v>
-      </c>
-      <c r="S149" s="7">
-        <v>22.094999999999999</v>
-      </c>
-      <c r="T149" s="7">
+      <c r="I149" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="J149" s="5">
+        <v>14.27</v>
+      </c>
+      <c r="K149" s="5">
+        <v>14.24</v>
+      </c>
+      <c r="L149" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="M149" s="5">
+        <v>14.92</v>
+      </c>
+      <c r="N149" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="O149" s="5">
+        <v>21.47</v>
+      </c>
+      <c r="P149" s="5">
+        <v>22.01</v>
+      </c>
+      <c r="Q149" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="R149" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S149" s="5">
+        <v>22.1</v>
+      </c>
+      <c r="T149" s="5">
         <v>20.61</v>
       </c>
-      <c r="U149" s="7">
-        <v>21.286999999999999</v>
+      <c r="U149" s="5">
+        <v>21.29</v>
       </c>
       <c r="V149" s="3"/>
       <c r="W149" s="2" t="s">
@@ -17554,50 +17554,50 @@
       <c r="F253" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G253" s="7">
+      <c r="G253" s="5">
         <v>6.64</v>
       </c>
-      <c r="H253" s="7">
-        <v>6.9180000000000001</v>
-      </c>
-      <c r="I253" s="7">
-        <v>6.5330000000000004</v>
-      </c>
-      <c r="J253" s="7">
-        <v>6.6660000000000004</v>
-      </c>
-      <c r="K253" s="7">
-        <v>6.319</v>
-      </c>
-      <c r="L253" s="7">
-        <v>5.6859999999999999</v>
-      </c>
-      <c r="M253" s="7">
-        <v>3.9740000000000002</v>
-      </c>
-      <c r="N253" s="7">
-        <v>4.2320000000000002</v>
-      </c>
-      <c r="O253" s="7">
+      <c r="H253" s="5">
+        <v>6.92</v>
+      </c>
+      <c r="I253" s="5">
+        <v>6.53</v>
+      </c>
+      <c r="J253" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="K253" s="5">
+        <v>6.32</v>
+      </c>
+      <c r="L253" s="5">
+        <v>5.69</v>
+      </c>
+      <c r="M253" s="5">
+        <v>3.97</v>
+      </c>
+      <c r="N253" s="5">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="O253" s="5">
         <v>5.72</v>
       </c>
-      <c r="P253" s="7">
+      <c r="P253" s="5">
         <v>6.2</v>
       </c>
-      <c r="Q253" s="7">
-        <v>6.5750000000000002</v>
-      </c>
-      <c r="R253" s="7">
-        <v>5.6740000000000004</v>
-      </c>
-      <c r="S253" s="7">
-        <v>5.7910000000000004</v>
-      </c>
-      <c r="T253" s="7">
-        <v>6.3390000000000004</v>
-      </c>
-      <c r="U253" s="7">
-        <v>6.0330000000000004</v>
+      <c r="Q253" s="5">
+        <v>6.58</v>
+      </c>
+      <c r="R253" s="5">
+        <v>5.67</v>
+      </c>
+      <c r="S253" s="5">
+        <v>5.79</v>
+      </c>
+      <c r="T253" s="5">
+        <v>6.34</v>
+      </c>
+      <c r="U253" s="5">
+        <v>6.03</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
@@ -17623,49 +17623,49 @@
       <c r="F254" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G254" s="7">
-        <v>6.5490000000000004</v>
-      </c>
-      <c r="H254" s="7">
-        <v>8.0779999999999994</v>
-      </c>
-      <c r="I254" s="7">
+      <c r="G254" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H254" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I254" s="5">
         <v>10.61</v>
       </c>
-      <c r="J254" s="7">
-        <v>10.676</v>
-      </c>
-      <c r="K254" s="7">
+      <c r="J254" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K254" s="5">
         <v>12.36</v>
       </c>
-      <c r="L254" s="7">
-        <v>13.401</v>
-      </c>
-      <c r="M254" s="7">
-        <v>13.342000000000001</v>
-      </c>
-      <c r="N254" s="7">
-        <v>13.082000000000001</v>
-      </c>
-      <c r="O254" s="7">
-        <v>13.026999999999999</v>
-      </c>
-      <c r="P254" s="7">
-        <v>14.356</v>
-      </c>
-      <c r="Q254" s="7">
-        <v>16.236999999999998</v>
-      </c>
-      <c r="R254" s="7">
-        <v>17.167000000000002</v>
-      </c>
-      <c r="S254" s="7">
-        <v>21.009</v>
-      </c>
-      <c r="T254" s="7">
-        <v>25.792999999999999</v>
-      </c>
-      <c r="U254" s="7">
+      <c r="L254" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M254" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N254" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O254" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P254" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R254" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S254" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T254" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U254" s="5">
         <v>30.37</v>
       </c>
       <c r="V254" s="3"/>
@@ -17692,50 +17692,50 @@
       <c r="F255" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G255" s="7">
-        <v>11.811999999999999</v>
-      </c>
-      <c r="H255" s="7">
+      <c r="G255" s="5">
+        <v>11.81</v>
+      </c>
+      <c r="H255" s="5">
         <v>13.24</v>
       </c>
-      <c r="I255" s="7">
-        <v>13.497</v>
-      </c>
-      <c r="J255" s="7">
-        <v>14.265000000000001</v>
-      </c>
-      <c r="K255" s="7">
-        <v>14.237</v>
-      </c>
-      <c r="L255" s="7">
-        <v>14.795</v>
-      </c>
-      <c r="M255" s="7">
-        <v>14.919</v>
-      </c>
-      <c r="N255" s="7">
-        <v>14.779</v>
-      </c>
-      <c r="O255" s="7">
-        <v>21.472999999999999</v>
-      </c>
-      <c r="P255" s="7">
-        <v>22.004999999999999</v>
-      </c>
-      <c r="Q255" s="7">
-        <v>22.143000000000001</v>
-      </c>
-      <c r="R255" s="7">
-        <v>20.978000000000002</v>
-      </c>
-      <c r="S255" s="7">
-        <v>22.094999999999999</v>
-      </c>
-      <c r="T255" s="7">
+      <c r="I255" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="J255" s="5">
+        <v>14.27</v>
+      </c>
+      <c r="K255" s="5">
+        <v>14.24</v>
+      </c>
+      <c r="L255" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="M255" s="5">
+        <v>14.92</v>
+      </c>
+      <c r="N255" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="O255" s="5">
+        <v>21.47</v>
+      </c>
+      <c r="P255" s="5">
+        <v>22.01</v>
+      </c>
+      <c r="Q255" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="R255" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S255" s="5">
+        <v>22.1</v>
+      </c>
+      <c r="T255" s="5">
         <v>20.61</v>
       </c>
-      <c r="U255" s="7">
-        <v>21.286999999999999</v>
+      <c r="U255" s="5">
+        <v>21.29</v>
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dregerj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C28685-D9C7-4CF7-8327-704E60F96E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB2DAF4-F40A-474B-B60B-EA05351C0E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cele_1-17" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="437">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -157,7 +157,7 @@
     <t>1.2.b Miejsca w placówkach stacjonarnej pomocy społecznej (łącznie z filiami) na 10 tys. mieszkańców</t>
   </si>
   <si>
-    <t>-</t>
+    <t>[–]</t>
   </si>
   <si>
     <t>Poprawa sytuacji mieszkaniowej</t>
@@ -166,9 +166,6 @@
     <t xml:space="preserve">1.3.a Liczba mieszkań przypadających na 1000 ludności </t>
   </si>
   <si>
-    <t>[–]</t>
-  </si>
-  <si>
     <t>Cel 2. Zero głodu</t>
   </si>
   <si>
@@ -1204,6 +1201,9 @@
     <t>16.1.b Odsetek osób deklarujących zaufanie do instytucji publicznych - wobec władz lokalnych miasta lub gminy</t>
   </si>
   <si>
+    <t>16.1.c Liczba spraw sądowych rozpatrzonych w I instancji na 100 tys. ludności</t>
+  </si>
+  <si>
     <t>Poprawa jakości stanowionego prawa i jego stosowania</t>
   </si>
   <si>
@@ -1225,25 +1225,25 @@
     <t>Większe wykorzystanie technologii informacyjno-komunikacyjnych w zarządzaniu państwem i komunikacji z obywatelami (w tym z przedsiębiorcami)</t>
   </si>
   <si>
-    <t>16.4.a Odsetek osób korzystających z Internetu w kontaktach z administracją publiczną do przekazywania wypełnionych formularzy</t>
-  </si>
-  <si>
-    <t>w wieku 16-24 lat</t>
-  </si>
-  <si>
-    <t>w wieku 25-34 lat</t>
-  </si>
-  <si>
-    <t>w wieku 35-44 lat</t>
-  </si>
-  <si>
-    <t>w wieku 45-54 lat</t>
-  </si>
-  <si>
-    <t>w wieku 55-64 lat</t>
-  </si>
-  <si>
-    <t>w wieku 65-74 lat</t>
+    <t>16.4.a Przedsiębiorstwa wykorzystujące usługę e-Doręczenia</t>
+  </si>
+  <si>
+    <t>16.4.b Odsetek osób korzystających z Internetu w kontaktach z administracją publiczną</t>
+  </si>
+  <si>
+    <t>16-24 lata</t>
+  </si>
+  <si>
+    <t>25-34 lata</t>
+  </si>
+  <si>
+    <t>35-44 lata</t>
+  </si>
+  <si>
+    <t>45-54 lata</t>
+  </si>
+  <si>
+    <t>65-74 lata</t>
   </si>
   <si>
     <t>Lepsze gospodarowanie środkami publicznymi, w tym efektywne wykorzystanie środków z UE</t>
@@ -1252,6 +1252,18 @@
     <t>16.5.a Stopa inwestycji sektora instytucji rządowych i samorządowych</t>
   </si>
   <si>
+    <t>Podniesienie poziomu odporności na cyberzagrożenia oraz zwiększenie poziomu ochrony informacji w państwie, a także promowanie wiedzy i dobrych praktyk umożliwiających obywatelom lepszą ochronę ich informacji</t>
+  </si>
+  <si>
+    <t>16.7.a Liczba incydentów teleinformatycznych obsługiwanych przez CERT Polska, zakwalifikowanych jako faktyczne incydenty cyberbezpieczeństwa</t>
+  </si>
+  <si>
+    <t>NASK - Państwowy Instytut Badawczy / CERT Polska</t>
+  </si>
+  <si>
+    <t>16.7.b Odsetek respondentów korzystających z internetu sprawdzających prawdziwość informacji lub treści znalezionych w serwisach informacyjnych lub mediach społecznościowych (w ciągu ostatnich trzech miesięcy)</t>
+  </si>
+  <si>
     <t>Cel 17. Partnerstwa na rzecz celów</t>
   </si>
   <si>
@@ -1327,7 +1339,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 23-07-2026, 12:34</t>
+    <t>Ostatnia aktualizacja: 27-07-2026, 13:51</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W319"/>
+  <dimension ref="A1:W311"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -2442,7 +2454,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G11" s="4">
         <v>349.6</v>
@@ -2511,7 +2523,7 @@
         <v>39</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G12" s="4">
         <v>388.1</v>
@@ -2580,7 +2592,7 @@
         <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G13" s="4">
         <v>290</v>
@@ -2634,13 +2646,13 @@
     </row>
     <row r="14" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>27</v>
@@ -2649,7 +2661,7 @@
         <v>28</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G14" s="5">
         <v>0.57999999999999996</v>
@@ -2698,18 +2710,18 @@
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>27</v>
@@ -2772,13 +2784,13 @@
     </row>
     <row r="16" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
@@ -2835,13 +2847,13 @@
     </row>
     <row r="17" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>27</v>
@@ -2893,18 +2905,18 @@
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>27</v>
@@ -2964,18 +2976,18 @@
         <v>15.7</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>27</v>
@@ -3038,13 +3050,13 @@
     </row>
     <row r="20" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>27</v>
@@ -3107,13 +3119,13 @@
     </row>
     <row r="21" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>27</v>
@@ -3122,7 +3134,7 @@
         <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="5">
         <v>1401.46</v>
@@ -3176,13 +3188,13 @@
     </row>
     <row r="22" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>27</v>
@@ -3245,16 +3257,16 @@
     </row>
     <row r="23" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>28</v>
@@ -3290,19 +3302,19 @@
     </row>
     <row r="24" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>34</v>
@@ -3335,19 +3347,19 @@
     </row>
     <row r="25" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>34</v>
@@ -3380,13 +3392,13 @@
     </row>
     <row r="26" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>27</v>
@@ -3395,7 +3407,7 @@
         <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G26" s="4">
         <v>1.9</v>
@@ -3425,19 +3437,19 @@
     </row>
     <row r="27" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>34</v>
@@ -3470,19 +3482,19 @@
     </row>
     <row r="28" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>34</v>
@@ -3515,19 +3527,19 @@
     </row>
     <row r="29" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>34</v>
@@ -3560,19 +3572,19 @@
     </row>
     <row r="30" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>34</v>
@@ -3605,13 +3617,13 @@
     </row>
     <row r="31" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>27</v>
@@ -3620,7 +3632,7 @@
         <v>28</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G31" s="4">
         <v>58</v>
@@ -3674,13 +3686,13 @@
     </row>
     <row r="32" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>27</v>
@@ -3689,7 +3701,7 @@
         <v>28</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="4">
         <v>61.6</v>
@@ -3743,16 +3755,16 @@
     </row>
     <row r="33" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>28</v>
@@ -3812,19 +3824,19 @@
     </row>
     <row r="34" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>32</v>
@@ -3881,19 +3893,19 @@
     </row>
     <row r="35" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>32</v>
@@ -3950,13 +3962,13 @@
     </row>
     <row r="36" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C36" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>37</v>
@@ -4019,13 +4031,13 @@
     </row>
     <row r="37" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>37</v>
@@ -4088,16 +4100,16 @@
     </row>
     <row r="38" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>28</v>
@@ -4157,19 +4169,19 @@
     </row>
     <row r="39" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>32</v>
@@ -4226,19 +4238,19 @@
     </row>
     <row r="40" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>32</v>
@@ -4295,13 +4307,13 @@
     </row>
     <row r="41" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>37</v>
@@ -4364,13 +4376,13 @@
     </row>
     <row r="42" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C42" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>37</v>
@@ -4433,16 +4445,16 @@
     </row>
     <row r="43" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C43" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>28</v>
@@ -4502,19 +4514,19 @@
     </row>
     <row r="44" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>32</v>
@@ -4571,19 +4583,19 @@
     </row>
     <row r="45" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C45" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>32</v>
@@ -4640,13 +4652,13 @@
     </row>
     <row r="46" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>37</v>
@@ -4709,13 +4721,13 @@
     </row>
     <row r="47" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C47" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>37</v>
@@ -4778,16 +4790,16 @@
     </row>
     <row r="48" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>28</v>
@@ -4847,19 +4859,19 @@
     </row>
     <row r="49" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C49" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>32</v>
@@ -4916,19 +4928,19 @@
     </row>
     <row r="50" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>32</v>
@@ -4985,13 +4997,13 @@
     </row>
     <row r="51" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>37</v>
@@ -5054,13 +5066,13 @@
     </row>
     <row r="52" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>37</v>
@@ -5123,13 +5135,13 @@
     </row>
     <row r="53" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>27</v>
@@ -5174,13 +5186,13 @@
     </row>
     <row r="54" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>27</v>
@@ -5225,16 +5237,16 @@
     </row>
     <row r="55" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>28</v>
@@ -5291,24 +5303,24 @@
         <v>2.9</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>34</v>
@@ -5362,24 +5374,24 @@
         <v>2.5</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>34</v>
@@ -5433,21 +5445,21 @@
         <v>3.3</v>
       </c>
       <c r="W57" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>28</v>
@@ -5483,19 +5495,19 @@
     </row>
     <row r="59" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>34</v>
@@ -5528,19 +5540,19 @@
     </row>
     <row r="60" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>34</v>
@@ -5573,19 +5585,19 @@
     </row>
     <row r="61" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>34</v>
@@ -5618,19 +5630,19 @@
     </row>
     <row r="62" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>34</v>
@@ -5663,16 +5675,16 @@
     </row>
     <row r="63" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>28</v>
@@ -5708,19 +5720,19 @@
     </row>
     <row r="64" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>34</v>
@@ -5753,19 +5765,19 @@
     </row>
     <row r="65" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>34</v>
@@ -5798,19 +5810,19 @@
     </row>
     <row r="66" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>34</v>
@@ -5843,19 +5855,19 @@
     </row>
     <row r="67" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>34</v>
@@ -5888,13 +5900,13 @@
     </row>
     <row r="68" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>37</v>
@@ -5931,13 +5943,13 @@
     </row>
     <row r="69" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>37</v>
@@ -5974,13 +5986,13 @@
     </row>
     <row r="70" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>37</v>
@@ -6017,16 +6029,16 @@
     </row>
     <row r="71" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>28</v>
@@ -6078,19 +6090,19 @@
     </row>
     <row r="72" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>34</v>
@@ -6139,19 +6151,19 @@
     </row>
     <row r="73" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E73" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>34</v>
@@ -6200,13 +6212,13 @@
     </row>
     <row r="74" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>27</v>
@@ -6250,18 +6262,18 @@
         <v>87.5</v>
       </c>
       <c r="W74" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:23" ht="54" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>27</v>
@@ -6270,7 +6282,7 @@
         <v>28</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G75" s="6">
         <v>28</v>
@@ -6319,18 +6331,18 @@
       </c>
       <c r="V75" s="3"/>
       <c r="W75" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:23" ht="54" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>27</v>
@@ -6386,18 +6398,18 @@
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
       <c r="W76" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>27</v>
@@ -6462,13 +6474,13 @@
     </row>
     <row r="78" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>27</v>
@@ -6521,13 +6533,13 @@
     </row>
     <row r="79" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>27</v>
@@ -6565,18 +6577,18 @@
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
       <c r="W79" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>27</v>
@@ -6614,18 +6626,18 @@
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
       <c r="W80" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>27</v>
@@ -6663,18 +6675,18 @@
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
       <c r="W81" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="82" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>27</v>
@@ -6712,18 +6724,18 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>27</v>
@@ -6761,18 +6773,18 @@
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
       <c r="W83" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>27</v>
@@ -6810,18 +6822,18 @@
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
       <c r="W84" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>37</v>
@@ -6881,18 +6893,18 @@
         <v>95.1</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>37</v>
@@ -6950,18 +6962,18 @@
       </c>
       <c r="V86" s="3"/>
       <c r="W86" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>37</v>
@@ -7019,18 +7031,18 @@
       </c>
       <c r="V87" s="3"/>
       <c r="W87" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>27</v>
@@ -7074,21 +7086,21 @@
         <v>75.2</v>
       </c>
       <c r="W88" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D89" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>28</v>
@@ -7150,19 +7162,19 @@
     </row>
     <row r="90" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>34</v>
@@ -7219,19 +7231,19 @@
     </row>
     <row r="91" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>34</v>
@@ -7288,19 +7300,19 @@
     </row>
     <row r="92" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>34</v>
@@ -7359,19 +7371,19 @@
     </row>
     <row r="93" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>34</v>
@@ -7428,19 +7440,19 @@
     </row>
     <row r="94" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>34</v>
@@ -7497,19 +7509,19 @@
     </row>
     <row r="95" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>34</v>
@@ -7566,19 +7578,19 @@
     </row>
     <row r="96" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>34</v>
@@ -7635,19 +7647,19 @@
     </row>
     <row r="97" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>34</v>
@@ -7704,19 +7716,19 @@
     </row>
     <row r="98" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>34</v>
@@ -7773,19 +7785,19 @@
     </row>
     <row r="99" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>34</v>
@@ -7842,16 +7854,16 @@
     </row>
     <row r="100" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>28</v>
@@ -7913,19 +7925,19 @@
     </row>
     <row r="101" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>34</v>
@@ -7984,19 +7996,19 @@
     </row>
     <row r="102" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>34</v>
@@ -8055,16 +8067,16 @@
     </row>
     <row r="103" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D103" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>28</v>
@@ -8111,24 +8123,24 @@
       </c>
       <c r="V103" s="3"/>
       <c r="W103" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D104" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>32</v>
@@ -8172,24 +8184,24 @@
       </c>
       <c r="V104" s="3"/>
       <c r="W104" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D105" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>32</v>
@@ -8233,21 +8245,21 @@
       </c>
       <c r="V105" s="3"/>
       <c r="W105" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="106" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>28</v>
@@ -8285,19 +8297,19 @@
     </row>
     <row r="107" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>34</v>
@@ -8332,19 +8344,19 @@
     </row>
     <row r="108" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>34</v>
@@ -8379,13 +8391,13 @@
     </row>
     <row r="109" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>37</v>
@@ -8424,13 +8436,13 @@
     </row>
     <row r="110" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>37</v>
@@ -8469,19 +8481,19 @@
     </row>
     <row r="111" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E111" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>34</v>
@@ -8516,19 +8528,19 @@
     </row>
     <row r="112" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>34</v>
@@ -8563,19 +8575,19 @@
     </row>
     <row r="113" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>34</v>
@@ -8610,19 +8622,19 @@
     </row>
     <row r="114" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>34</v>
@@ -8657,19 +8669,19 @@
     </row>
     <row r="115" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>34</v>
@@ -8704,19 +8716,19 @@
     </row>
     <row r="116" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>34</v>
@@ -8751,19 +8763,19 @@
     </row>
     <row r="117" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>34</v>
@@ -8796,19 +8808,19 @@
     </row>
     <row r="118" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>34</v>
@@ -8841,19 +8853,19 @@
     </row>
     <row r="119" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>34</v>
@@ -8886,19 +8898,19 @@
     </row>
     <row r="120" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>34</v>
@@ -8931,19 +8943,19 @@
     </row>
     <row r="121" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>34</v>
@@ -8976,19 +8988,19 @@
     </row>
     <row r="122" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>34</v>
@@ -9021,19 +9033,19 @@
     </row>
     <row r="123" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>34</v>
@@ -9066,13 +9078,13 @@
     </row>
     <row r="124" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>27</v>
@@ -9135,13 +9147,13 @@
     </row>
     <row r="125" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="C125" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>37</v>
@@ -9150,7 +9162,7 @@
         <v>28</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G125" s="4">
         <v>10</v>
@@ -9206,13 +9218,13 @@
     </row>
     <row r="126" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="C126" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>37</v>
@@ -9221,7 +9233,7 @@
         <v>39</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G126" s="4">
         <v>7.6</v>
@@ -9275,13 +9287,13 @@
     </row>
     <row r="127" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>37</v>
@@ -9290,7 +9302,7 @@
         <v>40</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G127" s="4">
         <v>14.4</v>
@@ -9344,13 +9356,13 @@
     </row>
     <row r="128" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>27</v>
@@ -9404,18 +9416,18 @@
         <v>42.5</v>
       </c>
       <c r="W128" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="129" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>37</v>
@@ -9478,13 +9490,13 @@
     </row>
     <row r="130" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B130" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>37</v>
@@ -9545,13 +9557,13 @@
     </row>
     <row r="131" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>37</v>
@@ -9612,13 +9624,13 @@
     </row>
     <row r="132" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>37</v>
@@ -9681,13 +9693,13 @@
     </row>
     <row r="133" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>37</v>
@@ -9750,13 +9762,13 @@
     </row>
     <row r="134" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B134" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>37</v>
@@ -9819,13 +9831,13 @@
     </row>
     <row r="135" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>27</v>
@@ -9890,13 +9902,13 @@
     </row>
     <row r="136" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C136" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>27</v>
@@ -9905,7 +9917,7 @@
         <v>28</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G136" s="4">
         <v>732401.6</v>
@@ -9952,18 +9964,18 @@
       </c>
       <c r="V136" s="3"/>
       <c r="W136" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="137" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="C137" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>27</v>
@@ -10019,24 +10031,24 @@
       </c>
       <c r="V137" s="3"/>
       <c r="W137" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="C138" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D138" s="2" t="s">
+      <c r="E138" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>34</v>
@@ -10072,24 +10084,24 @@
       </c>
       <c r="V138" s="3"/>
       <c r="W138" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="139" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="C139" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="E139" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>34</v>
@@ -10125,18 +10137,18 @@
       </c>
       <c r="V139" s="3"/>
       <c r="W139" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="140" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>37</v>
@@ -10199,13 +10211,13 @@
     </row>
     <row r="141" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>37</v>
@@ -10268,13 +10280,13 @@
     </row>
     <row r="142" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>37</v>
@@ -10337,13 +10349,13 @@
     </row>
     <row r="143" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>27</v>
@@ -10406,13 +10418,13 @@
     </row>
     <row r="144" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>27</v>
@@ -10421,7 +10433,7 @@
         <v>28</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G144" s="7">
         <v>0.26500000000000001</v>
@@ -10473,13 +10485,13 @@
     </row>
     <row r="145" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="C145" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>27</v>
@@ -10488,7 +10500,7 @@
         <v>28</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G145" s="5">
         <v>1.73</v>
@@ -10537,21 +10549,21 @@
       </c>
       <c r="V145" s="3"/>
       <c r="W145" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="146" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="D146" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>28</v>
@@ -10606,24 +10618,24 @@
       </c>
       <c r="V146" s="3"/>
       <c r="W146" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D147" s="2" t="s">
+      <c r="E147" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>34</v>
@@ -10675,24 +10687,24 @@
       </c>
       <c r="V147" s="3"/>
       <c r="W147" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="148" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="D148" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="E148" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>34</v>
@@ -10744,24 +10756,24 @@
       </c>
       <c r="V148" s="3"/>
       <c r="W148" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="149" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C149" s="2" t="s">
+      <c r="D149" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="E149" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>34</v>
@@ -10813,21 +10825,21 @@
       </c>
       <c r="V149" s="3"/>
       <c r="W149" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="150" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="D150" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>28</v>
@@ -10882,24 +10894,24 @@
       </c>
       <c r="V150" s="3"/>
       <c r="W150" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="E151" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>34</v>
@@ -10951,24 +10963,24 @@
       </c>
       <c r="V151" s="3"/>
       <c r="W151" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="152" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="E152" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>34</v>
@@ -11020,24 +11032,24 @@
       </c>
       <c r="V152" s="3"/>
       <c r="W152" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="153" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="D153" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="E153" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>34</v>
@@ -11089,18 +11101,18 @@
       </c>
       <c r="V153" s="3"/>
       <c r="W153" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="154" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C154" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>27</v>
@@ -11163,13 +11175,13 @@
     </row>
     <row r="155" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="C155" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>27</v>
@@ -11228,13 +11240,13 @@
     </row>
     <row r="156" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="C156" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>27</v>
@@ -11243,7 +11255,7 @@
         <v>28</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G156" s="6">
         <v>39</v>
@@ -11282,18 +11294,18 @@
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
       <c r="W156" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="157" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>27</v>
@@ -11302,7 +11314,7 @@
         <v>28</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="3"/>
@@ -11337,21 +11349,21 @@
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
       <c r="W157" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D158" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>28</v>
@@ -11411,19 +11423,19 @@
     </row>
     <row r="159" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D159" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E159" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>34</v>
@@ -11480,19 +11492,19 @@
     </row>
     <row r="160" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D160" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>34</v>
@@ -11549,19 +11561,19 @@
     </row>
     <row r="161" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="D161" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E161" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>34</v>
@@ -11618,19 +11630,19 @@
     </row>
     <row r="162" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D162" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>34</v>
@@ -11687,19 +11699,19 @@
     </row>
     <row r="163" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D163" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>34</v>
@@ -11756,19 +11768,19 @@
     </row>
     <row r="164" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D164" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>34</v>
@@ -11825,19 +11837,19 @@
     </row>
     <row r="165" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D165" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>34</v>
@@ -11894,19 +11906,19 @@
     </row>
     <row r="166" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D166" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>34</v>
@@ -11963,19 +11975,19 @@
     </row>
     <row r="167" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D167" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>34</v>
@@ -12032,19 +12044,19 @@
     </row>
     <row r="168" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D168" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>34</v>
@@ -12101,13 +12113,13 @@
     </row>
     <row r="169" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>37</v>
@@ -12170,13 +12182,13 @@
     </row>
     <row r="170" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>37</v>
@@ -12239,19 +12251,19 @@
     </row>
     <row r="171" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D171" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>34</v>
@@ -12308,19 +12320,19 @@
     </row>
     <row r="172" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D172" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E172" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>34</v>
@@ -12377,19 +12389,19 @@
     </row>
     <row r="173" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D173" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>34</v>
@@ -12446,19 +12458,19 @@
     </row>
     <row r="174" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D174" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>34</v>
@@ -12515,19 +12527,19 @@
     </row>
     <row r="175" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D175" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>34</v>
@@ -12584,16 +12596,16 @@
     </row>
     <row r="176" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D176" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>28</v>
@@ -12653,19 +12665,19 @@
     </row>
     <row r="177" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D177" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>34</v>
@@ -12722,19 +12734,19 @@
     </row>
     <row r="178" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="D178" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E178" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>34</v>
@@ -12791,16 +12803,16 @@
     </row>
     <row r="179" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D179" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>28</v>
@@ -12860,19 +12872,19 @@
     </row>
     <row r="180" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D180" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>34</v>
@@ -12929,19 +12941,19 @@
     </row>
     <row r="181" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D181" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E181" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E181" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>34</v>
@@ -12998,13 +13010,13 @@
     </row>
     <row r="182" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>37</v>
@@ -13067,13 +13079,13 @@
     </row>
     <row r="183" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>37</v>
@@ -13136,19 +13148,19 @@
     </row>
     <row r="184" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="D184" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E184" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>34</v>
@@ -13205,19 +13217,19 @@
     </row>
     <row r="185" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D185" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>34</v>
@@ -13274,19 +13286,19 @@
     </row>
     <row r="186" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C186" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D186" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>34</v>
@@ -13343,19 +13355,19 @@
     </row>
     <row r="187" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D187" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E187" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>34</v>
@@ -13412,16 +13424,16 @@
     </row>
     <row r="188" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>28</v>
@@ -13481,19 +13493,19 @@
     </row>
     <row r="189" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>34</v>
@@ -13550,19 +13562,19 @@
     </row>
     <row r="190" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E190" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>34</v>
@@ -13619,13 +13631,13 @@
     </row>
     <row r="191" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>37</v>
@@ -13688,13 +13700,13 @@
     </row>
     <row r="192" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>37</v>
@@ -13757,16 +13769,16 @@
     </row>
     <row r="193" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>28</v>
@@ -13828,19 +13840,19 @@
     </row>
     <row r="194" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>34</v>
@@ -13899,19 +13911,19 @@
     </row>
     <row r="195" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D195" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E195" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>34</v>
@@ -13970,16 +13982,16 @@
     </row>
     <row r="196" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D196" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>28</v>
@@ -14037,19 +14049,19 @@
     </row>
     <row r="197" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D197" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>32</v>
@@ -14104,19 +14116,19 @@
     </row>
     <row r="198" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="D198" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E198" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>32</v>
@@ -14171,13 +14183,13 @@
     </row>
     <row r="199" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="C199" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>27</v>
@@ -14186,7 +14198,7 @@
         <v>28</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="6">
@@ -14235,18 +14247,18 @@
         <v>39</v>
       </c>
       <c r="W199" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="200" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>27</v>
@@ -14304,18 +14316,18 @@
       </c>
       <c r="V200" s="3"/>
       <c r="W200" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="201" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>27</v>
@@ -14380,13 +14392,13 @@
     </row>
     <row r="202" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>27</v>
@@ -14395,7 +14407,7 @@
         <v>28</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G202" s="4">
         <v>30.8</v>
@@ -14432,18 +14444,18 @@
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
       <c r="W202" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="203" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>27</v>
@@ -14452,7 +14464,7 @@
         <v>28</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G203" s="4">
         <v>4.9000000000000004</v>
@@ -14506,13 +14518,13 @@
     </row>
     <row r="204" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="C204" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>250</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>27</v>
@@ -14575,13 +14587,13 @@
     </row>
     <row r="205" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="C205" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>27</v>
@@ -14644,13 +14656,13 @@
     </row>
     <row r="206" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>27</v>
@@ -14705,13 +14717,13 @@
     </row>
     <row r="207" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>37</v>
@@ -14720,7 +14732,7 @@
         <v>28</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G207" s="4">
         <v>31.1</v>
@@ -14774,13 +14786,13 @@
     </row>
     <row r="208" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>37</v>
@@ -14789,7 +14801,7 @@
         <v>39</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="3"/>
@@ -14831,13 +14843,13 @@
     </row>
     <row r="209" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>37</v>
@@ -14846,7 +14858,7 @@
         <v>40</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G209" s="3"/>
       <c r="H209" s="3"/>
@@ -14888,22 +14900,22 @@
     </row>
     <row r="210" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C210" s="2" t="s">
+      <c r="D210" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F210" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G210" s="3"/>
       <c r="H210" s="3"/>
@@ -14937,22 +14949,22 @@
     </row>
     <row r="211" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C211" s="2" t="s">
+      <c r="D211" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="F211" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="3"/>
@@ -14986,22 +14998,22 @@
     </row>
     <row r="212" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C212" s="2" t="s">
+      <c r="D212" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F212" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="3"/>
@@ -15035,22 +15047,22 @@
     </row>
     <row r="213" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="D213" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F213" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G213" s="3"/>
       <c r="H213" s="3"/>
@@ -15084,22 +15096,22 @@
     </row>
     <row r="214" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="D214" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F214" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G214" s="3"/>
       <c r="H214" s="3"/>
@@ -15133,22 +15145,22 @@
     </row>
     <row r="215" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="D215" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F215" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="3"/>
@@ -15182,22 +15194,22 @@
     </row>
     <row r="216" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="D216" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F216" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="3"/>
@@ -15231,13 +15243,13 @@
     </row>
     <row r="217" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>27</v>
@@ -15279,18 +15291,18 @@
         <v>372</v>
       </c>
       <c r="W217" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="218" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -15355,13 +15367,13 @@
     </row>
     <row r="219" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="C219" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>27</v>
@@ -15416,13 +15428,13 @@
     </row>
     <row r="220" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C220" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>27</v>
@@ -15431,7 +15443,7 @@
         <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G220" s="4">
         <v>24.7</v>
@@ -15485,13 +15497,13 @@
     </row>
     <row r="221" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C221" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>27</v>
@@ -15548,13 +15560,13 @@
     </row>
     <row r="222" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C222" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>27</v>
@@ -15617,13 +15629,13 @@
     </row>
     <row r="223" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C223" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>27</v>
@@ -15681,24 +15693,24 @@
       </c>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="224" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C224" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="E224" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>34</v>
@@ -15755,19 +15767,19 @@
     </row>
     <row r="225" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C225" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E225" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>34</v>
@@ -15824,19 +15836,19 @@
     </row>
     <row r="226" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C226" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D226" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D226" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E226" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>34</v>
@@ -15893,19 +15905,19 @@
     </row>
     <row r="227" spans="1:23" ht="63" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="C227" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E227" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>34</v>
@@ -15962,13 +15974,13 @@
     </row>
     <row r="228" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>27</v>
@@ -16003,13 +16015,13 @@
     </row>
     <row r="229" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>27</v>
@@ -16072,13 +16084,13 @@
     </row>
     <row r="230" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>27</v>
@@ -16141,13 +16153,13 @@
     </row>
     <row r="231" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>27</v>
@@ -16190,13 +16202,13 @@
     </row>
     <row r="232" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>27</v>
@@ -16239,13 +16251,13 @@
     </row>
     <row r="233" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>27</v>
@@ -16308,13 +16320,13 @@
     </row>
     <row r="234" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>27</v>
@@ -16323,7 +16335,7 @@
         <v>28</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G234" s="3"/>
       <c r="H234" s="3"/>
@@ -16373,13 +16385,13 @@
     </row>
     <row r="235" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>27</v>
@@ -16388,7 +16400,7 @@
         <v>28</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G235" s="3"/>
       <c r="H235" s="3"/>
@@ -16409,18 +16421,18 @@
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
       <c r="W235" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="236" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>27</v>
@@ -16429,7 +16441,7 @@
         <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G236" s="3"/>
       <c r="H236" s="3"/>
@@ -16479,13 +16491,13 @@
     </row>
     <row r="237" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>27</v>
@@ -16533,18 +16545,18 @@
       </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="238" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>27</v>
@@ -16607,13 +16619,13 @@
     </row>
     <row r="239" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B239" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16678,13 +16690,13 @@
     </row>
     <row r="240" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16749,13 +16761,13 @@
     </row>
     <row r="241" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>27</v>
@@ -16800,13 +16812,13 @@
     </row>
     <row r="242" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>27</v>
@@ -16853,13 +16865,13 @@
     </row>
     <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>27</v>
@@ -16868,7 +16880,7 @@
         <v>28</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G243" s="6">
         <v>22795</v>
@@ -16922,13 +16934,13 @@
     </row>
     <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>27</v>
@@ -16937,7 +16949,7 @@
         <v>28</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G244" s="6">
         <v>961</v>
@@ -16991,13 +17003,13 @@
     </row>
     <row r="245" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>27</v>
@@ -17055,18 +17067,18 @@
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="C246" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>27</v>
@@ -17075,7 +17087,7 @@
         <v>28</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G246" s="5">
         <v>0.59</v>
@@ -17124,18 +17136,18 @@
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B247" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="C247" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>27</v>
@@ -17144,7 +17156,7 @@
         <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G247" s="5">
         <v>16.5</v>
@@ -17193,18 +17205,18 @@
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="248" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="C248" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>27</v>
@@ -17262,18 +17274,18 @@
       </c>
       <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="249" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>27</v>
@@ -17325,18 +17337,18 @@
       <c r="U249" s="3"/>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="C250" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>27</v>
@@ -17345,7 +17357,7 @@
         <v>28</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G250" s="4">
         <v>100</v>
@@ -17394,18 +17406,18 @@
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="C251" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>27</v>
@@ -17414,7 +17426,7 @@
         <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G251" s="4">
         <v>100</v>
@@ -17463,21 +17475,21 @@
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C252" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="D252" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>28</v>
@@ -17532,24 +17544,24 @@
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="253" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C253" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="D253" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E253" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>34</v>
@@ -17601,24 +17613,24 @@
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="D254" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>34</v>
@@ -17670,24 +17682,24 @@
       </c>
       <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="D255" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>34</v>
@@ -17739,27 +17751,27 @@
       </c>
       <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G256" s="6">
         <v>563</v>
@@ -17813,22 +17825,22 @@
     </row>
     <row r="257" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F257" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E257" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="G257" s="6">
         <v>440</v>
@@ -17882,22 +17894,22 @@
     </row>
     <row r="258" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C258" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F258" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="G258" s="6">
         <v>123</v>
@@ -17951,13 +17963,13 @@
     </row>
     <row r="259" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>27</v>
@@ -17966,7 +17978,7 @@
         <v>28</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G259" s="6">
         <v>2218</v>
@@ -18017,18 +18029,18 @@
         <v>37777</v>
       </c>
       <c r="W259" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="260" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B260" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>27</v>
@@ -18089,22 +18101,22 @@
     </row>
     <row r="261" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D261" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E261" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F261" s="3" t="s">
         <v>338</v>
-      </c>
-      <c r="F261" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="G261" s="5">
         <v>137.94999999999999</v>
@@ -18158,22 +18170,22 @@
     </row>
     <row r="262" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G262" s="6">
         <v>5248</v>
@@ -18227,13 +18239,13 @@
     </row>
     <row r="263" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B263" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -18242,7 +18254,7 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G263" s="5">
         <v>0.55000000000000004</v>
@@ -18296,13 +18308,13 @@
     </row>
     <row r="264" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18311,7 +18323,7 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G264" s="4">
         <v>732401.6</v>
@@ -18358,18 +18370,18 @@
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="265" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18378,7 +18390,7 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="3"/>
@@ -18419,18 +18431,18 @@
         <v>5.95</v>
       </c>
       <c r="W265" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B266" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18439,7 +18451,7 @@
         <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="3"/>
@@ -18474,18 +18486,18 @@
         <v>86</v>
       </c>
       <c r="W266" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B267" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18494,7 +18506,7 @@
         <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="3"/>
@@ -18521,18 +18533,18 @@
         <v>4</v>
       </c>
       <c r="W267" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18541,7 +18553,7 @@
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G268" s="3"/>
       <c r="H268" s="3"/>
@@ -18570,24 +18582,24 @@
         <v>89</v>
       </c>
       <c r="W268" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="269" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="C269" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C269" s="2" t="s">
+      <c r="D269" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D269" s="2" t="s">
+      <c r="E269" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="E269" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>34</v>
@@ -18639,24 +18651,24 @@
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="C270" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C270" s="2" t="s">
+      <c r="D270" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D270" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="E270" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>34</v>
@@ -18708,24 +18720,24 @@
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="C271" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C271" s="2" t="s">
+      <c r="D271" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D271" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="E271" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>34</v>
@@ -18777,24 +18789,24 @@
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="272" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B272" s="2" t="s">
+      <c r="C272" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C272" s="2" t="s">
+      <c r="D272" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D272" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="E272" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>34</v>
@@ -18846,18 +18858,18 @@
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="273" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B273" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18866,7 +18878,7 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G273" s="4">
         <v>100</v>
@@ -18920,13 +18932,13 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B274" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -18935,7 +18947,7 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G274" s="4">
         <v>59.5</v>
@@ -18989,13 +19001,13 @@
     </row>
     <row r="275" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="C275" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>27</v>
@@ -19004,7 +19016,7 @@
         <v>28</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G275" s="4">
         <v>90.8</v>
@@ -19053,18 +19065,18 @@
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="276" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B276" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="C276" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -19122,18 +19134,18 @@
       </c>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="C277" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -19196,13 +19208,13 @@
     </row>
     <row r="278" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B278" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C278" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>27</v>
@@ -19211,7 +19223,7 @@
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G278" s="6">
         <v>28</v>
@@ -19260,18 +19272,18 @@
       </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>37</v>
@@ -19334,13 +19346,13 @@
     </row>
     <row r="280" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>37</v>
@@ -19403,13 +19415,13 @@
     </row>
     <row r="281" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>37</v>
@@ -19472,13 +19484,13 @@
     </row>
     <row r="282" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>27</v>
@@ -19541,13 +19553,13 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>27</v>
@@ -19556,7 +19568,7 @@
         <v>28</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G283" s="6">
         <v>70108</v>
@@ -19610,13 +19622,13 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>27</v>
@@ -19679,13 +19691,13 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B285" s="2" t="s">
+      <c r="C285" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>27</v>
@@ -19745,18 +19757,18 @@
         <v>86</v>
       </c>
       <c r="W285" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="C286" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>27</v>
@@ -19800,18 +19812,18 @@
       </c>
       <c r="V286" s="3"/>
       <c r="W286" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>391</v>
-      </c>
       <c r="C287" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>27</v>
@@ -19820,67 +19832,41 @@
         <v>28</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="G287" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H287" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I287" s="5">
-        <v>1</v>
-      </c>
-      <c r="J287" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K287" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L287" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M287" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N287" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O287" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P287" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q287" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R287" s="5">
-        <v>0.83</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G287" s="3"/>
+      <c r="H287" s="3"/>
+      <c r="I287" s="3"/>
+      <c r="J287" s="3"/>
+      <c r="K287" s="3"/>
+      <c r="L287" s="3"/>
+      <c r="M287" s="3"/>
+      <c r="N287" s="3"/>
+      <c r="O287" s="3"/>
+      <c r="P287" s="3"/>
+      <c r="Q287" s="3"/>
+      <c r="R287" s="3"/>
       <c r="S287" s="5">
-        <v>0.72</v>
+        <v>33109.31</v>
       </c>
       <c r="T287" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U287" s="5">
-        <v>0.69</v>
-      </c>
+        <v>33829.39</v>
+      </c>
+      <c r="U287" s="3"/>
       <c r="V287" s="3"/>
       <c r="W287" s="2" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D288" s="2" t="s">
         <v>27</v>
@@ -19889,124 +19875,130 @@
         <v>28</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>292</v>
+        <v>393</v>
       </c>
       <c r="G288" s="5">
-        <v>1.84</v>
+        <v>1.02</v>
       </c>
       <c r="H288" s="5">
-        <v>1.79</v>
+        <v>0.96</v>
       </c>
       <c r="I288" s="5">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J288" s="5">
-        <v>1.79</v>
+        <v>1.05</v>
       </c>
       <c r="K288" s="5">
-        <v>1.86</v>
+        <v>1.06</v>
       </c>
       <c r="L288" s="5">
-        <v>2.21</v>
+        <v>0.95</v>
       </c>
       <c r="M288" s="5">
-        <v>1.99</v>
+        <v>0.91</v>
       </c>
       <c r="N288" s="5">
-        <v>1.88</v>
+        <v>0.81</v>
       </c>
       <c r="O288" s="5">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="P288" s="5">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q288" s="5">
-        <v>2.21</v>
+        <v>0.85</v>
       </c>
       <c r="R288" s="5">
-        <v>2.19</v>
+        <v>0.83</v>
       </c>
       <c r="S288" s="5">
-        <v>2.21</v>
+        <v>0.72</v>
       </c>
       <c r="T288" s="5">
-        <v>3.27</v>
+        <v>0.78</v>
       </c>
       <c r="U288" s="5">
-        <v>4.07</v>
+        <v>0.69</v>
       </c>
       <c r="V288" s="3"/>
       <c r="W288" s="2" t="s">
-        <v>396</v>
+        <v>204</v>
       </c>
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G289" s="6">
-        <v>10</v>
-      </c>
-      <c r="H289" s="6">
-        <v>9</v>
-      </c>
-      <c r="I289" s="6">
-        <v>11</v>
-      </c>
-      <c r="J289" s="6">
-        <v>11</v>
-      </c>
-      <c r="K289" s="6">
-        <v>15</v>
-      </c>
-      <c r="L289" s="6">
-        <v>16</v>
-      </c>
-      <c r="M289" s="6">
-        <v>19</v>
-      </c>
-      <c r="N289" s="6">
-        <v>21</v>
-      </c>
-      <c r="O289" s="6">
-        <v>25</v>
-      </c>
-      <c r="P289" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q289" s="6">
-        <v>34</v>
-      </c>
-      <c r="R289" s="6">
-        <v>40</v>
-      </c>
-      <c r="S289" s="3"/>
-      <c r="T289" s="3"/>
-      <c r="U289" s="3"/>
+        <v>291</v>
+      </c>
+      <c r="G289" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H289" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I289" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J289" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K289" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L289" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M289" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N289" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O289" s="5">
+        <v>2</v>
+      </c>
+      <c r="P289" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q289" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R289" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S289" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T289" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U289" s="5">
+        <v>4.07</v>
+      </c>
       <c r="V289" s="3"/>
       <c r="W289" s="2" t="s">
-        <v>30</v>
+        <v>396</v>
       </c>
     </row>
     <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>397</v>
@@ -20015,1075 +20007,1123 @@
         <v>398</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G290" s="6">
-        <v>10</v>
-      </c>
-      <c r="H290" s="6">
-        <v>9</v>
-      </c>
-      <c r="I290" s="6">
-        <v>11</v>
-      </c>
-      <c r="J290" s="6">
-        <v>12</v>
-      </c>
-      <c r="K290" s="6">
-        <v>14</v>
-      </c>
-      <c r="L290" s="6">
-        <v>15</v>
-      </c>
-      <c r="M290" s="6">
-        <v>19</v>
-      </c>
-      <c r="N290" s="6">
-        <v>21</v>
-      </c>
-      <c r="O290" s="6">
-        <v>24</v>
-      </c>
-      <c r="P290" s="6">
-        <v>31</v>
-      </c>
-      <c r="Q290" s="6">
-        <v>32</v>
-      </c>
-      <c r="R290" s="6">
-        <v>39</v>
-      </c>
+      <c r="G290" s="3"/>
+      <c r="H290" s="3"/>
+      <c r="I290" s="3"/>
+      <c r="J290" s="3"/>
+      <c r="K290" s="3"/>
+      <c r="L290" s="3"/>
+      <c r="M290" s="3"/>
+      <c r="N290" s="3"/>
+      <c r="O290" s="3"/>
+      <c r="P290" s="3"/>
+      <c r="Q290" s="3"/>
+      <c r="R290" s="3"/>
       <c r="S290" s="3"/>
       <c r="T290" s="3"/>
-      <c r="U290" s="3"/>
-      <c r="V290" s="3"/>
+      <c r="U290" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="V290" s="4">
+        <v>51.3</v>
+      </c>
       <c r="W290" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G291" s="6">
-        <v>10</v>
-      </c>
-      <c r="H291" s="6">
-        <v>9</v>
-      </c>
-      <c r="I291" s="6">
-        <v>10</v>
-      </c>
-      <c r="J291" s="6">
-        <v>11</v>
-      </c>
-      <c r="K291" s="6">
-        <v>15</v>
-      </c>
-      <c r="L291" s="6">
-        <v>16</v>
-      </c>
-      <c r="M291" s="6">
-        <v>19</v>
-      </c>
-      <c r="N291" s="6">
-        <v>21</v>
-      </c>
-      <c r="O291" s="6">
-        <v>26</v>
-      </c>
-      <c r="P291" s="6">
-        <v>32</v>
-      </c>
-      <c r="Q291" s="6">
-        <v>35</v>
-      </c>
-      <c r="R291" s="6">
-        <v>41</v>
-      </c>
-      <c r="S291" s="3"/>
-      <c r="T291" s="3"/>
-      <c r="U291" s="3"/>
-      <c r="V291" s="3"/>
+      <c r="G291" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="H291" s="4">
+        <v>27.6</v>
+      </c>
+      <c r="I291" s="4">
+        <v>31.6</v>
+      </c>
+      <c r="J291" s="4">
+        <v>22.6</v>
+      </c>
+      <c r="K291" s="4">
+        <v>26.9</v>
+      </c>
+      <c r="L291" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="M291" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="N291" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="O291" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="P291" s="4">
+        <v>40.4</v>
+      </c>
+      <c r="Q291" s="4">
+        <v>41.9</v>
+      </c>
+      <c r="R291" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="S291" s="4">
+        <v>55.4</v>
+      </c>
+      <c r="T291" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="U291" s="4">
+        <v>61</v>
+      </c>
+      <c r="V291" s="4">
+        <v>61.1</v>
+      </c>
       <c r="W291" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>39</v>
+        <v>400</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G292" s="6">
-        <v>12</v>
-      </c>
-      <c r="H292" s="6">
-        <v>11</v>
-      </c>
-      <c r="I292" s="6">
-        <v>13</v>
-      </c>
-      <c r="J292" s="6">
-        <v>15</v>
-      </c>
-      <c r="K292" s="6">
-        <v>18</v>
-      </c>
-      <c r="L292" s="6">
-        <v>19</v>
-      </c>
-      <c r="M292" s="6">
-        <v>23</v>
-      </c>
-      <c r="N292" s="6">
-        <v>26</v>
-      </c>
-      <c r="O292" s="6">
-        <v>30</v>
-      </c>
-      <c r="P292" s="6">
-        <v>37</v>
-      </c>
-      <c r="Q292" s="6">
-        <v>39</v>
-      </c>
-      <c r="R292" s="6">
-        <v>46</v>
-      </c>
-      <c r="S292" s="3"/>
-      <c r="T292" s="3"/>
-      <c r="U292" s="3"/>
-      <c r="V292" s="3"/>
+      <c r="G292" s="4">
+        <v>31.5</v>
+      </c>
+      <c r="H292" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="I292" s="4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J292" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K292" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="L292" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="M292" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="N292" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="O292" s="4">
+        <v>29.5</v>
+      </c>
+      <c r="P292" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Q292" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R292" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="S292" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="T292" s="4">
+        <v>44</v>
+      </c>
+      <c r="U292" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="V292" s="4">
+        <v>48.9</v>
+      </c>
       <c r="W292" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>40</v>
+        <v>401</v>
       </c>
       <c r="F293" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G293" s="6">
-        <v>6</v>
-      </c>
-      <c r="H293" s="6">
-        <v>5</v>
-      </c>
-      <c r="I293" s="6">
-        <v>6</v>
-      </c>
-      <c r="J293" s="6">
-        <v>6</v>
-      </c>
-      <c r="K293" s="6">
-        <v>9</v>
-      </c>
-      <c r="L293" s="6">
-        <v>10</v>
-      </c>
-      <c r="M293" s="6">
-        <v>12</v>
-      </c>
-      <c r="N293" s="6">
-        <v>13</v>
-      </c>
-      <c r="O293" s="6">
-        <v>17</v>
-      </c>
-      <c r="P293" s="6">
-        <v>23</v>
-      </c>
-      <c r="Q293" s="6">
-        <v>25</v>
-      </c>
-      <c r="R293" s="6">
-        <v>31</v>
-      </c>
-      <c r="S293" s="3"/>
-      <c r="T293" s="3"/>
-      <c r="U293" s="3"/>
-      <c r="V293" s="3"/>
+      <c r="G293" s="4">
+        <v>47.6</v>
+      </c>
+      <c r="H293" s="4">
+        <v>46.2</v>
+      </c>
+      <c r="I293" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="J293" s="4">
+        <v>39</v>
+      </c>
+      <c r="K293" s="4">
+        <v>46</v>
+      </c>
+      <c r="L293" s="4">
+        <v>45</v>
+      </c>
+      <c r="M293" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="N293" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="O293" s="4">
+        <v>53</v>
+      </c>
+      <c r="P293" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="Q293" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="R293" s="4">
+        <v>68.3</v>
+      </c>
+      <c r="S293" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="T293" s="4">
+        <v>81</v>
+      </c>
+      <c r="U293" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="V293" s="4">
+        <v>81.8</v>
+      </c>
       <c r="W293" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G294" s="6">
-        <v>10</v>
-      </c>
-      <c r="H294" s="6">
-        <v>6</v>
-      </c>
-      <c r="I294" s="6">
-        <v>8</v>
-      </c>
-      <c r="J294" s="6">
-        <v>9</v>
-      </c>
-      <c r="K294" s="6">
-        <v>9</v>
-      </c>
-      <c r="L294" s="6">
-        <v>8</v>
-      </c>
-      <c r="M294" s="6">
-        <v>9</v>
-      </c>
-      <c r="N294" s="6">
-        <v>11</v>
-      </c>
-      <c r="O294" s="6">
-        <v>16</v>
-      </c>
-      <c r="P294" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q294" s="6">
-        <v>21</v>
-      </c>
-      <c r="R294" s="6">
-        <v>27</v>
-      </c>
-      <c r="S294" s="3"/>
-      <c r="T294" s="3"/>
-      <c r="U294" s="3"/>
-      <c r="V294" s="3"/>
+      <c r="G294" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="H294" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="I294" s="4">
+        <v>45.3</v>
+      </c>
+      <c r="J294" s="4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="K294" s="4">
+        <v>40.1</v>
+      </c>
+      <c r="L294" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="M294" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="N294" s="4">
+        <v>45</v>
+      </c>
+      <c r="O294" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="P294" s="4">
+        <v>57.6</v>
+      </c>
+      <c r="Q294" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="R294" s="4">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="S294" s="4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T294" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="U294" s="4">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="V294" s="4">
+        <v>78.3</v>
+      </c>
       <c r="W294" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F295" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G295" s="6">
-        <v>18</v>
-      </c>
-      <c r="H295" s="6">
-        <v>16</v>
-      </c>
-      <c r="I295" s="6">
-        <v>19</v>
-      </c>
-      <c r="J295" s="6">
-        <v>20</v>
-      </c>
-      <c r="K295" s="6">
+      <c r="G295" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="H295" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="I295" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="J295" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="K295" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="L295" s="4">
+        <v>26</v>
+      </c>
+      <c r="M295" s="4">
+        <v>30</v>
+      </c>
+      <c r="N295" s="4">
         <v>28</v>
       </c>
-      <c r="L295" s="6">
-        <v>28</v>
-      </c>
-      <c r="M295" s="6">
-        <v>32</v>
-      </c>
-      <c r="N295" s="6">
+      <c r="O295" s="4">
         <v>35</v>
       </c>
-      <c r="O295" s="6">
-        <v>39</v>
-      </c>
-      <c r="P295" s="6">
-        <v>47</v>
-      </c>
-      <c r="Q295" s="6">
-        <v>53</v>
-      </c>
-      <c r="R295" s="6">
-        <v>60</v>
-      </c>
-      <c r="S295" s="3"/>
-      <c r="T295" s="3"/>
-      <c r="U295" s="3"/>
-      <c r="V295" s="3"/>
+      <c r="P295" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="Q295" s="4">
+        <v>45.1</v>
+      </c>
+      <c r="R295" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="S295" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="T295" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="U295" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="V295" s="4">
+        <v>69.900000000000006</v>
+      </c>
       <c r="W295" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>401</v>
+        <v>213</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G296" s="6">
-        <v>13</v>
-      </c>
-      <c r="H296" s="6">
-        <v>13</v>
-      </c>
-      <c r="I296" s="6">
-        <v>16</v>
-      </c>
-      <c r="J296" s="6">
-        <v>19</v>
-      </c>
-      <c r="K296" s="6">
-        <v>24</v>
-      </c>
-      <c r="L296" s="6">
-        <v>25</v>
-      </c>
-      <c r="M296" s="6">
-        <v>27</v>
-      </c>
-      <c r="N296" s="6">
-        <v>33</v>
-      </c>
-      <c r="O296" s="6">
-        <v>36</v>
-      </c>
-      <c r="P296" s="6">
-        <v>46</v>
-      </c>
-      <c r="Q296" s="6">
-        <v>48</v>
-      </c>
-      <c r="R296" s="6">
-        <v>57</v>
-      </c>
-      <c r="S296" s="3"/>
-      <c r="T296" s="3"/>
-      <c r="U296" s="3"/>
-      <c r="V296" s="3"/>
+      <c r="G296" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H296" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="I296" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="J296" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="K296" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="L296" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="M296" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="N296" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="O296" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="P296" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="R296" s="4">
+        <v>35</v>
+      </c>
+      <c r="S296" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="T296" s="4">
+        <v>44.4</v>
+      </c>
+      <c r="U296" s="4">
+        <v>50.8</v>
+      </c>
+      <c r="V296" s="4">
+        <v>51.4</v>
+      </c>
       <c r="W296" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>397</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G297" s="6">
-        <v>9</v>
-      </c>
-      <c r="H297" s="6">
-        <v>9</v>
-      </c>
-      <c r="I297" s="6">
-        <v>11</v>
-      </c>
-      <c r="J297" s="6">
-        <v>12</v>
-      </c>
-      <c r="K297" s="6">
-        <v>15</v>
-      </c>
-      <c r="L297" s="6">
-        <v>15</v>
-      </c>
-      <c r="M297" s="6">
-        <v>18</v>
-      </c>
-      <c r="N297" s="6">
-        <v>19</v>
-      </c>
-      <c r="O297" s="6">
-        <v>25</v>
-      </c>
-      <c r="P297" s="6">
-        <v>32</v>
-      </c>
-      <c r="Q297" s="6">
-        <v>35</v>
-      </c>
-      <c r="R297" s="6">
-        <v>43</v>
-      </c>
-      <c r="S297" s="3"/>
-      <c r="T297" s="3"/>
-      <c r="U297" s="3"/>
-      <c r="V297" s="3"/>
+      <c r="G297" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H297" s="4">
+        <v>5</v>
+      </c>
+      <c r="I297" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J297" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K297" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L297" s="4">
+        <v>6</v>
+      </c>
+      <c r="M297" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N297" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O297" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P297" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q297" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R297" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S297" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T297" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U297" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V297" s="4">
+        <v>27.6</v>
+      </c>
       <c r="W297" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>403</v>
+        <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G298" s="6">
-        <v>4</v>
-      </c>
-      <c r="H298" s="6">
-        <v>5</v>
-      </c>
-      <c r="I298" s="6">
+      <c r="G298" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H298" s="4">
         <v>6</v>
       </c>
-      <c r="J298" s="6">
-        <v>6</v>
-      </c>
-      <c r="K298" s="6">
-        <v>7</v>
-      </c>
-      <c r="L298" s="6">
-        <v>10</v>
-      </c>
-      <c r="M298" s="6">
-        <v>12</v>
-      </c>
-      <c r="N298" s="6">
-        <v>12</v>
-      </c>
-      <c r="O298" s="6">
-        <v>14</v>
-      </c>
-      <c r="P298" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q298" s="6">
-        <v>23</v>
-      </c>
-      <c r="R298" s="6">
-        <v>29</v>
-      </c>
-      <c r="S298" s="3"/>
-      <c r="T298" s="3"/>
-      <c r="U298" s="3"/>
-      <c r="V298" s="3"/>
+      <c r="I298" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J298" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K298" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L298" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M298" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N298" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O298" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P298" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q298" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R298" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S298" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T298" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U298" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V298" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W298" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>404</v>
+        <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G299" s="6">
-        <v>2</v>
+        <v>674</v>
       </c>
       <c r="H299" s="6">
-        <v>2</v>
+        <v>605</v>
       </c>
       <c r="I299" s="6">
-        <v>2</v>
+        <v>1082</v>
       </c>
       <c r="J299" s="6">
-        <v>2</v>
+        <v>1219</v>
       </c>
       <c r="K299" s="6">
-        <v>4</v>
+        <v>1282</v>
       </c>
       <c r="L299" s="6">
-        <v>3</v>
+        <v>1456</v>
       </c>
       <c r="M299" s="6">
-        <v>4</v>
+        <v>1926</v>
       </c>
       <c r="N299" s="6">
-        <v>5</v>
+        <v>3182</v>
       </c>
       <c r="O299" s="6">
-        <v>6</v>
+        <v>3739</v>
       </c>
       <c r="P299" s="6">
-        <v>8</v>
+        <v>6484</v>
       </c>
       <c r="Q299" s="6">
-        <v>9</v>
+        <v>10420</v>
       </c>
       <c r="R299" s="6">
-        <v>11</v>
-      </c>
-      <c r="S299" s="3"/>
-      <c r="T299" s="3"/>
-      <c r="U299" s="3"/>
-      <c r="V299" s="3"/>
+        <v>29483</v>
+      </c>
+      <c r="S299" s="6">
+        <v>39683</v>
+      </c>
+      <c r="T299" s="6">
+        <v>80267</v>
+      </c>
+      <c r="U299" s="6">
+        <v>103449</v>
+      </c>
+      <c r="V299" s="6">
+        <v>260783</v>
+      </c>
       <c r="W299" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G300" s="6">
+      <c r="G300" s="3"/>
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+      <c r="L300" s="3"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="3"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="5">
+        <v>18.93</v>
+      </c>
+      <c r="S300" s="3"/>
+      <c r="T300" s="5">
+        <v>21.3</v>
+      </c>
+      <c r="U300" s="3"/>
+      <c r="V300" s="5">
+        <v>23.01</v>
+      </c>
+      <c r="W300" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D301" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H300" s="6">
-        <v>27</v>
-      </c>
-      <c r="I300" s="6">
+      <c r="E301" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J300" s="6">
-        <v>30</v>
-      </c>
-      <c r="K300" s="6">
-        <v>39</v>
-      </c>
-      <c r="L300" s="6">
-        <v>41</v>
-      </c>
-      <c r="M300" s="6">
-        <v>45</v>
-      </c>
-      <c r="N300" s="6">
-        <v>49</v>
-      </c>
-      <c r="O300" s="6">
-        <v>55</v>
-      </c>
-      <c r="P300" s="6">
-        <v>64</v>
-      </c>
-      <c r="Q300" s="6">
-        <v>62</v>
-      </c>
-      <c r="R300" s="6">
-        <v>71</v>
-      </c>
-      <c r="S300" s="3"/>
-      <c r="T300" s="3"/>
-      <c r="U300" s="3"/>
-      <c r="V300" s="3"/>
-      <c r="W300" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A301" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="F301" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G301" s="6">
-        <v>7</v>
-      </c>
-      <c r="H301" s="6">
-        <v>6</v>
-      </c>
-      <c r="I301" s="6">
-        <v>8</v>
-      </c>
-      <c r="J301" s="6">
-        <v>8</v>
-      </c>
-      <c r="K301" s="6">
-        <v>10</v>
-      </c>
-      <c r="L301" s="6">
-        <v>10</v>
-      </c>
-      <c r="M301" s="6">
-        <v>12</v>
-      </c>
-      <c r="N301" s="6">
-        <v>14</v>
-      </c>
-      <c r="O301" s="6">
-        <v>17</v>
-      </c>
-      <c r="P301" s="6">
-        <v>23</v>
-      </c>
-      <c r="Q301" s="6">
-        <v>25</v>
-      </c>
-      <c r="R301" s="6">
-        <v>29</v>
-      </c>
-      <c r="S301" s="3"/>
-      <c r="T301" s="3"/>
-      <c r="U301" s="3"/>
+        <v>414</v>
+      </c>
+      <c r="G301" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H301" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I301" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J301" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K301" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L301" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M301" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N301" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O301" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P301" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q301" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R301" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S301" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T301" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U301" s="5">
+        <v>1840.15</v>
+      </c>
       <c r="V301" s="3"/>
       <c r="W301" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G302" s="6">
-        <v>2</v>
-      </c>
-      <c r="H302" s="6">
-        <v>1</v>
-      </c>
-      <c r="I302" s="6">
-        <v>2</v>
-      </c>
-      <c r="J302" s="6">
-        <v>1</v>
-      </c>
-      <c r="K302" s="6">
-        <v>1</v>
-      </c>
-      <c r="L302" s="6">
-        <v>2</v>
-      </c>
-      <c r="M302" s="6">
-        <v>2</v>
-      </c>
-      <c r="N302" s="6">
-        <v>2</v>
-      </c>
-      <c r="O302" s="6">
-        <v>4</v>
-      </c>
-      <c r="P302" s="6">
-        <v>5</v>
-      </c>
-      <c r="Q302" s="6">
-        <v>5</v>
-      </c>
-      <c r="R302" s="6">
-        <v>8</v>
-      </c>
-      <c r="S302" s="3"/>
-      <c r="T302" s="3"/>
-      <c r="U302" s="3"/>
+        <v>414</v>
+      </c>
+      <c r="G302" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H302" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I302" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J302" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K302" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L302" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M302" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N302" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O302" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P302" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q302" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R302" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S302" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T302" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U302" s="5">
+        <v>705.25</v>
+      </c>
       <c r="V302" s="3"/>
       <c r="W302" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G303" s="6">
-        <v>14</v>
-      </c>
-      <c r="H303" s="6">
-        <v>13</v>
-      </c>
-      <c r="I303" s="6">
-        <v>15</v>
-      </c>
-      <c r="J303" s="6">
-        <v>17</v>
-      </c>
-      <c r="K303" s="6">
-        <v>21</v>
-      </c>
-      <c r="L303" s="6">
-        <v>23</v>
-      </c>
-      <c r="M303" s="6">
-        <v>25</v>
-      </c>
-      <c r="N303" s="6">
-        <v>29</v>
-      </c>
-      <c r="O303" s="6">
-        <v>33</v>
-      </c>
-      <c r="P303" s="6">
-        <v>42</v>
-      </c>
-      <c r="Q303" s="6">
-        <v>45</v>
-      </c>
-      <c r="R303" s="6">
-        <v>52</v>
-      </c>
-      <c r="S303" s="3"/>
-      <c r="T303" s="3"/>
-      <c r="U303" s="3"/>
+      <c r="G303" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H303" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I303" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J303" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K303" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L303" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M303" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N303" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O303" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P303" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q303" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R303" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S303" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T303" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U303" s="5">
+        <v>0.21</v>
+      </c>
       <c r="V303" s="3"/>
       <c r="W303" s="2" t="s">
-        <v>30</v>
+        <v>415</v>
       </c>
     </row>
     <row r="304" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>151</v>
+        <v>28</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G304" s="6">
-        <v>15</v>
-      </c>
-      <c r="H304" s="6">
-        <v>14</v>
-      </c>
-      <c r="I304" s="6">
-        <v>16</v>
-      </c>
-      <c r="J304" s="6">
-        <v>18</v>
-      </c>
-      <c r="K304" s="6">
-        <v>23</v>
-      </c>
-      <c r="L304" s="6">
-        <v>25</v>
-      </c>
-      <c r="M304" s="6">
-        <v>27</v>
-      </c>
-      <c r="N304" s="6">
-        <v>30</v>
-      </c>
-      <c r="O304" s="6">
-        <v>35</v>
-      </c>
-      <c r="P304" s="6">
-        <v>44</v>
-      </c>
-      <c r="Q304" s="6">
-        <v>46</v>
-      </c>
-      <c r="R304" s="6">
-        <v>54</v>
-      </c>
-      <c r="S304" s="3"/>
-      <c r="T304" s="3"/>
-      <c r="U304" s="3"/>
-      <c r="V304" s="3"/>
+        <v>422</v>
+      </c>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K304" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L304" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M304" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N304" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O304" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P304" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q304" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R304" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S304" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T304" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U304" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V304" s="7">
+        <v>5.3920000000000003</v>
+      </c>
       <c r="W304" s="2" t="s">
-        <v>30</v>
+        <v>415</v>
       </c>
     </row>
     <row r="305" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G305" s="6">
-        <v>8</v>
-      </c>
-      <c r="H305" s="6">
-        <v>5</v>
-      </c>
-      <c r="I305" s="6">
-        <v>6</v>
-      </c>
-      <c r="J305" s="6">
-        <v>7</v>
-      </c>
-      <c r="K305" s="6">
-        <v>7</v>
-      </c>
-      <c r="L305" s="6">
-        <v>7</v>
-      </c>
-      <c r="M305" s="6">
-        <v>7</v>
-      </c>
-      <c r="N305" s="6">
-        <v>11</v>
-      </c>
-      <c r="O305" s="6">
-        <v>10</v>
-      </c>
-      <c r="P305" s="6">
-        <v>17</v>
-      </c>
-      <c r="Q305" s="6">
-        <v>25</v>
-      </c>
-      <c r="R305" s="6">
-        <v>22</v>
-      </c>
-      <c r="S305" s="3"/>
-      <c r="T305" s="3"/>
-      <c r="U305" s="3"/>
+        <v>414</v>
+      </c>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="3"/>
+      <c r="J305" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K305" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L305" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M305" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N305" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O305" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P305" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q305" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R305" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S305" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T305" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U305" s="5">
+        <v>8.32</v>
+      </c>
       <c r="V305" s="3"/>
       <c r="W305" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="306" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G306" s="6">
-        <v>4</v>
-      </c>
-      <c r="H306" s="6">
-        <v>3</v>
-      </c>
-      <c r="I306" s="6">
-        <v>5</v>
-      </c>
-      <c r="J306" s="6">
-        <v>4</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
       <c r="K306" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L306" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M306" s="6">
+        <v>8</v>
+      </c>
+      <c r="N306" s="6">
+        <v>2</v>
+      </c>
+      <c r="O306" s="3"/>
+      <c r="P306" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q306" s="6">
+        <v>2</v>
+      </c>
+      <c r="R306" s="3"/>
+      <c r="S306" s="3"/>
+      <c r="T306" s="6">
+        <v>8</v>
+      </c>
+      <c r="U306" s="6">
         <v>7</v>
       </c>
-      <c r="N306" s="6">
-        <v>8</v>
-      </c>
-      <c r="O306" s="6">
-        <v>9</v>
-      </c>
-      <c r="P306" s="6">
-        <v>12</v>
-      </c>
-      <c r="Q306" s="6">
-        <v>14</v>
-      </c>
-      <c r="R306" s="6">
-        <v>17</v>
-      </c>
-      <c r="S306" s="3"/>
-      <c r="T306" s="3"/>
-      <c r="U306" s="3"/>
-      <c r="V306" s="3"/>
+      <c r="V306" s="6">
+        <v>2</v>
+      </c>
       <c r="W306" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="307" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>27</v>
@@ -21092,69 +21132,65 @@
         <v>28</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G307" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H307" s="4">
-        <v>6</v>
-      </c>
-      <c r="I307" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J307" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K307" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L307" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M307" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N307" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O307" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P307" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q307" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R307" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S307" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T307" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U307" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V307" s="4">
-        <v>5.2</v>
+        <v>427</v>
+      </c>
+      <c r="G307" s="3"/>
+      <c r="H307" s="3"/>
+      <c r="I307" s="6">
+        <v>2</v>
+      </c>
+      <c r="J307" s="6">
+        <v>2</v>
+      </c>
+      <c r="K307" s="6">
+        <v>1</v>
+      </c>
+      <c r="L307" s="6">
+        <v>1</v>
+      </c>
+      <c r="M307" s="6">
+        <v>1</v>
+      </c>
+      <c r="N307" s="6">
+        <v>1</v>
+      </c>
+      <c r="O307" s="6">
+        <v>1</v>
+      </c>
+      <c r="P307" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q307" s="6">
+        <v>4</v>
+      </c>
+      <c r="R307" s="6">
+        <v>1</v>
+      </c>
+      <c r="S307" s="6">
+        <v>1</v>
+      </c>
+      <c r="T307" s="6">
+        <v>0</v>
+      </c>
+      <c r="U307" s="6">
+        <v>4</v>
+      </c>
+      <c r="V307" s="6">
+        <v>2</v>
       </c>
       <c r="W307" s="2" t="s">
-        <v>30</v>
+        <v>428</v>
       </c>
     </row>
     <row r="308" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>27</v>
@@ -21163,67 +21199,61 @@
         <v>28</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G308" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H308" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I308" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J308" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K308" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L308" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M308" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N308" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O308" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P308" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q308" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R308" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S308" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T308" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U308" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V308" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G308" s="3"/>
+      <c r="H308" s="3"/>
+      <c r="I308" s="3"/>
+      <c r="J308" s="3"/>
+      <c r="K308" s="6">
+        <v>5</v>
+      </c>
+      <c r="L308" s="6">
+        <v>13</v>
+      </c>
+      <c r="M308" s="6">
+        <v>19</v>
+      </c>
+      <c r="N308" s="6">
+        <v>18</v>
+      </c>
+      <c r="O308" s="6">
+        <v>15</v>
+      </c>
+      <c r="P308" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q308" s="6">
+        <v>8</v>
+      </c>
+      <c r="R308" s="6">
+        <v>28</v>
+      </c>
+      <c r="S308" s="6">
+        <v>53</v>
+      </c>
+      <c r="T308" s="6">
+        <v>65</v>
+      </c>
+      <c r="U308" s="6">
+        <v>70</v>
+      </c>
+      <c r="V308" s="6">
+        <v>69</v>
+      </c>
       <c r="W308" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="309" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="309" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="B309" s="2" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>27</v>
@@ -21232,507 +21262,53 @@
         <v>28</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G309" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H309" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I309" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J309" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K309" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L309" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M309" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N309" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O309" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P309" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q309" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R309" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S309" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T309" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U309" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V309" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G309" s="3"/>
+      <c r="H309" s="3"/>
+      <c r="I309" s="3"/>
+      <c r="J309" s="3"/>
+      <c r="K309" s="3"/>
+      <c r="L309" s="3"/>
+      <c r="M309" s="3"/>
+      <c r="N309" s="3"/>
+      <c r="O309" s="3"/>
+      <c r="P309" s="3"/>
+      <c r="Q309" s="3"/>
+      <c r="R309" s="3"/>
+      <c r="S309" s="3"/>
+      <c r="T309" s="6">
+        <v>114</v>
+      </c>
+      <c r="U309" s="6">
+        <v>61</v>
+      </c>
+      <c r="V309" s="6">
+        <v>97</v>
+      </c>
       <c r="W309" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="310" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A310" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E310" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F310" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G310" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H310" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I310" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J310" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K310" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L310" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M310" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N310" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O310" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P310" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q310" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R310" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S310" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T310" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U310" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V310" s="3"/>
-      <c r="W310" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="311" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A311" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E311" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F311" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G311" s="3"/>
-      <c r="H311" s="3"/>
-      <c r="I311" s="3"/>
-      <c r="J311" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K311" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L311" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M311" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N311" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O311" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P311" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q311" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R311" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S311" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T311" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U311" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V311" s="7">
-        <v>5.3920000000000003</v>
-      </c>
-      <c r="W311" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="312" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A312" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E312" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F312" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G312" s="3"/>
-      <c r="H312" s="3"/>
-      <c r="I312" s="3"/>
-      <c r="J312" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K312" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L312" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M312" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N312" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O312" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P312" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q312" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R312" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S312" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T312" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U312" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V312" s="3"/>
-      <c r="W312" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="313" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A313" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F313" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="G313" s="3"/>
-      <c r="H313" s="3"/>
-      <c r="I313" s="3"/>
-      <c r="J313" s="3"/>
-      <c r="K313" s="6">
-        <v>1</v>
-      </c>
-      <c r="L313" s="6">
-        <v>1</v>
-      </c>
-      <c r="M313" s="6">
-        <v>8</v>
-      </c>
-      <c r="N313" s="6">
-        <v>2</v>
-      </c>
-      <c r="O313" s="3"/>
-      <c r="P313" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q313" s="6">
-        <v>2</v>
-      </c>
-      <c r="R313" s="3"/>
-      <c r="S313" s="3"/>
-      <c r="T313" s="6">
-        <v>8</v>
-      </c>
-      <c r="U313" s="6">
-        <v>7</v>
-      </c>
-      <c r="V313" s="6">
-        <v>2</v>
-      </c>
-      <c r="W313" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="314" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A314" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E314" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F314" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="G314" s="3"/>
-      <c r="H314" s="3"/>
-      <c r="I314" s="6">
-        <v>2</v>
-      </c>
-      <c r="J314" s="6">
-        <v>2</v>
-      </c>
-      <c r="K314" s="6">
-        <v>1</v>
-      </c>
-      <c r="L314" s="6">
-        <v>1</v>
-      </c>
-      <c r="M314" s="6">
-        <v>1</v>
-      </c>
-      <c r="N314" s="6">
-        <v>1</v>
-      </c>
-      <c r="O314" s="6">
-        <v>1</v>
-      </c>
-      <c r="P314" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q314" s="6">
-        <v>4</v>
-      </c>
-      <c r="R314" s="6">
-        <v>1</v>
-      </c>
-      <c r="S314" s="6">
-        <v>1</v>
-      </c>
-      <c r="T314" s="6">
-        <v>0</v>
-      </c>
-      <c r="U314" s="6">
-        <v>4</v>
-      </c>
-      <c r="V314" s="6">
-        <v>2</v>
-      </c>
-      <c r="W314" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="315" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A315" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E315" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F315" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G315" s="3"/>
-      <c r="H315" s="3"/>
-      <c r="I315" s="3"/>
-      <c r="J315" s="3"/>
-      <c r="K315" s="6">
-        <v>5</v>
-      </c>
-      <c r="L315" s="6">
-        <v>13</v>
-      </c>
-      <c r="M315" s="6">
-        <v>19</v>
-      </c>
-      <c r="N315" s="6">
-        <v>18</v>
-      </c>
-      <c r="O315" s="6">
-        <v>15</v>
-      </c>
-      <c r="P315" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q315" s="6">
-        <v>8</v>
-      </c>
-      <c r="R315" s="6">
-        <v>28</v>
-      </c>
-      <c r="S315" s="6">
-        <v>53</v>
-      </c>
-      <c r="T315" s="6">
-        <v>65</v>
-      </c>
-      <c r="U315" s="6">
-        <v>70</v>
-      </c>
-      <c r="V315" s="6">
-        <v>69</v>
-      </c>
-      <c r="W315" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="316" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A316" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E316" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F316" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G316" s="3"/>
-      <c r="H316" s="3"/>
-      <c r="I316" s="3"/>
-      <c r="J316" s="3"/>
-      <c r="K316" s="3"/>
-      <c r="L316" s="3"/>
-      <c r="M316" s="3"/>
-      <c r="N316" s="3"/>
-      <c r="O316" s="3"/>
-      <c r="P316" s="3"/>
-      <c r="Q316" s="3"/>
-      <c r="R316" s="3"/>
-      <c r="S316" s="3"/>
-      <c r="T316" s="6">
-        <v>114</v>
-      </c>
-      <c r="U316" s="6">
-        <v>61</v>
-      </c>
-      <c r="V316" s="6">
-        <v>97</v>
-      </c>
-      <c r="W316" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="317" spans="1:23" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="B319" s="8"/>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="310" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A311" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="B311" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A319:B319"/>
+    <mergeCell ref="A311:B311"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.39370078740157499" bottom="0.39370078740157499" header="0.39370078740157499" footer="0.39370078740157499"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId3"/>
 </worksheet>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E222AA-AAAA-4E68-B9E1-27C0443AB02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869EBA9E-FAD2-4B65-8D24-A7F46F5FFE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="425">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -835,39 +835,15 @@
     <t>11.1.a Narażenie na nadmierny hałas</t>
   </si>
   <si>
-    <t>11.1.b Przeciętna powierzchnia użytkowa mieszkania na 1 osobę w miastach</t>
+    <t>11.1.b Udział powierzchni parków spacerowo-wypoczynkowych i zieleńców w ogólnej powierzchni miasta</t>
+  </si>
+  <si>
+    <t>11.1.c Powierzchnia parków spacerowo-wypoczynkowych i zieleńców na 1 mieszkańca w mieście</t>
   </si>
   <si>
     <t>m2</t>
   </si>
   <si>
-    <t>11.1.c Odsetek ludności miejskiej żyjącej w mieszkaniach z przeciekającym dachem, wilgotnymi ścianami, podłogami lub fundamentami lub ze zgnilizną ram okiennych lub podłóg</t>
-  </si>
-  <si>
-    <t>11.1.d Udział autobusów na alternatywne paliwo w ogólnej liczbie autobusów służących do obsługi transportu miejskiego</t>
-  </si>
-  <si>
-    <t>11.1.e Liczba przewozów pasażerskich w przeliczeniu na 1 mieszkańca obszarów miejskich</t>
-  </si>
-  <si>
-    <t>11.1.f Odsetek odpadów komunalnych przeznaczonych do przetworzenia w określony sposób w relacji do ilości odpadów wytworzonych</t>
-  </si>
-  <si>
-    <t>wg sposobu przetworzenia</t>
-  </si>
-  <si>
-    <t>recykling</t>
-  </si>
-  <si>
-    <t>kompostowanie lub fermentacja</t>
-  </si>
-  <si>
-    <t>przekształcenia termiczne</t>
-  </si>
-  <si>
-    <t>składowanie</t>
-  </si>
-  <si>
     <t>Wsparcie miast w radzeniu sobie z nagłymi zmianami, kryzysami, zarówno społeczno-gospodarczymi, jak i natury środowiskowej oraz zagwarantowanie mieszkańcom bezpieczeństwa i wysokiej jakości życia</t>
   </si>
   <si>
@@ -880,7 +856,7 @@
     <t>11.2.c Odsetek mieszkańców korzystających z wodociągu na obszarach miejskich</t>
   </si>
   <si>
-    <t>11.2.d Udział ludności mieszkającej na terenach objętych procesami rewitalizacji w ogólnej liczbie ludności na obszarach miejskich</t>
+    <t>11.2.d Udział ludności mieszkającej na terenach objętych procesami rewitalizacji w ogólnej liczbie ludności w gminach miejskich</t>
   </si>
   <si>
     <t>11.2.e Udział powierzchni obszarów zdegradowanych w powierzchni ogółem gmin miejskich</t>
@@ -892,162 +868,162 @@
     <t>11.3.a Udział powierzchni objętej obowiązującymi miejscowymi planami zagospodarowania przestrzennego w gminach miejskich</t>
   </si>
   <si>
-    <t>11.3.b Relacja długości linii komunikacji miejskiej na wsi do długości linii komunikacji miejskiej w miastach</t>
+    <t>Budowa zrównoważonego, dostępnego dla każdego, bezpiecznego i przystępnego cenowo systemu transportowego, zwłaszcza poprzez rozwój i priorytetyzację transportu publicznego</t>
+  </si>
+  <si>
+    <t>11.4.a Długość linii komunikacji miejskiej na 1 tys. mieszkańców</t>
+  </si>
+  <si>
+    <t>kilometry</t>
+  </si>
+  <si>
+    <t>11.4.b Liczba pieszych i rowerzystów zabitych lub ciężko rannych w wypadkach na terenie zabudowanym w przeliczeniu na 100 tys. ludności</t>
+  </si>
+  <si>
+    <t>Komenda Główna Policji</t>
+  </si>
+  <si>
+    <t>11.4.c Liczba przewozów pasażerskich w przeliczeniu na 1 mieszkańca obszarów miejskich</t>
+  </si>
+  <si>
+    <t>11.4.d Udział autobusów na alternatywne paliwo w ogólnej liczbie autobusów służących do obsługi transportu miejskiego</t>
+  </si>
+  <si>
+    <t>Zaspokojenie potrzeb mieszkaniowych ludności miast dzięki budowie powszechnego i dostępnego rynku mieszkaniowego, w tym szczególnie poprzez rozwój mieszkalnictwa społecznego</t>
+  </si>
+  <si>
+    <t>11.5.a Liczba mieszkań oddanych do użytkowania w miastach w przeliczeniu na 1 tys. ludności</t>
+  </si>
+  <si>
+    <t>11.5.b Liczba mieszkań społecznych czynszowych oraz komunalnych oddanych do użytkowania w miastach w przeliczeniu na 1 tys. ludności</t>
+  </si>
+  <si>
+    <t>11.5.c Liczba gospodarstw domowych oczekujących na najem socjalny na obszarach miejskich ogółem</t>
+  </si>
+  <si>
+    <t>11.5.d Liczba mieszkań, będących w zasobach komunalnych gmin w miastach na prawach powiatu ogółem</t>
+  </si>
+  <si>
+    <t>Poprawa jakości powietrza poprzez redukcję "niskiej emisji" (tj. do 40 m n.p.g.) pochodzącej m.in. z kotłowni domowych i transportu drogowego</t>
+  </si>
+  <si>
+    <t>11.6.a Emisja zanieczyszczeń pyłowych w miastach na prawach powiatu ogółem</t>
+  </si>
+  <si>
+    <t>tony</t>
+  </si>
+  <si>
+    <t>11.6.b Odsetek zanieczyszczeń zatrzymanych lub zneutralizowanych w urządzeniach oczyszczających w zakładach szczególnie uciążliwych w miastach na prawach powiatu</t>
+  </si>
+  <si>
+    <t>wg typu zanieczyszczeń</t>
+  </si>
+  <si>
+    <t>gazowe (bez CO2)</t>
+  </si>
+  <si>
+    <t>pyłowe</t>
+  </si>
+  <si>
+    <t>11.6.c Liczba aglomeracji i miast powyżej 100 tys. mieszkańców, w których wartość wskaźnika średniego narażenia nie przekracza pułapu stężenia ekspozycji na pył PM2,5 na poziomie 20 µg/m3</t>
+  </si>
+  <si>
+    <t>Cel 12. Odpowiedzialna konsumpcja i produkcja</t>
+  </si>
+  <si>
+    <t>Zwiększenie wydajności wykorzystania zasobów oraz zmiana podejścia do zasobów polegająca na odejściu od ich linearnego zagospodarowania, a także zmiana wzorców konsumpcyjnych (rozwój gospodarki o obiegu zamkniętym)</t>
+  </si>
+  <si>
+    <t>12.1.a Produktywność zasobów</t>
+  </si>
+  <si>
+    <t>euro (w cenach stałych z 2015 r.)/kg</t>
+  </si>
+  <si>
+    <t>12.1.b Krajowa Konsumpcja Materialna (DMC) na 1 mieszkańca</t>
+  </si>
+  <si>
+    <t>12.1.c Wskaźnik powtórnego wykorzystania materiałów</t>
+  </si>
+  <si>
+    <t>Rozwój rolnictwa ekologicznego</t>
+  </si>
+  <si>
+    <t>12.2.a Udział powierzchni ekologicznych użytków rolnych z certyfikatem w gospodarstwach ekologicznych w powierzchni użytków rolnych ogółem w gospodarstwach rolnych</t>
+  </si>
+  <si>
+    <t>Cel 13. Działania w dziedzinie klimatu</t>
+  </si>
+  <si>
+    <t>Efektywne zmniejszanie koncentracji CO2 w atmosferze</t>
+  </si>
+  <si>
+    <t>13.1.a Dynamika emisji CO2 (2010=100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2010=100</t>
+  </si>
+  <si>
+    <t>Instytut Ochrony Środowiska - PIB Krajowy Ośrodek Bilansowania i Zarządzania  Emisjami (KOBIZE)</t>
+  </si>
+  <si>
+    <t>13.1.b Dynamika emisji gazów cieplarnianych (2010=100)</t>
+  </si>
+  <si>
+    <t>Wprowadzenie innowacyjnych technologii wykorzystania dostępnych źródeł energii, w tym rozwój geotermii</t>
+  </si>
+  <si>
+    <t>13.2.a Udział energii ze źródeł odnawialnych w końcowym zużyciu energii brutto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2.b Pozyskanie energii geotermalnej </t>
+  </si>
+  <si>
+    <t>TJ</t>
+  </si>
+  <si>
+    <t>w gospodarstwach domowych</t>
+  </si>
+  <si>
+    <t>w handlu i usługach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2.c Moc zainstalowana elektryczna w instalacjach OZE </t>
+  </si>
+  <si>
+    <t>megawat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agencja Rynku Energii S.A. </t>
+  </si>
+  <si>
+    <t>Wzmocnienie roli adaptacji do zmian klimatu jako równoważnego z mitygacją środka walki ze zmianą klimatu</t>
+  </si>
+  <si>
+    <t>13.3.a Inwestycje w działania na rzecz łagodzenia zmian klimatu w relacji do PKB</t>
+  </si>
+  <si>
+    <t>13.3.b Straty ekonomiczne związane z klimatem</t>
+  </si>
+  <si>
+    <t>na osobę (w cenach stałych)</t>
+  </si>
+  <si>
+    <t>euro</t>
+  </si>
+  <si>
+    <t>w mln (w cenach stałych)</t>
+  </si>
+  <si>
+    <t>Zwiększenie odporności kraju na skutki zmian klimatycznych</t>
+  </si>
+  <si>
+    <t>13.4.a Udział terenów zieleni w powierzchni ogółem</t>
   </si>
   <si>
     <t>Procent [%]</t>
   </si>
   <si>
-    <t>11.3.c Rozpiętość Wskaźnika Międzygałęziowej Dostępności Transportowej w Miejskich Obszarach Funkcjonalnych</t>
-  </si>
-  <si>
-    <t>[-]</t>
-  </si>
-  <si>
-    <t>Ministerstwo Funduszy i Polityki Regionalnej</t>
-  </si>
-  <si>
-    <t>Budowa zrównoważonego, dostępnego dla każdego, bezpiecznego i przystępnego cenowo systemu transportowego, zwłaszcza poprzez rozwój i priorytetyzację transportu publicznego</t>
-  </si>
-  <si>
-    <t>11.4.a Długość linii komunikacji miejskiej na 1 tys. mieszkańców</t>
-  </si>
-  <si>
-    <t>kilometry</t>
-  </si>
-  <si>
-    <t>11.4.b Liczba pieszych i rowerzystów zabitych lub ciężko rannych w wypadkach na terenie zabudowanym w przeliczeniu na 100 tys. ludności</t>
-  </si>
-  <si>
-    <t>Komenda Główna Policji</t>
-  </si>
-  <si>
-    <t>11.4.c Liczba przewozów pasażerskich w przeliczeniu na 1 mieszkańca obszarów miejskich</t>
-  </si>
-  <si>
-    <t>Zaspokojenie potrzeb mieszkaniowych ludności miast dzięki budowie powszechnego i dostępnego rynku mieszkaniowego, w tym szczególnie poprzez rozwój mieszkalnictwa społecznego</t>
-  </si>
-  <si>
-    <t>11.5.a Liczba mieszkań oddanych do użytkowania w miastach w przeliczeniu na 1 tys. ludności</t>
-  </si>
-  <si>
-    <t>11.5.b Liczba mieszkań społecznych czynszowych oraz komunalnych oddanych do użytkowania w miastach w przeliczeniu na 1 tys. ludności</t>
-  </si>
-  <si>
-    <t>11.5.c Liczba gospodarstw domowych oczekujących na najem socjalny na obszarach miejskich ogółem</t>
-  </si>
-  <si>
-    <t>11.5.d Liczba mieszkań, będących w zasobach komunalnych gmin w miastach na prawach powiatu ogółem</t>
-  </si>
-  <si>
-    <t>Poprawa jakości powietrza poprzez redukcję "niskiej emisji" (tj. do 40 m n.p.g.) pochodzącej m.in. z kotłowni domowych i transportu drogowego</t>
-  </si>
-  <si>
-    <t>11.6.a Emisja zanieczyszczeń pyłowych w miastach na prawach powiatu ogółem</t>
-  </si>
-  <si>
-    <t>tony</t>
-  </si>
-  <si>
-    <t>11.6.b Zdolność zainstalowanych urządzeń i instalacji do redukcji zanieczyszczeń w miastach na prawach powiatu ogółem</t>
-  </si>
-  <si>
-    <t>11.6.c Liczba aglomeracji i miast powyżej 100 tys. mieszkańców, w których wartość wskaźnika średniego narażenia nie przekracza pułapu stężenia ekspozycji na pył PM2,5 na poziomie 20 µg/m3</t>
-  </si>
-  <si>
-    <t>Cel 12. Odpowiedzialna konsumpcja i produkcja</t>
-  </si>
-  <si>
-    <t>Zwiększenie wydajności wykorzystania zasobów oraz zmiana podejścia do zasobów polegająca na odejściu od ich linearnego zagospodarowania, a także zmiana wzorców konsumpcyjnych (rozwój gospodarki o obiegu zamkniętym)</t>
-  </si>
-  <si>
-    <t>12.1.a Produktywność zasobów</t>
-  </si>
-  <si>
-    <t>euro (w cenach stałych z 2015 r.)/kg</t>
-  </si>
-  <si>
-    <t>12.1.b Krajowa Konsumpcja Materialna (DMC) na 1 mieszkańca</t>
-  </si>
-  <si>
-    <t>12.1.c Wskaźnik powtórnego wykorzystania materiałów</t>
-  </si>
-  <si>
-    <t>Rozwój rolnictwa ekologicznego</t>
-  </si>
-  <si>
-    <t>12.2.a Udział powierzchni ekologicznych użytków rolnych z certyfikatem w gospodarstwach ekologicznych w powierzchni użytków rolnych ogółem w gospodarstwach rolnych</t>
-  </si>
-  <si>
-    <t>Cel 13. Działania w dziedzinie klimatu</t>
-  </si>
-  <si>
-    <t>Efektywne zmniejszanie koncentracji CO2 w atmosferze</t>
-  </si>
-  <si>
-    <t>13.1.a Dynamika emisji CO2 (2010=100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2010=100</t>
-  </si>
-  <si>
-    <t>Instytut Ochrony Środowiska - PIB Krajowy Ośrodek Bilansowania i Zarządzania  Emisjami (KOBIZE)</t>
-  </si>
-  <si>
-    <t>13.1.b Dynamika emisji gazów cieplarnianych (2010=100)</t>
-  </si>
-  <si>
-    <t>Wprowadzenie innowacyjnych technologii wykorzystania dostępnych źródeł energii, w tym rozwój geotermii</t>
-  </si>
-  <si>
-    <t>13.2.a Udział energii ze źródeł odnawialnych w końcowym zużyciu energii brutto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2.b Pozyskanie energii geotermalnej </t>
-  </si>
-  <si>
-    <t>TJ</t>
-  </si>
-  <si>
-    <t>w gospodarstwach domowych</t>
-  </si>
-  <si>
-    <t>w handlu i usługach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2.c Moc zainstalowana elektryczna w instalacjach OZE </t>
-  </si>
-  <si>
-    <t>megawat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agencja Rynku Energii S.A. </t>
-  </si>
-  <si>
-    <t>Wzmocnienie roli adaptacji do zmian klimatu jako równoważnego z mitygacją środka walki ze zmianą klimatu</t>
-  </si>
-  <si>
-    <t>13.3.a Inwestycje w działania na rzecz łagodzenia zmian klimatu w relacji do PKB</t>
-  </si>
-  <si>
-    <t>13.3.b Straty ekonomiczne związane z klimatem</t>
-  </si>
-  <si>
-    <t>na osobę (w cenach stałych)</t>
-  </si>
-  <si>
-    <t>euro</t>
-  </si>
-  <si>
-    <t>w mln (w cenach stałych)</t>
-  </si>
-  <si>
-    <t>Zwiększenie odporności kraju na skutki zmian klimatycznych</t>
-  </si>
-  <si>
-    <t>13.4.a Udział terenów zieleni w powierzchni ogółem</t>
-  </si>
-  <si>
     <t>13.4.b Pojemność obiektów małej retencji wodnej</t>
   </si>
   <si>
@@ -1327,7 +1303,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 05-08-2026, 07:42</t>
+    <t>Ostatnia aktualizacja: 05-08-2026, 10:54</t>
   </si>
 </sst>
 </file>
@@ -1873,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W308"/>
+  <dimension ref="A1:W300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -15178,52 +15154,52 @@
         <v>28</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G215" s="4">
-        <v>24.7</v>
-      </c>
-      <c r="H215" s="4">
-        <v>25</v>
-      </c>
-      <c r="I215" s="4">
-        <v>25.4</v>
-      </c>
-      <c r="J215" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="K215" s="4">
-        <v>26.1</v>
-      </c>
-      <c r="L215" s="4">
-        <v>26.4</v>
-      </c>
-      <c r="M215" s="4">
-        <v>26.8</v>
-      </c>
-      <c r="N215" s="4">
-        <v>27.2</v>
-      </c>
-      <c r="O215" s="4">
-        <v>27.7</v>
-      </c>
-      <c r="P215" s="4">
-        <v>28.1</v>
-      </c>
-      <c r="Q215" s="4">
-        <v>29.2</v>
-      </c>
-      <c r="R215" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="S215" s="4">
-        <v>30.4</v>
-      </c>
-      <c r="T215" s="4">
-        <v>31</v>
-      </c>
-      <c r="U215" s="4">
-        <v>31.6</v>
+        <v>34</v>
+      </c>
+      <c r="G215" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H215" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="I215" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="J215" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K215" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="L215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="M215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="N215" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="O215" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="P215" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="Q215" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="R215" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="S215" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="T215" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="U215" s="5">
+        <v>1.21</v>
       </c>
       <c r="V215" s="3"/>
       <c r="W215" s="2" t="s">
@@ -15238,7 +15214,7 @@
         <v>266</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>27</v>
@@ -15247,61 +15223,67 @@
         <v>28</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="G216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="H216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="I216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="J216" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="K216" s="4">
+        <v>10.7</v>
+      </c>
+      <c r="L216" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="M216" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="N216" s="4">
+        <v>11.2</v>
+      </c>
+      <c r="O216" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="P216" s="4">
+        <v>11.8</v>
+      </c>
+      <c r="Q216" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="R216" s="4">
+        <v>12.3</v>
+      </c>
+      <c r="S216" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="T216" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="U216" s="4">
         <v>13</v>
       </c>
-      <c r="H216" s="4">
-        <v>10.3</v>
-      </c>
-      <c r="I216" s="4">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="J216" s="4">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="K216" s="4">
-        <v>8.9</v>
-      </c>
-      <c r="L216" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="M216" s="4">
-        <v>10.1</v>
-      </c>
-      <c r="N216" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="O216" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P216" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="Q216" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="R216" s="3"/>
-      <c r="S216" s="3"/>
-      <c r="T216" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="U216" s="3"/>
       <c r="V216" s="3"/>
       <c r="W216" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>27</v>
@@ -15310,67 +15292,39 @@
         <v>28</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G217" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H217" s="4">
-        <v>2.8</v>
-      </c>
-      <c r="I217" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="J217" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="K217" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="L217" s="4">
-        <v>3.6</v>
-      </c>
-      <c r="M217" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="N217" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="O217" s="4">
-        <v>7</v>
-      </c>
-      <c r="P217" s="4">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q217" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="R217" s="4">
-        <v>15.4</v>
-      </c>
-      <c r="S217" s="4">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="T217" s="4">
-        <v>21.6</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G217" s="3"/>
+      <c r="H217" s="3"/>
+      <c r="I217" s="3"/>
+      <c r="J217" s="3"/>
+      <c r="K217" s="3"/>
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+      <c r="P217" s="3"/>
+      <c r="Q217" s="3"/>
+      <c r="R217" s="3"/>
+      <c r="S217" s="3"/>
+      <c r="T217" s="3"/>
       <c r="U217" s="4">
-        <v>24.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="V217" s="3"/>
       <c r="W217" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="218" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>27</v>
@@ -15379,328 +15333,288 @@
         <v>28</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G218" s="4">
-        <v>166.5</v>
+        <v>88</v>
       </c>
       <c r="H218" s="4">
-        <v>166.2</v>
+        <v>88.4</v>
       </c>
       <c r="I218" s="4">
-        <v>165.6</v>
+        <v>91.7</v>
       </c>
       <c r="J218" s="4">
-        <v>155.5</v>
+        <v>93.3</v>
       </c>
       <c r="K218" s="4">
-        <v>159.69999999999999</v>
+        <v>93.9</v>
       </c>
       <c r="L218" s="4">
-        <v>158.30000000000001</v>
+        <v>94.6</v>
       </c>
       <c r="M218" s="4">
-        <v>162.69999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="N218" s="4">
-        <v>161.69999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="O218" s="4">
-        <v>163.4</v>
+        <v>94.6</v>
       </c>
       <c r="P218" s="4">
-        <v>167.6</v>
+        <v>94.8</v>
       </c>
       <c r="Q218" s="4">
-        <v>99.3</v>
+        <v>94.7</v>
       </c>
       <c r="R218" s="4">
-        <v>110.1</v>
+        <v>94.6</v>
       </c>
       <c r="S218" s="4">
-        <v>135.6</v>
+        <v>95</v>
       </c>
       <c r="T218" s="4">
-        <v>144.6</v>
+        <v>94.8</v>
       </c>
       <c r="U218" s="4">
-        <v>152.19999999999999</v>
+        <v>94.6</v>
       </c>
       <c r="V218" s="3"/>
       <c r="W218" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="219" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="219" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>275</v>
+        <v>28</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G219" s="5">
-        <v>14.82</v>
-      </c>
-      <c r="H219" s="5">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I219" s="5">
-        <v>10.3</v>
-      </c>
-      <c r="J219" s="5">
-        <v>13.27</v>
-      </c>
-      <c r="K219" s="5">
-        <v>21.1</v>
-      </c>
-      <c r="L219" s="5">
-        <v>26.39</v>
-      </c>
-      <c r="M219" s="5">
-        <v>27.84</v>
-      </c>
-      <c r="N219" s="5">
-        <v>26.73</v>
-      </c>
-      <c r="O219" s="5">
-        <v>26.18</v>
-      </c>
-      <c r="P219" s="5">
-        <v>25.03</v>
-      </c>
-      <c r="Q219" s="5">
-        <v>26.68</v>
-      </c>
-      <c r="R219" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="S219" s="5">
-        <v>26.72</v>
-      </c>
-      <c r="T219" s="5">
-        <v>15.76</v>
-      </c>
-      <c r="U219" s="5">
-        <v>18.34</v>
+      <c r="G219" s="4">
+        <v>95.3</v>
+      </c>
+      <c r="H219" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="I219" s="4">
+        <v>95.4</v>
+      </c>
+      <c r="J219" s="4">
+        <v>95.5</v>
+      </c>
+      <c r="K219" s="4">
+        <v>96.4</v>
+      </c>
+      <c r="L219" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="M219" s="4">
+        <v>96.5</v>
+      </c>
+      <c r="N219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="O219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="P219" s="4">
+        <v>96.6</v>
+      </c>
+      <c r="Q219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="R219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S219" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="T219" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="U219" s="4">
+        <v>96.8</v>
       </c>
       <c r="V219" s="3"/>
       <c r="W219" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>276</v>
+        <v>28</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G220" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="H220" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="I220" s="5">
-        <v>1.67</v>
-      </c>
-      <c r="J220" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="K220" s="5">
-        <v>5.42</v>
-      </c>
-      <c r="L220" s="5">
-        <v>6.09</v>
-      </c>
-      <c r="M220" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="N220" s="5">
-        <v>7.08</v>
-      </c>
-      <c r="O220" s="5">
-        <v>8.11</v>
-      </c>
-      <c r="P220" s="5">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="Q220" s="5">
-        <v>12.03</v>
-      </c>
-      <c r="R220" s="5">
-        <v>13.34</v>
-      </c>
-      <c r="S220" s="5">
-        <v>14.15</v>
-      </c>
-      <c r="T220" s="5">
-        <v>11.79</v>
-      </c>
-      <c r="U220" s="5">
-        <v>12.81</v>
+      <c r="G220" s="3"/>
+      <c r="H220" s="3"/>
+      <c r="I220" s="3"/>
+      <c r="J220" s="3"/>
+      <c r="K220" s="3"/>
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+      <c r="P220" s="3"/>
+      <c r="Q220" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="R220" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="S220" s="4">
+        <v>5.2</v>
+      </c>
+      <c r="T220" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="U220" s="4">
+        <v>10.7</v>
       </c>
       <c r="V220" s="3"/>
       <c r="W220" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="221" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G221" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="H221" s="5">
-        <v>0.37</v>
-      </c>
-      <c r="I221" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="J221" s="5">
-        <v>6.78</v>
-      </c>
-      <c r="K221" s="5">
-        <v>15.1</v>
-      </c>
-      <c r="L221" s="5">
-        <v>13.25</v>
-      </c>
-      <c r="M221" s="5">
-        <v>19.440000000000001</v>
-      </c>
-      <c r="N221" s="5">
-        <v>24.41</v>
-      </c>
-      <c r="O221" s="5">
-        <v>24.13</v>
-      </c>
-      <c r="P221" s="5">
-        <v>22.9</v>
-      </c>
-      <c r="Q221" s="5">
-        <v>21.52</v>
-      </c>
-      <c r="R221" s="5">
-        <v>21.01</v>
-      </c>
-      <c r="S221" s="5">
-        <v>21.07</v>
-      </c>
-      <c r="T221" s="5">
-        <v>20.66</v>
-      </c>
-      <c r="U221" s="5">
-        <v>21.92</v>
+      <c r="G221" s="3"/>
+      <c r="H221" s="3"/>
+      <c r="I221" s="3"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="3"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
+      <c r="Q221" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="R221" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S221" s="4">
+        <v>5</v>
+      </c>
+      <c r="T221" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="U221" s="4">
+        <v>14.5</v>
       </c>
       <c r="V221" s="3"/>
       <c r="W221" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="222" spans="1:23" ht="63" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>274</v>
+        <v>27</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>278</v>
+        <v>28</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G222" s="5">
-        <v>66.8</v>
-      </c>
-      <c r="H222" s="5">
-        <v>69.260000000000005</v>
-      </c>
-      <c r="I222" s="5">
-        <v>66.91</v>
-      </c>
-      <c r="J222" s="5">
-        <v>61.95</v>
-      </c>
-      <c r="K222" s="5">
-        <v>58.38</v>
-      </c>
-      <c r="L222" s="5">
-        <v>54.29</v>
-      </c>
-      <c r="M222" s="5">
-        <v>45.74</v>
-      </c>
-      <c r="N222" s="5">
-        <v>41.77</v>
-      </c>
-      <c r="O222" s="5">
-        <v>41.58</v>
-      </c>
-      <c r="P222" s="5">
-        <v>43.03</v>
-      </c>
-      <c r="Q222" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="R222" s="5">
-        <v>38.729999999999997</v>
-      </c>
-      <c r="S222" s="5">
-        <v>38.06</v>
-      </c>
-      <c r="T222" s="5">
-        <v>30.24</v>
-      </c>
-      <c r="U222" s="5">
-        <v>30.07</v>
+      <c r="G222" s="4">
+        <v>41.6</v>
+      </c>
+      <c r="H222" s="4">
+        <v>44.7</v>
+      </c>
+      <c r="I222" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="J222" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="K222" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="L222" s="4">
+        <v>49.8</v>
+      </c>
+      <c r="M222" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="N222" s="4">
+        <v>51.2</v>
+      </c>
+      <c r="O222" s="4">
+        <v>52.4</v>
+      </c>
+      <c r="P222" s="4">
+        <v>53.4</v>
+      </c>
+      <c r="Q222" s="4">
+        <v>53.9</v>
+      </c>
+      <c r="R222" s="4">
+        <v>54.8</v>
+      </c>
+      <c r="S222" s="4">
+        <v>55.8</v>
+      </c>
+      <c r="T222" s="4">
+        <v>53.6</v>
+      </c>
+      <c r="U222" s="4">
+        <v>54.5</v>
       </c>
       <c r="V222" s="3"/>
       <c r="W222" s="2" t="s">
@@ -15724,28 +15638,52 @@
         <v>28</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="3"/>
-      <c r="I223" s="3"/>
-      <c r="J223" s="3"/>
-      <c r="K223" s="3"/>
-      <c r="L223" s="3"/>
-      <c r="M223" s="3"/>
-      <c r="N223" s="3"/>
-      <c r="O223" s="3"/>
-      <c r="P223" s="3"/>
-      <c r="Q223" s="3"/>
-      <c r="R223" s="3"/>
-      <c r="S223" s="3"/>
-      <c r="T223" s="3"/>
-      <c r="U223" s="4">
-        <v>5.0999999999999996</v>
+      <c r="I223" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="J223" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="K223" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="L223" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="M223" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="N223" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="O223" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="P223" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="Q223" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="R223" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="S223" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="T223" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="U223" s="5">
+        <v>1.62</v>
       </c>
       <c r="V223" s="3"/>
       <c r="W223" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="224" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15756,7 +15694,7 @@
         <v>279</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>27</v>
@@ -15765,56 +15703,46 @@
         <v>28</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G224" s="4">
-        <v>88</v>
-      </c>
-      <c r="H224" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I224" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J224" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K224" s="4">
-        <v>93.9</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G224" s="3"/>
+      <c r="H224" s="3"/>
+      <c r="I224" s="3"/>
+      <c r="J224" s="3"/>
+      <c r="K224" s="3"/>
       <c r="L224" s="4">
-        <v>94.6</v>
+        <v>12.1</v>
       </c>
       <c r="M224" s="4">
-        <v>94.8</v>
+        <v>12.7</v>
       </c>
       <c r="N224" s="4">
-        <v>94.5</v>
+        <v>11.6</v>
       </c>
       <c r="O224" s="4">
-        <v>94.6</v>
+        <v>11.4</v>
       </c>
       <c r="P224" s="4">
-        <v>94.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q224" s="4">
-        <v>94.7</v>
+        <v>9</v>
       </c>
       <c r="R224" s="4">
-        <v>94.6</v>
+        <v>7.8</v>
       </c>
       <c r="S224" s="4">
-        <v>95</v>
+        <v>7.6</v>
       </c>
       <c r="T224" s="4">
-        <v>94.8</v>
+        <v>7.6</v>
       </c>
       <c r="U224" s="4">
-        <v>94.6</v>
+        <v>7.7</v>
       </c>
       <c r="V224" s="3"/>
       <c r="W224" s="2" t="s">
-        <v>30</v>
+        <v>283</v>
       </c>
     </row>
     <row r="225" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -15825,7 +15753,7 @@
         <v>279</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>27</v>
@@ -15834,52 +15762,52 @@
         <v>28</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G225" s="4">
-        <v>95.3</v>
+        <v>166.5</v>
       </c>
       <c r="H225" s="4">
-        <v>95.4</v>
+        <v>166.2</v>
       </c>
       <c r="I225" s="4">
-        <v>95.4</v>
+        <v>165.6</v>
       </c>
       <c r="J225" s="4">
-        <v>95.5</v>
+        <v>155.5</v>
       </c>
       <c r="K225" s="4">
-        <v>96.4</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="L225" s="4">
-        <v>96.5</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="M225" s="4">
-        <v>96.5</v>
+        <v>162.69999999999999</v>
       </c>
       <c r="N225" s="4">
-        <v>96.6</v>
+        <v>161.69999999999999</v>
       </c>
       <c r="O225" s="4">
-        <v>96.6</v>
+        <v>163.4</v>
       </c>
       <c r="P225" s="4">
-        <v>96.6</v>
+        <v>167.6</v>
       </c>
       <c r="Q225" s="4">
-        <v>96.7</v>
+        <v>99.3</v>
       </c>
       <c r="R225" s="4">
-        <v>96.7</v>
+        <v>110.1</v>
       </c>
       <c r="S225" s="4">
-        <v>96.7</v>
+        <v>135.6</v>
       </c>
       <c r="T225" s="4">
-        <v>96.8</v>
+        <v>144.6</v>
       </c>
       <c r="U225" s="4">
-        <v>96.8</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="V225" s="3"/>
       <c r="W225" s="2" t="s">
@@ -15894,7 +15822,7 @@
         <v>279</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>27</v>
@@ -15905,30 +15833,50 @@
       <c r="F226" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G226" s="3"/>
-      <c r="H226" s="3"/>
-      <c r="I226" s="3"/>
-      <c r="J226" s="3"/>
-      <c r="K226" s="3"/>
-      <c r="L226" s="3"/>
-      <c r="M226" s="3"/>
-      <c r="N226" s="3"/>
-      <c r="O226" s="3"/>
-      <c r="P226" s="3"/>
+      <c r="G226" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H226" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="I226" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="J226" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="K226" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="L226" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="M226" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="N226" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O226" s="4">
+        <v>7</v>
+      </c>
+      <c r="P226" s="4">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="Q226" s="4">
-        <v>5.4</v>
+        <v>12.2</v>
       </c>
       <c r="R226" s="4">
-        <v>5.3</v>
+        <v>15.4</v>
       </c>
       <c r="S226" s="4">
-        <v>5.2</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="T226" s="4">
-        <v>6.6</v>
+        <v>21.6</v>
       </c>
       <c r="U226" s="4">
-        <v>10.7</v>
+        <v>24.2</v>
       </c>
       <c r="V226" s="3"/>
       <c r="W226" s="2" t="s">
@@ -15940,10 +15888,10 @@
         <v>265</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>27</v>
@@ -15952,47 +15900,69 @@
         <v>28</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G227" s="3"/>
-      <c r="H227" s="3"/>
-      <c r="I227" s="3"/>
-      <c r="J227" s="3"/>
-      <c r="K227" s="3"/>
-      <c r="L227" s="3"/>
-      <c r="M227" s="3"/>
-      <c r="N227" s="3"/>
-      <c r="O227" s="3"/>
-      <c r="P227" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="G227" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="H227" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="I227" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J227" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K227" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="L227" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="M227" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N227" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O227" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="P227" s="4">
+        <v>6.1</v>
+      </c>
       <c r="Q227" s="4">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="R227" s="4">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="S227" s="4">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="T227" s="4">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="U227" s="4">
-        <v>14.5</v>
-      </c>
-      <c r="V227" s="3"/>
+        <v>5.8</v>
+      </c>
+      <c r="V227" s="4">
+        <v>6</v>
+      </c>
       <c r="W227" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="228" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>27</v>
@@ -16001,67 +15971,69 @@
         <v>28</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G228" s="4">
-        <v>41.6</v>
-      </c>
-      <c r="H228" s="4">
-        <v>44.7</v>
-      </c>
-      <c r="I228" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="J228" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="K228" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="L228" s="4">
-        <v>49.8</v>
-      </c>
-      <c r="M228" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="N228" s="4">
-        <v>51.2</v>
-      </c>
-      <c r="O228" s="4">
-        <v>52.4</v>
-      </c>
-      <c r="P228" s="4">
-        <v>53.4</v>
-      </c>
-      <c r="Q228" s="4">
-        <v>53.9</v>
-      </c>
-      <c r="R228" s="4">
-        <v>54.8</v>
-      </c>
-      <c r="S228" s="4">
-        <v>55.8</v>
-      </c>
-      <c r="T228" s="4">
-        <v>53.6</v>
-      </c>
-      <c r="U228" s="4">
-        <v>54.5</v>
-      </c>
-      <c r="V228" s="3"/>
+        <v>29</v>
+      </c>
+      <c r="G228" s="5">
+        <v>0.26</v>
+      </c>
+      <c r="H228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="I228" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J228" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K228" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="L228" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="M228" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="N228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="P228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="Q228" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="R228" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="S228" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="T228" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="U228" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="V228" s="5">
+        <v>0.25</v>
+      </c>
       <c r="W228" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="229" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>27</v>
@@ -16070,63 +16042,49 @@
         <v>28</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="3"/>
-      <c r="I229" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="J229" s="4">
-        <v>31.1</v>
-      </c>
-      <c r="K229" s="4">
-        <v>30.3</v>
-      </c>
-      <c r="L229" s="4">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="M229" s="4">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="N229" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="O229" s="4">
-        <v>37.5</v>
-      </c>
-      <c r="P229" s="4">
-        <v>35.9</v>
-      </c>
-      <c r="Q229" s="4">
-        <v>36.6</v>
-      </c>
-      <c r="R229" s="4">
-        <v>36.1</v>
-      </c>
-      <c r="S229" s="4">
-        <v>35.4</v>
-      </c>
-      <c r="T229" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="U229" s="4">
-        <v>35.4</v>
+      <c r="I229" s="3"/>
+      <c r="J229" s="3"/>
+      <c r="K229" s="3"/>
+      <c r="L229" s="3"/>
+      <c r="M229" s="3"/>
+      <c r="N229" s="3"/>
+      <c r="O229" s="3"/>
+      <c r="P229" s="6">
+        <v>74110</v>
+      </c>
+      <c r="Q229" s="6">
+        <v>68436</v>
+      </c>
+      <c r="R229" s="6">
+        <v>65117</v>
+      </c>
+      <c r="S229" s="6">
+        <v>64070</v>
+      </c>
+      <c r="T229" s="6">
+        <v>61349</v>
+      </c>
+      <c r="U229" s="6">
+        <v>59560</v>
       </c>
       <c r="V229" s="3"/>
       <c r="W229" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="230" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>27</v>
@@ -16135,39 +16093,51 @@
         <v>28</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
-      <c r="J230" s="3"/>
+      <c r="J230" s="6">
+        <v>546870</v>
+      </c>
       <c r="K230" s="3"/>
-      <c r="L230" s="3"/>
-      <c r="M230" s="3"/>
+      <c r="L230" s="6">
+        <v>512116</v>
+      </c>
+      <c r="M230" s="6">
+        <v>501544</v>
+      </c>
       <c r="N230" s="3"/>
-      <c r="O230" s="3"/>
+      <c r="O230" s="6">
+        <v>487452</v>
+      </c>
       <c r="P230" s="3"/>
-      <c r="Q230" s="5">
-        <v>83.49</v>
+      <c r="Q230" s="6">
+        <v>469607</v>
       </c>
       <c r="R230" s="3"/>
-      <c r="S230" s="3"/>
+      <c r="S230" s="6">
+        <v>457891</v>
+      </c>
       <c r="T230" s="3"/>
-      <c r="U230" s="3"/>
+      <c r="U230" s="6">
+        <v>446959</v>
+      </c>
       <c r="V230" s="3"/>
       <c r="W230" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="231" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="231" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B231" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="D231" s="2" t="s">
         <v>27</v>
@@ -16176,48 +16146,52 @@
         <v>28</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="G231" s="3"/>
-      <c r="H231" s="3"/>
-      <c r="I231" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="J231" s="5">
-        <v>1.41</v>
-      </c>
-      <c r="K231" s="5">
-        <v>1.43</v>
-      </c>
-      <c r="L231" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="M231" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="N231" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="O231" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="P231" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="Q231" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="R231" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="S231" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="T231" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="U231" s="5">
-        <v>1.62</v>
+        <v>293</v>
+      </c>
+      <c r="G231" s="6">
+        <v>22795</v>
+      </c>
+      <c r="H231" s="6">
+        <v>21359</v>
+      </c>
+      <c r="I231" s="6">
+        <v>20022</v>
+      </c>
+      <c r="J231" s="6">
+        <v>19636</v>
+      </c>
+      <c r="K231" s="6">
+        <v>18137</v>
+      </c>
+      <c r="L231" s="6">
+        <v>16793</v>
+      </c>
+      <c r="M231" s="6">
+        <v>15086</v>
+      </c>
+      <c r="N231" s="6">
+        <v>14505</v>
+      </c>
+      <c r="O231" s="6">
+        <v>14165</v>
+      </c>
+      <c r="P231" s="6">
+        <v>11466</v>
+      </c>
+      <c r="Q231" s="6">
+        <v>8767</v>
+      </c>
+      <c r="R231" s="6">
+        <v>8374</v>
+      </c>
+      <c r="S231" s="6">
+        <v>7344</v>
+      </c>
+      <c r="T231" s="6">
+        <v>5553</v>
+      </c>
+      <c r="U231" s="6">
+        <v>5297</v>
       </c>
       <c r="V231" s="3"/>
       <c r="W231" s="2" t="s">
@@ -16229,58 +16203,68 @@
         <v>265</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D232" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="E232" s="3" t="s">
-        <v>28</v>
+        <v>296</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G232" s="3"/>
-      <c r="H232" s="3"/>
-      <c r="I232" s="3"/>
-      <c r="J232" s="3"/>
-      <c r="K232" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="H232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="I232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="J232" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="K232" s="4">
+        <v>99.6</v>
+      </c>
       <c r="L232" s="4">
-        <v>12.1</v>
+        <v>99.6</v>
       </c>
       <c r="M232" s="4">
-        <v>12.7</v>
+        <v>99.7</v>
       </c>
       <c r="N232" s="4">
-        <v>11.6</v>
+        <v>99.7</v>
       </c>
       <c r="O232" s="4">
-        <v>11.4</v>
+        <v>99.7</v>
       </c>
       <c r="P232" s="4">
-        <v>10.6</v>
+        <v>99.7</v>
       </c>
       <c r="Q232" s="4">
-        <v>9</v>
+        <v>99.8</v>
       </c>
       <c r="R232" s="4">
-        <v>7.8</v>
+        <v>99.8</v>
       </c>
       <c r="S232" s="4">
-        <v>7.6</v>
+        <v>99.8</v>
       </c>
       <c r="T232" s="4">
-        <v>7.6</v>
+        <v>99.8</v>
       </c>
       <c r="U232" s="4">
-        <v>7.7</v>
+        <v>99.8</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
-        <v>296</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:23" ht="36" x14ac:dyDescent="0.25">
@@ -16288,64 +16272,64 @@
         <v>265</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E233" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F233" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G233" s="4">
-        <v>166.5</v>
+        <v>43.4</v>
       </c>
       <c r="H233" s="4">
-        <v>166.2</v>
+        <v>46.5</v>
       </c>
       <c r="I233" s="4">
-        <v>165.6</v>
+        <v>47.2</v>
       </c>
       <c r="J233" s="4">
-        <v>155.5</v>
+        <v>47.8</v>
       </c>
       <c r="K233" s="4">
-        <v>159.69999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="L233" s="4">
-        <v>158.30000000000001</v>
+        <v>46.5</v>
       </c>
       <c r="M233" s="4">
-        <v>162.69999999999999</v>
+        <v>51.4</v>
       </c>
       <c r="N233" s="4">
-        <v>161.69999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="O233" s="4">
-        <v>163.4</v>
+        <v>54</v>
       </c>
       <c r="P233" s="4">
-        <v>167.6</v>
+        <v>54.3</v>
       </c>
       <c r="Q233" s="4">
-        <v>99.3</v>
+        <v>58.5</v>
       </c>
       <c r="R233" s="4">
-        <v>110.1</v>
+        <v>61.4</v>
       </c>
       <c r="S233" s="4">
-        <v>135.6</v>
+        <v>60</v>
       </c>
       <c r="T233" s="4">
-        <v>144.6</v>
+        <v>62.3</v>
       </c>
       <c r="U233" s="4">
-        <v>152.19999999999999</v>
+        <v>59.6</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
@@ -16357,10 +16341,10 @@
         <v>265</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>27</v>
@@ -16371,67 +16355,65 @@
       <c r="F234" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G234" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="H234" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="I234" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J234" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="K234" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="L234" s="4">
-        <v>3.9</v>
-      </c>
-      <c r="M234" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N234" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="O234" s="4">
-        <v>5.4</v>
-      </c>
-      <c r="P234" s="4">
-        <v>6.1</v>
-      </c>
-      <c r="Q234" s="4">
-        <v>6.5</v>
-      </c>
-      <c r="R234" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="S234" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T234" s="4">
-        <v>6.3</v>
-      </c>
-      <c r="U234" s="4">
-        <v>5.8</v>
-      </c>
-      <c r="V234" s="4">
+      <c r="G234" s="6">
         <v>6</v>
       </c>
+      <c r="H234" s="6">
+        <v>8</v>
+      </c>
+      <c r="I234" s="6">
+        <v>8</v>
+      </c>
+      <c r="J234" s="6">
+        <v>10</v>
+      </c>
+      <c r="K234" s="6">
+        <v>9</v>
+      </c>
+      <c r="L234" s="6">
+        <v>10</v>
+      </c>
+      <c r="M234" s="6">
+        <v>11</v>
+      </c>
+      <c r="N234" s="6">
+        <v>13</v>
+      </c>
+      <c r="O234" s="6">
+        <v>12</v>
+      </c>
+      <c r="P234" s="6">
+        <v>16</v>
+      </c>
+      <c r="Q234" s="6">
+        <v>21</v>
+      </c>
+      <c r="R234" s="6">
+        <v>24</v>
+      </c>
+      <c r="S234" s="6">
+        <v>25</v>
+      </c>
+      <c r="T234" s="6">
+        <v>26</v>
+      </c>
+      <c r="U234" s="6">
+        <v>21</v>
+      </c>
+      <c r="V234" s="3"/>
       <c r="W234" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="235" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="235" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>27</v>
@@ -16440,69 +16422,67 @@
         <v>28</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>29</v>
+        <v>302</v>
       </c>
       <c r="G235" s="5">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="H235" s="5">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="I235" s="5">
-        <v>0.14000000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="J235" s="5">
-        <v>0.14000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="K235" s="5">
-        <v>0.16</v>
+        <v>0.66</v>
       </c>
       <c r="L235" s="5">
-        <v>0.11</v>
+        <v>0.69</v>
       </c>
       <c r="M235" s="5">
-        <v>0.12</v>
+        <v>0.69</v>
       </c>
       <c r="N235" s="5">
-        <v>0.13</v>
+        <v>0.69</v>
       </c>
       <c r="O235" s="5">
-        <v>0.13</v>
+        <v>0.71</v>
       </c>
       <c r="P235" s="5">
-        <v>0.18</v>
+        <v>0.78</v>
       </c>
       <c r="Q235" s="5">
-        <v>0.11</v>
+        <v>0.77</v>
       </c>
       <c r="R235" s="5">
-        <v>0.1</v>
+        <v>0.81</v>
       </c>
       <c r="S235" s="5">
-        <v>0.09</v>
+        <v>0.85</v>
       </c>
       <c r="T235" s="5">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="U235" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="V235" s="5">
-        <v>0.25</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="V235" s="3"/>
       <c r="W235" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="236" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="236" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>27</v>
@@ -16511,49 +16491,67 @@
         <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G236" s="3"/>
-      <c r="H236" s="3"/>
-      <c r="I236" s="3"/>
-      <c r="J236" s="3"/>
-      <c r="K236" s="3"/>
-      <c r="L236" s="3"/>
-      <c r="M236" s="3"/>
-      <c r="N236" s="3"/>
-      <c r="O236" s="3"/>
-      <c r="P236" s="6">
-        <v>74110</v>
-      </c>
-      <c r="Q236" s="6">
-        <v>68436</v>
-      </c>
-      <c r="R236" s="6">
-        <v>65117</v>
-      </c>
-      <c r="S236" s="6">
-        <v>64070</v>
-      </c>
-      <c r="T236" s="6">
-        <v>61349</v>
-      </c>
-      <c r="U236" s="6">
-        <v>59560</v>
+        <v>293</v>
+      </c>
+      <c r="G236" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="H236" s="5">
+        <v>20.43</v>
+      </c>
+      <c r="I236" s="5">
+        <v>17.52</v>
+      </c>
+      <c r="J236" s="5">
+        <v>16.72</v>
+      </c>
+      <c r="K236" s="5">
+        <v>16.579999999999998</v>
+      </c>
+      <c r="L236" s="5">
+        <v>16.47</v>
+      </c>
+      <c r="M236" s="5">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="N236" s="5">
+        <v>18.010000000000002</v>
+      </c>
+      <c r="O236" s="5">
+        <v>18.47</v>
+      </c>
+      <c r="P236" s="5">
+        <v>17.59</v>
+      </c>
+      <c r="Q236" s="5">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="R236" s="5">
+        <v>18.25</v>
+      </c>
+      <c r="S236" s="5">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="T236" s="5">
+        <v>17.34</v>
+      </c>
+      <c r="U236" s="5">
+        <v>16.68</v>
       </c>
       <c r="V236" s="3"/>
       <c r="W236" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="237" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="237" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>27</v>
@@ -16562,51 +16560,67 @@
         <v>28</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G237" s="3"/>
-      <c r="H237" s="3"/>
-      <c r="I237" s="3"/>
-      <c r="J237" s="6">
-        <v>546870</v>
-      </c>
-      <c r="K237" s="3"/>
-      <c r="L237" s="6">
-        <v>512116</v>
-      </c>
-      <c r="M237" s="6">
-        <v>501544</v>
-      </c>
-      <c r="N237" s="3"/>
-      <c r="O237" s="6">
-        <v>487452</v>
-      </c>
-      <c r="P237" s="3"/>
-      <c r="Q237" s="6">
-        <v>469607</v>
-      </c>
-      <c r="R237" s="3"/>
-      <c r="S237" s="6">
-        <v>457891</v>
-      </c>
-      <c r="T237" s="3"/>
-      <c r="U237" s="6">
-        <v>446959</v>
+        <v>34</v>
+      </c>
+      <c r="G237" s="4">
+        <v>11.1</v>
+      </c>
+      <c r="H237" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="I237" s="4">
+        <v>11</v>
+      </c>
+      <c r="J237" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="K237" s="4">
+        <v>13</v>
+      </c>
+      <c r="L237" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="M237" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="N237" s="4">
+        <v>10.4</v>
+      </c>
+      <c r="O237" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="P237" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q237" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="R237" s="4">
+        <v>7</v>
+      </c>
+      <c r="S237" s="4">
+        <v>6.7</v>
+      </c>
+      <c r="T237" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U237" s="4">
+        <v>7.7</v>
       </c>
       <c r="V237" s="3"/>
       <c r="W237" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="238" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="238" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>27</v>
@@ -16615,67 +16629,61 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G238" s="6">
-        <v>22795</v>
-      </c>
-      <c r="H238" s="6">
-        <v>21359</v>
-      </c>
-      <c r="I238" s="6">
-        <v>20022</v>
-      </c>
-      <c r="J238" s="6">
-        <v>19636</v>
-      </c>
-      <c r="K238" s="6">
-        <v>18137</v>
-      </c>
-      <c r="L238" s="6">
-        <v>16793</v>
-      </c>
-      <c r="M238" s="6">
-        <v>15086</v>
-      </c>
-      <c r="N238" s="6">
-        <v>14505</v>
-      </c>
-      <c r="O238" s="6">
-        <v>14165</v>
-      </c>
-      <c r="P238" s="6">
-        <v>11466</v>
-      </c>
-      <c r="Q238" s="6">
-        <v>8767</v>
-      </c>
-      <c r="R238" s="6">
-        <v>8374</v>
-      </c>
-      <c r="S238" s="6">
-        <v>7344</v>
-      </c>
-      <c r="T238" s="6">
-        <v>5553</v>
-      </c>
-      <c r="U238" s="6">
-        <v>5297</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G238" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H238" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I238" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J238" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K238" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L238" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M238" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N238" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O238" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P238" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q238" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R238" s="3"/>
+      <c r="S238" s="3"/>
+      <c r="T238" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="U238" s="3"/>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="239" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16684,67 +16692,67 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G239" s="6">
-        <v>961</v>
-      </c>
-      <c r="H239" s="6">
-        <v>136730</v>
-      </c>
-      <c r="I239" s="6">
-        <v>11553</v>
-      </c>
-      <c r="J239" s="6">
-        <v>15701</v>
-      </c>
-      <c r="K239" s="6">
-        <v>2758</v>
-      </c>
-      <c r="L239" s="6">
-        <v>69422</v>
-      </c>
-      <c r="M239" s="6">
-        <v>44764</v>
-      </c>
-      <c r="N239" s="6">
-        <v>78118</v>
-      </c>
-      <c r="O239" s="6">
-        <v>14958</v>
-      </c>
-      <c r="P239" s="6">
-        <v>68943</v>
-      </c>
-      <c r="Q239" s="6">
-        <v>57788</v>
-      </c>
-      <c r="R239" s="6">
-        <v>27276</v>
-      </c>
-      <c r="S239" s="6">
-        <v>256675</v>
-      </c>
-      <c r="T239" s="6">
-        <v>211015</v>
-      </c>
-      <c r="U239" s="6">
-        <v>1435</v>
+        <v>310</v>
+      </c>
+      <c r="G239" s="4">
+        <v>100</v>
+      </c>
+      <c r="H239" s="4">
+        <v>99.8</v>
+      </c>
+      <c r="I239" s="4">
+        <v>97.5</v>
+      </c>
+      <c r="J239" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K239" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L239" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M239" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="N239" s="4">
+        <v>100.7</v>
+      </c>
+      <c r="O239" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="P239" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q239" s="4">
+        <v>90.4</v>
+      </c>
+      <c r="R239" s="4">
+        <v>99</v>
+      </c>
+      <c r="S239" s="4">
+        <v>94.2</v>
+      </c>
+      <c r="T239" s="4">
+        <v>84.9</v>
+      </c>
+      <c r="U239" s="4">
+        <v>83.4</v>
       </c>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="240" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16753,607 +16761,615 @@
         <v>28</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G240" s="6">
-        <v>6</v>
-      </c>
-      <c r="H240" s="6">
-        <v>8</v>
-      </c>
-      <c r="I240" s="6">
-        <v>8</v>
-      </c>
-      <c r="J240" s="6">
-        <v>10</v>
-      </c>
-      <c r="K240" s="6">
-        <v>9</v>
-      </c>
-      <c r="L240" s="6">
-        <v>10</v>
-      </c>
-      <c r="M240" s="6">
-        <v>11</v>
-      </c>
-      <c r="N240" s="6">
-        <v>13</v>
-      </c>
-      <c r="O240" s="6">
-        <v>12</v>
-      </c>
-      <c r="P240" s="6">
-        <v>16</v>
-      </c>
-      <c r="Q240" s="6">
-        <v>21</v>
-      </c>
-      <c r="R240" s="6">
-        <v>24</v>
-      </c>
-      <c r="S240" s="6">
-        <v>25</v>
-      </c>
-      <c r="T240" s="6">
-        <v>26</v>
-      </c>
-      <c r="U240" s="6">
-        <v>21</v>
+        <v>310</v>
+      </c>
+      <c r="G240" s="4">
+        <v>100</v>
+      </c>
+      <c r="H240" s="4">
+        <v>99.7</v>
+      </c>
+      <c r="I240" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J240" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="K240" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="L240" s="4">
+        <v>94.3</v>
+      </c>
+      <c r="M240" s="4">
+        <v>96.9</v>
+      </c>
+      <c r="N240" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="O240" s="4">
+        <v>100.4</v>
+      </c>
+      <c r="P240" s="4">
+        <v>94.9</v>
+      </c>
+      <c r="Q240" s="4">
+        <v>91.2</v>
+      </c>
+      <c r="R240" s="4">
+        <v>98.2</v>
+      </c>
+      <c r="S240" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="T240" s="4">
+        <v>85.7</v>
+      </c>
+      <c r="U240" s="4">
+        <v>84.2</v>
       </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="241" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="G241" s="5">
-        <v>0.59</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="H241" s="5">
-        <v>0.5</v>
+        <v>10.34</v>
       </c>
       <c r="I241" s="5">
-        <v>0.59</v>
+        <v>10.96</v>
       </c>
       <c r="J241" s="5">
-        <v>0.63</v>
+        <v>11.45</v>
       </c>
       <c r="K241" s="5">
-        <v>0.66</v>
+        <v>11.61</v>
       </c>
       <c r="L241" s="5">
-        <v>0.69</v>
+        <v>11.88</v>
       </c>
       <c r="M241" s="5">
-        <v>0.69</v>
+        <v>11.4</v>
       </c>
       <c r="N241" s="5">
-        <v>0.69</v>
+        <v>11.06</v>
       </c>
       <c r="O241" s="5">
-        <v>0.71</v>
+        <v>14.94</v>
       </c>
       <c r="P241" s="5">
-        <v>0.78</v>
+        <v>15.38</v>
       </c>
       <c r="Q241" s="5">
-        <v>0.77</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="R241" s="5">
-        <v>0.81</v>
+        <v>15.6</v>
       </c>
       <c r="S241" s="5">
-        <v>0.85</v>
+        <v>16.64</v>
       </c>
       <c r="T241" s="5">
-        <v>0.9</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U241" s="5">
-        <v>0.97</v>
+        <v>17.77</v>
       </c>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="242" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="G242" s="5">
-        <v>16.5</v>
+        <v>6.64</v>
       </c>
       <c r="H242" s="5">
-        <v>20.43</v>
+        <v>6.92</v>
       </c>
       <c r="I242" s="5">
-        <v>17.52</v>
+        <v>6.53</v>
       </c>
       <c r="J242" s="5">
-        <v>16.72</v>
+        <v>6.67</v>
       </c>
       <c r="K242" s="5">
-        <v>16.579999999999998</v>
+        <v>6.32</v>
       </c>
       <c r="L242" s="5">
-        <v>16.47</v>
+        <v>5.69</v>
       </c>
       <c r="M242" s="5">
-        <v>16.920000000000002</v>
+        <v>3.97</v>
       </c>
       <c r="N242" s="5">
-        <v>18.010000000000002</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="O242" s="5">
-        <v>18.47</v>
+        <v>5.72</v>
       </c>
       <c r="P242" s="5">
-        <v>17.59</v>
+        <v>6.2</v>
       </c>
       <c r="Q242" s="5">
-        <v>17.579999999999998</v>
+        <v>6.58</v>
       </c>
       <c r="R242" s="5">
-        <v>18.25</v>
+        <v>5.67</v>
       </c>
       <c r="S242" s="5">
-        <v>18.309999999999999</v>
+        <v>5.79</v>
       </c>
       <c r="T242" s="5">
-        <v>17.34</v>
+        <v>6.34</v>
       </c>
       <c r="U242" s="5">
-        <v>16.68</v>
+        <v>6.03</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="243" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G243" s="4">
-        <v>11.1</v>
-      </c>
-      <c r="H243" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="I243" s="4">
-        <v>11</v>
-      </c>
-      <c r="J243" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="K243" s="4">
-        <v>13</v>
-      </c>
-      <c r="L243" s="4">
-        <v>11.9</v>
-      </c>
-      <c r="M243" s="4">
-        <v>10.6</v>
-      </c>
-      <c r="N243" s="4">
-        <v>10.4</v>
-      </c>
-      <c r="O243" s="4">
-        <v>10.5</v>
-      </c>
-      <c r="P243" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="Q243" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="R243" s="4">
-        <v>7</v>
-      </c>
-      <c r="S243" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="T243" s="4">
-        <v>7.8</v>
-      </c>
-      <c r="U243" s="4">
-        <v>7.7</v>
+      <c r="G243" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H243" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I243" s="5">
+        <v>10.61</v>
+      </c>
+      <c r="J243" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K243" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="L243" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M243" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N243" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O243" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P243" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q243" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R243" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S243" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T243" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U243" s="5">
+        <v>30.37</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="244" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C244" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="D244" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G244" s="5">
-        <v>2.0699999999999998</v>
+        <v>11.81</v>
       </c>
       <c r="H244" s="5">
-        <v>2.48</v>
+        <v>13.24</v>
       </c>
       <c r="I244" s="5">
-        <v>3.05</v>
+        <v>13.5</v>
       </c>
       <c r="J244" s="5">
-        <v>3.37</v>
+        <v>14.27</v>
       </c>
       <c r="K244" s="5">
-        <v>3.82</v>
+        <v>14.24</v>
       </c>
       <c r="L244" s="5">
-        <v>3.45</v>
+        <v>14.8</v>
       </c>
       <c r="M244" s="5">
-        <v>2.96</v>
+        <v>14.92</v>
       </c>
       <c r="N244" s="5">
-        <v>2.62</v>
+        <v>14.78</v>
       </c>
       <c r="O244" s="5">
-        <v>2.48</v>
+        <v>21.47</v>
       </c>
       <c r="P244" s="5">
-        <v>2.66</v>
+        <v>22.01</v>
       </c>
       <c r="Q244" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R244" s="3"/>
-      <c r="S244" s="3"/>
+        <v>22.14</v>
+      </c>
+      <c r="R244" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S244" s="5">
+        <v>22.1</v>
+      </c>
       <c r="T244" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="U244" s="3"/>
+        <v>20.61</v>
+      </c>
+      <c r="U244" s="5">
+        <v>21.29</v>
+      </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="245" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="245" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G245" s="4">
-        <v>100</v>
-      </c>
-      <c r="H245" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I245" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J245" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K245" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L245" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M245" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N245" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O245" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P245" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q245" s="4">
-        <v>90.4</v>
-      </c>
-      <c r="R245" s="4">
-        <v>99</v>
-      </c>
-      <c r="S245" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T245" s="4">
-        <v>84.9</v>
-      </c>
-      <c r="U245" s="4">
-        <v>83.4</v>
+        <v>316</v>
+      </c>
+      <c r="G245" s="6">
+        <v>563</v>
+      </c>
+      <c r="H245" s="6">
+        <v>531</v>
+      </c>
+      <c r="I245" s="6">
+        <v>661</v>
+      </c>
+      <c r="J245" s="6">
+        <v>778</v>
+      </c>
+      <c r="K245" s="6">
+        <v>847</v>
+      </c>
+      <c r="L245" s="6">
+        <v>909</v>
+      </c>
+      <c r="M245" s="6">
+        <v>930</v>
+      </c>
+      <c r="N245" s="6">
+        <v>946</v>
+      </c>
+      <c r="O245" s="6">
+        <v>991</v>
+      </c>
+      <c r="P245" s="6">
+        <v>1050</v>
+      </c>
+      <c r="Q245" s="6">
+        <v>1073</v>
+      </c>
+      <c r="R245" s="6">
+        <v>1189</v>
+      </c>
+      <c r="S245" s="6">
+        <v>1318</v>
+      </c>
+      <c r="T245" s="6">
+        <v>1372</v>
+      </c>
+      <c r="U245" s="6">
+        <v>1556</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="246" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="246" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F246" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G246" s="4">
-        <v>100</v>
-      </c>
-      <c r="H246" s="4">
-        <v>99.7</v>
-      </c>
-      <c r="I246" s="4">
-        <v>97.8</v>
-      </c>
-      <c r="J246" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="K246" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="L246" s="4">
-        <v>94.3</v>
-      </c>
-      <c r="M246" s="4">
-        <v>96.9</v>
-      </c>
-      <c r="N246" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="O246" s="4">
-        <v>100.4</v>
-      </c>
-      <c r="P246" s="4">
-        <v>94.9</v>
-      </c>
-      <c r="Q246" s="4">
-        <v>91.2</v>
-      </c>
-      <c r="R246" s="4">
-        <v>98.2</v>
-      </c>
-      <c r="S246" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="T246" s="4">
-        <v>85.7</v>
-      </c>
-      <c r="U246" s="4">
-        <v>84.2</v>
+      <c r="G246" s="6">
+        <v>440</v>
+      </c>
+      <c r="H246" s="6">
+        <v>101</v>
+      </c>
+      <c r="I246" s="6">
+        <v>151</v>
+      </c>
+      <c r="J246" s="6">
+        <v>217</v>
+      </c>
+      <c r="K246" s="6">
+        <v>239</v>
+      </c>
+      <c r="L246" s="6">
+        <v>674</v>
+      </c>
+      <c r="M246" s="6">
+        <v>705</v>
+      </c>
+      <c r="N246" s="6">
+        <v>712</v>
+      </c>
+      <c r="O246" s="6">
+        <v>743</v>
+      </c>
+      <c r="P246" s="6">
+        <v>788</v>
+      </c>
+      <c r="Q246" s="6">
+        <v>805</v>
+      </c>
+      <c r="R246" s="6">
+        <v>892</v>
+      </c>
+      <c r="S246" s="6">
+        <v>988</v>
+      </c>
+      <c r="T246" s="6">
+        <v>1029</v>
+      </c>
+      <c r="U246" s="6">
+        <v>1167</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>320</v>
+        <v>30</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G247" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H247" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I247" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J247" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K247" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L247" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M247" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N247" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O247" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P247" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q247" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R247" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S247" s="5">
-        <v>16.64</v>
-      </c>
-      <c r="T247" s="5">
-        <v>16.649999999999999</v>
-      </c>
-      <c r="U247" s="5">
-        <v>17.77</v>
+        <v>316</v>
+      </c>
+      <c r="G247" s="6">
+        <v>123</v>
+      </c>
+      <c r="H247" s="6">
+        <v>101</v>
+      </c>
+      <c r="I247" s="6">
+        <v>151</v>
+      </c>
+      <c r="J247" s="6">
+        <v>217</v>
+      </c>
+      <c r="K247" s="6">
+        <v>239</v>
+      </c>
+      <c r="L247" s="6">
+        <v>235</v>
+      </c>
+      <c r="M247" s="6">
+        <v>225</v>
+      </c>
+      <c r="N247" s="6">
+        <v>234</v>
+      </c>
+      <c r="O247" s="6">
+        <v>248</v>
+      </c>
+      <c r="P247" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q247" s="6">
+        <v>268</v>
+      </c>
+      <c r="R247" s="6">
+        <v>297</v>
+      </c>
+      <c r="S247" s="6">
+        <v>329</v>
+      </c>
+      <c r="T247" s="6">
+        <v>343</v>
+      </c>
+      <c r="U247" s="6">
+        <v>389</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="248" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>186</v>
+        <v>28</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G248" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="H248" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="I248" s="5">
-        <v>6.53</v>
-      </c>
-      <c r="J248" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="K248" s="5">
-        <v>6.32</v>
-      </c>
-      <c r="L248" s="5">
-        <v>5.69</v>
-      </c>
-      <c r="M248" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="N248" s="5">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="O248" s="5">
-        <v>5.72</v>
-      </c>
-      <c r="P248" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="Q248" s="5">
-        <v>6.58</v>
-      </c>
-      <c r="R248" s="5">
-        <v>5.67</v>
-      </c>
-      <c r="S248" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="T248" s="5">
-        <v>6.34</v>
-      </c>
-      <c r="U248" s="5">
-        <v>6.03</v>
-      </c>
-      <c r="V248" s="3"/>
+        <v>320</v>
+      </c>
+      <c r="G248" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H248" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I248" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J248" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K248" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L248" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M248" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N248" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O248" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P248" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q248" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R248" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S248" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T248" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U248" s="6">
+        <v>33623</v>
+      </c>
+      <c r="V248" s="6">
+        <v>37777</v>
+      </c>
       <c r="W248" s="2" t="s">
-        <v>88</v>
+        <v>321</v>
       </c>
     </row>
     <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>322</v>
@@ -17362,136 +17378,134 @@
         <v>323</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G249" s="5">
-        <v>6.55</v>
-      </c>
-      <c r="H249" s="5">
-        <v>8.08</v>
-      </c>
-      <c r="I249" s="5">
-        <v>10.61</v>
-      </c>
-      <c r="J249" s="5">
-        <v>10.68</v>
-      </c>
-      <c r="K249" s="5">
-        <v>12.36</v>
-      </c>
-      <c r="L249" s="5">
-        <v>13.4</v>
-      </c>
-      <c r="M249" s="5">
-        <v>13.34</v>
-      </c>
-      <c r="N249" s="5">
-        <v>13.08</v>
-      </c>
-      <c r="O249" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="P249" s="5">
-        <v>14.36</v>
-      </c>
-      <c r="Q249" s="5">
-        <v>16.239999999999998</v>
-      </c>
-      <c r="R249" s="5">
-        <v>17.170000000000002</v>
-      </c>
-      <c r="S249" s="5">
-        <v>21.01</v>
-      </c>
-      <c r="T249" s="5">
-        <v>25.79</v>
-      </c>
-      <c r="U249" s="5">
-        <v>30.37</v>
-      </c>
+      <c r="G249" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L249" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P249" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S249" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T249" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U249" s="3"/>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>322</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>188</v>
+        <v>325</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>34</v>
+        <v>326</v>
       </c>
       <c r="G250" s="5">
-        <v>11.81</v>
+        <v>137.94999999999999</v>
       </c>
       <c r="H250" s="5">
-        <v>13.24</v>
+        <v>0</v>
       </c>
       <c r="I250" s="5">
-        <v>13.5</v>
+        <v>0.18</v>
       </c>
       <c r="J250" s="5">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="K250" s="5">
-        <v>14.24</v>
+        <v>0</v>
       </c>
       <c r="L250" s="5">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="M250" s="5">
-        <v>14.92</v>
+        <v>0</v>
       </c>
       <c r="N250" s="5">
-        <v>14.78</v>
+        <v>2.29</v>
       </c>
       <c r="O250" s="5">
-        <v>21.47</v>
+        <v>25.44</v>
       </c>
       <c r="P250" s="5">
-        <v>22.01</v>
+        <v>0</v>
       </c>
       <c r="Q250" s="5">
-        <v>22.14</v>
+        <v>12.02</v>
       </c>
       <c r="R250" s="5">
-        <v>20.98</v>
+        <v>0.89</v>
       </c>
       <c r="S250" s="5">
-        <v>22.1</v>
+        <v>0.03</v>
       </c>
       <c r="T250" s="5">
-        <v>20.61</v>
+        <v>0.03</v>
       </c>
       <c r="U250" s="5">
-        <v>21.29</v>
+        <v>80.36</v>
       </c>
       <c r="V250" s="3"/>
       <c r="W250" s="2" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>322</v>
@@ -17500,211 +17514,209 @@
         <v>324</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>28</v>
+        <v>327</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G251" s="6">
-        <v>563</v>
+        <v>5248</v>
       </c>
       <c r="H251" s="6">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="I251" s="6">
-        <v>661</v>
+        <v>7</v>
       </c>
       <c r="J251" s="6">
-        <v>778</v>
+        <v>0</v>
       </c>
       <c r="K251" s="6">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="L251" s="6">
-        <v>909</v>
+        <v>0</v>
       </c>
       <c r="M251" s="6">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="N251" s="6">
-        <v>946</v>
+        <v>87</v>
       </c>
       <c r="O251" s="6">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="P251" s="6">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="Q251" s="6">
-        <v>1073</v>
+        <v>451</v>
       </c>
       <c r="R251" s="6">
-        <v>1189</v>
+        <v>33</v>
       </c>
       <c r="S251" s="6">
-        <v>1318</v>
+        <v>1</v>
       </c>
       <c r="T251" s="6">
-        <v>1372</v>
+        <v>1</v>
       </c>
       <c r="U251" s="6">
-        <v>1556</v>
+        <v>2938</v>
       </c>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>326</v>
+        <v>28</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G252" s="6">
-        <v>440</v>
-      </c>
-      <c r="H252" s="6">
-        <v>101</v>
-      </c>
-      <c r="I252" s="6">
-        <v>151</v>
-      </c>
-      <c r="J252" s="6">
-        <v>217</v>
-      </c>
-      <c r="K252" s="6">
-        <v>239</v>
-      </c>
-      <c r="L252" s="6">
-        <v>674</v>
-      </c>
-      <c r="M252" s="6">
-        <v>705</v>
-      </c>
-      <c r="N252" s="6">
-        <v>712</v>
-      </c>
-      <c r="O252" s="6">
-        <v>743</v>
-      </c>
-      <c r="P252" s="6">
-        <v>788</v>
-      </c>
-      <c r="Q252" s="6">
-        <v>805</v>
-      </c>
-      <c r="R252" s="6">
-        <v>892</v>
-      </c>
-      <c r="S252" s="6">
-        <v>988</v>
-      </c>
-      <c r="T252" s="6">
-        <v>1029</v>
-      </c>
-      <c r="U252" s="6">
-        <v>1167</v>
+        <v>330</v>
+      </c>
+      <c r="G252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J252" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="L252" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="M252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="N252" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Q252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R252" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="T252" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="U252" s="5">
+        <v>0.59</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="253" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>327</v>
+        <v>28</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G253" s="6">
-        <v>123</v>
-      </c>
-      <c r="H253" s="6">
-        <v>101</v>
-      </c>
-      <c r="I253" s="6">
-        <v>151</v>
-      </c>
-      <c r="J253" s="6">
-        <v>217</v>
-      </c>
-      <c r="K253" s="6">
-        <v>239</v>
-      </c>
-      <c r="L253" s="6">
-        <v>235</v>
-      </c>
-      <c r="M253" s="6">
-        <v>225</v>
-      </c>
-      <c r="N253" s="6">
-        <v>234</v>
-      </c>
-      <c r="O253" s="6">
-        <v>248</v>
-      </c>
-      <c r="P253" s="6">
-        <v>263</v>
-      </c>
-      <c r="Q253" s="6">
-        <v>268</v>
-      </c>
-      <c r="R253" s="6">
-        <v>297</v>
-      </c>
-      <c r="S253" s="6">
-        <v>329</v>
-      </c>
-      <c r="T253" s="6">
-        <v>343</v>
-      </c>
-      <c r="U253" s="6">
-        <v>389</v>
+        <v>167</v>
+      </c>
+      <c r="G253" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H253" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I253" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J253" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K253" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L253" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M253" s="4">
+        <v>826034.2</v>
+      </c>
+      <c r="N253" s="3"/>
+      <c r="O253" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P253" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q253" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R253" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S253" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T253" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U253" s="4">
+        <v>881284.3</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="254" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17713,69 +17725,59 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G254" s="6">
-        <v>2218</v>
-      </c>
-      <c r="H254" s="6">
-        <v>3117</v>
-      </c>
-      <c r="I254" s="6">
-        <v>4139</v>
-      </c>
-      <c r="J254" s="6">
-        <v>5205</v>
-      </c>
-      <c r="K254" s="6">
-        <v>5793</v>
-      </c>
-      <c r="L254" s="6">
-        <v>7105</v>
-      </c>
-      <c r="M254" s="6">
-        <v>8017</v>
-      </c>
-      <c r="N254" s="6">
-        <v>8195</v>
-      </c>
-      <c r="O254" s="6">
-        <v>8486</v>
-      </c>
-      <c r="P254" s="6">
-        <v>9547</v>
-      </c>
-      <c r="Q254" s="6">
-        <v>12490</v>
-      </c>
-      <c r="R254" s="6">
-        <v>16935</v>
-      </c>
-      <c r="S254" s="6">
-        <v>22670</v>
-      </c>
-      <c r="T254" s="6">
-        <v>28779</v>
-      </c>
-      <c r="U254" s="6">
-        <v>33623</v>
-      </c>
-      <c r="V254" s="6">
-        <v>37777</v>
+        <v>281</v>
+      </c>
+      <c r="G254" s="3"/>
+      <c r="H254" s="3"/>
+      <c r="I254" s="3"/>
+      <c r="J254" s="3"/>
+      <c r="K254" s="3"/>
+      <c r="L254" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M254" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N254" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O254" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P254" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q254" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R254" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S254" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T254" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U254" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V254" s="5">
+        <v>5.95</v>
       </c>
       <c r="W254" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="255" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17784,455 +17786,425 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G255" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="H255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="K255" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="L255" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="M255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="N255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="O255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="P255" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="Q255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="R255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S255" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="T255" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="U255" s="3"/>
-      <c r="V255" s="3"/>
+        <v>330</v>
+      </c>
+      <c r="G255" s="3"/>
+      <c r="H255" s="3"/>
+      <c r="I255" s="3"/>
+      <c r="J255" s="3"/>
+      <c r="K255" s="3"/>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
+      <c r="N255" s="3"/>
+      <c r="O255" s="6">
+        <v>1</v>
+      </c>
+      <c r="P255" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q255" s="6">
+        <v>63</v>
+      </c>
+      <c r="R255" s="6">
+        <v>66</v>
+      </c>
+      <c r="S255" s="6">
+        <v>70</v>
+      </c>
+      <c r="T255" s="6">
+        <v>75</v>
+      </c>
+      <c r="U255" s="6">
+        <v>80</v>
+      </c>
+      <c r="V255" s="6">
+        <v>86</v>
+      </c>
       <c r="W255" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G256" s="5">
-        <v>137.94999999999999</v>
-      </c>
-      <c r="H256" s="5">
-        <v>0</v>
-      </c>
-      <c r="I256" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="J256" s="5">
-        <v>0</v>
-      </c>
-      <c r="K256" s="5">
-        <v>0</v>
-      </c>
-      <c r="L256" s="5">
-        <v>0</v>
-      </c>
-      <c r="M256" s="5">
-        <v>0</v>
-      </c>
-      <c r="N256" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="O256" s="5">
-        <v>25.44</v>
-      </c>
-      <c r="P256" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q256" s="5">
-        <v>12.02</v>
-      </c>
-      <c r="R256" s="5">
-        <v>0.89</v>
-      </c>
-      <c r="S256" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="T256" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="U256" s="5">
-        <v>80.36</v>
-      </c>
-      <c r="V256" s="3"/>
+        <v>339</v>
+      </c>
+      <c r="G256" s="3"/>
+      <c r="H256" s="3"/>
+      <c r="I256" s="3"/>
+      <c r="J256" s="3"/>
+      <c r="K256" s="3"/>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
+      <c r="N256" s="3"/>
+      <c r="O256" s="3"/>
+      <c r="P256" s="3"/>
+      <c r="Q256" s="3"/>
+      <c r="R256" s="3"/>
+      <c r="S256" s="6">
+        <v>16</v>
+      </c>
+      <c r="T256" s="6">
+        <v>7</v>
+      </c>
+      <c r="U256" s="6">
+        <v>6</v>
+      </c>
+      <c r="V256" s="6">
+        <v>4</v>
+      </c>
       <c r="W256" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G257" s="6">
-        <v>5248</v>
-      </c>
-      <c r="H257" s="6">
-        <v>0</v>
-      </c>
-      <c r="I257" s="6">
-        <v>7</v>
-      </c>
-      <c r="J257" s="6">
-        <v>0</v>
-      </c>
-      <c r="K257" s="6">
-        <v>0</v>
-      </c>
-      <c r="L257" s="6">
-        <v>0</v>
-      </c>
-      <c r="M257" s="6">
-        <v>0</v>
-      </c>
-      <c r="N257" s="6">
-        <v>87</v>
-      </c>
-      <c r="O257" s="6">
-        <v>966</v>
-      </c>
-      <c r="P257" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="6">
-        <v>451</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="G257" s="3"/>
+      <c r="H257" s="3"/>
+      <c r="I257" s="3"/>
+      <c r="J257" s="3"/>
+      <c r="K257" s="3"/>
+      <c r="L257" s="3"/>
+      <c r="M257" s="3"/>
+      <c r="N257" s="3"/>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="3"/>
       <c r="R257" s="6">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="S257" s="6">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="T257" s="6">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="U257" s="6">
-        <v>2938</v>
-      </c>
-      <c r="V257" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="V257" s="6">
+        <v>89</v>
+      </c>
       <c r="W257" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="258" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>27</v>
+        <v>347</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>28</v>
+        <v>348</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="I258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J258" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="K258" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="L258" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="M258" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="N258" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="O258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="P258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="R258" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="S258" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="T258" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="U258" s="5">
-        <v>0.59</v>
+        <v>34</v>
+      </c>
+      <c r="G258" s="6">
+        <v>40</v>
+      </c>
+      <c r="H258" s="6">
+        <v>60</v>
+      </c>
+      <c r="I258" s="6">
+        <v>40</v>
+      </c>
+      <c r="J258" s="6">
+        <v>40</v>
+      </c>
+      <c r="K258" s="6">
+        <v>40</v>
+      </c>
+      <c r="L258" s="6">
+        <v>40</v>
+      </c>
+      <c r="M258" s="6">
+        <v>60</v>
+      </c>
+      <c r="N258" s="6">
+        <v>40</v>
+      </c>
+      <c r="O258" s="6">
+        <v>40</v>
+      </c>
+      <c r="P258" s="6">
+        <v>40</v>
+      </c>
+      <c r="Q258" s="6">
+        <v>60</v>
+      </c>
+      <c r="R258" s="6">
+        <v>67</v>
+      </c>
+      <c r="S258" s="6">
+        <v>50</v>
+      </c>
+      <c r="T258" s="6">
+        <v>67</v>
+      </c>
+      <c r="U258" s="6">
+        <v>67</v>
       </c>
       <c r="V258" s="3"/>
       <c r="W258" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>27</v>
+        <v>347</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G259" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H259" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I259" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J259" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K259" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L259" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M259" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N259" s="3"/>
-      <c r="O259" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P259" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q259" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R259" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S259" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T259" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U259" s="4">
-        <v>881284.3</v>
+        <v>34</v>
+      </c>
+      <c r="G259" s="6">
+        <v>40</v>
+      </c>
+      <c r="H259" s="6">
+        <v>60</v>
+      </c>
+      <c r="I259" s="6">
+        <v>20</v>
+      </c>
+      <c r="J259" s="6">
+        <v>20</v>
+      </c>
+      <c r="K259" s="6">
+        <v>20</v>
+      </c>
+      <c r="L259" s="6">
+        <v>40</v>
+      </c>
+      <c r="M259" s="6">
+        <v>60</v>
+      </c>
+      <c r="N259" s="6">
+        <v>40</v>
+      </c>
+      <c r="O259" s="6">
+        <v>25</v>
+      </c>
+      <c r="P259" s="6">
+        <v>25</v>
+      </c>
+      <c r="Q259" s="6">
+        <v>20</v>
+      </c>
+      <c r="R259" s="6">
+        <v>17</v>
+      </c>
+      <c r="S259" s="6">
+        <v>0</v>
+      </c>
+      <c r="T259" s="6">
+        <v>17</v>
+      </c>
+      <c r="U259" s="6">
+        <v>0</v>
       </c>
       <c r="V259" s="3"/>
       <c r="W259" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="260" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>27</v>
+        <v>347</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="G260" s="3"/>
-      <c r="H260" s="3"/>
-      <c r="I260" s="3"/>
-      <c r="J260" s="3"/>
-      <c r="K260" s="3"/>
-      <c r="L260" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="M260" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="N260" s="5">
-        <v>7.54</v>
-      </c>
-      <c r="O260" s="5">
-        <v>10.15</v>
-      </c>
-      <c r="P260" s="5">
-        <v>12.38</v>
-      </c>
-      <c r="Q260" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="R260" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="S260" s="5">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="T260" s="5">
-        <v>6.25</v>
-      </c>
-      <c r="U260" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V260" s="5">
-        <v>5.95</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G260" s="6">
+        <v>0</v>
+      </c>
+      <c r="H260" s="6">
+        <v>0</v>
+      </c>
+      <c r="I260" s="6">
+        <v>20</v>
+      </c>
+      <c r="J260" s="6">
+        <v>20</v>
+      </c>
+      <c r="K260" s="6">
+        <v>20</v>
+      </c>
+      <c r="L260" s="6">
+        <v>0</v>
+      </c>
+      <c r="M260" s="6">
+        <v>0</v>
+      </c>
+      <c r="N260" s="6">
+        <v>0</v>
+      </c>
+      <c r="O260" s="6">
+        <v>0</v>
+      </c>
+      <c r="P260" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q260" s="6">
+        <v>40</v>
+      </c>
+      <c r="R260" s="6">
+        <v>17</v>
+      </c>
+      <c r="S260" s="6">
+        <v>17</v>
+      </c>
+      <c r="T260" s="6">
+        <v>17</v>
+      </c>
+      <c r="U260" s="6">
+        <v>50</v>
+      </c>
+      <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="261" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>27</v>
+        <v>347</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>28</v>
+        <v>352</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G261" s="3"/>
-      <c r="H261" s="3"/>
-      <c r="I261" s="3"/>
-      <c r="J261" s="3"/>
-      <c r="K261" s="3"/>
-      <c r="L261" s="3"/>
-      <c r="M261" s="3"/>
-      <c r="N261" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G261" s="6">
+        <v>60</v>
+      </c>
+      <c r="H261" s="6">
+        <v>40</v>
+      </c>
+      <c r="I261" s="6">
+        <v>60</v>
+      </c>
+      <c r="J261" s="6">
+        <v>60</v>
+      </c>
+      <c r="K261" s="6">
+        <v>60</v>
+      </c>
+      <c r="L261" s="6">
+        <v>60</v>
+      </c>
+      <c r="M261" s="6">
+        <v>40</v>
+      </c>
+      <c r="N261" s="6">
+        <v>60</v>
+      </c>
       <c r="O261" s="6">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="P261" s="6">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="Q261" s="6">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="R261" s="6">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="S261" s="6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T261" s="6">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>80</v>
-      </c>
-      <c r="V261" s="6">
-        <v>86</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" ht="99" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="B262" s="2" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>27</v>
@@ -18241,45 +18213,67 @@
         <v>28</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G262" s="3"/>
-      <c r="H262" s="3"/>
-      <c r="I262" s="3"/>
-      <c r="J262" s="3"/>
-      <c r="K262" s="3"/>
-      <c r="L262" s="3"/>
-      <c r="M262" s="3"/>
-      <c r="N262" s="3"/>
-      <c r="O262" s="3"/>
-      <c r="P262" s="3"/>
-      <c r="Q262" s="3"/>
-      <c r="R262" s="3"/>
-      <c r="S262" s="6">
-        <v>16</v>
-      </c>
-      <c r="T262" s="6">
-        <v>7</v>
-      </c>
-      <c r="U262" s="6">
-        <v>6</v>
-      </c>
-      <c r="V262" s="6">
-        <v>4</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G262" s="4">
+        <v>100</v>
+      </c>
+      <c r="H262" s="4">
+        <v>100.8</v>
+      </c>
+      <c r="I262" s="4">
+        <v>99.9</v>
+      </c>
+      <c r="J262" s="4">
+        <v>101.8</v>
+      </c>
+      <c r="K262" s="4">
+        <v>104.9</v>
+      </c>
+      <c r="L262" s="4">
+        <v>106</v>
+      </c>
+      <c r="M262" s="4">
+        <v>119.9</v>
+      </c>
+      <c r="N262" s="4">
+        <v>119.4</v>
+      </c>
+      <c r="O262" s="4">
+        <v>130</v>
+      </c>
+      <c r="P262" s="4">
+        <v>189.5</v>
+      </c>
+      <c r="Q262" s="4">
+        <v>186.6</v>
+      </c>
+      <c r="R262" s="4">
+        <v>190.1</v>
+      </c>
+      <c r="S262" s="4">
+        <v>200.8</v>
+      </c>
+      <c r="T262" s="4">
+        <v>205.6</v>
+      </c>
+      <c r="U262" s="4">
+        <v>208.5</v>
+      </c>
+      <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>27</v>
@@ -18288,446 +18282,466 @@
         <v>28</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="G263" s="3"/>
-      <c r="H263" s="3"/>
-      <c r="I263" s="3"/>
-      <c r="J263" s="3"/>
-      <c r="K263" s="3"/>
-      <c r="L263" s="3"/>
-      <c r="M263" s="3"/>
-      <c r="N263" s="3"/>
-      <c r="O263" s="3"/>
-      <c r="P263" s="3"/>
-      <c r="Q263" s="3"/>
-      <c r="R263" s="6">
-        <v>133</v>
-      </c>
-      <c r="S263" s="6">
-        <v>80</v>
-      </c>
-      <c r="T263" s="6">
-        <v>97</v>
-      </c>
-      <c r="U263" s="6">
-        <v>44</v>
-      </c>
-      <c r="V263" s="6">
-        <v>89</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="G263" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="H263" s="4">
+        <v>57.7</v>
+      </c>
+      <c r="I263" s="4">
+        <v>58.8</v>
+      </c>
+      <c r="J263" s="4">
+        <v>64.3</v>
+      </c>
+      <c r="K263" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="L263" s="4">
+        <v>69.5</v>
+      </c>
+      <c r="M263" s="4">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="N263" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O263" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="P263" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="Q263" s="4">
+        <v>88.5</v>
+      </c>
+      <c r="R263" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S263" s="4">
+        <v>119</v>
+      </c>
+      <c r="T263" s="4">
+        <v>136.4</v>
+      </c>
+      <c r="U263" s="4">
+        <v>124.2</v>
+      </c>
+      <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="264" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>356</v>
+        <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G264" s="6">
-        <v>40</v>
-      </c>
-      <c r="H264" s="6">
-        <v>60</v>
-      </c>
-      <c r="I264" s="6">
-        <v>40</v>
-      </c>
-      <c r="J264" s="6">
-        <v>40</v>
-      </c>
-      <c r="K264" s="6">
-        <v>40</v>
-      </c>
-      <c r="L264" s="6">
-        <v>40</v>
-      </c>
-      <c r="M264" s="6">
-        <v>60</v>
-      </c>
-      <c r="N264" s="6">
-        <v>40</v>
-      </c>
-      <c r="O264" s="6">
-        <v>40</v>
-      </c>
-      <c r="P264" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q264" s="6">
-        <v>60</v>
-      </c>
-      <c r="R264" s="6">
-        <v>67</v>
-      </c>
-      <c r="S264" s="6">
-        <v>50</v>
-      </c>
-      <c r="T264" s="6">
-        <v>67</v>
-      </c>
-      <c r="U264" s="6">
-        <v>67</v>
+        <v>362</v>
+      </c>
+      <c r="G264" s="4">
+        <v>90.8</v>
+      </c>
+      <c r="H264" s="4">
+        <v>88.8</v>
+      </c>
+      <c r="I264" s="4">
+        <v>86.5</v>
+      </c>
+      <c r="J264" s="4">
+        <v>87</v>
+      </c>
+      <c r="K264" s="4">
+        <v>85</v>
+      </c>
+      <c r="L264" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="M264" s="4">
+        <v>88.7</v>
+      </c>
+      <c r="N264" s="4">
+        <v>84.6</v>
+      </c>
+      <c r="O264" s="4">
+        <v>77.3</v>
+      </c>
+      <c r="P264" s="4">
+        <v>79.7</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="R264" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="S264" s="4">
+        <v>77</v>
+      </c>
+      <c r="T264" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U264" s="4">
+        <v>76.3</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>358</v>
+        <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G265" s="6">
-        <v>40</v>
-      </c>
-      <c r="H265" s="6">
-        <v>60</v>
-      </c>
-      <c r="I265" s="6">
-        <v>20</v>
-      </c>
-      <c r="J265" s="6">
-        <v>20</v>
-      </c>
-      <c r="K265" s="6">
-        <v>20</v>
-      </c>
-      <c r="L265" s="6">
-        <v>40</v>
-      </c>
-      <c r="M265" s="6">
-        <v>60</v>
-      </c>
-      <c r="N265" s="6">
-        <v>40</v>
-      </c>
-      <c r="O265" s="6">
-        <v>25</v>
-      </c>
-      <c r="P265" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q265" s="6">
-        <v>20</v>
-      </c>
-      <c r="R265" s="6">
-        <v>17</v>
-      </c>
-      <c r="S265" s="6">
-        <v>0</v>
-      </c>
-      <c r="T265" s="6">
-        <v>17</v>
-      </c>
-      <c r="U265" s="6">
-        <v>0</v>
+      <c r="G265" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H265" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I265" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K265" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L265" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M265" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q265" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R265" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S265" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T265" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U265" s="7">
+        <v>0.192</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="266" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G266" s="6">
-        <v>0</v>
-      </c>
-      <c r="H266" s="6">
-        <v>0</v>
-      </c>
-      <c r="I266" s="6">
-        <v>20</v>
-      </c>
-      <c r="J266" s="6">
-        <v>20</v>
-      </c>
-      <c r="K266" s="6">
-        <v>20</v>
-      </c>
-      <c r="L266" s="6">
-        <v>0</v>
-      </c>
-      <c r="M266" s="6">
-        <v>0</v>
-      </c>
-      <c r="N266" s="6">
-        <v>0</v>
-      </c>
-      <c r="O266" s="6">
-        <v>0</v>
-      </c>
-      <c r="P266" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q266" s="6">
-        <v>40</v>
-      </c>
-      <c r="R266" s="6">
-        <v>17</v>
-      </c>
-      <c r="S266" s="6">
-        <v>17</v>
-      </c>
-      <c r="T266" s="6">
-        <v>17</v>
-      </c>
-      <c r="U266" s="6">
-        <v>50</v>
+      <c r="G266" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="H266" s="4">
+        <v>30.5</v>
+      </c>
+      <c r="I266" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="J266" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="K266" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="L266" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="M266" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="N266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="O266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="P266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="Q266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R266" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="S266" s="4">
+        <v>31</v>
+      </c>
+      <c r="T266" s="4">
+        <v>31</v>
+      </c>
+      <c r="U266" s="4">
+        <v>31</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="267" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>355</v>
+        <v>27</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>360</v>
+        <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="G267" s="6">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="H267" s="6">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="I267" s="6">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="J267" s="6">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K267" s="6">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="L267" s="6">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="M267" s="6">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N267" s="6">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="O267" s="6">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="P267" s="6">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="Q267" s="6">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="R267" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S267" s="6">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="T267" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U267" s="6">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="268" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>363</v>
+        <v>34</v>
       </c>
       <c r="G268" s="4">
-        <v>100</v>
+        <v>64.7</v>
       </c>
       <c r="H268" s="4">
-        <v>100.8</v>
+        <v>65.7</v>
       </c>
       <c r="I268" s="4">
-        <v>99.9</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J268" s="4">
-        <v>101.8</v>
+        <v>70.3</v>
       </c>
       <c r="K268" s="4">
-        <v>104.9</v>
+        <v>71.5</v>
       </c>
       <c r="L268" s="4">
-        <v>106</v>
+        <v>72.7</v>
       </c>
       <c r="M268" s="4">
-        <v>119.9</v>
+        <v>73.5</v>
       </c>
       <c r="N268" s="4">
-        <v>119.4</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="P268" s="4">
-        <v>189.5</v>
+        <v>74.5</v>
       </c>
       <c r="Q268" s="4">
-        <v>186.6</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R268" s="4">
-        <v>190.1</v>
+        <v>75.2</v>
       </c>
       <c r="S268" s="4">
-        <v>200.8</v>
+        <v>75.7</v>
       </c>
       <c r="T268" s="4">
-        <v>205.6</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U268" s="4">
-        <v>208.5</v>
+        <v>76.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
       <c r="G269" s="4">
-        <v>59.5</v>
+        <v>88</v>
       </c>
       <c r="H269" s="4">
-        <v>57.7</v>
+        <v>88.4</v>
       </c>
       <c r="I269" s="4">
-        <v>58.8</v>
+        <v>91.7</v>
       </c>
       <c r="J269" s="4">
-        <v>64.3</v>
+        <v>93.3</v>
       </c>
       <c r="K269" s="4">
-        <v>68.7</v>
+        <v>93.9</v>
       </c>
       <c r="L269" s="4">
-        <v>69.5</v>
+        <v>94.6</v>
       </c>
       <c r="M269" s="4">
-        <v>72.900000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="N269" s="4">
-        <v>78.099999999999994</v>
+        <v>94.5</v>
       </c>
       <c r="O269" s="4">
-        <v>91.8</v>
+        <v>94.6</v>
       </c>
       <c r="P269" s="4">
-        <v>93.9</v>
+        <v>94.8</v>
       </c>
       <c r="Q269" s="4">
-        <v>88.5</v>
+        <v>94.7</v>
       </c>
       <c r="R269" s="4">
-        <v>96.7</v>
+        <v>94.6</v>
       </c>
       <c r="S269" s="4">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="T269" s="4">
-        <v>136.4</v>
+        <v>94.8</v>
       </c>
       <c r="U269" s="4">
-        <v>124.2</v>
+        <v>94.6</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
@@ -18736,82 +18750,82 @@
     </row>
     <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B270" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C270" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="D270" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>370</v>
+        <v>34</v>
       </c>
       <c r="G270" s="4">
-        <v>90.8</v>
+        <v>28.5</v>
       </c>
       <c r="H270" s="4">
-        <v>88.8</v>
+        <v>30.6</v>
       </c>
       <c r="I270" s="4">
-        <v>86.5</v>
+        <v>33.1</v>
       </c>
       <c r="J270" s="4">
-        <v>87</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="K270" s="4">
-        <v>85</v>
+        <v>37.4</v>
       </c>
       <c r="L270" s="4">
-        <v>87.4</v>
+        <v>39.6</v>
       </c>
       <c r="M270" s="4">
-        <v>88.7</v>
+        <v>41.2</v>
       </c>
       <c r="N270" s="4">
-        <v>84.6</v>
+        <v>42</v>
       </c>
       <c r="O270" s="4">
-        <v>77.3</v>
+        <v>42.9</v>
       </c>
       <c r="P270" s="4">
-        <v>79.7</v>
+        <v>44</v>
       </c>
       <c r="Q270" s="4">
-        <v>81.900000000000006</v>
+        <v>45.4</v>
       </c>
       <c r="R270" s="4">
-        <v>74.8</v>
+        <v>46.5</v>
       </c>
       <c r="S270" s="4">
-        <v>77</v>
+        <v>47.2</v>
       </c>
       <c r="T270" s="4">
-        <v>77.2</v>
+        <v>48.2</v>
       </c>
       <c r="U270" s="4">
-        <v>76.3</v>
+        <v>49.3</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
     </row>
     <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>27</v>
@@ -18822,65 +18836,65 @@
       <c r="F271" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G271" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H271" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I271" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K271" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L271" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M271" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P271" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q271" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R271" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S271" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T271" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U271" s="7">
-        <v>0.192</v>
+      <c r="G271" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H271" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I271" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J271" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K271" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L271" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M271" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N271" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O271" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P271" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q271" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R271" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S271" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T271" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U271" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D272" s="2" t="s">
         <v>27</v>
@@ -18889,67 +18903,67 @@
         <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G272" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="H272" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="I272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="J272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="K272" s="4">
-        <v>30.7</v>
-      </c>
-      <c r="L272" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="M272" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="N272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="O272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="P272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="Q272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R272" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="S272" s="4">
-        <v>31</v>
-      </c>
-      <c r="T272" s="4">
-        <v>31</v>
-      </c>
-      <c r="U272" s="4">
-        <v>31</v>
+        <v>372</v>
+      </c>
+      <c r="G272" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H272" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I272" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J272" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K272" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L272" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M272" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N272" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O272" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P272" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R272" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S272" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T272" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U272" s="6">
+        <v>104040</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18958,70 +18972,70 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G273" s="6">
-        <v>28</v>
-      </c>
-      <c r="H273" s="6">
-        <v>27</v>
-      </c>
-      <c r="I273" s="6">
-        <v>26</v>
-      </c>
-      <c r="J273" s="6">
-        <v>25</v>
-      </c>
-      <c r="K273" s="6">
-        <v>24</v>
-      </c>
-      <c r="L273" s="6">
-        <v>23</v>
-      </c>
-      <c r="M273" s="6">
-        <v>22</v>
-      </c>
-      <c r="N273" s="6">
-        <v>22</v>
-      </c>
-      <c r="O273" s="6">
-        <v>22</v>
-      </c>
-      <c r="P273" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q273" s="6">
-        <v>19</v>
-      </c>
-      <c r="R273" s="6">
-        <v>17</v>
-      </c>
-      <c r="S273" s="6">
-        <v>16</v>
-      </c>
-      <c r="T273" s="6">
-        <v>16</v>
-      </c>
-      <c r="U273" s="6">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="G273" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H273" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I273" s="4">
+        <v>6</v>
+      </c>
+      <c r="J273" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K273" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L273" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M273" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N273" s="4">
+        <v>3</v>
+      </c>
+      <c r="O273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P273" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q273" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R273" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S273" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T273" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U273" s="4">
+        <v>4.5</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="274" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>376</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>28</v>
@@ -19029,203 +19043,165 @@
       <c r="F274" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G274" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H274" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I274" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J274" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K274" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L274" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M274" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N274" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O274" s="4">
-        <v>74</v>
-      </c>
-      <c r="P274" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q274" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R274" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S274" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T274" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U274" s="4">
-        <v>76.2</v>
-      </c>
-      <c r="V274" s="3"/>
+      <c r="G274" s="6">
+        <v>70</v>
+      </c>
+      <c r="H274" s="6">
+        <v>75</v>
+      </c>
+      <c r="I274" s="6">
+        <v>66</v>
+      </c>
+      <c r="J274" s="6">
+        <v>64</v>
+      </c>
+      <c r="K274" s="6">
+        <v>70</v>
+      </c>
+      <c r="L274" s="6">
+        <v>66</v>
+      </c>
+      <c r="M274" s="6">
+        <v>80</v>
+      </c>
+      <c r="N274" s="6">
+        <v>89</v>
+      </c>
+      <c r="O274" s="6">
+        <v>86</v>
+      </c>
+      <c r="P274" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q274" s="6">
+        <v>85</v>
+      </c>
+      <c r="R274" s="6">
+        <v>82</v>
+      </c>
+      <c r="S274" s="6">
+        <v>83</v>
+      </c>
+      <c r="T274" s="6">
+        <v>88</v>
+      </c>
+      <c r="U274" s="6">
+        <v>88</v>
+      </c>
+      <c r="V274" s="6">
+        <v>86</v>
+      </c>
       <c r="W274" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="275" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G275" s="4">
-        <v>88</v>
-      </c>
-      <c r="H275" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I275" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J275" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K275" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N275" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q275" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R275" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S275" s="4">
-        <v>95</v>
-      </c>
-      <c r="T275" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U275" s="4">
-        <v>94.6</v>
+      <c r="G275" s="6">
+        <v>55</v>
+      </c>
+      <c r="H275" s="3"/>
+      <c r="I275" s="6">
+        <v>58</v>
+      </c>
+      <c r="J275" s="3"/>
+      <c r="K275" s="6">
+        <v>60</v>
+      </c>
+      <c r="L275" s="3"/>
+      <c r="M275" s="6">
+        <v>64</v>
+      </c>
+      <c r="N275" s="3"/>
+      <c r="O275" s="6">
+        <v>65</v>
+      </c>
+      <c r="P275" s="3"/>
+      <c r="Q275" s="6">
+        <v>74</v>
+      </c>
+      <c r="R275" s="3"/>
+      <c r="S275" s="6">
+        <v>63</v>
+      </c>
+      <c r="T275" s="3"/>
+      <c r="U275" s="6">
+        <v>71</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="276" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G276" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H276" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I276" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J276" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K276" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L276" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M276" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N276" s="4">
         <v>42</v>
       </c>
-      <c r="O276" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P276" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q276" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R276" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S276" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T276" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U276" s="4">
-        <v>49.3</v>
-      </c>
+      <c r="G276" s="3"/>
+      <c r="H276" s="3"/>
+      <c r="I276" s="3"/>
+      <c r="J276" s="3"/>
+      <c r="K276" s="3"/>
+      <c r="L276" s="3"/>
+      <c r="M276" s="3"/>
+      <c r="N276" s="3"/>
+      <c r="O276" s="3"/>
+      <c r="P276" s="3"/>
+      <c r="Q276" s="3"/>
+      <c r="R276" s="3"/>
+      <c r="S276" s="5">
+        <v>33109.31</v>
+      </c>
+      <c r="T276" s="5">
+        <v>33829.39</v>
+      </c>
+      <c r="U276" s="3"/>
       <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="277" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -19234,67 +19210,67 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G277" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="H277" s="4">
-        <v>64.8</v>
-      </c>
-      <c r="I277" s="4">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="J277" s="4">
-        <v>69.8</v>
-      </c>
-      <c r="K277" s="4">
-        <v>70.5</v>
-      </c>
-      <c r="L277" s="4">
-        <v>70.900000000000006</v>
-      </c>
-      <c r="M277" s="4">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="N277" s="4">
-        <v>72.5</v>
-      </c>
-      <c r="O277" s="4">
-        <v>73.2</v>
-      </c>
-      <c r="P277" s="4">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="Q277" s="4">
-        <v>73.3</v>
-      </c>
-      <c r="R277" s="4">
-        <v>72.8</v>
-      </c>
-      <c r="S277" s="4">
-        <v>76.3</v>
-      </c>
-      <c r="T277" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="U277" s="4">
-        <v>78.599999999999994</v>
+        <v>203</v>
+      </c>
+      <c r="G277" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H277" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I277" s="5">
+        <v>1</v>
+      </c>
+      <c r="J277" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K277" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L277" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M277" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N277" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O277" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P277" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q277" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R277" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S277" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T277" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U277" s="5">
+        <v>0.69</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>30</v>
+        <v>204</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>27</v>
@@ -19303,67 +19279,67 @@
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="G278" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H278" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I278" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J278" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K278" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L278" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M278" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N278" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O278" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P278" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q278" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R278" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S278" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T278" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U278" s="6">
-        <v>104040</v>
+        <v>330</v>
+      </c>
+      <c r="G278" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I278" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J278" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K278" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M278" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N278" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O278" s="5">
+        <v>2</v>
+      </c>
+      <c r="P278" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R278" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S278" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T278" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U278" s="5">
+        <v>4.07</v>
       </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>30</v>
+        <v>384</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>27</v>
@@ -19374,68 +19350,42 @@
       <c r="F279" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G279" s="4">
-        <v>2.9</v>
-      </c>
-      <c r="H279" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="I279" s="4">
-        <v>6</v>
-      </c>
-      <c r="J279" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K279" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="L279" s="4">
-        <v>4.2</v>
-      </c>
-      <c r="M279" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="N279" s="4">
-        <v>3</v>
-      </c>
-      <c r="O279" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="P279" s="4">
-        <v>3.4</v>
-      </c>
-      <c r="Q279" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="R279" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="S279" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="T279" s="4">
-        <v>5.8</v>
-      </c>
+      <c r="G279" s="3"/>
+      <c r="H279" s="3"/>
+      <c r="I279" s="3"/>
+      <c r="J279" s="3"/>
+      <c r="K279" s="3"/>
+      <c r="L279" s="3"/>
+      <c r="M279" s="3"/>
+      <c r="N279" s="3"/>
+      <c r="O279" s="3"/>
+      <c r="P279" s="3"/>
+      <c r="Q279" s="3"/>
+      <c r="R279" s="3"/>
+      <c r="S279" s="3"/>
+      <c r="T279" s="3"/>
       <c r="U279" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="V279" s="3"/>
+        <v>30.2</v>
+      </c>
+      <c r="V279" s="4">
+        <v>51.3</v>
+      </c>
       <c r="W279" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>28</v>
@@ -19443,332 +19393,408 @@
       <c r="F280" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G280" s="6">
-        <v>70</v>
-      </c>
-      <c r="H280" s="6">
-        <v>75</v>
-      </c>
-      <c r="I280" s="6">
-        <v>66</v>
-      </c>
-      <c r="J280" s="6">
-        <v>64</v>
-      </c>
-      <c r="K280" s="6">
-        <v>70</v>
-      </c>
-      <c r="L280" s="6">
-        <v>66</v>
-      </c>
-      <c r="M280" s="6">
-        <v>80</v>
-      </c>
-      <c r="N280" s="6">
-        <v>89</v>
-      </c>
-      <c r="O280" s="6">
-        <v>86</v>
-      </c>
-      <c r="P280" s="6">
-        <v>89</v>
-      </c>
-      <c r="Q280" s="6">
-        <v>85</v>
-      </c>
-      <c r="R280" s="6">
-        <v>82</v>
-      </c>
-      <c r="S280" s="6">
-        <v>83</v>
-      </c>
-      <c r="T280" s="6">
-        <v>88</v>
-      </c>
-      <c r="U280" s="6">
-        <v>88</v>
-      </c>
-      <c r="V280" s="6">
-        <v>86</v>
+      <c r="G280" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="H280" s="4">
+        <v>27.6</v>
+      </c>
+      <c r="I280" s="4">
+        <v>31.6</v>
+      </c>
+      <c r="J280" s="4">
+        <v>22.6</v>
+      </c>
+      <c r="K280" s="4">
+        <v>26.9</v>
+      </c>
+      <c r="L280" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="M280" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="N280" s="4">
+        <v>30.8</v>
+      </c>
+      <c r="O280" s="4">
+        <v>35.5</v>
+      </c>
+      <c r="P280" s="4">
+        <v>40.4</v>
+      </c>
+      <c r="Q280" s="4">
+        <v>41.9</v>
+      </c>
+      <c r="R280" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="S280" s="4">
+        <v>55.4</v>
+      </c>
+      <c r="T280" s="4">
+        <v>58.5</v>
+      </c>
+      <c r="U280" s="4">
+        <v>61</v>
+      </c>
+      <c r="V280" s="4">
+        <v>61.1</v>
       </c>
       <c r="W280" s="2" t="s">
-        <v>385</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>28</v>
+        <v>388</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G281" s="6">
-        <v>55</v>
-      </c>
-      <c r="H281" s="3"/>
-      <c r="I281" s="6">
-        <v>58</v>
-      </c>
-      <c r="J281" s="3"/>
-      <c r="K281" s="6">
-        <v>60</v>
-      </c>
-      <c r="L281" s="3"/>
-      <c r="M281" s="6">
-        <v>64</v>
-      </c>
-      <c r="N281" s="3"/>
-      <c r="O281" s="6">
-        <v>65</v>
-      </c>
-      <c r="P281" s="3"/>
-      <c r="Q281" s="6">
-        <v>74</v>
-      </c>
-      <c r="R281" s="3"/>
-      <c r="S281" s="6">
-        <v>63</v>
-      </c>
-      <c r="T281" s="3"/>
-      <c r="U281" s="6">
-        <v>71</v>
-      </c>
-      <c r="V281" s="3"/>
+      <c r="G281" s="4">
+        <v>31.5</v>
+      </c>
+      <c r="H281" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="I281" s="4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J281" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K281" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="L281" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="M281" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="N281" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="O281" s="4">
+        <v>29.5</v>
+      </c>
+      <c r="P281" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Q281" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R281" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="S281" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="T281" s="4">
+        <v>44</v>
+      </c>
+      <c r="U281" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="V281" s="4">
+        <v>48.9</v>
+      </c>
       <c r="W281" s="2" t="s">
-        <v>385</v>
+        <v>30</v>
       </c>
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>387</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>28</v>
+        <v>389</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G282" s="3"/>
-      <c r="H282" s="3"/>
-      <c r="I282" s="3"/>
-      <c r="J282" s="3"/>
-      <c r="K282" s="3"/>
-      <c r="L282" s="3"/>
-      <c r="M282" s="3"/>
-      <c r="N282" s="3"/>
-      <c r="O282" s="3"/>
-      <c r="P282" s="3"/>
-      <c r="Q282" s="3"/>
-      <c r="R282" s="3"/>
-      <c r="S282" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T282" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U282" s="3"/>
-      <c r="V282" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G282" s="4">
+        <v>47.6</v>
+      </c>
+      <c r="H282" s="4">
+        <v>46.2</v>
+      </c>
+      <c r="I282" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="J282" s="4">
+        <v>39</v>
+      </c>
+      <c r="K282" s="4">
+        <v>46</v>
+      </c>
+      <c r="L282" s="4">
+        <v>45</v>
+      </c>
+      <c r="M282" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="N282" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="O282" s="4">
+        <v>53</v>
+      </c>
+      <c r="P282" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="Q282" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="R282" s="4">
+        <v>68.3</v>
+      </c>
+      <c r="S282" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="T282" s="4">
+        <v>81</v>
+      </c>
+      <c r="U282" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="V282" s="4">
+        <v>81.8</v>
+      </c>
       <c r="W282" s="2" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>28</v>
+        <v>390</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G283" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H283" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I283" s="5">
-        <v>1</v>
-      </c>
-      <c r="J283" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K283" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L283" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M283" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N283" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O283" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P283" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q283" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R283" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S283" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T283" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U283" s="5">
-        <v>0.69</v>
-      </c>
-      <c r="V283" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G283" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="H283" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="I283" s="4">
+        <v>45.3</v>
+      </c>
+      <c r="J283" s="4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="K283" s="4">
+        <v>40.1</v>
+      </c>
+      <c r="L283" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="M283" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="N283" s="4">
+        <v>45</v>
+      </c>
+      <c r="O283" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="P283" s="4">
+        <v>57.6</v>
+      </c>
+      <c r="Q283" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="R283" s="4">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="S283" s="4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T283" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="U283" s="4">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="V283" s="4">
+        <v>78.3</v>
+      </c>
       <c r="W283" s="2" t="s">
-        <v>204</v>
+        <v>30</v>
       </c>
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E284" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E284" s="3" t="s">
+      <c r="F284" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G284" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="H284" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="I284" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="J284" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="K284" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="L284" s="4">
+        <v>26</v>
+      </c>
+      <c r="M284" s="4">
+        <v>30</v>
+      </c>
+      <c r="N284" s="4">
         <v>28</v>
       </c>
-      <c r="F284" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G284" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H284" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I284" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J284" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K284" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M284" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N284" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O284" s="5">
-        <v>2</v>
-      </c>
-      <c r="P284" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R284" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S284" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T284" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U284" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="V284" s="3"/>
+      <c r="O284" s="4">
+        <v>35</v>
+      </c>
+      <c r="P284" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="Q284" s="4">
+        <v>45.1</v>
+      </c>
+      <c r="R284" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="S284" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="T284" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="U284" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="V284" s="4">
+        <v>69.900000000000006</v>
+      </c>
       <c r="W284" s="2" t="s">
-        <v>392</v>
+        <v>30</v>
       </c>
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G285" s="3"/>
-      <c r="H285" s="3"/>
-      <c r="I285" s="3"/>
-      <c r="J285" s="3"/>
-      <c r="K285" s="3"/>
-      <c r="L285" s="3"/>
-      <c r="M285" s="3"/>
-      <c r="N285" s="3"/>
-      <c r="O285" s="3"/>
-      <c r="P285" s="3"/>
-      <c r="Q285" s="3"/>
-      <c r="R285" s="3"/>
-      <c r="S285" s="3"/>
-      <c r="T285" s="3"/>
+      <c r="G285" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H285" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="I285" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="J285" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="K285" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="L285" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="M285" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="N285" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="O285" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="P285" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="Q285" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="R285" s="4">
+        <v>35</v>
+      </c>
+      <c r="S285" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="T285" s="4">
+        <v>44.4</v>
+      </c>
       <c r="U285" s="4">
-        <v>30.2</v>
+        <v>50.8</v>
       </c>
       <c r="V285" s="4">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="W285" s="2" t="s">
         <v>30</v>
@@ -19776,70 +19802,70 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>28</v>
+        <v>392</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G286" s="4">
-        <v>28.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H286" s="4">
+        <v>5</v>
+      </c>
+      <c r="I286" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J286" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K286" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L286" s="4">
+        <v>6</v>
+      </c>
+      <c r="M286" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N286" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O286" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P286" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q286" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R286" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S286" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T286" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U286" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V286" s="4">
         <v>27.6</v>
-      </c>
-      <c r="I286" s="4">
-        <v>31.6</v>
-      </c>
-      <c r="J286" s="4">
-        <v>22.6</v>
-      </c>
-      <c r="K286" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="L286" s="4">
-        <v>26.6</v>
-      </c>
-      <c r="M286" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="N286" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="O286" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="P286" s="4">
-        <v>40.4</v>
-      </c>
-      <c r="Q286" s="4">
-        <v>41.9</v>
-      </c>
-      <c r="R286" s="4">
-        <v>47.5</v>
-      </c>
-      <c r="S286" s="4">
-        <v>55.4</v>
-      </c>
-      <c r="T286" s="4">
-        <v>58.5</v>
-      </c>
-      <c r="U286" s="4">
-        <v>61</v>
-      </c>
-      <c r="V286" s="4">
-        <v>61.1</v>
       </c>
       <c r="W286" s="2" t="s">
         <v>30</v>
@@ -19847,439 +19873,407 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>393</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>396</v>
+        <v>28</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G287" s="4">
-        <v>31.5</v>
+        <v>5.7</v>
       </c>
       <c r="H287" s="4">
-        <v>27.9</v>
+        <v>6</v>
       </c>
       <c r="I287" s="4">
-        <v>36.799999999999997</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J287" s="4">
-        <v>20.2</v>
+        <v>4.3</v>
       </c>
       <c r="K287" s="4">
-        <v>23.9</v>
+        <v>4.7</v>
       </c>
       <c r="L287" s="4">
-        <v>20.8</v>
+        <v>4.5</v>
       </c>
       <c r="M287" s="4">
-        <v>20.5</v>
+        <v>3.3</v>
       </c>
       <c r="N287" s="4">
-        <v>22.4</v>
+        <v>3.8</v>
       </c>
       <c r="O287" s="4">
-        <v>29.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="P287" s="4">
-        <v>29.8</v>
+        <v>4.3</v>
       </c>
       <c r="Q287" s="4">
-        <v>30.9</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="R287" s="4">
-        <v>35.6</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="S287" s="4">
-        <v>42.1</v>
+        <v>3.8</v>
       </c>
       <c r="T287" s="4">
-        <v>44</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="U287" s="4">
-        <v>47.7</v>
+        <v>4.8</v>
       </c>
       <c r="V287" s="4">
-        <v>48.9</v>
+        <v>5.2</v>
       </c>
       <c r="W287" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C288" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G288" s="6">
+        <v>674</v>
+      </c>
+      <c r="H288" s="6">
+        <v>605</v>
+      </c>
+      <c r="I288" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J288" s="6">
+        <v>1219</v>
+      </c>
+      <c r="K288" s="6">
+        <v>1282</v>
+      </c>
+      <c r="L288" s="6">
+        <v>1456</v>
+      </c>
+      <c r="M288" s="6">
+        <v>1926</v>
+      </c>
+      <c r="N288" s="6">
+        <v>3182</v>
+      </c>
+      <c r="O288" s="6">
+        <v>3739</v>
+      </c>
+      <c r="P288" s="6">
+        <v>6484</v>
+      </c>
+      <c r="Q288" s="6">
+        <v>10420</v>
+      </c>
+      <c r="R288" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S288" s="6">
+        <v>39683</v>
+      </c>
+      <c r="T288" s="6">
+        <v>80267</v>
+      </c>
+      <c r="U288" s="6">
+        <v>103449</v>
+      </c>
+      <c r="V288" s="6">
+        <v>260783</v>
+      </c>
+      <c r="W288" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E288" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G288" s="4">
-        <v>47.6</v>
-      </c>
-      <c r="H288" s="4">
-        <v>46.2</v>
-      </c>
-      <c r="I288" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="J288" s="4">
-        <v>39</v>
-      </c>
-      <c r="K288" s="4">
-        <v>46</v>
-      </c>
-      <c r="L288" s="4">
-        <v>45</v>
-      </c>
-      <c r="M288" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="N288" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="O288" s="4">
-        <v>53</v>
-      </c>
-      <c r="P288" s="4">
-        <v>58.6</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>59.9</v>
-      </c>
-      <c r="R288" s="4">
-        <v>68.3</v>
-      </c>
-      <c r="S288" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="T288" s="4">
-        <v>81</v>
-      </c>
-      <c r="U288" s="4">
-        <v>81.2</v>
-      </c>
-      <c r="V288" s="4">
-        <v>81.8</v>
-      </c>
-      <c r="W288" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A289" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="C289" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>398</v>
+        <v>28</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G289" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="H289" s="4">
-        <v>36.9</v>
-      </c>
-      <c r="I289" s="4">
-        <v>45.3</v>
-      </c>
-      <c r="J289" s="4">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="K289" s="4">
-        <v>40.1</v>
-      </c>
-      <c r="L289" s="4">
-        <v>38.6</v>
-      </c>
-      <c r="M289" s="4">
-        <v>40.5</v>
-      </c>
-      <c r="N289" s="4">
-        <v>45</v>
-      </c>
-      <c r="O289" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="P289" s="4">
-        <v>57.6</v>
-      </c>
-      <c r="Q289" s="4">
-        <v>59.4</v>
-      </c>
-      <c r="R289" s="4">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="S289" s="4">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="T289" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="U289" s="4">
-        <v>81.099999999999994</v>
-      </c>
-      <c r="V289" s="4">
-        <v>78.3</v>
+      <c r="G289" s="3"/>
+      <c r="H289" s="3"/>
+      <c r="I289" s="3"/>
+      <c r="J289" s="3"/>
+      <c r="K289" s="3"/>
+      <c r="L289" s="3"/>
+      <c r="M289" s="3"/>
+      <c r="N289" s="3"/>
+      <c r="O289" s="3"/>
+      <c r="P289" s="3"/>
+      <c r="Q289" s="3"/>
+      <c r="R289" s="5">
+        <v>18.93</v>
+      </c>
+      <c r="S289" s="3"/>
+      <c r="T289" s="5">
+        <v>21.3</v>
+      </c>
+      <c r="U289" s="3"/>
+      <c r="V289" s="5">
+        <v>23.01</v>
       </c>
       <c r="W289" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E290" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G290" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H290" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I290" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J290" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K290" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L290" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M290" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N290" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O290" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P290" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q290" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R290" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S290" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T290" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U290" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V290" s="3"/>
+      <c r="W290" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F290" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G290" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="H290" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="I290" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="J290" s="4">
-        <v>21.5</v>
-      </c>
-      <c r="K290" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="L290" s="4">
-        <v>26</v>
-      </c>
-      <c r="M290" s="4">
-        <v>30</v>
-      </c>
-      <c r="N290" s="4">
+      <c r="B291" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E291" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O290" s="4">
-        <v>35</v>
-      </c>
-      <c r="P290" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="Q290" s="4">
-        <v>45.1</v>
-      </c>
-      <c r="R290" s="4">
-        <v>51.7</v>
-      </c>
-      <c r="S290" s="4">
-        <v>62.4</v>
-      </c>
-      <c r="T290" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="U290" s="4">
-        <v>68.8</v>
-      </c>
-      <c r="V290" s="4">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="W290" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="F291" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G291" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="H291" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="I291" s="4">
-        <v>17.2</v>
-      </c>
-      <c r="J291" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="K291" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="L291" s="4">
-        <v>18.3</v>
-      </c>
-      <c r="M291" s="4">
-        <v>19.8</v>
-      </c>
-      <c r="N291" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="O291" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="P291" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="Q291" s="4">
-        <v>29.4</v>
-      </c>
-      <c r="R291" s="4">
-        <v>35</v>
-      </c>
-      <c r="S291" s="4">
-        <v>39.5</v>
-      </c>
-      <c r="T291" s="4">
-        <v>44.4</v>
-      </c>
-      <c r="U291" s="4">
-        <v>50.8</v>
-      </c>
-      <c r="V291" s="4">
-        <v>51.4</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="G291" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H291" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I291" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J291" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K291" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L291" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M291" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N291" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O291" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P291" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q291" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R291" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S291" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T291" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U291" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V291" s="3"/>
       <c r="W291" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>400</v>
+        <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G292" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H292" s="4">
-        <v>5</v>
-      </c>
-      <c r="I292" s="4">
-        <v>6.8</v>
-      </c>
-      <c r="J292" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="K292" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="L292" s="4">
-        <v>6</v>
-      </c>
-      <c r="M292" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="N292" s="4">
-        <v>8.4</v>
-      </c>
-      <c r="O292" s="4">
-        <v>10.9</v>
-      </c>
-      <c r="P292" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="Q292" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="R292" s="4">
-        <v>15.8</v>
-      </c>
-      <c r="S292" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="T292" s="4">
-        <v>26.1</v>
-      </c>
-      <c r="U292" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="V292" s="4">
-        <v>27.6</v>
-      </c>
+      <c r="G292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H292" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K292" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L292" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N292" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q292" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R292" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S292" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T292" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U292" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -20288,69 +20282,63 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G293" s="4">
-        <v>5.7</v>
-      </c>
-      <c r="H293" s="4">
-        <v>6</v>
-      </c>
-      <c r="I293" s="4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="J293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="K293" s="4">
-        <v>4.7</v>
-      </c>
-      <c r="L293" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="M293" s="4">
-        <v>3.3</v>
-      </c>
-      <c r="N293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="O293" s="4">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="P293" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="Q293" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="R293" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S293" s="4">
-        <v>3.8</v>
-      </c>
-      <c r="T293" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="U293" s="4">
-        <v>4.8</v>
-      </c>
-      <c r="V293" s="4">
-        <v>5.2</v>
+        <v>410</v>
+      </c>
+      <c r="G293" s="3"/>
+      <c r="H293" s="3"/>
+      <c r="I293" s="3"/>
+      <c r="J293" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K293" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L293" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M293" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N293" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O293" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P293" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q293" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R293" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S293" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T293" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U293" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V293" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W293" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>27</v>
@@ -20359,69 +20347,61 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G294" s="6">
-        <v>674</v>
-      </c>
-      <c r="H294" s="6">
-        <v>605</v>
-      </c>
-      <c r="I294" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J294" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K294" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L294" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M294" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N294" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O294" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P294" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q294" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R294" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S294" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T294" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U294" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V294" s="6">
-        <v>260783</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="G294" s="3"/>
+      <c r="H294" s="3"/>
+      <c r="I294" s="3"/>
+      <c r="J294" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K294" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L294" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M294" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N294" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O294" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P294" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q294" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R294" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S294" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T294" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U294" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="295" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>27</v>
@@ -20430,43 +20410,55 @@
         <v>28</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>34</v>
+        <v>415</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
-      <c r="K295" s="3"/>
-      <c r="L295" s="3"/>
-      <c r="M295" s="3"/>
-      <c r="N295" s="3"/>
+      <c r="K295" s="6">
+        <v>1</v>
+      </c>
+      <c r="L295" s="6">
+        <v>1</v>
+      </c>
+      <c r="M295" s="6">
+        <v>8</v>
+      </c>
+      <c r="N295" s="6">
+        <v>2</v>
+      </c>
       <c r="O295" s="3"/>
-      <c r="P295" s="3"/>
-      <c r="Q295" s="3"/>
-      <c r="R295" s="5">
-        <v>18.93</v>
-      </c>
+      <c r="P295" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q295" s="6">
+        <v>2</v>
+      </c>
+      <c r="R295" s="3"/>
       <c r="S295" s="3"/>
-      <c r="T295" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U295" s="3"/>
-      <c r="V295" s="5">
-        <v>23.01</v>
+      <c r="T295" s="6">
+        <v>8</v>
+      </c>
+      <c r="U295" s="6">
+        <v>7</v>
+      </c>
+      <c r="V295" s="6">
+        <v>2</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>88</v>
+        <v>416</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20475,67 +20467,65 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G296" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H296" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I296" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J296" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K296" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L296" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M296" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N296" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O296" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P296" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R296" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S296" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T296" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U296" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V296" s="3"/>
+        <v>415</v>
+      </c>
+      <c r="G296" s="3"/>
+      <c r="H296" s="3"/>
+      <c r="I296" s="6">
+        <v>2</v>
+      </c>
+      <c r="J296" s="6">
+        <v>2</v>
+      </c>
+      <c r="K296" s="6">
+        <v>1</v>
+      </c>
+      <c r="L296" s="6">
+        <v>1</v>
+      </c>
+      <c r="M296" s="6">
+        <v>1</v>
+      </c>
+      <c r="N296" s="6">
+        <v>1</v>
+      </c>
+      <c r="O296" s="6">
+        <v>1</v>
+      </c>
+      <c r="P296" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q296" s="6">
+        <v>4</v>
+      </c>
+      <c r="R296" s="6">
+        <v>1</v>
+      </c>
+      <c r="S296" s="6">
+        <v>1</v>
+      </c>
+      <c r="T296" s="6">
+        <v>0</v>
+      </c>
+      <c r="U296" s="6">
+        <v>4</v>
+      </c>
+      <c r="V296" s="6">
+        <v>2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20544,67 +20534,61 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G297" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H297" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I297" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J297" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K297" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L297" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M297" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N297" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O297" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P297" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q297" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R297" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S297" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T297" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U297" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V297" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G297" s="3"/>
+      <c r="H297" s="3"/>
+      <c r="I297" s="3"/>
+      <c r="J297" s="3"/>
+      <c r="K297" s="6">
+        <v>5</v>
+      </c>
+      <c r="L297" s="6">
+        <v>13</v>
+      </c>
+      <c r="M297" s="6">
+        <v>19</v>
+      </c>
+      <c r="N297" s="6">
+        <v>18</v>
+      </c>
+      <c r="O297" s="6">
+        <v>15</v>
+      </c>
+      <c r="P297" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q297" s="6">
+        <v>8</v>
+      </c>
+      <c r="R297" s="6">
+        <v>28</v>
+      </c>
+      <c r="S297" s="6">
+        <v>53</v>
+      </c>
+      <c r="T297" s="6">
+        <v>65</v>
+      </c>
+      <c r="U297" s="6">
+        <v>70</v>
+      </c>
+      <c r="V297" s="6">
+        <v>69</v>
+      </c>
       <c r="W297" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20613,433 +20597,47 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G298" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H298" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I298" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J298" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K298" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L298" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M298" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N298" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q298" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R298" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S298" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T298" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U298" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V298" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+      <c r="S298" s="3"/>
+      <c r="T298" s="6">
+        <v>114</v>
+      </c>
+      <c r="U298" s="6">
+        <v>61</v>
+      </c>
+      <c r="V298" s="6">
+        <v>97</v>
+      </c>
       <c r="W298" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K299" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L299" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M299" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N299" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O299" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P299" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q299" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R299" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S299" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T299" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U299" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V299" s="7">
-        <v>5.3920000000000003</v>
-      </c>
-      <c r="W299" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K300" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L300" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M300" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N300" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O300" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P300" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q300" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R300" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S300" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T300" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U300" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V300" s="3"/>
-      <c r="W300" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A301" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F301" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="G301" s="3"/>
-      <c r="H301" s="3"/>
-      <c r="I301" s="3"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="6">
-        <v>1</v>
-      </c>
-      <c r="L301" s="6">
-        <v>1</v>
-      </c>
-      <c r="M301" s="6">
-        <v>8</v>
-      </c>
-      <c r="N301" s="6">
-        <v>2</v>
-      </c>
-      <c r="O301" s="3"/>
-      <c r="P301" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q301" s="6">
-        <v>2</v>
-      </c>
-      <c r="R301" s="3"/>
-      <c r="S301" s="3"/>
-      <c r="T301" s="6">
-        <v>8</v>
-      </c>
-      <c r="U301" s="6">
-        <v>7</v>
-      </c>
-      <c r="V301" s="6">
-        <v>2</v>
-      </c>
-      <c r="W301" s="2" t="s">
+    </row>
+    <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="10" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="302" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="G302" s="3"/>
-      <c r="H302" s="3"/>
-      <c r="I302" s="6">
-        <v>2</v>
-      </c>
-      <c r="J302" s="6">
-        <v>2</v>
-      </c>
-      <c r="K302" s="6">
-        <v>1</v>
-      </c>
-      <c r="L302" s="6">
-        <v>1</v>
-      </c>
-      <c r="M302" s="6">
-        <v>1</v>
-      </c>
-      <c r="N302" s="6">
-        <v>1</v>
-      </c>
-      <c r="O302" s="6">
-        <v>1</v>
-      </c>
-      <c r="P302" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="6">
-        <v>4</v>
-      </c>
-      <c r="R302" s="6">
-        <v>1</v>
-      </c>
-      <c r="S302" s="6">
-        <v>1</v>
-      </c>
-      <c r="T302" s="6">
-        <v>0</v>
-      </c>
-      <c r="U302" s="6">
-        <v>4</v>
-      </c>
-      <c r="V302" s="6">
-        <v>2</v>
-      </c>
-      <c r="W302" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="303" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D303" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G303" s="3"/>
-      <c r="H303" s="3"/>
-      <c r="I303" s="3"/>
-      <c r="J303" s="3"/>
-      <c r="K303" s="6">
-        <v>5</v>
-      </c>
-      <c r="L303" s="6">
-        <v>13</v>
-      </c>
-      <c r="M303" s="6">
-        <v>19</v>
-      </c>
-      <c r="N303" s="6">
-        <v>18</v>
-      </c>
-      <c r="O303" s="6">
-        <v>15</v>
-      </c>
-      <c r="P303" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q303" s="6">
-        <v>8</v>
-      </c>
-      <c r="R303" s="6">
-        <v>28</v>
-      </c>
-      <c r="S303" s="6">
-        <v>53</v>
-      </c>
-      <c r="T303" s="6">
-        <v>65</v>
-      </c>
-      <c r="U303" s="6">
-        <v>70</v>
-      </c>
-      <c r="V303" s="6">
-        <v>69</v>
-      </c>
-      <c r="W303" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="304" spans="1:23" ht="27" x14ac:dyDescent="0.25">
-      <c r="A304" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E304" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F304" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G304" s="3"/>
-      <c r="H304" s="3"/>
-      <c r="I304" s="3"/>
-      <c r="J304" s="3"/>
-      <c r="K304" s="3"/>
-      <c r="L304" s="3"/>
-      <c r="M304" s="3"/>
-      <c r="N304" s="3"/>
-      <c r="O304" s="3"/>
-      <c r="P304" s="3"/>
-      <c r="Q304" s="3"/>
-      <c r="R304" s="3"/>
-      <c r="S304" s="3"/>
-      <c r="T304" s="6">
-        <v>114</v>
-      </c>
-      <c r="U304" s="6">
-        <v>61</v>
-      </c>
-      <c r="V304" s="6">
-        <v>97</v>
-      </c>
-      <c r="W304" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" spans="1:2" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="B307" s="8"/>
-    </row>
-    <row r="308" spans="1:2" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B300" s="8"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A307:B307"/>
+    <mergeCell ref="A300:B300"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869EBA9E-FAD2-4B65-8D24-A7F46F5FFE8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693E0B69-CEEE-4AF8-975B-8BAA80649F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="430">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -946,12 +946,27 @@
     <t>12.1.c Wskaźnik powtórnego wykorzystania materiałów</t>
   </si>
   <si>
+    <t>12.1.d Ilość marnowanej żywności na mieszkańca</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
     <t>Rozwój rolnictwa ekologicznego</t>
   </si>
   <si>
     <t>12.2.a Udział powierzchni ekologicznych użytków rolnych z certyfikatem w gospodarstwach ekologicznych w powierzchni użytków rolnych ogółem w gospodarstwach rolnych</t>
   </si>
   <si>
+    <t>12.2.b Liczba ekologicznych gospodarstw rolnych</t>
+  </si>
+  <si>
+    <t>tys.</t>
+  </si>
+  <si>
+    <t>Główny Inspektorat Jakości Handlowej Artykułów Rolno-Spożywczych</t>
+  </si>
+  <si>
     <t>Cel 13. Działania w dziedzinie klimatu</t>
   </si>
   <si>
@@ -1303,7 +1318,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 05-08-2026, 10:54</t>
+    <t>Ostatnia aktualizacja: 05-08-2026, 13:23</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W300"/>
+  <dimension ref="A1:W302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -16612,15 +16627,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="238" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>299</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="D238" s="2" t="s">
         <v>27</v>
@@ -16629,61 +16644,45 @@
         <v>28</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G238" s="5">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H238" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="I238" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="J238" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="K238" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="L238" s="5">
-        <v>3.45</v>
-      </c>
-      <c r="M238" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="N238" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="O238" s="5">
-        <v>2.48</v>
-      </c>
-      <c r="P238" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="Q238" s="5">
-        <v>2.68</v>
-      </c>
-      <c r="R238" s="3"/>
-      <c r="S238" s="3"/>
-      <c r="T238" s="5">
-        <v>3.1</v>
+        <v>306</v>
+      </c>
+      <c r="G238" s="3"/>
+      <c r="H238" s="3"/>
+      <c r="I238" s="3"/>
+      <c r="J238" s="3"/>
+      <c r="K238" s="3"/>
+      <c r="L238" s="3"/>
+      <c r="M238" s="3"/>
+      <c r="N238" s="3"/>
+      <c r="O238" s="3"/>
+      <c r="P238" s="3"/>
+      <c r="Q238" s="6">
+        <v>120</v>
+      </c>
+      <c r="R238" s="6">
+        <v>122</v>
+      </c>
+      <c r="S238" s="6">
+        <v>123</v>
+      </c>
+      <c r="T238" s="6">
+        <v>127</v>
       </c>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
       <c r="W238" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="239" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="239" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B239" s="2" t="s">
+      <c r="C239" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="D239" s="2" t="s">
         <v>27</v>
@@ -16692,67 +16691,61 @@
         <v>28</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="G239" s="4">
-        <v>100</v>
-      </c>
-      <c r="H239" s="4">
-        <v>99.8</v>
-      </c>
-      <c r="I239" s="4">
-        <v>97.5</v>
-      </c>
-      <c r="J239" s="4">
-        <v>96.3</v>
-      </c>
-      <c r="K239" s="4">
-        <v>92.6</v>
-      </c>
-      <c r="L239" s="4">
-        <v>93.6</v>
-      </c>
-      <c r="M239" s="4">
-        <v>96.8</v>
-      </c>
-      <c r="N239" s="4">
-        <v>100.7</v>
-      </c>
-      <c r="O239" s="4">
-        <v>100.5</v>
-      </c>
-      <c r="P239" s="4">
-        <v>95</v>
-      </c>
-      <c r="Q239" s="4">
-        <v>90.4</v>
-      </c>
-      <c r="R239" s="4">
-        <v>99</v>
-      </c>
-      <c r="S239" s="4">
-        <v>94.2</v>
-      </c>
-      <c r="T239" s="4">
-        <v>84.9</v>
-      </c>
-      <c r="U239" s="4">
-        <v>83.4</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G239" s="5">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H239" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I239" s="5">
+        <v>3.05</v>
+      </c>
+      <c r="J239" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="K239" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="L239" s="5">
+        <v>3.45</v>
+      </c>
+      <c r="M239" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="N239" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="O239" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="P239" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="Q239" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="R239" s="3"/>
+      <c r="S239" s="3"/>
+      <c r="T239" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="U239" s="3"/>
       <c r="V239" s="3"/>
       <c r="W239" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="240" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="240" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="C240" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D240" s="2" t="s">
         <v>27</v>
@@ -16764,58 +16757,58 @@
         <v>310</v>
       </c>
       <c r="G240" s="4">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="H240" s="4">
-        <v>99.7</v>
+        <v>23.4</v>
       </c>
       <c r="I240" s="4">
-        <v>97.8</v>
+        <v>25.9</v>
       </c>
       <c r="J240" s="4">
-        <v>96.7</v>
+        <v>26.6</v>
       </c>
       <c r="K240" s="4">
-        <v>93.6</v>
+        <v>24.8</v>
       </c>
       <c r="L240" s="4">
-        <v>94.3</v>
+        <v>22.3</v>
       </c>
       <c r="M240" s="4">
-        <v>96.9</v>
+        <v>22.4</v>
       </c>
       <c r="N240" s="4">
-        <v>100.5</v>
+        <v>20.3</v>
       </c>
       <c r="O240" s="4">
-        <v>100.4</v>
+        <v>19.2</v>
       </c>
       <c r="P240" s="4">
-        <v>94.9</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="Q240" s="4">
-        <v>91.2</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="R240" s="4">
-        <v>98.2</v>
+        <v>20</v>
       </c>
       <c r="S240" s="4">
-        <v>93.6</v>
+        <v>21.2</v>
       </c>
       <c r="T240" s="4">
-        <v>85.7</v>
+        <v>22.4</v>
       </c>
       <c r="U240" s="4">
-        <v>84.2</v>
+        <v>23.2</v>
       </c>
       <c r="V240" s="3"/>
       <c r="W240" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="241" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>313</v>
@@ -16824,196 +16817,196 @@
         <v>314</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G241" s="5">
-        <v>9.2799999999999994</v>
-      </c>
-      <c r="H241" s="5">
-        <v>10.34</v>
-      </c>
-      <c r="I241" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="J241" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="K241" s="5">
-        <v>11.61</v>
-      </c>
-      <c r="L241" s="5">
-        <v>11.88</v>
-      </c>
-      <c r="M241" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="N241" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="O241" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="P241" s="5">
-        <v>15.38</v>
-      </c>
-      <c r="Q241" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="R241" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="S241" s="5">
-        <v>16.64</v>
-      </c>
-      <c r="T241" s="5">
-        <v>16.649999999999999</v>
-      </c>
-      <c r="U241" s="5">
-        <v>17.77</v>
+        <v>315</v>
+      </c>
+      <c r="G241" s="4">
+        <v>100</v>
+      </c>
+      <c r="H241" s="4">
+        <v>99.8</v>
+      </c>
+      <c r="I241" s="4">
+        <v>97.5</v>
+      </c>
+      <c r="J241" s="4">
+        <v>96.3</v>
+      </c>
+      <c r="K241" s="4">
+        <v>92.6</v>
+      </c>
+      <c r="L241" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="M241" s="4">
+        <v>96.8</v>
+      </c>
+      <c r="N241" s="4">
+        <v>100.7</v>
+      </c>
+      <c r="O241" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="P241" s="4">
+        <v>95</v>
+      </c>
+      <c r="Q241" s="4">
+        <v>90.4</v>
+      </c>
+      <c r="R241" s="4">
+        <v>99</v>
+      </c>
+      <c r="S241" s="4">
+        <v>94.2</v>
+      </c>
+      <c r="T241" s="4">
+        <v>84.9</v>
+      </c>
+      <c r="U241" s="4">
+        <v>83.4</v>
       </c>
       <c r="V241" s="3"/>
       <c r="W241" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="242" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="242" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>313</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>185</v>
+        <v>27</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>186</v>
+        <v>28</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G242" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="H242" s="5">
-        <v>6.92</v>
-      </c>
-      <c r="I242" s="5">
-        <v>6.53</v>
-      </c>
-      <c r="J242" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="K242" s="5">
-        <v>6.32</v>
-      </c>
-      <c r="L242" s="5">
-        <v>5.69</v>
-      </c>
-      <c r="M242" s="5">
-        <v>3.97</v>
-      </c>
-      <c r="N242" s="5">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="O242" s="5">
-        <v>5.72</v>
-      </c>
-      <c r="P242" s="5">
-        <v>6.2</v>
-      </c>
-      <c r="Q242" s="5">
-        <v>6.58</v>
-      </c>
-      <c r="R242" s="5">
-        <v>5.67</v>
-      </c>
-      <c r="S242" s="5">
-        <v>5.79</v>
-      </c>
-      <c r="T242" s="5">
-        <v>6.34</v>
-      </c>
-      <c r="U242" s="5">
-        <v>6.03</v>
+        <v>315</v>
+      </c>
+      <c r="G242" s="4">
+        <v>100</v>
+      </c>
+      <c r="H242" s="4">
+        <v>99.7</v>
+      </c>
+      <c r="I242" s="4">
+        <v>97.8</v>
+      </c>
+      <c r="J242" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="K242" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="L242" s="4">
+        <v>94.3</v>
+      </c>
+      <c r="M242" s="4">
+        <v>96.9</v>
+      </c>
+      <c r="N242" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="O242" s="4">
+        <v>100.4</v>
+      </c>
+      <c r="P242" s="4">
+        <v>94.9</v>
+      </c>
+      <c r="Q242" s="4">
+        <v>91.2</v>
+      </c>
+      <c r="R242" s="4">
+        <v>98.2</v>
+      </c>
+      <c r="S242" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="T242" s="4">
+        <v>85.7</v>
+      </c>
+      <c r="U242" s="4">
+        <v>84.2</v>
       </c>
       <c r="V242" s="3"/>
       <c r="W242" s="2" t="s">
-        <v>88</v>
+        <v>316</v>
       </c>
     </row>
     <row r="243" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G243" s="5">
-        <v>6.55</v>
+        <v>9.2799999999999994</v>
       </c>
       <c r="H243" s="5">
-        <v>8.08</v>
+        <v>10.34</v>
       </c>
       <c r="I243" s="5">
-        <v>10.61</v>
+        <v>10.96</v>
       </c>
       <c r="J243" s="5">
-        <v>10.68</v>
+        <v>11.45</v>
       </c>
       <c r="K243" s="5">
-        <v>12.36</v>
+        <v>11.61</v>
       </c>
       <c r="L243" s="5">
-        <v>13.4</v>
+        <v>11.88</v>
       </c>
       <c r="M243" s="5">
-        <v>13.34</v>
+        <v>11.4</v>
       </c>
       <c r="N243" s="5">
-        <v>13.08</v>
+        <v>11.06</v>
       </c>
       <c r="O243" s="5">
-        <v>13.03</v>
+        <v>14.94</v>
       </c>
       <c r="P243" s="5">
-        <v>14.36</v>
+        <v>15.38</v>
       </c>
       <c r="Q243" s="5">
-        <v>16.239999999999998</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="R243" s="5">
-        <v>17.170000000000002</v>
+        <v>15.6</v>
       </c>
       <c r="S243" s="5">
-        <v>21.01</v>
+        <v>16.64</v>
       </c>
       <c r="T243" s="5">
-        <v>25.79</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="U243" s="5">
-        <v>30.37</v>
+        <v>17.77</v>
       </c>
       <c r="V243" s="3"/>
       <c r="W243" s="2" t="s">
@@ -17022,67 +17015,67 @@
     </row>
     <row r="244" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G244" s="5">
-        <v>11.81</v>
+        <v>6.64</v>
       </c>
       <c r="H244" s="5">
-        <v>13.24</v>
+        <v>6.92</v>
       </c>
       <c r="I244" s="5">
-        <v>13.5</v>
+        <v>6.53</v>
       </c>
       <c r="J244" s="5">
-        <v>14.27</v>
+        <v>6.67</v>
       </c>
       <c r="K244" s="5">
-        <v>14.24</v>
+        <v>6.32</v>
       </c>
       <c r="L244" s="5">
-        <v>14.8</v>
+        <v>5.69</v>
       </c>
       <c r="M244" s="5">
-        <v>14.92</v>
+        <v>3.97</v>
       </c>
       <c r="N244" s="5">
-        <v>14.78</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="O244" s="5">
-        <v>21.47</v>
+        <v>5.72</v>
       </c>
       <c r="P244" s="5">
-        <v>22.01</v>
+        <v>6.2</v>
       </c>
       <c r="Q244" s="5">
-        <v>22.14</v>
+        <v>6.58</v>
       </c>
       <c r="R244" s="5">
-        <v>20.98</v>
+        <v>5.67</v>
       </c>
       <c r="S244" s="5">
-        <v>22.1</v>
+        <v>5.79</v>
       </c>
       <c r="T244" s="5">
-        <v>20.61</v>
+        <v>6.34</v>
       </c>
       <c r="U244" s="5">
-        <v>21.29</v>
+        <v>6.03</v>
       </c>
       <c r="V244" s="3"/>
       <c r="W244" s="2" t="s">
@@ -17091,205 +17084,205 @@
     </row>
     <row r="245" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G245" s="6">
-        <v>563</v>
-      </c>
-      <c r="H245" s="6">
-        <v>531</v>
-      </c>
-      <c r="I245" s="6">
-        <v>661</v>
-      </c>
-      <c r="J245" s="6">
-        <v>778</v>
-      </c>
-      <c r="K245" s="6">
-        <v>847</v>
-      </c>
-      <c r="L245" s="6">
-        <v>909</v>
-      </c>
-      <c r="M245" s="6">
-        <v>930</v>
-      </c>
-      <c r="N245" s="6">
-        <v>946</v>
-      </c>
-      <c r="O245" s="6">
-        <v>991</v>
-      </c>
-      <c r="P245" s="6">
-        <v>1050</v>
-      </c>
-      <c r="Q245" s="6">
-        <v>1073</v>
-      </c>
-      <c r="R245" s="6">
-        <v>1189</v>
-      </c>
-      <c r="S245" s="6">
-        <v>1318</v>
-      </c>
-      <c r="T245" s="6">
-        <v>1372</v>
-      </c>
-      <c r="U245" s="6">
-        <v>1556</v>
+        <v>34</v>
+      </c>
+      <c r="G245" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="H245" s="5">
+        <v>8.08</v>
+      </c>
+      <c r="I245" s="5">
+        <v>10.61</v>
+      </c>
+      <c r="J245" s="5">
+        <v>10.68</v>
+      </c>
+      <c r="K245" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="L245" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="M245" s="5">
+        <v>13.34</v>
+      </c>
+      <c r="N245" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="O245" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="P245" s="5">
+        <v>14.36</v>
+      </c>
+      <c r="Q245" s="5">
+        <v>16.239999999999998</v>
+      </c>
+      <c r="R245" s="5">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="S245" s="5">
+        <v>21.01</v>
+      </c>
+      <c r="T245" s="5">
+        <v>25.79</v>
+      </c>
+      <c r="U245" s="5">
+        <v>30.37</v>
       </c>
       <c r="V245" s="3"/>
       <c r="W245" s="2" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
     </row>
     <row r="246" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>317</v>
+        <v>188</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G246" s="6">
-        <v>440</v>
-      </c>
-      <c r="H246" s="6">
-        <v>101</v>
-      </c>
-      <c r="I246" s="6">
-        <v>151</v>
-      </c>
-      <c r="J246" s="6">
-        <v>217</v>
-      </c>
-      <c r="K246" s="6">
-        <v>239</v>
-      </c>
-      <c r="L246" s="6">
-        <v>674</v>
-      </c>
-      <c r="M246" s="6">
-        <v>705</v>
-      </c>
-      <c r="N246" s="6">
-        <v>712</v>
-      </c>
-      <c r="O246" s="6">
-        <v>743</v>
-      </c>
-      <c r="P246" s="6">
-        <v>788</v>
-      </c>
-      <c r="Q246" s="6">
-        <v>805</v>
-      </c>
-      <c r="R246" s="6">
-        <v>892</v>
-      </c>
-      <c r="S246" s="6">
-        <v>988</v>
-      </c>
-      <c r="T246" s="6">
-        <v>1029</v>
-      </c>
-      <c r="U246" s="6">
-        <v>1167</v>
+        <v>34</v>
+      </c>
+      <c r="G246" s="5">
+        <v>11.81</v>
+      </c>
+      <c r="H246" s="5">
+        <v>13.24</v>
+      </c>
+      <c r="I246" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="J246" s="5">
+        <v>14.27</v>
+      </c>
+      <c r="K246" s="5">
+        <v>14.24</v>
+      </c>
+      <c r="L246" s="5">
+        <v>14.8</v>
+      </c>
+      <c r="M246" s="5">
+        <v>14.92</v>
+      </c>
+      <c r="N246" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="O246" s="5">
+        <v>21.47</v>
+      </c>
+      <c r="P246" s="5">
+        <v>22.01</v>
+      </c>
+      <c r="Q246" s="5">
+        <v>22.14</v>
+      </c>
+      <c r="R246" s="5">
+        <v>20.98</v>
+      </c>
+      <c r="S246" s="5">
+        <v>22.1</v>
+      </c>
+      <c r="T246" s="5">
+        <v>20.61</v>
+      </c>
+      <c r="U246" s="5">
+        <v>21.29</v>
       </c>
       <c r="V246" s="3"/>
       <c r="W246" s="2" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
     </row>
     <row r="247" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D247" s="2" t="s">
         <v>185</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>318</v>
+        <v>28</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G247" s="6">
-        <v>123</v>
+        <v>563</v>
       </c>
       <c r="H247" s="6">
-        <v>101</v>
+        <v>531</v>
       </c>
       <c r="I247" s="6">
-        <v>151</v>
+        <v>661</v>
       </c>
       <c r="J247" s="6">
-        <v>217</v>
+        <v>778</v>
       </c>
       <c r="K247" s="6">
-        <v>239</v>
+        <v>847</v>
       </c>
       <c r="L247" s="6">
-        <v>235</v>
+        <v>909</v>
       </c>
       <c r="M247" s="6">
-        <v>225</v>
+        <v>930</v>
       </c>
       <c r="N247" s="6">
-        <v>234</v>
+        <v>946</v>
       </c>
       <c r="O247" s="6">
-        <v>248</v>
+        <v>991</v>
       </c>
       <c r="P247" s="6">
-        <v>263</v>
+        <v>1050</v>
       </c>
       <c r="Q247" s="6">
-        <v>268</v>
+        <v>1073</v>
       </c>
       <c r="R247" s="6">
-        <v>297</v>
+        <v>1189</v>
       </c>
       <c r="S247" s="6">
-        <v>329</v>
+        <v>1318</v>
       </c>
       <c r="T247" s="6">
-        <v>343</v>
+        <v>1372</v>
       </c>
       <c r="U247" s="6">
-        <v>389</v>
+        <v>1556</v>
       </c>
       <c r="V247" s="3"/>
       <c r="W247" s="2" t="s">
@@ -17298,148 +17291,148 @@
     </row>
     <row r="248" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G248" s="6">
-        <v>2218</v>
+        <v>440</v>
       </c>
       <c r="H248" s="6">
-        <v>3117</v>
+        <v>101</v>
       </c>
       <c r="I248" s="6">
-        <v>4139</v>
+        <v>151</v>
       </c>
       <c r="J248" s="6">
-        <v>5205</v>
+        <v>217</v>
       </c>
       <c r="K248" s="6">
-        <v>5793</v>
+        <v>239</v>
       </c>
       <c r="L248" s="6">
-        <v>7105</v>
+        <v>674</v>
       </c>
       <c r="M248" s="6">
-        <v>8017</v>
+        <v>705</v>
       </c>
       <c r="N248" s="6">
-        <v>8195</v>
+        <v>712</v>
       </c>
       <c r="O248" s="6">
-        <v>8486</v>
+        <v>743</v>
       </c>
       <c r="P248" s="6">
-        <v>9547</v>
+        <v>788</v>
       </c>
       <c r="Q248" s="6">
-        <v>12490</v>
+        <v>805</v>
       </c>
       <c r="R248" s="6">
-        <v>16935</v>
+        <v>892</v>
       </c>
       <c r="S248" s="6">
-        <v>22670</v>
+        <v>988</v>
       </c>
       <c r="T248" s="6">
-        <v>28779</v>
+        <v>1029</v>
       </c>
       <c r="U248" s="6">
-        <v>33623</v>
-      </c>
-      <c r="V248" s="6">
-        <v>37777</v>
-      </c>
+        <v>1167</v>
+      </c>
+      <c r="V248" s="3"/>
       <c r="W248" s="2" t="s">
-        <v>321</v>
+        <v>30</v>
       </c>
     </row>
     <row r="249" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E249" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F249" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G249" s="4">
-        <v>0.4</v>
-      </c>
-      <c r="H249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="I249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="J249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="K249" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="L249" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="M249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="N249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="O249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="P249" s="4">
-        <v>0.7</v>
-      </c>
-      <c r="Q249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="R249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="S249" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="T249" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="U249" s="3"/>
+        <v>321</v>
+      </c>
+      <c r="G249" s="6">
+        <v>123</v>
+      </c>
+      <c r="H249" s="6">
+        <v>101</v>
+      </c>
+      <c r="I249" s="6">
+        <v>151</v>
+      </c>
+      <c r="J249" s="6">
+        <v>217</v>
+      </c>
+      <c r="K249" s="6">
+        <v>239</v>
+      </c>
+      <c r="L249" s="6">
+        <v>235</v>
+      </c>
+      <c r="M249" s="6">
+        <v>225</v>
+      </c>
+      <c r="N249" s="6">
+        <v>234</v>
+      </c>
+      <c r="O249" s="6">
+        <v>248</v>
+      </c>
+      <c r="P249" s="6">
+        <v>263</v>
+      </c>
+      <c r="Q249" s="6">
+        <v>268</v>
+      </c>
+      <c r="R249" s="6">
+        <v>297</v>
+      </c>
+      <c r="S249" s="6">
+        <v>329</v>
+      </c>
+      <c r="T249" s="6">
+        <v>343</v>
+      </c>
+      <c r="U249" s="6">
+        <v>389</v>
+      </c>
       <c r="V249" s="3"/>
       <c r="W249" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="250" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>324</v>
@@ -17448,136 +17441,136 @@
         <v>27</v>
       </c>
       <c r="E250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F250" s="3" t="s">
+      <c r="G250" s="6">
+        <v>2218</v>
+      </c>
+      <c r="H250" s="6">
+        <v>3117</v>
+      </c>
+      <c r="I250" s="6">
+        <v>4139</v>
+      </c>
+      <c r="J250" s="6">
+        <v>5205</v>
+      </c>
+      <c r="K250" s="6">
+        <v>5793</v>
+      </c>
+      <c r="L250" s="6">
+        <v>7105</v>
+      </c>
+      <c r="M250" s="6">
+        <v>8017</v>
+      </c>
+      <c r="N250" s="6">
+        <v>8195</v>
+      </c>
+      <c r="O250" s="6">
+        <v>8486</v>
+      </c>
+      <c r="P250" s="6">
+        <v>9547</v>
+      </c>
+      <c r="Q250" s="6">
+        <v>12490</v>
+      </c>
+      <c r="R250" s="6">
+        <v>16935</v>
+      </c>
+      <c r="S250" s="6">
+        <v>22670</v>
+      </c>
+      <c r="T250" s="6">
+        <v>28779</v>
+      </c>
+      <c r="U250" s="6">
+        <v>33623</v>
+      </c>
+      <c r="V250" s="6">
+        <v>37777</v>
+      </c>
+      <c r="W250" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="G250" s="5">
-        <v>137.94999999999999</v>
-      </c>
-      <c r="H250" s="5">
-        <v>0</v>
-      </c>
-      <c r="I250" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="J250" s="5">
-        <v>0</v>
-      </c>
-      <c r="K250" s="5">
-        <v>0</v>
-      </c>
-      <c r="L250" s="5">
-        <v>0</v>
-      </c>
-      <c r="M250" s="5">
-        <v>0</v>
-      </c>
-      <c r="N250" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="O250" s="5">
-        <v>25.44</v>
-      </c>
-      <c r="P250" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q250" s="5">
-        <v>12.02</v>
-      </c>
-      <c r="R250" s="5">
-        <v>0.89</v>
-      </c>
-      <c r="S250" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="T250" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="U250" s="5">
-        <v>80.36</v>
-      </c>
-      <c r="V250" s="3"/>
-      <c r="W250" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="251" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>327</v>
+        <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G251" s="6">
-        <v>5248</v>
-      </c>
-      <c r="H251" s="6">
-        <v>0</v>
-      </c>
-      <c r="I251" s="6">
-        <v>7</v>
-      </c>
-      <c r="J251" s="6">
-        <v>0</v>
-      </c>
-      <c r="K251" s="6">
-        <v>0</v>
-      </c>
-      <c r="L251" s="6">
-        <v>0</v>
-      </c>
-      <c r="M251" s="6">
-        <v>0</v>
-      </c>
-      <c r="N251" s="6">
-        <v>87</v>
-      </c>
-      <c r="O251" s="6">
-        <v>966</v>
-      </c>
-      <c r="P251" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q251" s="6">
-        <v>451</v>
-      </c>
-      <c r="R251" s="6">
-        <v>33</v>
-      </c>
-      <c r="S251" s="6">
-        <v>1</v>
-      </c>
-      <c r="T251" s="6">
-        <v>1</v>
-      </c>
-      <c r="U251" s="6">
-        <v>2938</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G251" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="H251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K251" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="L251" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="M251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P251" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="S251" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="T251" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U251" s="3"/>
       <c r="V251" s="3"/>
       <c r="W251" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="252" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>329</v>
@@ -17586,137 +17579,139 @@
         <v>27</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>28</v>
+        <v>330</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G252" s="5">
-        <v>0.55000000000000004</v>
+        <v>137.94999999999999</v>
       </c>
       <c r="H252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="I252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0.18</v>
       </c>
       <c r="J252" s="5">
-        <v>0.55000000000000004</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="L252" s="5">
-        <v>0.56000000000000005</v>
+        <v>0</v>
       </c>
       <c r="M252" s="5">
-        <v>0.56999999999999995</v>
+        <v>0</v>
       </c>
       <c r="N252" s="5">
-        <v>0.56999999999999995</v>
+        <v>2.29</v>
       </c>
       <c r="O252" s="5">
-        <v>0.57999999999999996</v>
+        <v>25.44</v>
       </c>
       <c r="P252" s="5">
-        <v>0.57999999999999996</v>
+        <v>0</v>
       </c>
       <c r="Q252" s="5">
-        <v>0.57999999999999996</v>
+        <v>12.02</v>
       </c>
       <c r="R252" s="5">
-        <v>0.57999999999999996</v>
+        <v>0.89</v>
       </c>
       <c r="S252" s="5">
-        <v>0.59</v>
+        <v>0.03</v>
       </c>
       <c r="T252" s="5">
-        <v>0.59</v>
+        <v>0.03</v>
       </c>
       <c r="U252" s="5">
-        <v>0.59</v>
+        <v>80.36</v>
       </c>
       <c r="V252" s="3"/>
       <c r="W252" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="253" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>28</v>
+        <v>332</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G253" s="4">
-        <v>732401.6</v>
-      </c>
-      <c r="H253" s="4">
-        <v>740630</v>
-      </c>
-      <c r="I253" s="4">
-        <v>753624</v>
-      </c>
-      <c r="J253" s="4">
-        <v>752240.3</v>
-      </c>
-      <c r="K253" s="4">
-        <v>804401.8</v>
-      </c>
-      <c r="L253" s="4">
-        <v>830309.8</v>
-      </c>
-      <c r="M253" s="4">
-        <v>826034.2</v>
-      </c>
-      <c r="N253" s="3"/>
-      <c r="O253" s="4">
-        <v>846693.5</v>
-      </c>
-      <c r="P253" s="4">
-        <v>839607.4</v>
-      </c>
-      <c r="Q253" s="4">
-        <v>852978.8</v>
-      </c>
-      <c r="R253" s="4">
-        <v>855928.1</v>
-      </c>
-      <c r="S253" s="4">
-        <v>859996.9</v>
-      </c>
-      <c r="T253" s="4">
-        <v>870987.2</v>
-      </c>
-      <c r="U253" s="4">
-        <v>881284.3</v>
+        <v>331</v>
+      </c>
+      <c r="G253" s="6">
+        <v>5248</v>
+      </c>
+      <c r="H253" s="6">
+        <v>0</v>
+      </c>
+      <c r="I253" s="6">
+        <v>7</v>
+      </c>
+      <c r="J253" s="6">
+        <v>0</v>
+      </c>
+      <c r="K253" s="6">
+        <v>0</v>
+      </c>
+      <c r="L253" s="6">
+        <v>0</v>
+      </c>
+      <c r="M253" s="6">
+        <v>0</v>
+      </c>
+      <c r="N253" s="6">
+        <v>87</v>
+      </c>
+      <c r="O253" s="6">
+        <v>966</v>
+      </c>
+      <c r="P253" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q253" s="6">
+        <v>451</v>
+      </c>
+      <c r="R253" s="6">
+        <v>33</v>
+      </c>
+      <c r="S253" s="6">
+        <v>1</v>
+      </c>
+      <c r="T253" s="6">
+        <v>1</v>
+      </c>
+      <c r="U253" s="6">
+        <v>2938</v>
       </c>
       <c r="V253" s="3"/>
       <c r="W253" s="2" t="s">
-        <v>168</v>
+        <v>27</v>
       </c>
     </row>
     <row r="254" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>27</v>
@@ -17725,59 +17720,67 @@
         <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G254" s="3"/>
-      <c r="H254" s="3"/>
-      <c r="I254" s="3"/>
-      <c r="J254" s="3"/>
-      <c r="K254" s="3"/>
+        <v>335</v>
+      </c>
+      <c r="G254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J254" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K254" s="5">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="L254" s="5">
-        <v>6.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M254" s="5">
-        <v>7.58</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N254" s="5">
-        <v>7.54</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="O254" s="5">
-        <v>10.15</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P254" s="5">
-        <v>12.38</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Q254" s="5">
-        <v>12.53</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="R254" s="5">
-        <v>5.95</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S254" s="5">
-        <v>4.7300000000000004</v>
+        <v>0.59</v>
       </c>
       <c r="T254" s="5">
-        <v>6.25</v>
+        <v>0.59</v>
       </c>
       <c r="U254" s="5">
-        <v>5.6</v>
-      </c>
-      <c r="V254" s="5">
-        <v>5.95</v>
-      </c>
+        <v>0.59</v>
+      </c>
+      <c r="V254" s="3"/>
       <c r="W254" s="2" t="s">
-        <v>333</v>
+        <v>30</v>
       </c>
     </row>
     <row r="255" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>27</v>
@@ -17786,53 +17789,65 @@
         <v>28</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G255" s="3"/>
-      <c r="H255" s="3"/>
-      <c r="I255" s="3"/>
-      <c r="J255" s="3"/>
-      <c r="K255" s="3"/>
-      <c r="L255" s="3"/>
-      <c r="M255" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="G255" s="4">
+        <v>732401.6</v>
+      </c>
+      <c r="H255" s="4">
+        <v>740630</v>
+      </c>
+      <c r="I255" s="4">
+        <v>753624</v>
+      </c>
+      <c r="J255" s="4">
+        <v>752240.3</v>
+      </c>
+      <c r="K255" s="4">
+        <v>804401.8</v>
+      </c>
+      <c r="L255" s="4">
+        <v>830309.8</v>
+      </c>
+      <c r="M255" s="4">
+        <v>826034.2</v>
+      </c>
       <c r="N255" s="3"/>
-      <c r="O255" s="6">
-        <v>1</v>
-      </c>
-      <c r="P255" s="6">
-        <v>54</v>
-      </c>
-      <c r="Q255" s="6">
-        <v>63</v>
-      </c>
-      <c r="R255" s="6">
-        <v>66</v>
-      </c>
-      <c r="S255" s="6">
-        <v>70</v>
-      </c>
-      <c r="T255" s="6">
-        <v>75</v>
-      </c>
-      <c r="U255" s="6">
-        <v>80</v>
-      </c>
-      <c r="V255" s="6">
-        <v>86</v>
-      </c>
+      <c r="O255" s="4">
+        <v>846693.5</v>
+      </c>
+      <c r="P255" s="4">
+        <v>839607.4</v>
+      </c>
+      <c r="Q255" s="4">
+        <v>852978.8</v>
+      </c>
+      <c r="R255" s="4">
+        <v>855928.1</v>
+      </c>
+      <c r="S255" s="4">
+        <v>859996.9</v>
+      </c>
+      <c r="T255" s="4">
+        <v>870987.2</v>
+      </c>
+      <c r="U255" s="4">
+        <v>881284.3</v>
+      </c>
+      <c r="V255" s="3"/>
       <c r="W255" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="256" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="256" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>27</v>
@@ -17841,45 +17856,59 @@
         <v>28</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="G256" s="3"/>
       <c r="H256" s="3"/>
       <c r="I256" s="3"/>
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
-      <c r="L256" s="3"/>
-      <c r="M256" s="3"/>
-      <c r="N256" s="3"/>
-      <c r="O256" s="3"/>
-      <c r="P256" s="3"/>
-      <c r="Q256" s="3"/>
-      <c r="R256" s="3"/>
-      <c r="S256" s="6">
-        <v>16</v>
-      </c>
-      <c r="T256" s="6">
-        <v>7</v>
-      </c>
-      <c r="U256" s="6">
-        <v>6</v>
-      </c>
-      <c r="V256" s="6">
-        <v>4</v>
+      <c r="L256" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="M256" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="N256" s="5">
+        <v>7.54</v>
+      </c>
+      <c r="O256" s="5">
+        <v>10.15</v>
+      </c>
+      <c r="P256" s="5">
+        <v>12.38</v>
+      </c>
+      <c r="Q256" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="R256" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="S256" s="5">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="T256" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="U256" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="V256" s="5">
+        <v>5.95</v>
       </c>
       <c r="W256" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="257" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>27</v>
@@ -17888,7 +17917,7 @@
         <v>28</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="3"/>
@@ -17898,451 +17927,415 @@
       <c r="L257" s="3"/>
       <c r="M257" s="3"/>
       <c r="N257" s="3"/>
-      <c r="O257" s="3"/>
-      <c r="P257" s="3"/>
-      <c r="Q257" s="3"/>
+      <c r="O257" s="6">
+        <v>1</v>
+      </c>
+      <c r="P257" s="6">
+        <v>54</v>
+      </c>
+      <c r="Q257" s="6">
+        <v>63</v>
+      </c>
       <c r="R257" s="6">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="S257" s="6">
+        <v>70</v>
+      </c>
+      <c r="T257" s="6">
+        <v>75</v>
+      </c>
+      <c r="U257" s="6">
         <v>80</v>
       </c>
-      <c r="T257" s="6">
-        <v>97</v>
-      </c>
-      <c r="U257" s="6">
-        <v>44</v>
-      </c>
       <c r="V257" s="6">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="W257" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" ht="99" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="258" spans="1:23" ht="81" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
+      <c r="D258" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F258" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B258" s="2" t="s">
+      <c r="G258" s="3"/>
+      <c r="H258" s="3"/>
+      <c r="I258" s="3"/>
+      <c r="J258" s="3"/>
+      <c r="K258" s="3"/>
+      <c r="L258" s="3"/>
+      <c r="M258" s="3"/>
+      <c r="N258" s="3"/>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="3"/>
+      <c r="R258" s="3"/>
+      <c r="S258" s="6">
+        <v>16</v>
+      </c>
+      <c r="T258" s="6">
+        <v>7</v>
+      </c>
+      <c r="U258" s="6">
+        <v>6</v>
+      </c>
+      <c r="V258" s="6">
+        <v>4</v>
+      </c>
+      <c r="W258" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G258" s="6">
-        <v>40</v>
-      </c>
-      <c r="H258" s="6">
-        <v>60</v>
-      </c>
-      <c r="I258" s="6">
-        <v>40</v>
-      </c>
-      <c r="J258" s="6">
-        <v>40</v>
-      </c>
-      <c r="K258" s="6">
-        <v>40</v>
-      </c>
-      <c r="L258" s="6">
-        <v>40</v>
-      </c>
-      <c r="M258" s="6">
-        <v>60</v>
-      </c>
-      <c r="N258" s="6">
-        <v>40</v>
-      </c>
-      <c r="O258" s="6">
-        <v>40</v>
-      </c>
-      <c r="P258" s="6">
-        <v>40</v>
-      </c>
-      <c r="Q258" s="6">
-        <v>60</v>
-      </c>
-      <c r="R258" s="6">
-        <v>67</v>
-      </c>
-      <c r="S258" s="6">
-        <v>50</v>
-      </c>
-      <c r="T258" s="6">
-        <v>67</v>
-      </c>
-      <c r="U258" s="6">
-        <v>67</v>
-      </c>
-      <c r="V258" s="3"/>
-      <c r="W258" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="259" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>346</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F259" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E259" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G259" s="6">
-        <v>40</v>
-      </c>
-      <c r="H259" s="6">
-        <v>60</v>
-      </c>
-      <c r="I259" s="6">
-        <v>20</v>
-      </c>
-      <c r="J259" s="6">
-        <v>20</v>
-      </c>
-      <c r="K259" s="6">
-        <v>20</v>
-      </c>
-      <c r="L259" s="6">
-        <v>40</v>
-      </c>
-      <c r="M259" s="6">
-        <v>60</v>
-      </c>
-      <c r="N259" s="6">
-        <v>40</v>
-      </c>
-      <c r="O259" s="6">
-        <v>25</v>
-      </c>
-      <c r="P259" s="6">
-        <v>25</v>
-      </c>
-      <c r="Q259" s="6">
-        <v>20</v>
-      </c>
+      <c r="G259" s="3"/>
+      <c r="H259" s="3"/>
+      <c r="I259" s="3"/>
+      <c r="J259" s="3"/>
+      <c r="K259" s="3"/>
+      <c r="L259" s="3"/>
+      <c r="M259" s="3"/>
+      <c r="N259" s="3"/>
+      <c r="O259" s="3"/>
+      <c r="P259" s="3"/>
+      <c r="Q259" s="3"/>
       <c r="R259" s="6">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="S259" s="6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T259" s="6">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="U259" s="6">
-        <v>0</v>
-      </c>
-      <c r="V259" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="V259" s="6">
+        <v>89</v>
+      </c>
       <c r="W259" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="260" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K260" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M260" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P260" s="6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q260" s="6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R260" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="S260" s="6">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="T260" s="6">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="U260" s="6">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="V260" s="3"/>
       <c r="W260" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G261" s="6">
+        <v>40</v>
+      </c>
+      <c r="H261" s="6">
         <v>60</v>
       </c>
-      <c r="H261" s="6">
+      <c r="I261" s="6">
+        <v>20</v>
+      </c>
+      <c r="J261" s="6">
+        <v>20</v>
+      </c>
+      <c r="K261" s="6">
+        <v>20</v>
+      </c>
+      <c r="L261" s="6">
         <v>40</v>
       </c>
-      <c r="I261" s="6">
+      <c r="M261" s="6">
         <v>60</v>
       </c>
-      <c r="J261" s="6">
-        <v>60</v>
-      </c>
-      <c r="K261" s="6">
-        <v>60</v>
-      </c>
-      <c r="L261" s="6">
-        <v>60</v>
-      </c>
-      <c r="M261" s="6">
+      <c r="N261" s="6">
         <v>40</v>
       </c>
-      <c r="N261" s="6">
-        <v>60</v>
-      </c>
       <c r="O261" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="P261" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="Q261" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="R261" s="6">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="S261" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T261" s="6">
         <v>17</v>
       </c>
       <c r="U261" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="V261" s="3"/>
       <c r="W261" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="262" spans="1:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="B262" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>28</v>
+        <v>356</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G262" s="4">
-        <v>100</v>
-      </c>
-      <c r="H262" s="4">
-        <v>100.8</v>
-      </c>
-      <c r="I262" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J262" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K262" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L262" s="4">
-        <v>106</v>
-      </c>
-      <c r="M262" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N262" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O262" s="4">
-        <v>130</v>
-      </c>
-      <c r="P262" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q262" s="4">
-        <v>186.6</v>
-      </c>
-      <c r="R262" s="4">
-        <v>190.1</v>
-      </c>
-      <c r="S262" s="4">
-        <v>200.8</v>
-      </c>
-      <c r="T262" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U262" s="4">
-        <v>208.5</v>
+        <v>34</v>
+      </c>
+      <c r="G262" s="6">
+        <v>0</v>
+      </c>
+      <c r="H262" s="6">
+        <v>0</v>
+      </c>
+      <c r="I262" s="6">
+        <v>20</v>
+      </c>
+      <c r="J262" s="6">
+        <v>20</v>
+      </c>
+      <c r="K262" s="6">
+        <v>20</v>
+      </c>
+      <c r="L262" s="6">
+        <v>0</v>
+      </c>
+      <c r="M262" s="6">
+        <v>0</v>
+      </c>
+      <c r="N262" s="6">
+        <v>0</v>
+      </c>
+      <c r="O262" s="6">
+        <v>0</v>
+      </c>
+      <c r="P262" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q262" s="6">
+        <v>40</v>
+      </c>
+      <c r="R262" s="6">
+        <v>17</v>
+      </c>
+      <c r="S262" s="6">
+        <v>17</v>
+      </c>
+      <c r="T262" s="6">
+        <v>17</v>
+      </c>
+      <c r="U262" s="6">
+        <v>50</v>
       </c>
       <c r="V262" s="3"/>
       <c r="W262" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="263" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C263" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E263" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E263" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F263" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G263" s="4">
-        <v>59.5</v>
-      </c>
-      <c r="H263" s="4">
-        <v>57.7</v>
-      </c>
-      <c r="I263" s="4">
-        <v>58.8</v>
-      </c>
-      <c r="J263" s="4">
-        <v>64.3</v>
-      </c>
-      <c r="K263" s="4">
-        <v>68.7</v>
-      </c>
-      <c r="L263" s="4">
-        <v>69.5</v>
-      </c>
-      <c r="M263" s="4">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="N263" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="O263" s="4">
-        <v>91.8</v>
-      </c>
-      <c r="P263" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="Q263" s="4">
-        <v>88.5</v>
-      </c>
-      <c r="R263" s="4">
-        <v>96.7</v>
-      </c>
-      <c r="S263" s="4">
-        <v>119</v>
-      </c>
-      <c r="T263" s="4">
-        <v>136.4</v>
-      </c>
-      <c r="U263" s="4">
-        <v>124.2</v>
+        <v>34</v>
+      </c>
+      <c r="G263" s="6">
+        <v>60</v>
+      </c>
+      <c r="H263" s="6">
+        <v>40</v>
+      </c>
+      <c r="I263" s="6">
+        <v>60</v>
+      </c>
+      <c r="J263" s="6">
+        <v>60</v>
+      </c>
+      <c r="K263" s="6">
+        <v>60</v>
+      </c>
+      <c r="L263" s="6">
+        <v>60</v>
+      </c>
+      <c r="M263" s="6">
+        <v>40</v>
+      </c>
+      <c r="N263" s="6">
+        <v>60</v>
+      </c>
+      <c r="O263" s="6">
+        <v>75</v>
+      </c>
+      <c r="P263" s="6">
+        <v>75</v>
+      </c>
+      <c r="Q263" s="6">
+        <v>40</v>
+      </c>
+      <c r="R263" s="6">
+        <v>33</v>
+      </c>
+      <c r="S263" s="6">
+        <v>50</v>
+      </c>
+      <c r="T263" s="6">
+        <v>17</v>
+      </c>
+      <c r="U263" s="6">
+        <v>25</v>
       </c>
       <c r="V263" s="3"/>
       <c r="W263" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="264" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18351,67 +18344,67 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G264" s="4">
-        <v>90.8</v>
+        <v>100</v>
       </c>
       <c r="H264" s="4">
-        <v>88.8</v>
+        <v>100.8</v>
       </c>
       <c r="I264" s="4">
-        <v>86.5</v>
+        <v>99.9</v>
       </c>
       <c r="J264" s="4">
-        <v>87</v>
+        <v>101.8</v>
       </c>
       <c r="K264" s="4">
-        <v>85</v>
+        <v>104.9</v>
       </c>
       <c r="L264" s="4">
-        <v>87.4</v>
+        <v>106</v>
       </c>
       <c r="M264" s="4">
-        <v>88.7</v>
+        <v>119.9</v>
       </c>
       <c r="N264" s="4">
-        <v>84.6</v>
+        <v>119.4</v>
       </c>
       <c r="O264" s="4">
-        <v>77.3</v>
+        <v>130</v>
       </c>
       <c r="P264" s="4">
-        <v>79.7</v>
+        <v>189.5</v>
       </c>
       <c r="Q264" s="4">
-        <v>81.900000000000006</v>
+        <v>186.6</v>
       </c>
       <c r="R264" s="4">
-        <v>74.8</v>
+        <v>190.1</v>
       </c>
       <c r="S264" s="4">
-        <v>77</v>
+        <v>200.8</v>
       </c>
       <c r="T264" s="4">
-        <v>77.2</v>
+        <v>205.6</v>
       </c>
       <c r="U264" s="4">
-        <v>76.3</v>
+        <v>208.5</v>
       </c>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>27</v>
@@ -18420,67 +18413,67 @@
         <v>28</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G265" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H265" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I265" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K265" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L265" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M265" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q265" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R265" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S265" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T265" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U265" s="7">
-        <v>0.192</v>
+        <v>363</v>
+      </c>
+      <c r="G265" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="H265" s="4">
+        <v>57.7</v>
+      </c>
+      <c r="I265" s="4">
+        <v>58.8</v>
+      </c>
+      <c r="J265" s="4">
+        <v>64.3</v>
+      </c>
+      <c r="K265" s="4">
+        <v>68.7</v>
+      </c>
+      <c r="L265" s="4">
+        <v>69.5</v>
+      </c>
+      <c r="M265" s="4">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="N265" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="O265" s="4">
+        <v>91.8</v>
+      </c>
+      <c r="P265" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="Q265" s="4">
+        <v>88.5</v>
+      </c>
+      <c r="R265" s="4">
+        <v>96.7</v>
+      </c>
+      <c r="S265" s="4">
+        <v>119</v>
+      </c>
+      <c r="T265" s="4">
+        <v>136.4</v>
+      </c>
+      <c r="U265" s="4">
+        <v>124.2</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
-        <v>364</v>
+        <v>30</v>
       </c>
     </row>
     <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>27</v>
@@ -18489,67 +18482,67 @@
         <v>28</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c r="G266" s="4">
-        <v>30.5</v>
+        <v>90.8</v>
       </c>
       <c r="H266" s="4">
-        <v>30.5</v>
+        <v>88.8</v>
       </c>
       <c r="I266" s="4">
-        <v>30.6</v>
+        <v>86.5</v>
       </c>
       <c r="J266" s="4">
-        <v>30.6</v>
+        <v>87</v>
       </c>
       <c r="K266" s="4">
-        <v>30.7</v>
+        <v>85</v>
       </c>
       <c r="L266" s="4">
-        <v>30.8</v>
+        <v>87.4</v>
       </c>
       <c r="M266" s="4">
-        <v>30.8</v>
+        <v>88.7</v>
       </c>
       <c r="N266" s="4">
-        <v>30.9</v>
+        <v>84.6</v>
       </c>
       <c r="O266" s="4">
-        <v>30.9</v>
+        <v>77.3</v>
       </c>
       <c r="P266" s="4">
-        <v>30.9</v>
+        <v>79.7</v>
       </c>
       <c r="Q266" s="4">
-        <v>30.9</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="R266" s="4">
-        <v>30.9</v>
+        <v>74.8</v>
       </c>
       <c r="S266" s="4">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="T266" s="4">
-        <v>31</v>
+        <v>77.2</v>
       </c>
       <c r="U266" s="4">
-        <v>31</v>
+        <v>76.3</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
     </row>
     <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18558,70 +18551,70 @@
         <v>28</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G267" s="6">
-        <v>28</v>
-      </c>
-      <c r="H267" s="6">
-        <v>27</v>
-      </c>
-      <c r="I267" s="6">
-        <v>26</v>
-      </c>
-      <c r="J267" s="6">
-        <v>25</v>
-      </c>
-      <c r="K267" s="6">
-        <v>24</v>
-      </c>
-      <c r="L267" s="6">
-        <v>23</v>
-      </c>
-      <c r="M267" s="6">
-        <v>22</v>
-      </c>
-      <c r="N267" s="6">
-        <v>22</v>
-      </c>
-      <c r="O267" s="6">
-        <v>22</v>
-      </c>
-      <c r="P267" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q267" s="6">
-        <v>19</v>
-      </c>
-      <c r="R267" s="6">
-        <v>17</v>
-      </c>
-      <c r="S267" s="6">
-        <v>16</v>
-      </c>
-      <c r="T267" s="6">
-        <v>16</v>
-      </c>
-      <c r="U267" s="6">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="G267" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H267" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I267" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K267" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L267" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M267" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P267" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q267" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R267" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S267" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T267" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U267" s="7">
+        <v>0.192</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>108</v>
+        <v>369</v>
       </c>
     </row>
     <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>28</v>
@@ -18630,49 +18623,49 @@
         <v>34</v>
       </c>
       <c r="G268" s="4">
-        <v>64.7</v>
+        <v>30.5</v>
       </c>
       <c r="H268" s="4">
-        <v>65.7</v>
+        <v>30.5</v>
       </c>
       <c r="I268" s="4">
-        <v>68.599999999999994</v>
+        <v>30.6</v>
       </c>
       <c r="J268" s="4">
-        <v>70.3</v>
+        <v>30.6</v>
       </c>
       <c r="K268" s="4">
-        <v>71.5</v>
+        <v>30.7</v>
       </c>
       <c r="L268" s="4">
-        <v>72.7</v>
+        <v>30.8</v>
       </c>
       <c r="M268" s="4">
-        <v>73.5</v>
+        <v>30.8</v>
       </c>
       <c r="N268" s="4">
-        <v>73.599999999999994</v>
+        <v>30.9</v>
       </c>
       <c r="O268" s="4">
-        <v>74</v>
+        <v>30.9</v>
       </c>
       <c r="P268" s="4">
-        <v>74.5</v>
+        <v>30.9</v>
       </c>
       <c r="Q268" s="4">
-        <v>74.900000000000006</v>
+        <v>30.9</v>
       </c>
       <c r="R268" s="4">
-        <v>75.2</v>
+        <v>30.9</v>
       </c>
       <c r="S268" s="4">
-        <v>75.7</v>
+        <v>31</v>
       </c>
       <c r="T268" s="4">
-        <v>75.900000000000006</v>
+        <v>31</v>
       </c>
       <c r="U268" s="4">
-        <v>76.2</v>
+        <v>31</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
@@ -18681,136 +18674,136 @@
     </row>
     <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G269" s="4">
-        <v>88</v>
-      </c>
-      <c r="H269" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I269" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J269" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K269" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N269" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q269" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R269" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S269" s="4">
-        <v>95</v>
-      </c>
-      <c r="T269" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U269" s="4">
-        <v>94.6</v>
+        <v>107</v>
+      </c>
+      <c r="G269" s="6">
+        <v>28</v>
+      </c>
+      <c r="H269" s="6">
+        <v>27</v>
+      </c>
+      <c r="I269" s="6">
+        <v>26</v>
+      </c>
+      <c r="J269" s="6">
+        <v>25</v>
+      </c>
+      <c r="K269" s="6">
+        <v>24</v>
+      </c>
+      <c r="L269" s="6">
+        <v>23</v>
+      </c>
+      <c r="M269" s="6">
+        <v>22</v>
+      </c>
+      <c r="N269" s="6">
+        <v>22</v>
+      </c>
+      <c r="O269" s="6">
+        <v>22</v>
+      </c>
+      <c r="P269" s="6">
+        <v>21</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>19</v>
+      </c>
+      <c r="R269" s="6">
+        <v>17</v>
+      </c>
+      <c r="S269" s="6">
+        <v>16</v>
+      </c>
+      <c r="T269" s="6">
+        <v>16</v>
+      </c>
+      <c r="U269" s="6">
+        <v>15</v>
       </c>
       <c r="V269" s="3"/>
       <c r="W269" s="2" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
     </row>
     <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D270" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G270" s="4">
-        <v>28.5</v>
+        <v>64.7</v>
       </c>
       <c r="H270" s="4">
-        <v>30.6</v>
+        <v>65.7</v>
       </c>
       <c r="I270" s="4">
-        <v>33.1</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="J270" s="4">
-        <v>35.299999999999997</v>
+        <v>70.3</v>
       </c>
       <c r="K270" s="4">
-        <v>37.4</v>
+        <v>71.5</v>
       </c>
       <c r="L270" s="4">
-        <v>39.6</v>
+        <v>72.7</v>
       </c>
       <c r="M270" s="4">
-        <v>41.2</v>
+        <v>73.5</v>
       </c>
       <c r="N270" s="4">
-        <v>42</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="O270" s="4">
-        <v>42.9</v>
+        <v>74</v>
       </c>
       <c r="P270" s="4">
-        <v>44</v>
+        <v>74.5</v>
       </c>
       <c r="Q270" s="4">
-        <v>45.4</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="R270" s="4">
-        <v>46.5</v>
+        <v>75.2</v>
       </c>
       <c r="S270" s="4">
-        <v>47.2</v>
+        <v>75.7</v>
       </c>
       <c r="T270" s="4">
-        <v>48.2</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="U270" s="4">
-        <v>49.3</v>
+        <v>76.2</v>
       </c>
       <c r="V270" s="3"/>
       <c r="W270" s="2" t="s">
@@ -18819,151 +18812,151 @@
     </row>
     <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G271" s="4">
-        <v>65.7</v>
+        <v>88</v>
       </c>
       <c r="H271" s="4">
-        <v>64.8</v>
+        <v>88.4</v>
       </c>
       <c r="I271" s="4">
-        <v>67.400000000000006</v>
+        <v>91.7</v>
       </c>
       <c r="J271" s="4">
-        <v>69.8</v>
+        <v>93.3</v>
       </c>
       <c r="K271" s="4">
-        <v>70.5</v>
+        <v>93.9</v>
       </c>
       <c r="L271" s="4">
-        <v>70.900000000000006</v>
+        <v>94.6</v>
       </c>
       <c r="M271" s="4">
-        <v>71.400000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="N271" s="4">
-        <v>72.5</v>
+        <v>94.5</v>
       </c>
       <c r="O271" s="4">
-        <v>73.2</v>
+        <v>94.6</v>
       </c>
       <c r="P271" s="4">
-        <v>73.900000000000006</v>
+        <v>94.8</v>
       </c>
       <c r="Q271" s="4">
-        <v>73.3</v>
+        <v>94.7</v>
       </c>
       <c r="R271" s="4">
-        <v>72.8</v>
+        <v>94.6</v>
       </c>
       <c r="S271" s="4">
-        <v>76.3</v>
+        <v>95</v>
       </c>
       <c r="T271" s="4">
-        <v>78.099999999999994</v>
+        <v>94.8</v>
       </c>
       <c r="U271" s="4">
-        <v>78.599999999999994</v>
+        <v>94.6</v>
       </c>
       <c r="V271" s="3"/>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G272" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H272" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I272" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J272" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K272" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L272" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M272" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N272" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O272" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P272" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q272" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R272" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S272" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T272" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U272" s="6">
-        <v>104040</v>
+        <v>34</v>
+      </c>
+      <c r="G272" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="H272" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="I272" s="4">
+        <v>33.1</v>
+      </c>
+      <c r="J272" s="4">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K272" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="L272" s="4">
+        <v>39.6</v>
+      </c>
+      <c r="M272" s="4">
+        <v>41.2</v>
+      </c>
+      <c r="N272" s="4">
+        <v>42</v>
+      </c>
+      <c r="O272" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="P272" s="4">
+        <v>44</v>
+      </c>
+      <c r="Q272" s="4">
+        <v>45.4</v>
+      </c>
+      <c r="R272" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="S272" s="4">
+        <v>47.2</v>
+      </c>
+      <c r="T272" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="U272" s="4">
+        <v>49.3</v>
       </c>
       <c r="V272" s="3"/>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="273" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18975,49 +18968,49 @@
         <v>34</v>
       </c>
       <c r="G273" s="4">
-        <v>2.9</v>
+        <v>65.7</v>
       </c>
       <c r="H273" s="4">
-        <v>3.8</v>
+        <v>64.8</v>
       </c>
       <c r="I273" s="4">
-        <v>6</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="J273" s="4">
-        <v>4.3</v>
+        <v>69.8</v>
       </c>
       <c r="K273" s="4">
-        <v>4.5999999999999996</v>
+        <v>70.5</v>
       </c>
       <c r="L273" s="4">
-        <v>4.2</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="M273" s="4">
-        <v>3.1</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="N273" s="4">
-        <v>3</v>
+        <v>72.5</v>
       </c>
       <c r="O273" s="4">
-        <v>3.2</v>
+        <v>73.2</v>
       </c>
       <c r="P273" s="4">
-        <v>3.4</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="Q273" s="4">
-        <v>3.2</v>
+        <v>73.3</v>
       </c>
       <c r="R273" s="4">
-        <v>4.5</v>
+        <v>72.8</v>
       </c>
       <c r="S273" s="4">
-        <v>6.6</v>
+        <v>76.3</v>
       </c>
       <c r="T273" s="4">
-        <v>5.8</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="U273" s="4">
-        <v>4.5</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
@@ -19026,7 +19019,7 @@
     </row>
     <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>375</v>
@@ -19041,63 +19034,61 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>34</v>
+        <v>377</v>
       </c>
       <c r="G274" s="6">
-        <v>70</v>
+        <v>70108</v>
       </c>
       <c r="H274" s="6">
-        <v>75</v>
+        <v>248240</v>
       </c>
       <c r="I274" s="6">
-        <v>66</v>
+        <v>168221</v>
       </c>
       <c r="J274" s="6">
-        <v>64</v>
+        <v>72837</v>
       </c>
       <c r="K274" s="6">
-        <v>70</v>
+        <v>64283</v>
       </c>
       <c r="L274" s="6">
-        <v>66</v>
+        <v>68694</v>
       </c>
       <c r="M274" s="6">
-        <v>80</v>
+        <v>60135</v>
       </c>
       <c r="N274" s="6">
-        <v>89</v>
+        <v>46337</v>
       </c>
       <c r="O274" s="6">
-        <v>86</v>
+        <v>50289</v>
       </c>
       <c r="P274" s="6">
-        <v>89</v>
+        <v>104107</v>
       </c>
       <c r="Q274" s="6">
-        <v>85</v>
+        <v>201963</v>
       </c>
       <c r="R274" s="6">
-        <v>82</v>
+        <v>84506</v>
       </c>
       <c r="S274" s="6">
-        <v>83</v>
+        <v>295948</v>
       </c>
       <c r="T274" s="6">
-        <v>88</v>
+        <v>123796</v>
       </c>
       <c r="U274" s="6">
-        <v>88</v>
-      </c>
-      <c r="V274" s="6">
-        <v>86</v>
-      </c>
+        <v>104040</v>
+      </c>
+      <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>375</v>
@@ -19114,51 +19105,65 @@
       <c r="F275" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G275" s="6">
-        <v>55</v>
-      </c>
-      <c r="H275" s="3"/>
-      <c r="I275" s="6">
-        <v>58</v>
-      </c>
-      <c r="J275" s="3"/>
-      <c r="K275" s="6">
-        <v>60</v>
-      </c>
-      <c r="L275" s="3"/>
-      <c r="M275" s="6">
-        <v>64</v>
-      </c>
-      <c r="N275" s="3"/>
-      <c r="O275" s="6">
-        <v>65</v>
-      </c>
-      <c r="P275" s="3"/>
-      <c r="Q275" s="6">
-        <v>74</v>
-      </c>
-      <c r="R275" s="3"/>
-      <c r="S275" s="6">
-        <v>63</v>
-      </c>
-      <c r="T275" s="3"/>
-      <c r="U275" s="6">
-        <v>71</v>
+      <c r="G275" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H275" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="I275" s="4">
+        <v>6</v>
+      </c>
+      <c r="J275" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K275" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="L275" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="M275" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="N275" s="4">
+        <v>3</v>
+      </c>
+      <c r="O275" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="P275" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Q275" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="R275" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="S275" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="T275" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="U275" s="4">
+        <v>4.5</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>27</v>
@@ -19167,41 +19172,69 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G276" s="3"/>
-      <c r="H276" s="3"/>
-      <c r="I276" s="3"/>
-      <c r="J276" s="3"/>
-      <c r="K276" s="3"/>
-      <c r="L276" s="3"/>
-      <c r="M276" s="3"/>
-      <c r="N276" s="3"/>
-      <c r="O276" s="3"/>
-      <c r="P276" s="3"/>
-      <c r="Q276" s="3"/>
-      <c r="R276" s="3"/>
-      <c r="S276" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T276" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U276" s="3"/>
-      <c r="V276" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G276" s="6">
+        <v>70</v>
+      </c>
+      <c r="H276" s="6">
+        <v>75</v>
+      </c>
+      <c r="I276" s="6">
+        <v>66</v>
+      </c>
+      <c r="J276" s="6">
+        <v>64</v>
+      </c>
+      <c r="K276" s="6">
+        <v>70</v>
+      </c>
+      <c r="L276" s="6">
+        <v>66</v>
+      </c>
+      <c r="M276" s="6">
+        <v>80</v>
+      </c>
+      <c r="N276" s="6">
+        <v>89</v>
+      </c>
+      <c r="O276" s="6">
+        <v>86</v>
+      </c>
+      <c r="P276" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q276" s="6">
+        <v>85</v>
+      </c>
+      <c r="R276" s="6">
+        <v>82</v>
+      </c>
+      <c r="S276" s="6">
+        <v>83</v>
+      </c>
+      <c r="T276" s="6">
+        <v>88</v>
+      </c>
+      <c r="U276" s="6">
+        <v>88</v>
+      </c>
+      <c r="V276" s="6">
+        <v>86</v>
+      </c>
       <c r="W276" s="2" t="s">
-        <v>88</v>
+        <v>382</v>
       </c>
     </row>
     <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>380</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D277" s="2" t="s">
         <v>27</v>
@@ -19210,67 +19243,53 @@
         <v>28</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G277" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H277" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I277" s="5">
-        <v>1</v>
-      </c>
-      <c r="J277" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K277" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L277" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M277" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N277" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O277" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P277" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q277" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R277" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S277" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T277" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U277" s="5">
-        <v>0.69</v>
+        <v>34</v>
+      </c>
+      <c r="G277" s="6">
+        <v>55</v>
+      </c>
+      <c r="H277" s="3"/>
+      <c r="I277" s="6">
+        <v>58</v>
+      </c>
+      <c r="J277" s="3"/>
+      <c r="K277" s="6">
+        <v>60</v>
+      </c>
+      <c r="L277" s="3"/>
+      <c r="M277" s="6">
+        <v>64</v>
+      </c>
+      <c r="N277" s="3"/>
+      <c r="O277" s="6">
+        <v>65</v>
+      </c>
+      <c r="P277" s="3"/>
+      <c r="Q277" s="6">
+        <v>74</v>
+      </c>
+      <c r="R277" s="3"/>
+      <c r="S277" s="6">
+        <v>63</v>
+      </c>
+      <c r="T277" s="3"/>
+      <c r="U277" s="6">
+        <v>71</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>204</v>
+        <v>382</v>
       </c>
     </row>
     <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>27</v>
@@ -19279,61 +19298,35 @@
         <v>28</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G278" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H278" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I278" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J278" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K278" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L278" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M278" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N278" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O278" s="5">
-        <v>2</v>
-      </c>
-      <c r="P278" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q278" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R278" s="5">
-        <v>2.19</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G278" s="3"/>
+      <c r="H278" s="3"/>
+      <c r="I278" s="3"/>
+      <c r="J278" s="3"/>
+      <c r="K278" s="3"/>
+      <c r="L278" s="3"/>
+      <c r="M278" s="3"/>
+      <c r="N278" s="3"/>
+      <c r="O278" s="3"/>
+      <c r="P278" s="3"/>
+      <c r="Q278" s="3"/>
+      <c r="R278" s="3"/>
       <c r="S278" s="5">
-        <v>2.21</v>
+        <v>33109.31</v>
       </c>
       <c r="T278" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U278" s="5">
-        <v>4.07</v>
-      </c>
+        <v>33829.39</v>
+      </c>
+      <c r="U278" s="3"/>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>384</v>
+        <v>88</v>
       </c>
     </row>
     <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>385</v>
@@ -19348,169 +19341,165 @@
         <v>28</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G279" s="3"/>
-      <c r="H279" s="3"/>
-      <c r="I279" s="3"/>
-      <c r="J279" s="3"/>
-      <c r="K279" s="3"/>
-      <c r="L279" s="3"/>
-      <c r="M279" s="3"/>
-      <c r="N279" s="3"/>
-      <c r="O279" s="3"/>
-      <c r="P279" s="3"/>
-      <c r="Q279" s="3"/>
-      <c r="R279" s="3"/>
-      <c r="S279" s="3"/>
-      <c r="T279" s="3"/>
-      <c r="U279" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="V279" s="4">
-        <v>51.3</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G279" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H279" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I279" s="5">
+        <v>1</v>
+      </c>
+      <c r="J279" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K279" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L279" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M279" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N279" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O279" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P279" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q279" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R279" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S279" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T279" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U279" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="V279" s="3"/>
       <c r="W279" s="2" t="s">
-        <v>30</v>
+        <v>204</v>
       </c>
     </row>
     <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G280" s="4">
-        <v>28.1</v>
-      </c>
-      <c r="H280" s="4">
-        <v>27.6</v>
-      </c>
-      <c r="I280" s="4">
-        <v>31.6</v>
-      </c>
-      <c r="J280" s="4">
-        <v>22.6</v>
-      </c>
-      <c r="K280" s="4">
-        <v>26.9</v>
-      </c>
-      <c r="L280" s="4">
-        <v>26.6</v>
-      </c>
-      <c r="M280" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="N280" s="4">
-        <v>30.8</v>
-      </c>
-      <c r="O280" s="4">
-        <v>35.5</v>
-      </c>
-      <c r="P280" s="4">
-        <v>40.4</v>
-      </c>
-      <c r="Q280" s="4">
-        <v>41.9</v>
-      </c>
-      <c r="R280" s="4">
-        <v>47.5</v>
-      </c>
-      <c r="S280" s="4">
-        <v>55.4</v>
-      </c>
-      <c r="T280" s="4">
-        <v>58.5</v>
-      </c>
-      <c r="U280" s="4">
-        <v>61</v>
-      </c>
-      <c r="V280" s="4">
-        <v>61.1</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G280" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H280" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I280" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J280" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K280" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M280" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N280" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O280" s="5">
+        <v>2</v>
+      </c>
+      <c r="P280" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R280" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S280" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T280" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U280" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="V280" s="3"/>
       <c r="W280" s="2" t="s">
-        <v>30</v>
+        <v>389</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>388</v>
+        <v>28</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G281" s="4">
-        <v>31.5</v>
-      </c>
-      <c r="H281" s="4">
-        <v>27.9</v>
-      </c>
-      <c r="I281" s="4">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="J281" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="K281" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="L281" s="4">
-        <v>20.8</v>
-      </c>
-      <c r="M281" s="4">
-        <v>20.5</v>
-      </c>
-      <c r="N281" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="O281" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="P281" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="Q281" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R281" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="S281" s="4">
-        <v>42.1</v>
-      </c>
-      <c r="T281" s="4">
-        <v>44</v>
-      </c>
+      <c r="G281" s="3"/>
+      <c r="H281" s="3"/>
+      <c r="I281" s="3"/>
+      <c r="J281" s="3"/>
+      <c r="K281" s="3"/>
+      <c r="L281" s="3"/>
+      <c r="M281" s="3"/>
+      <c r="N281" s="3"/>
+      <c r="O281" s="3"/>
+      <c r="P281" s="3"/>
+      <c r="Q281" s="3"/>
+      <c r="R281" s="3"/>
+      <c r="S281" s="3"/>
+      <c r="T281" s="3"/>
       <c r="U281" s="4">
-        <v>47.7</v>
+        <v>30.2</v>
       </c>
       <c r="V281" s="4">
-        <v>48.9</v>
+        <v>51.3</v>
       </c>
       <c r="W281" s="2" t="s">
         <v>30</v>
@@ -19518,70 +19507,70 @@
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>389</v>
+        <v>28</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G282" s="4">
-        <v>47.6</v>
+        <v>28.1</v>
       </c>
       <c r="H282" s="4">
-        <v>46.2</v>
+        <v>27.6</v>
       </c>
       <c r="I282" s="4">
-        <v>50.6</v>
+        <v>31.6</v>
       </c>
       <c r="J282" s="4">
-        <v>39</v>
+        <v>22.6</v>
       </c>
       <c r="K282" s="4">
-        <v>46</v>
+        <v>26.9</v>
       </c>
       <c r="L282" s="4">
-        <v>45</v>
+        <v>26.6</v>
       </c>
       <c r="M282" s="4">
-        <v>48.1</v>
+        <v>30.2</v>
       </c>
       <c r="N282" s="4">
-        <v>48.1</v>
+        <v>30.8</v>
       </c>
       <c r="O282" s="4">
-        <v>53</v>
+        <v>35.5</v>
       </c>
       <c r="P282" s="4">
-        <v>58.6</v>
+        <v>40.4</v>
       </c>
       <c r="Q282" s="4">
-        <v>59.9</v>
+        <v>41.9</v>
       </c>
       <c r="R282" s="4">
-        <v>68.3</v>
+        <v>47.5</v>
       </c>
       <c r="S282" s="4">
-        <v>75.2</v>
+        <v>55.4</v>
       </c>
       <c r="T282" s="4">
-        <v>81</v>
+        <v>58.5</v>
       </c>
       <c r="U282" s="4">
-        <v>81.2</v>
+        <v>61</v>
       </c>
       <c r="V282" s="4">
-        <v>81.8</v>
+        <v>61.1</v>
       </c>
       <c r="W282" s="2" t="s">
         <v>30</v>
@@ -19589,70 +19578,70 @@
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D283" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G283" s="4">
-        <v>37.6</v>
+        <v>31.5</v>
       </c>
       <c r="H283" s="4">
-        <v>36.9</v>
+        <v>27.9</v>
       </c>
       <c r="I283" s="4">
-        <v>45.3</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="J283" s="4">
-        <v>35.200000000000003</v>
+        <v>20.2</v>
       </c>
       <c r="K283" s="4">
-        <v>40.1</v>
+        <v>23.9</v>
       </c>
       <c r="L283" s="4">
-        <v>38.6</v>
+        <v>20.8</v>
       </c>
       <c r="M283" s="4">
-        <v>40.5</v>
+        <v>20.5</v>
       </c>
       <c r="N283" s="4">
-        <v>45</v>
+        <v>22.4</v>
       </c>
       <c r="O283" s="4">
-        <v>49.6</v>
+        <v>29.5</v>
       </c>
       <c r="P283" s="4">
-        <v>57.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q283" s="4">
-        <v>59.4</v>
+        <v>30.9</v>
       </c>
       <c r="R283" s="4">
-        <v>65.900000000000006</v>
+        <v>35.6</v>
       </c>
       <c r="S283" s="4">
-        <v>75.599999999999994</v>
+        <v>42.1</v>
       </c>
       <c r="T283" s="4">
-        <v>78.3</v>
+        <v>44</v>
       </c>
       <c r="U283" s="4">
-        <v>81.099999999999994</v>
+        <v>47.7</v>
       </c>
       <c r="V283" s="4">
-        <v>78.3</v>
+        <v>48.9</v>
       </c>
       <c r="W283" s="2" t="s">
         <v>30</v>
@@ -19660,70 +19649,70 @@
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G284" s="4">
-        <v>26.2</v>
+        <v>47.6</v>
       </c>
       <c r="H284" s="4">
-        <v>26.3</v>
+        <v>46.2</v>
       </c>
       <c r="I284" s="4">
-        <v>28.7</v>
+        <v>50.6</v>
       </c>
       <c r="J284" s="4">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="K284" s="4">
-        <v>26.2</v>
+        <v>46</v>
       </c>
       <c r="L284" s="4">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="M284" s="4">
-        <v>30</v>
+        <v>48.1</v>
       </c>
       <c r="N284" s="4">
-        <v>28</v>
+        <v>48.1</v>
       </c>
       <c r="O284" s="4">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="P284" s="4">
-        <v>41.4</v>
+        <v>58.6</v>
       </c>
       <c r="Q284" s="4">
-        <v>45.1</v>
+        <v>59.9</v>
       </c>
       <c r="R284" s="4">
-        <v>51.7</v>
+        <v>68.3</v>
       </c>
       <c r="S284" s="4">
-        <v>62.4</v>
+        <v>75.2</v>
       </c>
       <c r="T284" s="4">
-        <v>65.7</v>
+        <v>81</v>
       </c>
       <c r="U284" s="4">
-        <v>68.8</v>
+        <v>81.2</v>
       </c>
       <c r="V284" s="4">
-        <v>69.900000000000006</v>
+        <v>81.8</v>
       </c>
       <c r="W284" s="2" t="s">
         <v>30</v>
@@ -19731,70 +19720,70 @@
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>215</v>
+        <v>395</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G285" s="4">
-        <v>13.5</v>
+        <v>37.6</v>
       </c>
       <c r="H285" s="4">
-        <v>15.7</v>
+        <v>36.9</v>
       </c>
       <c r="I285" s="4">
-        <v>17.2</v>
+        <v>45.3</v>
       </c>
       <c r="J285" s="4">
-        <v>12.7</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="K285" s="4">
-        <v>15.5</v>
+        <v>40.1</v>
       </c>
       <c r="L285" s="4">
-        <v>18.3</v>
+        <v>38.6</v>
       </c>
       <c r="M285" s="4">
-        <v>19.8</v>
+        <v>40.5</v>
       </c>
       <c r="N285" s="4">
-        <v>18.8</v>
+        <v>45</v>
       </c>
       <c r="O285" s="4">
-        <v>22.4</v>
+        <v>49.6</v>
       </c>
       <c r="P285" s="4">
-        <v>28.5</v>
+        <v>57.6</v>
       </c>
       <c r="Q285" s="4">
-        <v>29.4</v>
+        <v>59.4</v>
       </c>
       <c r="R285" s="4">
-        <v>35</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="S285" s="4">
-        <v>39.5</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="T285" s="4">
-        <v>44.4</v>
+        <v>78.3</v>
       </c>
       <c r="U285" s="4">
-        <v>50.8</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="V285" s="4">
-        <v>51.4</v>
+        <v>78.3</v>
       </c>
       <c r="W285" s="2" t="s">
         <v>30</v>
@@ -19802,70 +19791,70 @@
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G286" s="4">
-        <v>4.0999999999999996</v>
+        <v>26.2</v>
       </c>
       <c r="H286" s="4">
-        <v>5</v>
+        <v>26.3</v>
       </c>
       <c r="I286" s="4">
-        <v>6.8</v>
+        <v>28.7</v>
       </c>
       <c r="J286" s="4">
-        <v>3.7</v>
+        <v>21.5</v>
       </c>
       <c r="K286" s="4">
-        <v>6.6</v>
+        <v>26.2</v>
       </c>
       <c r="L286" s="4">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="M286" s="4">
-        <v>8.6999999999999993</v>
+        <v>30</v>
       </c>
       <c r="N286" s="4">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="O286" s="4">
-        <v>10.9</v>
+        <v>35</v>
       </c>
       <c r="P286" s="4">
-        <v>12.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q286" s="4">
-        <v>13.5</v>
+        <v>45.1</v>
       </c>
       <c r="R286" s="4">
-        <v>15.8</v>
+        <v>51.7</v>
       </c>
       <c r="S286" s="4">
-        <v>23.6</v>
+        <v>62.4</v>
       </c>
       <c r="T286" s="4">
-        <v>26.1</v>
+        <v>65.7</v>
       </c>
       <c r="U286" s="4">
-        <v>27.4</v>
+        <v>68.8</v>
       </c>
       <c r="V286" s="4">
-        <v>27.6</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="W286" s="2" t="s">
         <v>30</v>
@@ -19873,155 +19862,155 @@
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G287" s="4">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="H287" s="4">
-        <v>6</v>
+        <v>15.7</v>
       </c>
       <c r="I287" s="4">
-        <v>4.9000000000000004</v>
+        <v>17.2</v>
       </c>
       <c r="J287" s="4">
-        <v>4.3</v>
+        <v>12.7</v>
       </c>
       <c r="K287" s="4">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="L287" s="4">
-        <v>4.5</v>
+        <v>18.3</v>
       </c>
       <c r="M287" s="4">
-        <v>3.3</v>
+        <v>19.8</v>
       </c>
       <c r="N287" s="4">
-        <v>3.8</v>
+        <v>18.8</v>
       </c>
       <c r="O287" s="4">
-        <v>4.5999999999999996</v>
+        <v>22.4</v>
       </c>
       <c r="P287" s="4">
-        <v>4.3</v>
+        <v>28.5</v>
       </c>
       <c r="Q287" s="4">
-        <v>4.4000000000000004</v>
+        <v>29.4</v>
       </c>
       <c r="R287" s="4">
-        <v>4.0999999999999996</v>
+        <v>35</v>
       </c>
       <c r="S287" s="4">
-        <v>3.8</v>
+        <v>39.5</v>
       </c>
       <c r="T287" s="4">
-        <v>5.0999999999999996</v>
+        <v>44.4</v>
       </c>
       <c r="U287" s="4">
-        <v>4.8</v>
+        <v>50.8</v>
       </c>
       <c r="V287" s="4">
-        <v>5.2</v>
+        <v>51.4</v>
       </c>
       <c r="W287" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="288" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>28</v>
+        <v>397</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G288" s="6">
-        <v>674</v>
-      </c>
-      <c r="H288" s="6">
-        <v>605</v>
-      </c>
-      <c r="I288" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J288" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K288" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L288" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M288" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N288" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O288" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P288" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q288" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R288" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S288" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T288" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U288" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V288" s="6">
-        <v>260783</v>
+        <v>34</v>
+      </c>
+      <c r="G288" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H288" s="4">
+        <v>5</v>
+      </c>
+      <c r="I288" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J288" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K288" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L288" s="4">
+        <v>6</v>
+      </c>
+      <c r="M288" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N288" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O288" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P288" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q288" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R288" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S288" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T288" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U288" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V288" s="4">
+        <v>27.6</v>
       </c>
       <c r="W288" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="289" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>27</v>
@@ -20032,35 +20021,61 @@
       <c r="F289" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G289" s="3"/>
-      <c r="H289" s="3"/>
-      <c r="I289" s="3"/>
-      <c r="J289" s="3"/>
-      <c r="K289" s="3"/>
-      <c r="L289" s="3"/>
-      <c r="M289" s="3"/>
-      <c r="N289" s="3"/>
-      <c r="O289" s="3"/>
-      <c r="P289" s="3"/>
-      <c r="Q289" s="3"/>
-      <c r="R289" s="5">
-        <v>18.93</v>
-      </c>
-      <c r="S289" s="3"/>
-      <c r="T289" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U289" s="3"/>
-      <c r="V289" s="5">
-        <v>23.01</v>
+      <c r="G289" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H289" s="4">
+        <v>6</v>
+      </c>
+      <c r="I289" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K289" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L289" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M289" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O289" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P289" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R289" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S289" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T289" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U289" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V289" s="4">
+        <v>5.2</v>
       </c>
       <c r="W289" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="290" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="290" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>400</v>
@@ -20075,67 +20090,69 @@
         <v>28</v>
       </c>
       <c r="F290" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G290" s="6">
+        <v>674</v>
+      </c>
+      <c r="H290" s="6">
+        <v>605</v>
+      </c>
+      <c r="I290" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J290" s="6">
+        <v>1219</v>
+      </c>
+      <c r="K290" s="6">
+        <v>1282</v>
+      </c>
+      <c r="L290" s="6">
+        <v>1456</v>
+      </c>
+      <c r="M290" s="6">
+        <v>1926</v>
+      </c>
+      <c r="N290" s="6">
+        <v>3182</v>
+      </c>
+      <c r="O290" s="6">
+        <v>3739</v>
+      </c>
+      <c r="P290" s="6">
+        <v>6484</v>
+      </c>
+      <c r="Q290" s="6">
+        <v>10420</v>
+      </c>
+      <c r="R290" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S290" s="6">
+        <v>39683</v>
+      </c>
+      <c r="T290" s="6">
+        <v>80267</v>
+      </c>
+      <c r="U290" s="6">
+        <v>103449</v>
+      </c>
+      <c r="V290" s="6">
+        <v>260783</v>
+      </c>
+      <c r="W290" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="G290" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H290" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I290" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J290" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K290" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L290" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M290" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N290" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O290" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P290" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q290" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R290" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S290" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T290" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U290" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V290" s="3"/>
-      <c r="W290" s="2" t="s">
+    </row>
+    <row r="291" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>403</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>27</v>
@@ -20144,67 +20161,43 @@
         <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G291" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H291" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I291" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J291" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K291" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L291" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M291" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N291" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O291" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P291" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q291" s="5">
-        <v>225.08</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G291" s="3"/>
+      <c r="H291" s="3"/>
+      <c r="I291" s="3"/>
+      <c r="J291" s="3"/>
+      <c r="K291" s="3"/>
+      <c r="L291" s="3"/>
+      <c r="M291" s="3"/>
+      <c r="N291" s="3"/>
+      <c r="O291" s="3"/>
+      <c r="P291" s="3"/>
+      <c r="Q291" s="3"/>
       <c r="R291" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S291" s="5">
-        <v>2661.32</v>
-      </c>
+        <v>18.93</v>
+      </c>
+      <c r="S291" s="3"/>
       <c r="T291" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U291" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V291" s="3"/>
+        <v>21.3</v>
+      </c>
+      <c r="U291" s="3"/>
+      <c r="V291" s="5">
+        <v>23.01</v>
+      </c>
       <c r="W291" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B292" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>27</v>
@@ -20213,67 +20206,67 @@
         <v>28</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>34</v>
+        <v>407</v>
       </c>
       <c r="G292" s="5">
-        <v>0.08</v>
+        <v>377.75</v>
       </c>
       <c r="H292" s="5">
-        <v>0.08</v>
+        <v>417.47</v>
       </c>
       <c r="I292" s="5">
-        <v>0.09</v>
+        <v>421.06</v>
       </c>
       <c r="J292" s="5">
-        <v>0.1</v>
+        <v>487.12</v>
       </c>
       <c r="K292" s="5">
-        <v>0.09</v>
+        <v>451.84</v>
       </c>
       <c r="L292" s="5">
-        <v>0.1</v>
+        <v>440.89</v>
       </c>
       <c r="M292" s="5">
-        <v>0.15</v>
+        <v>662.95</v>
       </c>
       <c r="N292" s="5">
-        <v>0.13</v>
+        <v>679.46</v>
       </c>
       <c r="O292" s="5">
-        <v>0.14000000000000001</v>
+        <v>766.04</v>
       </c>
       <c r="P292" s="5">
-        <v>0.14000000000000001</v>
+        <v>776.56</v>
       </c>
       <c r="Q292" s="5">
-        <v>0.14000000000000001</v>
+        <v>829.27</v>
       </c>
       <c r="R292" s="5">
-        <v>0.15</v>
+        <v>983.51</v>
       </c>
       <c r="S292" s="5">
-        <v>0.53</v>
+        <v>3494.39</v>
       </c>
       <c r="T292" s="5">
-        <v>0.33</v>
+        <v>2580.38</v>
       </c>
       <c r="U292" s="5">
-        <v>0.21</v>
+        <v>1840.15</v>
       </c>
       <c r="V292" s="3"/>
       <c r="W292" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>27</v>
@@ -20282,57 +20275,61 @@
         <v>28</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G293" s="3"/>
-      <c r="H293" s="3"/>
-      <c r="I293" s="3"/>
-      <c r="J293" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K293" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L293" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M293" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N293" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O293" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P293" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q293" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R293" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S293" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T293" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U293" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V293" s="7">
-        <v>5.3920000000000003</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="G293" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H293" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I293" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J293" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K293" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L293" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M293" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N293" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O293" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P293" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q293" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R293" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S293" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T293" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U293" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V293" s="3"/>
       <c r="W293" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>411</v>
@@ -20347,55 +20344,61 @@
         <v>28</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G294" s="3"/>
-      <c r="H294" s="3"/>
-      <c r="I294" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G294" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H294" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I294" s="5">
+        <v>0.09</v>
+      </c>
       <c r="J294" s="5">
-        <v>8.07</v>
+        <v>0.1</v>
       </c>
       <c r="K294" s="5">
-        <v>3.54</v>
+        <v>0.09</v>
       </c>
       <c r="L294" s="5">
-        <v>2.98</v>
+        <v>0.1</v>
       </c>
       <c r="M294" s="5">
-        <v>2.44</v>
+        <v>0.15</v>
       </c>
       <c r="N294" s="5">
-        <v>2.25</v>
+        <v>0.13</v>
       </c>
       <c r="O294" s="5">
-        <v>63.36</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="P294" s="5">
-        <v>7.61</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Q294" s="5">
-        <v>6.64</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="R294" s="5">
-        <v>3.65</v>
+        <v>0.15</v>
       </c>
       <c r="S294" s="5">
-        <v>9.59</v>
+        <v>0.53</v>
       </c>
       <c r="T294" s="5">
-        <v>4.2699999999999996</v>
+        <v>0.33</v>
       </c>
       <c r="U294" s="5">
-        <v>8.32</v>
+        <v>0.21</v>
       </c>
       <c r="V294" s="3"/>
       <c r="W294" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="295" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>413</v>
@@ -20415,50 +20418,58 @@
       <c r="G295" s="3"/>
       <c r="H295" s="3"/>
       <c r="I295" s="3"/>
-      <c r="J295" s="3"/>
-      <c r="K295" s="6">
-        <v>1</v>
-      </c>
-      <c r="L295" s="6">
-        <v>1</v>
-      </c>
-      <c r="M295" s="6">
-        <v>8</v>
-      </c>
-      <c r="N295" s="6">
-        <v>2</v>
-      </c>
-      <c r="O295" s="3"/>
-      <c r="P295" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q295" s="6">
-        <v>2</v>
-      </c>
-      <c r="R295" s="3"/>
-      <c r="S295" s="3"/>
-      <c r="T295" s="6">
-        <v>8</v>
-      </c>
-      <c r="U295" s="6">
-        <v>7</v>
-      </c>
-      <c r="V295" s="6">
-        <v>2</v>
+      <c r="J295" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K295" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L295" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M295" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N295" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O295" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P295" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q295" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R295" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S295" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T295" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U295" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V295" s="7">
+        <v>5.3920000000000003</v>
       </c>
       <c r="W295" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="296" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B296" s="2" t="s">
+      <c r="C296" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20467,65 +20478,61 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="3"/>
-      <c r="I296" s="6">
-        <v>2</v>
-      </c>
-      <c r="J296" s="6">
-        <v>2</v>
-      </c>
-      <c r="K296" s="6">
-        <v>1</v>
-      </c>
-      <c r="L296" s="6">
-        <v>1</v>
-      </c>
-      <c r="M296" s="6">
-        <v>1</v>
-      </c>
-      <c r="N296" s="6">
-        <v>1</v>
-      </c>
-      <c r="O296" s="6">
-        <v>1</v>
-      </c>
-      <c r="P296" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q296" s="6">
-        <v>4</v>
-      </c>
-      <c r="R296" s="6">
-        <v>1</v>
-      </c>
-      <c r="S296" s="6">
-        <v>1</v>
-      </c>
-      <c r="T296" s="6">
-        <v>0</v>
-      </c>
-      <c r="U296" s="6">
-        <v>4</v>
-      </c>
-      <c r="V296" s="6">
-        <v>2</v>
-      </c>
+      <c r="I296" s="3"/>
+      <c r="J296" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K296" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L296" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M296" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N296" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O296" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P296" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q296" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R296" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S296" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T296" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U296" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V296" s="3"/>
       <c r="W296" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
     <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B297" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20534,61 +20541,55 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
       <c r="J297" s="3"/>
       <c r="K297" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L297" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M297" s="6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="N297" s="6">
-        <v>18</v>
-      </c>
-      <c r="O297" s="6">
-        <v>15</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O297" s="3"/>
       <c r="P297" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Q297" s="6">
+        <v>2</v>
+      </c>
+      <c r="R297" s="3"/>
+      <c r="S297" s="3"/>
+      <c r="T297" s="6">
         <v>8</v>
       </c>
-      <c r="R297" s="6">
-        <v>28</v>
-      </c>
-      <c r="S297" s="6">
-        <v>53</v>
-      </c>
-      <c r="T297" s="6">
-        <v>65</v>
-      </c>
       <c r="U297" s="6">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="V297" s="6">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20597,47 +20598,177 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>32</v>
+        <v>420</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
-      <c r="I298" s="3"/>
-      <c r="J298" s="3"/>
-      <c r="K298" s="3"/>
-      <c r="L298" s="3"/>
-      <c r="M298" s="3"/>
-      <c r="N298" s="3"/>
-      <c r="O298" s="3"/>
-      <c r="P298" s="3"/>
-      <c r="Q298" s="3"/>
-      <c r="R298" s="3"/>
-      <c r="S298" s="3"/>
+      <c r="I298" s="6">
+        <v>2</v>
+      </c>
+      <c r="J298" s="6">
+        <v>2</v>
+      </c>
+      <c r="K298" s="6">
+        <v>1</v>
+      </c>
+      <c r="L298" s="6">
+        <v>1</v>
+      </c>
+      <c r="M298" s="6">
+        <v>1</v>
+      </c>
+      <c r="N298" s="6">
+        <v>1</v>
+      </c>
+      <c r="O298" s="6">
+        <v>1</v>
+      </c>
+      <c r="P298" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q298" s="6">
+        <v>4</v>
+      </c>
+      <c r="R298" s="6">
+        <v>1</v>
+      </c>
+      <c r="S298" s="6">
+        <v>1</v>
+      </c>
       <c r="T298" s="6">
+        <v>0</v>
+      </c>
+      <c r="U298" s="6">
+        <v>4</v>
+      </c>
+      <c r="V298" s="6">
+        <v>2</v>
+      </c>
+      <c r="W298" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G299" s="3"/>
+      <c r="H299" s="3"/>
+      <c r="I299" s="3"/>
+      <c r="J299" s="3"/>
+      <c r="K299" s="6">
+        <v>5</v>
+      </c>
+      <c r="L299" s="6">
+        <v>13</v>
+      </c>
+      <c r="M299" s="6">
+        <v>19</v>
+      </c>
+      <c r="N299" s="6">
+        <v>18</v>
+      </c>
+      <c r="O299" s="6">
+        <v>15</v>
+      </c>
+      <c r="P299" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q299" s="6">
+        <v>8</v>
+      </c>
+      <c r="R299" s="6">
+        <v>28</v>
+      </c>
+      <c r="S299" s="6">
+        <v>53</v>
+      </c>
+      <c r="T299" s="6">
+        <v>65</v>
+      </c>
+      <c r="U299" s="6">
+        <v>70</v>
+      </c>
+      <c r="V299" s="6">
+        <v>69</v>
+      </c>
+      <c r="W299" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G300" s="3"/>
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+      <c r="L300" s="3"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="3"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="3"/>
+      <c r="S300" s="3"/>
+      <c r="T300" s="6">
         <v>114</v>
       </c>
-      <c r="U298" s="6">
+      <c r="U300" s="6">
         <v>61</v>
       </c>
-      <c r="V298" s="6">
+      <c r="V300" s="6">
         <v>97</v>
       </c>
-      <c r="W298" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="299" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="B300" s="8"/>
+      <c r="W300" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="B302" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A300:B300"/>
+    <mergeCell ref="A302:B302"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693E0B69-CEEE-4AF8-975B-8BAA80649F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9593D-5E76-4B79-A5CB-B0CA08559419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="439">
   <si>
     <t>sdg.gov.pl</t>
   </si>
@@ -1105,13 +1105,25 @@
     <t>odsetek stad ryb które są nadmiernie eksploatowane (overexploited) na Morzu Bałtyckim</t>
   </si>
   <si>
+    <t>14.1.b Odsetek morskich obszarów chronionych</t>
+  </si>
+  <si>
     <t>Zwiększenie udziału sektora gospodarki morskiej w PKB oraz wzrostu zatrudnienia w gospodarce morskiej</t>
   </si>
   <si>
-    <t>14.2.a Dynamika przeciętnego zatrudnienia w gospodarce morskiej (2010=100)</t>
-  </si>
-  <si>
-    <t>2010=100</t>
+    <t>14.2.a Dynamika przeciętnego zatrudnienia w gospodarce morskiej (rok poprzedni=100)</t>
+  </si>
+  <si>
+    <t>prywatny</t>
+  </si>
+  <si>
+    <t>rok poprzedni=100</t>
+  </si>
+  <si>
+    <t>publiczny</t>
+  </si>
+  <si>
+    <t>14.2.b Udział gospodarki morskiej w wartości brutto środków trwałych gospodarki narodowej</t>
   </si>
   <si>
     <t>Wzmocnienie pozycji polskich portów morskich, zwiększenie konkurencyjności transportu morskiego oraz zapewnienie bezpieczeństwa morskiego</t>
@@ -1123,6 +1135,21 @@
     <t xml:space="preserve">miliony ton [mln t] </t>
   </si>
   <si>
+    <t>14.3.b Ruch pasażerów w portach morskich (krajowy)</t>
+  </si>
+  <si>
+    <t>wg ruchu pasażerów</t>
+  </si>
+  <si>
+    <t>przyjazdy</t>
+  </si>
+  <si>
+    <t>wyjazdy</t>
+  </si>
+  <si>
+    <t>14.3.c Ruch pasażerów w portach morskich (międzynarodowy)</t>
+  </si>
+  <si>
     <t>Cel 15. Życie na lądzie</t>
   </si>
   <si>
@@ -1318,7 +1345,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 05-08-2026, 13:23</t>
+    <t>Ostatnia aktualizacja: 07-08-2026, 10:19</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W302"/>
+  <dimension ref="A1:W309"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -18327,15 +18354,15 @@
         <v>354</v>
       </c>
     </row>
-    <row r="264" spans="1:23" ht="18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:23" ht="81" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>349</v>
       </c>
       <c r="B264" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>27</v>
@@ -18344,205 +18371,183 @@
         <v>28</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="G264" s="4">
-        <v>100</v>
-      </c>
-      <c r="H264" s="4">
-        <v>100.8</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="G264" s="3"/>
+      <c r="H264" s="3"/>
       <c r="I264" s="4">
-        <v>99.9</v>
-      </c>
-      <c r="J264" s="4">
-        <v>101.8</v>
-      </c>
-      <c r="K264" s="4">
-        <v>104.9</v>
-      </c>
-      <c r="L264" s="4">
-        <v>106</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="J264" s="3"/>
+      <c r="K264" s="3"/>
+      <c r="L264" s="3"/>
       <c r="M264" s="4">
-        <v>119.9</v>
-      </c>
-      <c r="N264" s="4">
-        <v>119.4</v>
-      </c>
-      <c r="O264" s="4">
-        <v>130</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="N264" s="3"/>
+      <c r="O264" s="3"/>
       <c r="P264" s="4">
-        <v>189.5</v>
-      </c>
-      <c r="Q264" s="4">
-        <v>186.6</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="Q264" s="3"/>
       <c r="R264" s="4">
-        <v>190.1</v>
+        <v>21.9</v>
       </c>
       <c r="S264" s="4">
-        <v>200.8</v>
+        <v>21.9</v>
       </c>
       <c r="T264" s="4">
-        <v>205.6</v>
-      </c>
-      <c r="U264" s="4">
-        <v>208.5</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="U264" s="3"/>
       <c r="V264" s="3"/>
       <c r="W264" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="265" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>349</v>
       </c>
       <c r="B265" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E265" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C265" s="2" t="s">
+      <c r="F265" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E265" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F265" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="G265" s="4">
-        <v>59.5</v>
-      </c>
+      <c r="G265" s="3"/>
       <c r="H265" s="4">
-        <v>57.7</v>
+        <v>101.8</v>
       </c>
       <c r="I265" s="4">
-        <v>58.8</v>
+        <v>100</v>
       </c>
       <c r="J265" s="4">
-        <v>64.3</v>
+        <v>101.8</v>
       </c>
       <c r="K265" s="4">
-        <v>68.7</v>
+        <v>103.2</v>
       </c>
       <c r="L265" s="4">
-        <v>69.5</v>
+        <v>101.8</v>
       </c>
       <c r="M265" s="4">
-        <v>72.900000000000006</v>
+        <v>115.4</v>
       </c>
       <c r="N265" s="4">
-        <v>78.099999999999994</v>
+        <v>98.6</v>
       </c>
       <c r="O265" s="4">
-        <v>91.8</v>
+        <v>110.3</v>
       </c>
       <c r="P265" s="4">
-        <v>93.9</v>
+        <v>149.6</v>
       </c>
       <c r="Q265" s="4">
-        <v>88.5</v>
+        <v>98.5</v>
       </c>
       <c r="R265" s="4">
-        <v>96.7</v>
+        <v>102.3</v>
       </c>
       <c r="S265" s="4">
-        <v>119</v>
+        <v>106.1</v>
       </c>
       <c r="T265" s="4">
-        <v>136.4</v>
+        <v>102.7</v>
       </c>
       <c r="U265" s="4">
-        <v>124.2</v>
+        <v>101</v>
       </c>
       <c r="V265" s="3"/>
       <c r="W265" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>28</v>
+        <v>363</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G266" s="4">
-        <v>90.8</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="G266" s="3"/>
       <c r="H266" s="4">
-        <v>88.8</v>
+        <v>95.6</v>
       </c>
       <c r="I266" s="4">
-        <v>86.5</v>
+        <v>94.8</v>
       </c>
       <c r="J266" s="4">
-        <v>87</v>
+        <v>102.6</v>
       </c>
       <c r="K266" s="4">
-        <v>85</v>
+        <v>102.1</v>
       </c>
       <c r="L266" s="4">
-        <v>87.4</v>
+        <v>96.9</v>
       </c>
       <c r="M266" s="4">
-        <v>88.7</v>
+        <v>99.7</v>
       </c>
       <c r="N266" s="4">
-        <v>84.6</v>
+        <v>106.1</v>
       </c>
       <c r="O266" s="4">
-        <v>77.3</v>
+        <v>100.5</v>
       </c>
       <c r="P266" s="4">
-        <v>79.7</v>
+        <v>119</v>
       </c>
       <c r="Q266" s="4">
-        <v>81.900000000000006</v>
+        <v>98.4</v>
       </c>
       <c r="R266" s="4">
-        <v>74.8</v>
+        <v>98.1</v>
       </c>
       <c r="S266" s="4">
-        <v>77</v>
+        <v>101.5</v>
       </c>
       <c r="T266" s="4">
-        <v>77.2</v>
+        <v>98.9</v>
       </c>
       <c r="U266" s="4">
-        <v>76.3</v>
+        <v>105.5</v>
       </c>
       <c r="V266" s="3"/>
       <c r="W266" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="267" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" ht="18" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>27</v>
@@ -18553,65 +18558,65 @@
       <c r="F267" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G267" s="7">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="H267" s="7">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="I267" s="7">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="J267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="K267" s="7">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="L267" s="7">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="M267" s="7">
-        <v>0.20699999999999999</v>
-      </c>
-      <c r="N267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="O267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="P267" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="Q267" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="R267" s="7">
-        <v>0.19900000000000001</v>
-      </c>
-      <c r="S267" s="7">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="T267" s="7">
-        <v>0.192</v>
-      </c>
-      <c r="U267" s="7">
-        <v>0.192</v>
+      <c r="G267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="H267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="I267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="K267" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="L267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="M267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="O267" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="P267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="Q267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="R267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="S267" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="T267" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="U267" s="4">
+        <v>0.8</v>
       </c>
       <c r="V267" s="3"/>
       <c r="W267" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="268" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>365</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>27</v>
@@ -18620,343 +18625,351 @@
         <v>28</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>34</v>
+        <v>367</v>
       </c>
       <c r="G268" s="4">
-        <v>30.5</v>
+        <v>59.5</v>
       </c>
       <c r="H268" s="4">
-        <v>30.5</v>
+        <v>57.7</v>
       </c>
       <c r="I268" s="4">
-        <v>30.6</v>
+        <v>58.8</v>
       </c>
       <c r="J268" s="4">
-        <v>30.6</v>
+        <v>64.3</v>
       </c>
       <c r="K268" s="4">
-        <v>30.7</v>
+        <v>68.7</v>
       </c>
       <c r="L268" s="4">
-        <v>30.8</v>
+        <v>69.5</v>
       </c>
       <c r="M268" s="4">
-        <v>30.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="N268" s="4">
-        <v>30.9</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O268" s="4">
-        <v>30.9</v>
+        <v>91.8</v>
       </c>
       <c r="P268" s="4">
-        <v>30.9</v>
+        <v>93.9</v>
       </c>
       <c r="Q268" s="4">
-        <v>30.9</v>
+        <v>88.5</v>
       </c>
       <c r="R268" s="4">
-        <v>30.9</v>
+        <v>96.7</v>
       </c>
       <c r="S268" s="4">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="T268" s="4">
-        <v>31</v>
+        <v>136.4</v>
       </c>
       <c r="U268" s="4">
-        <v>31</v>
+        <v>124.2</v>
       </c>
       <c r="V268" s="3"/>
       <c r="W268" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="269" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B269" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G269" s="6">
+        <v>493249</v>
+      </c>
+      <c r="H269" s="6">
+        <v>474154</v>
+      </c>
+      <c r="I269" s="6">
+        <v>372834</v>
+      </c>
+      <c r="J269" s="6">
+        <v>302421</v>
+      </c>
+      <c r="K269" s="6">
+        <v>232736</v>
+      </c>
+      <c r="L269" s="6">
+        <v>284915</v>
+      </c>
+      <c r="M269" s="6">
+        <v>334020</v>
+      </c>
+      <c r="N269" s="6">
+        <v>279852</v>
+      </c>
+      <c r="O269" s="6">
+        <v>330941</v>
+      </c>
+      <c r="P269" s="6">
+        <v>351775</v>
+      </c>
+      <c r="Q269" s="6">
+        <v>176029</v>
+      </c>
+      <c r="R269" s="6">
+        <v>275628</v>
+      </c>
+      <c r="S269" s="6">
+        <v>257955</v>
+      </c>
+      <c r="T269" s="6">
+        <v>261424</v>
+      </c>
+      <c r="U269" s="6">
+        <v>353616</v>
+      </c>
+      <c r="V269" s="6">
+        <v>303091</v>
+      </c>
+      <c r="W269" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E270" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E269" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G269" s="6">
-        <v>28</v>
-      </c>
-      <c r="H269" s="6">
-        <v>27</v>
-      </c>
-      <c r="I269" s="6">
-        <v>26</v>
-      </c>
-      <c r="J269" s="6">
-        <v>25</v>
-      </c>
-      <c r="K269" s="6">
-        <v>24</v>
-      </c>
-      <c r="L269" s="6">
-        <v>23</v>
-      </c>
-      <c r="M269" s="6">
-        <v>22</v>
-      </c>
-      <c r="N269" s="6">
-        <v>22</v>
-      </c>
-      <c r="O269" s="6">
-        <v>22</v>
-      </c>
-      <c r="P269" s="6">
-        <v>21</v>
-      </c>
-      <c r="Q269" s="6">
-        <v>19</v>
-      </c>
-      <c r="R269" s="6">
-        <v>17</v>
-      </c>
-      <c r="S269" s="6">
-        <v>16</v>
-      </c>
-      <c r="T269" s="6">
-        <v>16</v>
-      </c>
-      <c r="U269" s="6">
-        <v>15</v>
-      </c>
-      <c r="V269" s="3"/>
-      <c r="W269" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="270" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="F270" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G270" s="4">
-        <v>64.7</v>
-      </c>
-      <c r="H270" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="I270" s="4">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="J270" s="4">
-        <v>70.3</v>
-      </c>
-      <c r="K270" s="4">
-        <v>71.5</v>
-      </c>
-      <c r="L270" s="4">
-        <v>72.7</v>
-      </c>
-      <c r="M270" s="4">
-        <v>73.5</v>
-      </c>
-      <c r="N270" s="4">
-        <v>73.599999999999994</v>
-      </c>
-      <c r="O270" s="4">
-        <v>74</v>
-      </c>
-      <c r="P270" s="4">
-        <v>74.5</v>
-      </c>
-      <c r="Q270" s="4">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="R270" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="S270" s="4">
-        <v>75.7</v>
-      </c>
-      <c r="T270" s="4">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="U270" s="4">
-        <v>76.2</v>
-      </c>
-      <c r="V270" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G270" s="6">
+        <v>485152</v>
+      </c>
+      <c r="H270" s="6">
+        <v>474731</v>
+      </c>
+      <c r="I270" s="6">
+        <v>372768</v>
+      </c>
+      <c r="J270" s="6">
+        <v>301883</v>
+      </c>
+      <c r="K270" s="6">
+        <v>233889</v>
+      </c>
+      <c r="L270" s="6">
+        <v>285054</v>
+      </c>
+      <c r="M270" s="6">
+        <v>334120</v>
+      </c>
+      <c r="N270" s="6">
+        <v>279520</v>
+      </c>
+      <c r="O270" s="6">
+        <v>330602</v>
+      </c>
+      <c r="P270" s="6">
+        <v>351685</v>
+      </c>
+      <c r="Q270" s="6">
+        <v>175421</v>
+      </c>
+      <c r="R270" s="6">
+        <v>276413</v>
+      </c>
+      <c r="S270" s="6">
+        <v>262425</v>
+      </c>
+      <c r="T270" s="6">
+        <v>256157</v>
+      </c>
+      <c r="U270" s="6">
+        <v>346671</v>
+      </c>
+      <c r="V270" s="6">
+        <v>299556</v>
+      </c>
       <c r="W270" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="271" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>37</v>
+        <v>369</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>39</v>
+        <v>370</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G271" s="4">
-        <v>88</v>
-      </c>
-      <c r="H271" s="4">
-        <v>88.4</v>
-      </c>
-      <c r="I271" s="4">
-        <v>91.7</v>
-      </c>
-      <c r="J271" s="4">
-        <v>93.3</v>
-      </c>
-      <c r="K271" s="4">
-        <v>93.9</v>
-      </c>
-      <c r="L271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="M271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="N271" s="4">
-        <v>94.5</v>
-      </c>
-      <c r="O271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="P271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="Q271" s="4">
-        <v>94.7</v>
-      </c>
-      <c r="R271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="S271" s="4">
-        <v>95</v>
-      </c>
-      <c r="T271" s="4">
-        <v>94.8</v>
-      </c>
-      <c r="U271" s="4">
-        <v>94.6</v>
-      </c>
-      <c r="V271" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G271" s="6">
+        <v>759502</v>
+      </c>
+      <c r="H271" s="6">
+        <v>781353</v>
+      </c>
+      <c r="I271" s="6">
+        <v>802702</v>
+      </c>
+      <c r="J271" s="6">
+        <v>787070</v>
+      </c>
+      <c r="K271" s="6">
+        <v>875518</v>
+      </c>
+      <c r="L271" s="6">
+        <v>919666</v>
+      </c>
+      <c r="M271" s="6">
+        <v>962501</v>
+      </c>
+      <c r="N271" s="6">
+        <v>1011758</v>
+      </c>
+      <c r="O271" s="6">
+        <v>1029218</v>
+      </c>
+      <c r="P271" s="6">
+        <v>1057440</v>
+      </c>
+      <c r="Q271" s="6">
+        <v>780543</v>
+      </c>
+      <c r="R271" s="6">
+        <v>882463</v>
+      </c>
+      <c r="S271" s="6">
+        <v>885794</v>
+      </c>
+      <c r="T271" s="6">
+        <v>871811</v>
+      </c>
+      <c r="U271" s="6">
+        <v>872944</v>
+      </c>
+      <c r="V271" s="6">
+        <v>884918</v>
+      </c>
       <c r="W271" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="272" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B272" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E272" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C272" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E272" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="F272" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G272" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="H272" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="I272" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="J272" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="K272" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="L272" s="4">
-        <v>39.6</v>
-      </c>
-      <c r="M272" s="4">
-        <v>41.2</v>
-      </c>
-      <c r="N272" s="4">
-        <v>42</v>
-      </c>
-      <c r="O272" s="4">
-        <v>42.9</v>
-      </c>
-      <c r="P272" s="4">
-        <v>44</v>
-      </c>
-      <c r="Q272" s="4">
-        <v>45.4</v>
-      </c>
-      <c r="R272" s="4">
-        <v>46.5</v>
-      </c>
-      <c r="S272" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="T272" s="4">
-        <v>48.2</v>
-      </c>
-      <c r="U272" s="4">
-        <v>49.3</v>
-      </c>
-      <c r="V272" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="G272" s="6">
+        <v>781553</v>
+      </c>
+      <c r="H272" s="6">
+        <v>802785</v>
+      </c>
+      <c r="I272" s="6">
+        <v>809836</v>
+      </c>
+      <c r="J272" s="6">
+        <v>809712</v>
+      </c>
+      <c r="K272" s="6">
+        <v>878045</v>
+      </c>
+      <c r="L272" s="6">
+        <v>931632</v>
+      </c>
+      <c r="M272" s="6">
+        <v>970959</v>
+      </c>
+      <c r="N272" s="6">
+        <v>1013639</v>
+      </c>
+      <c r="O272" s="6">
+        <v>1029660</v>
+      </c>
+      <c r="P272" s="6">
+        <v>1026283</v>
+      </c>
+      <c r="Q272" s="6">
+        <v>773182</v>
+      </c>
+      <c r="R272" s="6">
+        <v>881969</v>
+      </c>
+      <c r="S272" s="6">
+        <v>929215</v>
+      </c>
+      <c r="T272" s="6">
+        <v>862113</v>
+      </c>
+      <c r="U272" s="6">
+        <v>853481</v>
+      </c>
+      <c r="V272" s="6">
+        <v>873943</v>
+      </c>
       <c r="W272" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="273" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>27</v>
@@ -18965,67 +18978,67 @@
         <v>28</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>34</v>
+        <v>376</v>
       </c>
       <c r="G273" s="4">
-        <v>65.7</v>
+        <v>90.8</v>
       </c>
       <c r="H273" s="4">
-        <v>64.8</v>
+        <v>88.8</v>
       </c>
       <c r="I273" s="4">
-        <v>67.400000000000006</v>
+        <v>86.5</v>
       </c>
       <c r="J273" s="4">
-        <v>69.8</v>
+        <v>87</v>
       </c>
       <c r="K273" s="4">
-        <v>70.5</v>
+        <v>85</v>
       </c>
       <c r="L273" s="4">
-        <v>70.900000000000006</v>
+        <v>87.4</v>
       </c>
       <c r="M273" s="4">
-        <v>71.400000000000006</v>
+        <v>88.7</v>
       </c>
       <c r="N273" s="4">
-        <v>72.5</v>
+        <v>84.6</v>
       </c>
       <c r="O273" s="4">
-        <v>73.2</v>
+        <v>77.3</v>
       </c>
       <c r="P273" s="4">
-        <v>73.900000000000006</v>
+        <v>79.7</v>
       </c>
       <c r="Q273" s="4">
-        <v>73.3</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="R273" s="4">
-        <v>72.8</v>
+        <v>74.8</v>
       </c>
       <c r="S273" s="4">
+        <v>77</v>
+      </c>
+      <c r="T273" s="4">
+        <v>77.2</v>
+      </c>
+      <c r="U273" s="4">
         <v>76.3</v>
-      </c>
-      <c r="T273" s="4">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="U273" s="4">
-        <v>78.599999999999994</v>
       </c>
       <c r="V273" s="3"/>
       <c r="W273" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="274" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="274" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>27</v>
@@ -19034,67 +19047,67 @@
         <v>28</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G274" s="6">
-        <v>70108</v>
-      </c>
-      <c r="H274" s="6">
-        <v>248240</v>
-      </c>
-      <c r="I274" s="6">
-        <v>168221</v>
-      </c>
-      <c r="J274" s="6">
-        <v>72837</v>
-      </c>
-      <c r="K274" s="6">
-        <v>64283</v>
-      </c>
-      <c r="L274" s="6">
-        <v>68694</v>
-      </c>
-      <c r="M274" s="6">
-        <v>60135</v>
-      </c>
-      <c r="N274" s="6">
-        <v>46337</v>
-      </c>
-      <c r="O274" s="6">
-        <v>50289</v>
-      </c>
-      <c r="P274" s="6">
-        <v>104107</v>
-      </c>
-      <c r="Q274" s="6">
-        <v>201963</v>
-      </c>
-      <c r="R274" s="6">
-        <v>84506</v>
-      </c>
-      <c r="S274" s="6">
-        <v>295948</v>
-      </c>
-      <c r="T274" s="6">
-        <v>123796</v>
-      </c>
-      <c r="U274" s="6">
-        <v>104040</v>
+        <v>34</v>
+      </c>
+      <c r="G274" s="7">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="H274" s="7">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="I274" s="7">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="J274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="K274" s="7">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="L274" s="7">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="M274" s="7">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="N274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="O274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P274" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="Q274" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R274" s="7">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="S274" s="7">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T274" s="7">
+        <v>0.192</v>
+      </c>
+      <c r="U274" s="7">
+        <v>0.192</v>
       </c>
       <c r="V274" s="3"/>
       <c r="W274" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="275" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="275" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>27</v>
@@ -19106,58 +19119,58 @@
         <v>34</v>
       </c>
       <c r="G275" s="4">
-        <v>2.9</v>
+        <v>30.5</v>
       </c>
       <c r="H275" s="4">
-        <v>3.8</v>
+        <v>30.5</v>
       </c>
       <c r="I275" s="4">
-        <v>6</v>
+        <v>30.6</v>
       </c>
       <c r="J275" s="4">
-        <v>4.3</v>
+        <v>30.6</v>
       </c>
       <c r="K275" s="4">
-        <v>4.5999999999999996</v>
+        <v>30.7</v>
       </c>
       <c r="L275" s="4">
-        <v>4.2</v>
+        <v>30.8</v>
       </c>
       <c r="M275" s="4">
-        <v>3.1</v>
+        <v>30.8</v>
       </c>
       <c r="N275" s="4">
-        <v>3</v>
+        <v>30.9</v>
       </c>
       <c r="O275" s="4">
-        <v>3.2</v>
+        <v>30.9</v>
       </c>
       <c r="P275" s="4">
-        <v>3.4</v>
+        <v>30.9</v>
       </c>
       <c r="Q275" s="4">
-        <v>3.2</v>
+        <v>30.9</v>
       </c>
       <c r="R275" s="4">
-        <v>4.5</v>
+        <v>30.9</v>
       </c>
       <c r="S275" s="4">
-        <v>6.6</v>
+        <v>31</v>
       </c>
       <c r="T275" s="4">
-        <v>5.8</v>
+        <v>31</v>
       </c>
       <c r="U275" s="4">
-        <v>4.5</v>
+        <v>31</v>
       </c>
       <c r="V275" s="3"/>
       <c r="W275" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="276" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>380</v>
@@ -19172,72 +19185,70 @@
         <v>28</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="G276" s="6">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="H276" s="6">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="I276" s="6">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="J276" s="6">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="K276" s="6">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="L276" s="6">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M276" s="6">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="N276" s="6">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="O276" s="6">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="P276" s="6">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="Q276" s="6">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="R276" s="6">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="S276" s="6">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="T276" s="6">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="U276" s="6">
-        <v>88</v>
-      </c>
-      <c r="V276" s="6">
-        <v>86</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="V276" s="3"/>
       <c r="W276" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="277" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="277" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>380</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>28</v>
@@ -19245,163 +19256,203 @@
       <c r="F277" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G277" s="6">
-        <v>55</v>
-      </c>
-      <c r="H277" s="3"/>
-      <c r="I277" s="6">
-        <v>58</v>
-      </c>
-      <c r="J277" s="3"/>
-      <c r="K277" s="6">
-        <v>60</v>
-      </c>
-      <c r="L277" s="3"/>
-      <c r="M277" s="6">
-        <v>64</v>
-      </c>
-      <c r="N277" s="3"/>
-      <c r="O277" s="6">
-        <v>65</v>
-      </c>
-      <c r="P277" s="3"/>
-      <c r="Q277" s="6">
+      <c r="G277" s="4">
+        <v>64.7</v>
+      </c>
+      <c r="H277" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="I277" s="4">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="J277" s="4">
+        <v>70.3</v>
+      </c>
+      <c r="K277" s="4">
+        <v>71.5</v>
+      </c>
+      <c r="L277" s="4">
+        <v>72.7</v>
+      </c>
+      <c r="M277" s="4">
+        <v>73.5</v>
+      </c>
+      <c r="N277" s="4">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="O277" s="4">
         <v>74</v>
       </c>
-      <c r="R277" s="3"/>
-      <c r="S277" s="6">
-        <v>63</v>
-      </c>
-      <c r="T277" s="3"/>
-      <c r="U277" s="6">
-        <v>71</v>
+      <c r="P277" s="4">
+        <v>74.5</v>
+      </c>
+      <c r="Q277" s="4">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="R277" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="S277" s="4">
+        <v>75.7</v>
+      </c>
+      <c r="T277" s="4">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="U277" s="4">
+        <v>76.2</v>
       </c>
       <c r="V277" s="3"/>
       <c r="W277" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="278" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="278" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>380</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G278" s="3"/>
-      <c r="H278" s="3"/>
-      <c r="I278" s="3"/>
-      <c r="J278" s="3"/>
-      <c r="K278" s="3"/>
-      <c r="L278" s="3"/>
-      <c r="M278" s="3"/>
-      <c r="N278" s="3"/>
-      <c r="O278" s="3"/>
-      <c r="P278" s="3"/>
-      <c r="Q278" s="3"/>
-      <c r="R278" s="3"/>
-      <c r="S278" s="5">
-        <v>33109.31</v>
-      </c>
-      <c r="T278" s="5">
-        <v>33829.39</v>
-      </c>
-      <c r="U278" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G278" s="4">
+        <v>88</v>
+      </c>
+      <c r="H278" s="4">
+        <v>88.4</v>
+      </c>
+      <c r="I278" s="4">
+        <v>91.7</v>
+      </c>
+      <c r="J278" s="4">
+        <v>93.3</v>
+      </c>
+      <c r="K278" s="4">
+        <v>93.9</v>
+      </c>
+      <c r="L278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="M278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="N278" s="4">
+        <v>94.5</v>
+      </c>
+      <c r="O278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="P278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="Q278" s="4">
+        <v>94.7</v>
+      </c>
+      <c r="R278" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="S278" s="4">
+        <v>95</v>
+      </c>
+      <c r="T278" s="4">
+        <v>94.8</v>
+      </c>
+      <c r="U278" s="4">
+        <v>94.6</v>
+      </c>
       <c r="V278" s="3"/>
       <c r="W278" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="279" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="279" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G279" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="H279" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="I279" s="5">
-        <v>1</v>
-      </c>
-      <c r="J279" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="K279" s="5">
-        <v>1.06</v>
-      </c>
-      <c r="L279" s="5">
-        <v>0.95</v>
-      </c>
-      <c r="M279" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="N279" s="5">
-        <v>0.81</v>
-      </c>
-      <c r="O279" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="P279" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="Q279" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="R279" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="S279" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="T279" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="U279" s="5">
-        <v>0.69</v>
+        <v>34</v>
+      </c>
+      <c r="G279" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="H279" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="I279" s="4">
+        <v>33.1</v>
+      </c>
+      <c r="J279" s="4">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K279" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="L279" s="4">
+        <v>39.6</v>
+      </c>
+      <c r="M279" s="4">
+        <v>41.2</v>
+      </c>
+      <c r="N279" s="4">
+        <v>42</v>
+      </c>
+      <c r="O279" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="P279" s="4">
+        <v>44</v>
+      </c>
+      <c r="Q279" s="4">
+        <v>45.4</v>
+      </c>
+      <c r="R279" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="S279" s="4">
+        <v>47.2</v>
+      </c>
+      <c r="T279" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="U279" s="4">
+        <v>49.3</v>
       </c>
       <c r="V279" s="3"/>
       <c r="W279" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="280" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="280" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>27</v>
@@ -19410,67 +19461,67 @@
         <v>28</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G280" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="H280" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="I280" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="J280" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="K280" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="L280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="M280" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="N280" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="O280" s="5">
-        <v>2</v>
-      </c>
-      <c r="P280" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="Q280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="R280" s="5">
-        <v>2.19</v>
-      </c>
-      <c r="S280" s="5">
-        <v>2.21</v>
-      </c>
-      <c r="T280" s="5">
-        <v>3.27</v>
-      </c>
-      <c r="U280" s="5">
-        <v>4.07</v>
+        <v>34</v>
+      </c>
+      <c r="G280" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="H280" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="I280" s="4">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="J280" s="4">
+        <v>69.8</v>
+      </c>
+      <c r="K280" s="4">
+        <v>70.5</v>
+      </c>
+      <c r="L280" s="4">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="M280" s="4">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="N280" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="O280" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="P280" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="Q280" s="4">
+        <v>73.3</v>
+      </c>
+      <c r="R280" s="4">
+        <v>72.8</v>
+      </c>
+      <c r="S280" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="T280" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="U280" s="4">
+        <v>78.599999999999994</v>
       </c>
       <c r="V280" s="3"/>
       <c r="W280" s="2" t="s">
-        <v>389</v>
+        <v>30</v>
       </c>
     </row>
     <row r="281" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>27</v>
@@ -19479,44 +19530,70 @@
         <v>28</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G281" s="3"/>
-      <c r="H281" s="3"/>
-      <c r="I281" s="3"/>
-      <c r="J281" s="3"/>
-      <c r="K281" s="3"/>
-      <c r="L281" s="3"/>
-      <c r="M281" s="3"/>
-      <c r="N281" s="3"/>
-      <c r="O281" s="3"/>
-      <c r="P281" s="3"/>
-      <c r="Q281" s="3"/>
-      <c r="R281" s="3"/>
-      <c r="S281" s="3"/>
-      <c r="T281" s="3"/>
-      <c r="U281" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="V281" s="4">
-        <v>51.3</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="G281" s="6">
+        <v>70108</v>
+      </c>
+      <c r="H281" s="6">
+        <v>248240</v>
+      </c>
+      <c r="I281" s="6">
+        <v>168221</v>
+      </c>
+      <c r="J281" s="6">
+        <v>72837</v>
+      </c>
+      <c r="K281" s="6">
+        <v>64283</v>
+      </c>
+      <c r="L281" s="6">
+        <v>68694</v>
+      </c>
+      <c r="M281" s="6">
+        <v>60135</v>
+      </c>
+      <c r="N281" s="6">
+        <v>46337</v>
+      </c>
+      <c r="O281" s="6">
+        <v>50289</v>
+      </c>
+      <c r="P281" s="6">
+        <v>104107</v>
+      </c>
+      <c r="Q281" s="6">
+        <v>201963</v>
+      </c>
+      <c r="R281" s="6">
+        <v>84506</v>
+      </c>
+      <c r="S281" s="6">
+        <v>295948</v>
+      </c>
+      <c r="T281" s="6">
+        <v>123796</v>
+      </c>
+      <c r="U281" s="6">
+        <v>104040</v>
+      </c>
+      <c r="V281" s="3"/>
       <c r="W281" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="282" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>28</v>
@@ -19525,478 +19602,400 @@
         <v>34</v>
       </c>
       <c r="G282" s="4">
-        <v>28.1</v>
+        <v>2.9</v>
       </c>
       <c r="H282" s="4">
-        <v>27.6</v>
+        <v>3.8</v>
       </c>
       <c r="I282" s="4">
-        <v>31.6</v>
+        <v>6</v>
       </c>
       <c r="J282" s="4">
-        <v>22.6</v>
+        <v>4.3</v>
       </c>
       <c r="K282" s="4">
-        <v>26.9</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="L282" s="4">
-        <v>26.6</v>
+        <v>4.2</v>
       </c>
       <c r="M282" s="4">
-        <v>30.2</v>
+        <v>3.1</v>
       </c>
       <c r="N282" s="4">
-        <v>30.8</v>
+        <v>3</v>
       </c>
       <c r="O282" s="4">
-        <v>35.5</v>
+        <v>3.2</v>
       </c>
       <c r="P282" s="4">
-        <v>40.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q282" s="4">
-        <v>41.9</v>
+        <v>3.2</v>
       </c>
       <c r="R282" s="4">
-        <v>47.5</v>
+        <v>4.5</v>
       </c>
       <c r="S282" s="4">
-        <v>55.4</v>
+        <v>6.6</v>
       </c>
       <c r="T282" s="4">
-        <v>58.5</v>
+        <v>5.8</v>
       </c>
       <c r="U282" s="4">
-        <v>61</v>
-      </c>
-      <c r="V282" s="4">
-        <v>61.1</v>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="V282" s="3"/>
       <c r="W282" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="283" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B283" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C283" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="D283" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>393</v>
+        <v>28</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G283" s="4">
-        <v>31.5</v>
-      </c>
-      <c r="H283" s="4">
-        <v>27.9</v>
-      </c>
-      <c r="I283" s="4">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="J283" s="4">
-        <v>20.2</v>
-      </c>
-      <c r="K283" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="L283" s="4">
-        <v>20.8</v>
-      </c>
-      <c r="M283" s="4">
-        <v>20.5</v>
-      </c>
-      <c r="N283" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="O283" s="4">
-        <v>29.5</v>
-      </c>
-      <c r="P283" s="4">
-        <v>29.8</v>
-      </c>
-      <c r="Q283" s="4">
-        <v>30.9</v>
-      </c>
-      <c r="R283" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="S283" s="4">
-        <v>42.1</v>
-      </c>
-      <c r="T283" s="4">
-        <v>44</v>
-      </c>
-      <c r="U283" s="4">
-        <v>47.7</v>
-      </c>
-      <c r="V283" s="4">
-        <v>48.9</v>
+      <c r="G283" s="6">
+        <v>70</v>
+      </c>
+      <c r="H283" s="6">
+        <v>75</v>
+      </c>
+      <c r="I283" s="6">
+        <v>66</v>
+      </c>
+      <c r="J283" s="6">
+        <v>64</v>
+      </c>
+      <c r="K283" s="6">
+        <v>70</v>
+      </c>
+      <c r="L283" s="6">
+        <v>66</v>
+      </c>
+      <c r="M283" s="6">
+        <v>80</v>
+      </c>
+      <c r="N283" s="6">
+        <v>89</v>
+      </c>
+      <c r="O283" s="6">
+        <v>86</v>
+      </c>
+      <c r="P283" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q283" s="6">
+        <v>85</v>
+      </c>
+      <c r="R283" s="6">
+        <v>82</v>
+      </c>
+      <c r="S283" s="6">
+        <v>83</v>
+      </c>
+      <c r="T283" s="6">
+        <v>88</v>
+      </c>
+      <c r="U283" s="6">
+        <v>88</v>
+      </c>
+      <c r="V283" s="6">
+        <v>86</v>
       </c>
       <c r="W283" s="2" t="s">
-        <v>30</v>
+        <v>391</v>
       </c>
     </row>
     <row r="284" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>392</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G284" s="4">
-        <v>47.6</v>
-      </c>
-      <c r="H284" s="4">
-        <v>46.2</v>
-      </c>
-      <c r="I284" s="4">
-        <v>50.6</v>
-      </c>
-      <c r="J284" s="4">
-        <v>39</v>
-      </c>
-      <c r="K284" s="4">
-        <v>46</v>
-      </c>
-      <c r="L284" s="4">
-        <v>45</v>
-      </c>
-      <c r="M284" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="N284" s="4">
-        <v>48.1</v>
-      </c>
-      <c r="O284" s="4">
-        <v>53</v>
-      </c>
-      <c r="P284" s="4">
-        <v>58.6</v>
-      </c>
-      <c r="Q284" s="4">
-        <v>59.9</v>
-      </c>
-      <c r="R284" s="4">
-        <v>68.3</v>
-      </c>
-      <c r="S284" s="4">
-        <v>75.2</v>
-      </c>
-      <c r="T284" s="4">
-        <v>81</v>
-      </c>
-      <c r="U284" s="4">
-        <v>81.2</v>
-      </c>
-      <c r="V284" s="4">
-        <v>81.8</v>
-      </c>
+      <c r="G284" s="6">
+        <v>55</v>
+      </c>
+      <c r="H284" s="3"/>
+      <c r="I284" s="6">
+        <v>58</v>
+      </c>
+      <c r="J284" s="3"/>
+      <c r="K284" s="6">
+        <v>60</v>
+      </c>
+      <c r="L284" s="3"/>
+      <c r="M284" s="6">
+        <v>64</v>
+      </c>
+      <c r="N284" s="3"/>
+      <c r="O284" s="6">
+        <v>65</v>
+      </c>
+      <c r="P284" s="3"/>
+      <c r="Q284" s="6">
+        <v>74</v>
+      </c>
+      <c r="R284" s="3"/>
+      <c r="S284" s="6">
+        <v>63</v>
+      </c>
+      <c r="T284" s="3"/>
+      <c r="U284" s="6">
+        <v>71</v>
+      </c>
+      <c r="V284" s="3"/>
       <c r="W284" s="2" t="s">
-        <v>30</v>
+        <v>391</v>
       </c>
     </row>
     <row r="285" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G285" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="H285" s="4">
-        <v>36.9</v>
-      </c>
-      <c r="I285" s="4">
-        <v>45.3</v>
-      </c>
-      <c r="J285" s="4">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="K285" s="4">
-        <v>40.1</v>
-      </c>
-      <c r="L285" s="4">
-        <v>38.6</v>
-      </c>
-      <c r="M285" s="4">
-        <v>40.5</v>
-      </c>
-      <c r="N285" s="4">
-        <v>45</v>
-      </c>
-      <c r="O285" s="4">
-        <v>49.6</v>
-      </c>
-      <c r="P285" s="4">
-        <v>57.6</v>
-      </c>
-      <c r="Q285" s="4">
-        <v>59.4</v>
-      </c>
-      <c r="R285" s="4">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="S285" s="4">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="T285" s="4">
-        <v>78.3</v>
-      </c>
-      <c r="U285" s="4">
-        <v>81.099999999999994</v>
-      </c>
-      <c r="V285" s="4">
-        <v>78.3</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="G285" s="3"/>
+      <c r="H285" s="3"/>
+      <c r="I285" s="3"/>
+      <c r="J285" s="3"/>
+      <c r="K285" s="3"/>
+      <c r="L285" s="3"/>
+      <c r="M285" s="3"/>
+      <c r="N285" s="3"/>
+      <c r="O285" s="3"/>
+      <c r="P285" s="3"/>
+      <c r="Q285" s="3"/>
+      <c r="R285" s="3"/>
+      <c r="S285" s="5">
+        <v>33109.31</v>
+      </c>
+      <c r="T285" s="5">
+        <v>33829.39</v>
+      </c>
+      <c r="U285" s="3"/>
+      <c r="V285" s="3"/>
       <c r="W285" s="2" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
     </row>
     <row r="286" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>396</v>
+        <v>28</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G286" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="H286" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="I286" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="J286" s="4">
-        <v>21.5</v>
-      </c>
-      <c r="K286" s="4">
-        <v>26.2</v>
-      </c>
-      <c r="L286" s="4">
-        <v>26</v>
-      </c>
-      <c r="M286" s="4">
-        <v>30</v>
-      </c>
-      <c r="N286" s="4">
-        <v>28</v>
-      </c>
-      <c r="O286" s="4">
-        <v>35</v>
-      </c>
-      <c r="P286" s="4">
-        <v>41.4</v>
-      </c>
-      <c r="Q286" s="4">
-        <v>45.1</v>
-      </c>
-      <c r="R286" s="4">
-        <v>51.7</v>
-      </c>
-      <c r="S286" s="4">
-        <v>62.4</v>
-      </c>
-      <c r="T286" s="4">
-        <v>65.7</v>
-      </c>
-      <c r="U286" s="4">
-        <v>68.8</v>
-      </c>
-      <c r="V286" s="4">
-        <v>69.900000000000006</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G286" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H286" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="I286" s="5">
+        <v>1</v>
+      </c>
+      <c r="J286" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="K286" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="L286" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="M286" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="N286" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="O286" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="P286" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="Q286" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="R286" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="S286" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="T286" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="U286" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="V286" s="3"/>
       <c r="W286" s="2" t="s">
-        <v>30</v>
+        <v>204</v>
       </c>
     </row>
     <row r="287" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G287" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="H287" s="4">
-        <v>15.7</v>
-      </c>
-      <c r="I287" s="4">
-        <v>17.2</v>
-      </c>
-      <c r="J287" s="4">
-        <v>12.7</v>
-      </c>
-      <c r="K287" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="L287" s="4">
-        <v>18.3</v>
-      </c>
-      <c r="M287" s="4">
-        <v>19.8</v>
-      </c>
-      <c r="N287" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="O287" s="4">
-        <v>22.4</v>
-      </c>
-      <c r="P287" s="4">
-        <v>28.5</v>
-      </c>
-      <c r="Q287" s="4">
-        <v>29.4</v>
-      </c>
-      <c r="R287" s="4">
-        <v>35</v>
-      </c>
-      <c r="S287" s="4">
-        <v>39.5</v>
-      </c>
-      <c r="T287" s="4">
-        <v>44.4</v>
-      </c>
-      <c r="U287" s="4">
-        <v>50.8</v>
-      </c>
-      <c r="V287" s="4">
-        <v>51.4</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="G287" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="H287" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="I287" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="J287" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="K287" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="L287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="M287" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="N287" s="5">
+        <v>1.88</v>
+      </c>
+      <c r="O287" s="5">
+        <v>2</v>
+      </c>
+      <c r="P287" s="5">
+        <v>1.96</v>
+      </c>
+      <c r="Q287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="R287" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="S287" s="5">
+        <v>2.21</v>
+      </c>
+      <c r="T287" s="5">
+        <v>3.27</v>
+      </c>
+      <c r="U287" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="V287" s="3"/>
       <c r="W287" s="2" t="s">
-        <v>30</v>
+        <v>398</v>
       </c>
     </row>
     <row r="288" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G288" s="4">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="H288" s="4">
-        <v>5</v>
-      </c>
-      <c r="I288" s="4">
-        <v>6.8</v>
-      </c>
-      <c r="J288" s="4">
-        <v>3.7</v>
-      </c>
-      <c r="K288" s="4">
-        <v>6.6</v>
-      </c>
-      <c r="L288" s="4">
-        <v>6</v>
-      </c>
-      <c r="M288" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="N288" s="4">
-        <v>8.4</v>
-      </c>
-      <c r="O288" s="4">
-        <v>10.9</v>
-      </c>
-      <c r="P288" s="4">
-        <v>12.2</v>
-      </c>
-      <c r="Q288" s="4">
-        <v>13.5</v>
-      </c>
-      <c r="R288" s="4">
-        <v>15.8</v>
-      </c>
-      <c r="S288" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="T288" s="4">
-        <v>26.1</v>
-      </c>
+      <c r="G288" s="3"/>
+      <c r="H288" s="3"/>
+      <c r="I288" s="3"/>
+      <c r="J288" s="3"/>
+      <c r="K288" s="3"/>
+      <c r="L288" s="3"/>
+      <c r="M288" s="3"/>
+      <c r="N288" s="3"/>
+      <c r="O288" s="3"/>
+      <c r="P288" s="3"/>
+      <c r="Q288" s="3"/>
+      <c r="R288" s="3"/>
+      <c r="S288" s="3"/>
+      <c r="T288" s="3"/>
       <c r="U288" s="4">
-        <v>27.4</v>
+        <v>30.2</v>
       </c>
       <c r="V288" s="4">
-        <v>27.6</v>
+        <v>51.3</v>
       </c>
       <c r="W288" s="2" t="s">
         <v>30</v>
@@ -20004,16 +20003,16 @@
     </row>
     <row r="289" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>28</v>
@@ -20022,454 +20021,492 @@
         <v>34</v>
       </c>
       <c r="G289" s="4">
-        <v>5.7</v>
+        <v>28.1</v>
       </c>
       <c r="H289" s="4">
-        <v>6</v>
+        <v>27.6</v>
       </c>
       <c r="I289" s="4">
-        <v>4.9000000000000004</v>
+        <v>31.6</v>
       </c>
       <c r="J289" s="4">
-        <v>4.3</v>
+        <v>22.6</v>
       </c>
       <c r="K289" s="4">
-        <v>4.7</v>
+        <v>26.9</v>
       </c>
       <c r="L289" s="4">
-        <v>4.5</v>
+        <v>26.6</v>
       </c>
       <c r="M289" s="4">
-        <v>3.3</v>
+        <v>30.2</v>
       </c>
       <c r="N289" s="4">
-        <v>3.8</v>
+        <v>30.8</v>
       </c>
       <c r="O289" s="4">
-        <v>4.5999999999999996</v>
+        <v>35.5</v>
       </c>
       <c r="P289" s="4">
-        <v>4.3</v>
+        <v>40.4</v>
       </c>
       <c r="Q289" s="4">
-        <v>4.4000000000000004</v>
+        <v>41.9</v>
       </c>
       <c r="R289" s="4">
-        <v>4.0999999999999996</v>
+        <v>47.5</v>
       </c>
       <c r="S289" s="4">
-        <v>3.8</v>
+        <v>55.4</v>
       </c>
       <c r="T289" s="4">
-        <v>5.0999999999999996</v>
+        <v>58.5</v>
       </c>
       <c r="U289" s="4">
-        <v>4.8</v>
+        <v>61</v>
       </c>
       <c r="V289" s="4">
-        <v>5.2</v>
+        <v>61.1</v>
       </c>
       <c r="W289" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="290" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>401</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>28</v>
+        <v>402</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G290" s="6">
-        <v>674</v>
-      </c>
-      <c r="H290" s="6">
-        <v>605</v>
-      </c>
-      <c r="I290" s="6">
-        <v>1082</v>
-      </c>
-      <c r="J290" s="6">
-        <v>1219</v>
-      </c>
-      <c r="K290" s="6">
-        <v>1282</v>
-      </c>
-      <c r="L290" s="6">
-        <v>1456</v>
-      </c>
-      <c r="M290" s="6">
-        <v>1926</v>
-      </c>
-      <c r="N290" s="6">
-        <v>3182</v>
-      </c>
-      <c r="O290" s="6">
-        <v>3739</v>
-      </c>
-      <c r="P290" s="6">
-        <v>6484</v>
-      </c>
-      <c r="Q290" s="6">
-        <v>10420</v>
-      </c>
-      <c r="R290" s="6">
-        <v>29483</v>
-      </c>
-      <c r="S290" s="6">
-        <v>39683</v>
-      </c>
-      <c r="T290" s="6">
-        <v>80267</v>
-      </c>
-      <c r="U290" s="6">
-        <v>103449</v>
-      </c>
-      <c r="V290" s="6">
-        <v>260783</v>
+        <v>34</v>
+      </c>
+      <c r="G290" s="4">
+        <v>31.5</v>
+      </c>
+      <c r="H290" s="4">
+        <v>27.9</v>
+      </c>
+      <c r="I290" s="4">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="J290" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="K290" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="L290" s="4">
+        <v>20.8</v>
+      </c>
+      <c r="M290" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="N290" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="O290" s="4">
+        <v>29.5</v>
+      </c>
+      <c r="P290" s="4">
+        <v>29.8</v>
+      </c>
+      <c r="Q290" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="R290" s="4">
+        <v>35.6</v>
+      </c>
+      <c r="S290" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="T290" s="4">
+        <v>44</v>
+      </c>
+      <c r="U290" s="4">
+        <v>47.7</v>
+      </c>
+      <c r="V290" s="4">
+        <v>48.9</v>
       </c>
       <c r="W290" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="291" spans="1:23" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="291" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E291" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G291" s="3"/>
-      <c r="H291" s="3"/>
-      <c r="I291" s="3"/>
-      <c r="J291" s="3"/>
-      <c r="K291" s="3"/>
-      <c r="L291" s="3"/>
-      <c r="M291" s="3"/>
-      <c r="N291" s="3"/>
-      <c r="O291" s="3"/>
-      <c r="P291" s="3"/>
-      <c r="Q291" s="3"/>
-      <c r="R291" s="5">
-        <v>18.93</v>
-      </c>
-      <c r="S291" s="3"/>
-      <c r="T291" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="U291" s="3"/>
-      <c r="V291" s="5">
-        <v>23.01</v>
+      <c r="G291" s="4">
+        <v>47.6</v>
+      </c>
+      <c r="H291" s="4">
+        <v>46.2</v>
+      </c>
+      <c r="I291" s="4">
+        <v>50.6</v>
+      </c>
+      <c r="J291" s="4">
+        <v>39</v>
+      </c>
+      <c r="K291" s="4">
+        <v>46</v>
+      </c>
+      <c r="L291" s="4">
+        <v>45</v>
+      </c>
+      <c r="M291" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="N291" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="O291" s="4">
+        <v>53</v>
+      </c>
+      <c r="P291" s="4">
+        <v>58.6</v>
+      </c>
+      <c r="Q291" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="R291" s="4">
+        <v>68.3</v>
+      </c>
+      <c r="S291" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="T291" s="4">
+        <v>81</v>
+      </c>
+      <c r="U291" s="4">
+        <v>81.2</v>
+      </c>
+      <c r="V291" s="4">
+        <v>81.8</v>
       </c>
       <c r="W291" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="292" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E292" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B292" s="2" t="s">
+      <c r="F292" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G292" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="H292" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="I292" s="4">
+        <v>45.3</v>
+      </c>
+      <c r="J292" s="4">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="K292" s="4">
+        <v>40.1</v>
+      </c>
+      <c r="L292" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="M292" s="4">
+        <v>40.5</v>
+      </c>
+      <c r="N292" s="4">
+        <v>45</v>
+      </c>
+      <c r="O292" s="4">
+        <v>49.6</v>
+      </c>
+      <c r="P292" s="4">
+        <v>57.6</v>
+      </c>
+      <c r="Q292" s="4">
+        <v>59.4</v>
+      </c>
+      <c r="R292" s="4">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="S292" s="4">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T292" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="U292" s="4">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="V292" s="4">
+        <v>78.3</v>
+      </c>
+      <c r="W292" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="293" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E293" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C292" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E292" s="3" t="s">
+      <c r="F293" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G293" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="H293" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="I293" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="J293" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="K293" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="L293" s="4">
+        <v>26</v>
+      </c>
+      <c r="M293" s="4">
+        <v>30</v>
+      </c>
+      <c r="N293" s="4">
         <v>28</v>
       </c>
-      <c r="F292" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G292" s="5">
-        <v>377.75</v>
-      </c>
-      <c r="H292" s="5">
-        <v>417.47</v>
-      </c>
-      <c r="I292" s="5">
-        <v>421.06</v>
-      </c>
-      <c r="J292" s="5">
-        <v>487.12</v>
-      </c>
-      <c r="K292" s="5">
-        <v>451.84</v>
-      </c>
-      <c r="L292" s="5">
-        <v>440.89</v>
-      </c>
-      <c r="M292" s="5">
-        <v>662.95</v>
-      </c>
-      <c r="N292" s="5">
-        <v>679.46</v>
-      </c>
-      <c r="O292" s="5">
-        <v>766.04</v>
-      </c>
-      <c r="P292" s="5">
-        <v>776.56</v>
-      </c>
-      <c r="Q292" s="5">
-        <v>829.27</v>
-      </c>
-      <c r="R292" s="5">
-        <v>983.51</v>
-      </c>
-      <c r="S292" s="5">
-        <v>3494.39</v>
-      </c>
-      <c r="T292" s="5">
-        <v>2580.38</v>
-      </c>
-      <c r="U292" s="5">
-        <v>1840.15</v>
-      </c>
-      <c r="V292" s="3"/>
-      <c r="W292" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="293" spans="1:23" ht="36" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E293" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G293" s="5">
-        <v>96.04</v>
-      </c>
-      <c r="H293" s="5">
-        <v>90.68</v>
-      </c>
-      <c r="I293" s="5">
-        <v>111.55</v>
-      </c>
-      <c r="J293" s="5">
-        <v>127.11</v>
-      </c>
-      <c r="K293" s="5">
-        <v>82.28</v>
-      </c>
-      <c r="L293" s="5">
-        <v>100.19</v>
-      </c>
-      <c r="M293" s="5">
-        <v>148.99</v>
-      </c>
-      <c r="N293" s="5">
-        <v>222.11</v>
-      </c>
-      <c r="O293" s="5">
-        <v>244.93</v>
-      </c>
-      <c r="P293" s="5">
-        <v>223.31</v>
-      </c>
-      <c r="Q293" s="5">
-        <v>225.08</v>
-      </c>
-      <c r="R293" s="5">
-        <v>296.20999999999998</v>
-      </c>
-      <c r="S293" s="5">
-        <v>2661.32</v>
-      </c>
-      <c r="T293" s="5">
-        <v>1701.94</v>
-      </c>
-      <c r="U293" s="5">
-        <v>705.25</v>
-      </c>
-      <c r="V293" s="3"/>
+      <c r="O293" s="4">
+        <v>35</v>
+      </c>
+      <c r="P293" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="Q293" s="4">
+        <v>45.1</v>
+      </c>
+      <c r="R293" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="S293" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="T293" s="4">
+        <v>65.7</v>
+      </c>
+      <c r="U293" s="4">
+        <v>68.8</v>
+      </c>
+      <c r="V293" s="4">
+        <v>69.900000000000006</v>
+      </c>
       <c r="W293" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="294" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="294" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>28</v>
+        <v>215</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G294" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="H294" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="I294" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="J294" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="K294" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="L294" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="M294" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="N294" s="5">
-        <v>0.13</v>
-      </c>
-      <c r="O294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="P294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="Q294" s="5">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="R294" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="S294" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="T294" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="U294" s="5">
-        <v>0.21</v>
-      </c>
-      <c r="V294" s="3"/>
+      <c r="G294" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="H294" s="4">
+        <v>15.7</v>
+      </c>
+      <c r="I294" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="J294" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="K294" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="L294" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="M294" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="N294" s="4">
+        <v>18.8</v>
+      </c>
+      <c r="O294" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="P294" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="Q294" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="R294" s="4">
+        <v>35</v>
+      </c>
+      <c r="S294" s="4">
+        <v>39.5</v>
+      </c>
+      <c r="T294" s="4">
+        <v>44.4</v>
+      </c>
+      <c r="U294" s="4">
+        <v>50.8</v>
+      </c>
+      <c r="V294" s="4">
+        <v>51.4</v>
+      </c>
       <c r="W294" s="2" t="s">
-        <v>408</v>
+        <v>30</v>
       </c>
     </row>
     <row r="295" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>28</v>
+        <v>406</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="G295" s="3"/>
-      <c r="H295" s="3"/>
-      <c r="I295" s="3"/>
-      <c r="J295" s="7">
-        <v>2.2850000000000001</v>
-      </c>
-      <c r="K295" s="7">
-        <v>1.1160000000000001</v>
-      </c>
-      <c r="L295" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="M295" s="7">
-        <v>3.7469999999999999</v>
-      </c>
-      <c r="N295" s="7">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="O295" s="7">
-        <v>3.367</v>
-      </c>
-      <c r="P295" s="7">
-        <v>6.8940000000000001</v>
-      </c>
-      <c r="Q295" s="7">
-        <v>4.077</v>
-      </c>
-      <c r="R295" s="7">
-        <v>4.49</v>
-      </c>
-      <c r="S295" s="7">
-        <v>11.999000000000001</v>
-      </c>
-      <c r="T295" s="7">
-        <v>16.606000000000002</v>
-      </c>
-      <c r="U295" s="7">
-        <v>20.382000000000001</v>
-      </c>
-      <c r="V295" s="7">
-        <v>5.3920000000000003</v>
+        <v>34</v>
+      </c>
+      <c r="G295" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H295" s="4">
+        <v>5</v>
+      </c>
+      <c r="I295" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J295" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="K295" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="L295" s="4">
+        <v>6</v>
+      </c>
+      <c r="M295" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N295" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="O295" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="P295" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="Q295" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="R295" s="4">
+        <v>15.8</v>
+      </c>
+      <c r="S295" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="T295" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="U295" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="V295" s="4">
+        <v>27.6</v>
       </c>
       <c r="W295" s="2" t="s">
-        <v>408</v>
+        <v>30</v>
       </c>
     </row>
     <row r="296" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>27</v>
@@ -20478,61 +20515,69 @@
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G296" s="3"/>
-      <c r="H296" s="3"/>
-      <c r="I296" s="3"/>
-      <c r="J296" s="5">
-        <v>8.07</v>
-      </c>
-      <c r="K296" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="L296" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="M296" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="N296" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O296" s="5">
-        <v>63.36</v>
-      </c>
-      <c r="P296" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="Q296" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="R296" s="5">
-        <v>3.65</v>
-      </c>
-      <c r="S296" s="5">
-        <v>9.59</v>
-      </c>
-      <c r="T296" s="5">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U296" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="V296" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="G296" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="H296" s="4">
+        <v>6</v>
+      </c>
+      <c r="I296" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="K296" s="4">
+        <v>4.7</v>
+      </c>
+      <c r="L296" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="M296" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="N296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="O296" s="4">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P296" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R296" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S296" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="T296" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="U296" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="V296" s="4">
+        <v>5.2</v>
+      </c>
       <c r="W296" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="297" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>27</v>
@@ -20541,55 +20586,69 @@
         <v>28</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="G297" s="6">
+        <v>674</v>
+      </c>
+      <c r="H297" s="6">
+        <v>605</v>
+      </c>
+      <c r="I297" s="6">
+        <v>1082</v>
+      </c>
+      <c r="J297" s="6">
+        <v>1219</v>
+      </c>
       <c r="K297" s="6">
-        <v>1</v>
+        <v>1282</v>
       </c>
       <c r="L297" s="6">
-        <v>1</v>
+        <v>1456</v>
       </c>
       <c r="M297" s="6">
-        <v>8</v>
+        <v>1926</v>
       </c>
       <c r="N297" s="6">
-        <v>2</v>
-      </c>
-      <c r="O297" s="3"/>
+        <v>3182</v>
+      </c>
+      <c r="O297" s="6">
+        <v>3739</v>
+      </c>
       <c r="P297" s="6">
-        <v>1</v>
+        <v>6484</v>
       </c>
       <c r="Q297" s="6">
-        <v>2</v>
-      </c>
-      <c r="R297" s="3"/>
-      <c r="S297" s="3"/>
+        <v>10420</v>
+      </c>
+      <c r="R297" s="6">
+        <v>29483</v>
+      </c>
+      <c r="S297" s="6">
+        <v>39683</v>
+      </c>
       <c r="T297" s="6">
-        <v>8</v>
+        <v>80267</v>
       </c>
       <c r="U297" s="6">
-        <v>7</v>
+        <v>103449</v>
       </c>
       <c r="V297" s="6">
-        <v>2</v>
+        <v>260783</v>
       </c>
       <c r="W297" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="298" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="298" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>27</v>
@@ -20598,65 +20657,43 @@
         <v>28</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>420</v>
+        <v>34</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="3"/>
-      <c r="I298" s="6">
-        <v>2</v>
-      </c>
-      <c r="J298" s="6">
-        <v>2</v>
-      </c>
-      <c r="K298" s="6">
-        <v>1</v>
-      </c>
-      <c r="L298" s="6">
-        <v>1</v>
-      </c>
-      <c r="M298" s="6">
-        <v>1</v>
-      </c>
-      <c r="N298" s="6">
-        <v>1</v>
-      </c>
-      <c r="O298" s="6">
-        <v>1</v>
-      </c>
-      <c r="P298" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q298" s="6">
-        <v>4</v>
-      </c>
-      <c r="R298" s="6">
-        <v>1</v>
-      </c>
-      <c r="S298" s="6">
-        <v>1</v>
-      </c>
-      <c r="T298" s="6">
-        <v>0</v>
-      </c>
-      <c r="U298" s="6">
-        <v>4</v>
-      </c>
-      <c r="V298" s="6">
-        <v>2</v>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="5">
+        <v>18.93</v>
+      </c>
+      <c r="S298" s="3"/>
+      <c r="T298" s="5">
+        <v>21.3</v>
+      </c>
+      <c r="U298" s="3"/>
+      <c r="V298" s="5">
+        <v>23.01</v>
       </c>
       <c r="W298" s="2" t="s">
-        <v>421</v>
+        <v>88</v>
       </c>
     </row>
     <row r="299" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>27</v>
@@ -20665,61 +20702,67 @@
         <v>28</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="3"/>
-      <c r="K299" s="6">
-        <v>5</v>
-      </c>
-      <c r="L299" s="6">
-        <v>13</v>
-      </c>
-      <c r="M299" s="6">
-        <v>19</v>
-      </c>
-      <c r="N299" s="6">
-        <v>18</v>
-      </c>
-      <c r="O299" s="6">
-        <v>15</v>
-      </c>
-      <c r="P299" s="6">
-        <v>15</v>
-      </c>
-      <c r="Q299" s="6">
-        <v>8</v>
-      </c>
-      <c r="R299" s="6">
-        <v>28</v>
-      </c>
-      <c r="S299" s="6">
-        <v>53</v>
-      </c>
-      <c r="T299" s="6">
-        <v>65</v>
-      </c>
-      <c r="U299" s="6">
-        <v>70</v>
-      </c>
-      <c r="V299" s="6">
-        <v>69</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="G299" s="5">
+        <v>377.75</v>
+      </c>
+      <c r="H299" s="5">
+        <v>417.47</v>
+      </c>
+      <c r="I299" s="5">
+        <v>421.06</v>
+      </c>
+      <c r="J299" s="5">
+        <v>487.12</v>
+      </c>
+      <c r="K299" s="5">
+        <v>451.84</v>
+      </c>
+      <c r="L299" s="5">
+        <v>440.89</v>
+      </c>
+      <c r="M299" s="5">
+        <v>662.95</v>
+      </c>
+      <c r="N299" s="5">
+        <v>679.46</v>
+      </c>
+      <c r="O299" s="5">
+        <v>766.04</v>
+      </c>
+      <c r="P299" s="5">
+        <v>776.56</v>
+      </c>
+      <c r="Q299" s="5">
+        <v>829.27</v>
+      </c>
+      <c r="R299" s="5">
+        <v>983.51</v>
+      </c>
+      <c r="S299" s="5">
+        <v>3494.39</v>
+      </c>
+      <c r="T299" s="5">
+        <v>2580.38</v>
+      </c>
+      <c r="U299" s="5">
+        <v>1840.15</v>
+      </c>
+      <c r="V299" s="3"/>
       <c r="W299" s="2" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="300" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="300" spans="1:23" ht="36" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>27</v>
@@ -20728,47 +20771,500 @@
         <v>28</v>
       </c>
       <c r="F300" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G300" s="5">
+        <v>96.04</v>
+      </c>
+      <c r="H300" s="5">
+        <v>90.68</v>
+      </c>
+      <c r="I300" s="5">
+        <v>111.55</v>
+      </c>
+      <c r="J300" s="5">
+        <v>127.11</v>
+      </c>
+      <c r="K300" s="5">
+        <v>82.28</v>
+      </c>
+      <c r="L300" s="5">
+        <v>100.19</v>
+      </c>
+      <c r="M300" s="5">
+        <v>148.99</v>
+      </c>
+      <c r="N300" s="5">
+        <v>222.11</v>
+      </c>
+      <c r="O300" s="5">
+        <v>244.93</v>
+      </c>
+      <c r="P300" s="5">
+        <v>223.31</v>
+      </c>
+      <c r="Q300" s="5">
+        <v>225.08</v>
+      </c>
+      <c r="R300" s="5">
+        <v>296.20999999999998</v>
+      </c>
+      <c r="S300" s="5">
+        <v>2661.32</v>
+      </c>
+      <c r="T300" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="U300" s="5">
+        <v>705.25</v>
+      </c>
+      <c r="V300" s="3"/>
+      <c r="W300" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="301" spans="1:23" ht="81" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G301" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="H301" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="I301" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="J301" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="K301" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="L301" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="M301" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="N301" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q301" s="5">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R301" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="S301" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="T301" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="U301" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="V301" s="3"/>
+      <c r="W301" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="302" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G302" s="3"/>
+      <c r="H302" s="3"/>
+      <c r="I302" s="3"/>
+      <c r="J302" s="7">
+        <v>2.2850000000000001</v>
+      </c>
+      <c r="K302" s="7">
+        <v>1.1160000000000001</v>
+      </c>
+      <c r="L302" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="M302" s="7">
+        <v>3.7469999999999999</v>
+      </c>
+      <c r="N302" s="7">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="O302" s="7">
+        <v>3.367</v>
+      </c>
+      <c r="P302" s="7">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="Q302" s="7">
+        <v>4.077</v>
+      </c>
+      <c r="R302" s="7">
+        <v>4.49</v>
+      </c>
+      <c r="S302" s="7">
+        <v>11.999000000000001</v>
+      </c>
+      <c r="T302" s="7">
+        <v>16.606000000000002</v>
+      </c>
+      <c r="U302" s="7">
+        <v>20.382000000000001</v>
+      </c>
+      <c r="V302" s="7">
+        <v>5.3920000000000003</v>
+      </c>
+      <c r="W302" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="303" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G303" s="3"/>
+      <c r="H303" s="3"/>
+      <c r="I303" s="3"/>
+      <c r="J303" s="5">
+        <v>8.07</v>
+      </c>
+      <c r="K303" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="L303" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="M303" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="N303" s="5">
+        <v>2.25</v>
+      </c>
+      <c r="O303" s="5">
+        <v>63.36</v>
+      </c>
+      <c r="P303" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="Q303" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="R303" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="S303" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="T303" s="5">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U303" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="V303" s="3"/>
+      <c r="W303" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="304" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="6">
+        <v>1</v>
+      </c>
+      <c r="L304" s="6">
+        <v>1</v>
+      </c>
+      <c r="M304" s="6">
+        <v>8</v>
+      </c>
+      <c r="N304" s="6">
+        <v>2</v>
+      </c>
+      <c r="O304" s="3"/>
+      <c r="P304" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q304" s="6">
+        <v>2</v>
+      </c>
+      <c r="R304" s="3"/>
+      <c r="S304" s="3"/>
+      <c r="T304" s="6">
+        <v>8</v>
+      </c>
+      <c r="U304" s="6">
+        <v>7</v>
+      </c>
+      <c r="V304" s="6">
+        <v>2</v>
+      </c>
+      <c r="W304" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="305" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="6">
+        <v>2</v>
+      </c>
+      <c r="J305" s="6">
+        <v>2</v>
+      </c>
+      <c r="K305" s="6">
+        <v>1</v>
+      </c>
+      <c r="L305" s="6">
+        <v>1</v>
+      </c>
+      <c r="M305" s="6">
+        <v>1</v>
+      </c>
+      <c r="N305" s="6">
+        <v>1</v>
+      </c>
+      <c r="O305" s="6">
+        <v>1</v>
+      </c>
+      <c r="P305" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q305" s="6">
+        <v>4</v>
+      </c>
+      <c r="R305" s="6">
+        <v>1</v>
+      </c>
+      <c r="S305" s="6">
+        <v>1</v>
+      </c>
+      <c r="T305" s="6">
+        <v>0</v>
+      </c>
+      <c r="U305" s="6">
+        <v>4</v>
+      </c>
+      <c r="V305" s="6">
+        <v>2</v>
+      </c>
+      <c r="W305" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="306" spans="1:23" ht="36" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F306" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G300" s="3"/>
-      <c r="H300" s="3"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="3"/>
-      <c r="K300" s="3"/>
-      <c r="L300" s="3"/>
-      <c r="M300" s="3"/>
-      <c r="N300" s="3"/>
-      <c r="O300" s="3"/>
-      <c r="P300" s="3"/>
-      <c r="Q300" s="3"/>
-      <c r="R300" s="3"/>
-      <c r="S300" s="3"/>
-      <c r="T300" s="6">
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="6">
+        <v>5</v>
+      </c>
+      <c r="L306" s="6">
+        <v>13</v>
+      </c>
+      <c r="M306" s="6">
+        <v>19</v>
+      </c>
+      <c r="N306" s="6">
+        <v>18</v>
+      </c>
+      <c r="O306" s="6">
+        <v>15</v>
+      </c>
+      <c r="P306" s="6">
+        <v>15</v>
+      </c>
+      <c r="Q306" s="6">
+        <v>8</v>
+      </c>
+      <c r="R306" s="6">
+        <v>28</v>
+      </c>
+      <c r="S306" s="6">
+        <v>53</v>
+      </c>
+      <c r="T306" s="6">
+        <v>65</v>
+      </c>
+      <c r="U306" s="6">
+        <v>70</v>
+      </c>
+      <c r="V306" s="6">
+        <v>69</v>
+      </c>
+      <c r="W306" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="307" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G307" s="3"/>
+      <c r="H307" s="3"/>
+      <c r="I307" s="3"/>
+      <c r="J307" s="3"/>
+      <c r="K307" s="3"/>
+      <c r="L307" s="3"/>
+      <c r="M307" s="3"/>
+      <c r="N307" s="3"/>
+      <c r="O307" s="3"/>
+      <c r="P307" s="3"/>
+      <c r="Q307" s="3"/>
+      <c r="R307" s="3"/>
+      <c r="S307" s="3"/>
+      <c r="T307" s="6">
         <v>114</v>
       </c>
-      <c r="U300" s="6">
+      <c r="U307" s="6">
         <v>61</v>
       </c>
-      <c r="V300" s="6">
+      <c r="V307" s="6">
         <v>97</v>
       </c>
-      <c r="W300" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="301" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="B302" s="8"/>
+      <c r="W307" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="308" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B309" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:C3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A302:B302"/>
+    <mergeCell ref="A309:B309"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/excel/pl/wskazniki_krajowe.xlsx
+++ b/assets/excel/pl/wskazniki_krajowe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidwab\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD9593D-5E76-4B79-A5CB-B0CA08559419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B62654C-D261-4F7E-A695-B06CC33ADC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1345,7 +1345,7 @@
     <t>Ministerstwo Rozwoju i Technologii/Kancelaria Prezesa Rady Ministrów</t>
   </si>
   <si>
-    <t>Ostatnia aktualizacja: 07-08-2026, 10:19</t>
+    <t>Ostatnia aktualizacja: 07-08-2026, 12:58</t>
   </si>
 </sst>
 </file>
@@ -16260,49 +16260,49 @@
         <v>34</v>
       </c>
       <c r="G232" s="4">
-        <v>99.6</v>
+        <v>43.4</v>
       </c>
       <c r="H232" s="4">
-        <v>99.6</v>
+        <v>46.5</v>
       </c>
       <c r="I232" s="4">
-        <v>99.6</v>
+        <v>47.2</v>
       </c>
       <c r="J232" s="4">
-        <v>99.6</v>
+        <v>47.8</v>
       </c>
       <c r="K232" s="4">
-        <v>99.6</v>
+        <v>46.4</v>
       </c>
       <c r="L232" s="4">
-        <v>99.6</v>
+        <v>46.5</v>
       </c>
       <c r="M232" s="4">
-        <v>99.7</v>
+        <v>51.4</v>
       </c>
       <c r="N232" s="4">
-        <v>99.7</v>
+        <v>53.8</v>
       </c>
       <c r="O232" s="4">
-        <v>99.7</v>
+        <v>54</v>
       </c>
       <c r="P232" s="4">
-        <v>99.7</v>
+        <v>54.3</v>
       </c>
       <c r="Q232" s="4">
-        <v>99.8</v>
+        <v>58.5</v>
       </c>
       <c r="R232" s="4">
-        <v>99.8</v>
+        <v>61.4</v>
       </c>
       <c r="S232" s="4">
-        <v>99.8</v>
+        <v>60</v>
       </c>
       <c r="T232" s="4">
-        <v>99.8</v>
+        <v>62.3</v>
       </c>
       <c r="U232" s="4">
-        <v>99.8</v>
+        <v>59.6</v>
       </c>
       <c r="V232" s="3"/>
       <c r="W232" s="2" t="s">
@@ -16329,49 +16329,49 @@
         <v>34</v>
       </c>
       <c r="G233" s="4">
-        <v>43.4</v>
+        <v>99.6</v>
       </c>
       <c r="H233" s="4">
-        <v>46.5</v>
+        <v>99.6</v>
       </c>
       <c r="I233" s="4">
-        <v>47.2</v>
+        <v>99.6</v>
       </c>
       <c r="J233" s="4">
-        <v>47.8</v>
+        <v>99.6</v>
       </c>
       <c r="K233" s="4">
-        <v>46.4</v>
+        <v>99.6</v>
       </c>
       <c r="L233" s="4">
-        <v>46.5</v>
+        <v>99.6</v>
       </c>
       <c r="M233" s="4">
-        <v>51.4</v>
+        <v>99.7</v>
       </c>
       <c r="N233" s="4">
-        <v>53.8</v>
+        <v>99.7</v>
       </c>
       <c r="O233" s="4">
-        <v>54</v>
+        <v>99.7</v>
       </c>
       <c r="P233" s="4">
-        <v>54.3</v>
+        <v>99.7</v>
       </c>
       <c r="Q233" s="4">
-        <v>58.5</v>
+        <v>99.8</v>
       </c>
       <c r="R233" s="4">
-        <v>61.4</v>
+        <v>99.8</v>
       </c>
       <c r="S233" s="4">
-        <v>60</v>
+        <v>99.8</v>
       </c>
       <c r="T233" s="4">
-        <v>62.3</v>
+        <v>99.8</v>
       </c>
       <c r="U233" s="4">
-        <v>59.6</v>
+        <v>99.8</v>
       </c>
       <c r="V233" s="3"/>
       <c r="W233" s="2" t="s">
